--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D662A976-9A01-9045-91A8-123837131BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFD05D3-5EA7-E040-B604-A8F221F87DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="29400" windowHeight="16900" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -55,7 +55,32 @@
     <author>Ugne Keliauskaite</author>
   </authors>
   <commentList>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{8133A74B-A2B7-1F46-B1E6-817B58D06909}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{FB35ED95-2CC7-344D-994B-16920F4F8BAC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ugne Keliauskaite:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+in 2024 sold
+11,203 in 2023</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{8133A74B-A2B7-1F46-B1E6-817B58D06909}">
       <text>
         <r>
           <rPr>
@@ -88,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
       <text>
         <r>
           <rPr>
@@ -112,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{1CB05A61-ED73-9F40-8D60-A96C94868F7E}">
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{1CB05A61-ED73-9F40-8D60-A96C94868F7E}">
       <text>
         <r>
           <rPr>
@@ -136,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{BB069DC0-8A6E-5949-BC1C-028E6717895D}">
+    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{BB069DC0-8A6E-5949-BC1C-028E6717895D}">
       <text>
         <r>
           <rPr>
@@ -160,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
       <text>
         <r>
           <rPr>
@@ -193,32 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{FB35ED95-2CC7-344D-994B-16920F4F8BAC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ugne Keliauskaite:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-in 2024 sold
-11,203 in 2023</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
       <text>
         <r>
           <rPr>
@@ -242,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C87" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -290,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E101" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
+    <comment ref="E100" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
       <text>
         <r>
           <rPr>
@@ -314,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
+    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
       <text>
         <r>
           <rPr>
@@ -1555,7 +1555,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3567" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="1309">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -6706,7 +6706,215 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{E9361510-FC41-794E-963D-B228D8116D9F}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFD9E1F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7011,6 +7219,27 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Shweta Movalia" id="{DE1BC2FF-7138-40AC-B5C7-251C7D2E0B00}" userId="S::smovalia@rhg.com::e5c2e265-8fad-4382-897b-9b4f5d6b34a1" providerId="AD"/>
 </personList>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I107" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I107" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I107">
+    <sortCondition ref="A1:A107"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{8195EC2C-EAFD-0248-8064-890DEBB2CF88}" name="country" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{6D1EA899-5C16-9C45-99E8-4DEB01873247}" name="city" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{370650D5-6DD9-6B4E-9175-7EFEE1896586}" name="investment_type" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{9E50EEA0-4B08-C24B-B9DD-82808F97FE2D}" name="investment_status" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{64210756-8BE1-8E41-AE97-DED54BB2C3A7}" name="reported_production" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{D1ECD513-C00E-5A41-8FCD-5B5994F74BDB}" name="production_date_original" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{16C1B018-C17F-1D42-9D20-14601B26CA45}" name="production_date_current" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{CF19F16F-E593-1846-973E-64DBF9B072F7}" name="production_reported" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7341,18 +7570,18 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -7386,92 +7615,98 @@
       <c r="J1" s="337"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="152" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D2" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="338"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I2" s="337">
-        <v>17646</v>
+      <c r="A2" s="163" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="163" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="163" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="341" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H2" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I2" s="161">
+        <v>50000</v>
       </c>
       <c r="J2" s="337"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B3" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="152" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D3" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="338"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I3" s="337">
-        <v>16874</v>
-      </c>
+      <c r="A3" s="163" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="163" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="163" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="163" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="341"/>
+      <c r="G3" s="164">
+        <v>44249</v>
+      </c>
+      <c r="H3" s="164">
+        <v>44249</v>
+      </c>
+      <c r="I3" s="161"/>
       <c r="J3" s="337"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B4" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C4" s="152" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D4" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="338"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I4" s="337">
-        <v>2117</v>
-      </c>
+      <c r="A4" s="163" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="163" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="163" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="341" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H4" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I4" s="161"/>
       <c r="J4" s="337"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="152" t="s">
-        <v>1063</v>
+        <v>211</v>
       </c>
       <c r="B5" s="152" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C5" s="152" t="s">
-        <v>1137</v>
+        <v>1082</v>
       </c>
       <c r="D5" s="152" t="s">
         <v>60</v>
@@ -7482,173 +7717,171 @@
       <c r="F5" s="338"/>
       <c r="G5" s="152"/>
       <c r="H5" s="339">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I5" s="337">
-        <v>18174</v>
+        <v>17646</v>
       </c>
       <c r="J5" s="337"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B6" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="152" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D6" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="152" t="s">
+      <c r="A6" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="163" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="163" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="105" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="163" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="342">
+        <v>2018</v>
+      </c>
+      <c r="G6" s="126">
+        <v>43252</v>
+      </c>
+      <c r="H6" s="105"/>
+      <c r="I6" s="124">
+        <v>50339</v>
+      </c>
+      <c r="J6" s="337"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="163" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="338"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I6" s="337">
-        <v>615</v>
-      </c>
-      <c r="J6" s="337"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B7" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="152" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D7" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="338"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="164">
-        <v>45657</v>
-      </c>
-      <c r="I7" s="337">
-        <v>71051</v>
+      <c r="F7" s="342">
+        <v>2024</v>
+      </c>
+      <c r="G7" s="126">
+        <v>45292</v>
+      </c>
+      <c r="H7" s="105"/>
+      <c r="I7" s="124">
+        <v>15411</v>
       </c>
       <c r="J7" s="337"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="163" t="s">
-        <v>57</v>
+      <c r="A8" s="105" t="s">
+        <v>211</v>
       </c>
       <c r="B8" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="163" t="s">
-        <v>59</v>
+      <c r="C8" s="105" t="s">
+        <v>224</v>
       </c>
       <c r="D8" s="163" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="E8" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="340">
-        <v>42370</v>
-      </c>
-      <c r="G8" s="163"/>
-      <c r="I8" s="161">
-        <v>28225</v>
+      <c r="F8" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G8" s="126">
+        <v>43983</v>
+      </c>
+      <c r="H8" s="105"/>
+      <c r="I8" s="124">
+        <v>28334</v>
       </c>
       <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="163" t="s">
-        <v>57</v>
+        <v>230</v>
       </c>
       <c r="B9" s="163" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="C9" s="163" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="D9" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E9" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="340">
-        <v>45128</v>
+      <c r="F9" s="341">
+        <v>2020</v>
       </c>
       <c r="G9" s="163"/>
-      <c r="H9" s="164">
-        <v>45657</v>
-      </c>
-      <c r="I9" s="161">
-        <v>123209</v>
-      </c>
+      <c r="H9" s="163"/>
+      <c r="I9" s="161"/>
       <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="163" t="s">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="B10" s="163" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="C10" s="163" t="s">
-        <v>99</v>
+        <v>242</v>
       </c>
       <c r="D10" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E10" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="340"/>
-      <c r="G10" s="164">
-        <v>41535</v>
-      </c>
-      <c r="H10" s="164">
-        <v>41535</v>
-      </c>
-      <c r="I10" s="124">
-        <f>250000/9</f>
-        <v>27777.777777777777</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F10" s="341" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
+      <c r="I10" s="161"/>
       <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="163" t="s">
-        <v>57</v>
+        <v>253</v>
       </c>
       <c r="B11" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C11" s="163" t="s">
-        <v>99</v>
+        <v>254</v>
       </c>
       <c r="D11" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E11" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="340"/>
+        <v>124</v>
+      </c>
+      <c r="F11" s="341" t="s">
+        <v>256</v>
+      </c>
       <c r="G11" s="164">
-        <v>45355</v>
+        <v>46203</v>
       </c>
       <c r="H11" s="164">
-        <v>45355</v>
-      </c>
-      <c r="I11" s="124">
-        <v>100000</v>
-      </c>
+        <v>46203</v>
+      </c>
+      <c r="I11" s="161"/>
       <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -7659,7 +7892,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="163" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D12" s="163" t="s">
         <v>60</v>
@@ -7667,17 +7900,12 @@
       <c r="E12" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="341">
-        <v>2015</v>
-      </c>
-      <c r="G12" s="164">
-        <v>42185</v>
-      </c>
-      <c r="H12" s="164">
-        <v>42185</v>
-      </c>
+      <c r="F12" s="340">
+        <v>42370</v>
+      </c>
+      <c r="G12" s="163"/>
       <c r="I12" s="161">
-        <v>20016</v>
+        <v>28225</v>
       </c>
       <c r="J12" s="161"/>
     </row>
@@ -7689,7 +7917,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="163" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D13" s="163" t="s">
         <v>71</v>
@@ -7697,14 +7925,16 @@
       <c r="E13" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="341"/>
-      <c r="G13" s="164">
-        <v>44491</v>
-      </c>
+      <c r="F13" s="340">
+        <v>45128</v>
+      </c>
+      <c r="G13" s="163"/>
       <c r="H13" s="164">
-        <v>44491</v>
-      </c>
-      <c r="I13" s="161"/>
+        <v>45657</v>
+      </c>
+      <c r="I13" s="161">
+        <v>123209</v>
+      </c>
       <c r="J13" s="161"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -7715,22 +7945,25 @@
         <v>58</v>
       </c>
       <c r="C14" s="163" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D14" s="163" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E14" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" s="341"/>
+        <v>61</v>
+      </c>
+      <c r="F14" s="340"/>
       <c r="G14" s="164">
-        <v>46752</v>
+        <v>41535</v>
       </c>
       <c r="H14" s="164">
-        <v>46752</v>
-      </c>
-      <c r="I14" s="161"/>
+        <v>41535</v>
+      </c>
+      <c r="I14" s="124">
+        <f>250000/9</f>
+        <v>27777.777777777777</v>
+      </c>
       <c r="J14" s="161"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -7741,24 +7974,23 @@
         <v>58</v>
       </c>
       <c r="C15" s="163" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="250" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E15" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="342"/>
+      <c r="F15" s="340"/>
       <c r="G15" s="164">
-        <v>44876</v>
+        <v>45355</v>
       </c>
       <c r="H15" s="164">
-        <v>44876</v>
+        <v>45355</v>
       </c>
       <c r="I15" s="124">
-        <f>342521*0.33</f>
-        <v>113031.93000000001</v>
+        <v>100000</v>
       </c>
       <c r="J15" s="124"/>
     </row>
@@ -7770,24 +8002,25 @@
         <v>58</v>
       </c>
       <c r="C16" s="163" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="105" t="s">
-        <v>71</v>
+        <v>109</v>
+      </c>
+      <c r="D16" s="163" t="s">
+        <v>60</v>
       </c>
       <c r="E16" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="342"/>
+      <c r="F16" s="341">
+        <v>2015</v>
+      </c>
       <c r="G16" s="164">
-        <v>45744</v>
+        <v>42185</v>
       </c>
       <c r="H16" s="164">
-        <v>45744</v>
-      </c>
-      <c r="I16" s="124">
-        <f>I15+120*365</f>
-        <v>156831.93</v>
+        <v>42185</v>
+      </c>
+      <c r="I16" s="161">
+        <v>20016</v>
       </c>
       <c r="J16" s="124"/>
     </row>
@@ -7796,27 +8029,25 @@
         <v>57</v>
       </c>
       <c r="B17" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C17" s="163" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D17" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E17" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="341"/>
       <c r="G17" s="164">
-        <v>43655</v>
+        <v>44491</v>
       </c>
       <c r="H17" s="164">
-        <v>43655</v>
-      </c>
-      <c r="I17" s="124">
-        <v>46387</v>
-      </c>
+        <v>44491</v>
+      </c>
+      <c r="I17" s="161"/>
       <c r="J17" s="124"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -7824,22 +8055,24 @@
         <v>57</v>
       </c>
       <c r="B18" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C18" s="163" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D18" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E18" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F18" s="341" t="s">
-        <v>151</v>
-      </c>
-      <c r="G18" s="163"/>
-      <c r="H18" s="163"/>
+        <v>124</v>
+      </c>
+      <c r="F18" s="341"/>
+      <c r="G18" s="164">
+        <v>46752</v>
+      </c>
+      <c r="H18" s="164">
+        <v>46752</v>
+      </c>
       <c r="I18" s="161"/>
       <c r="J18" s="161"/>
     </row>
@@ -7848,28 +8081,27 @@
         <v>57</v>
       </c>
       <c r="B19" s="163" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="C19" s="163" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" s="163" t="s">
-        <v>143</v>
+        <v>130</v>
+      </c>
+      <c r="D19" s="250" t="s">
+        <v>71</v>
       </c>
       <c r="E19" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="341" t="s">
-        <v>166</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F19" s="342"/>
       <c r="G19" s="164">
-        <v>46022</v>
+        <v>44876</v>
       </c>
       <c r="H19" s="164">
-        <v>46022</v>
-      </c>
-      <c r="I19" s="161">
-        <v>150000</v>
+        <v>44876</v>
+      </c>
+      <c r="I19" s="124">
+        <f>342521*0.33</f>
+        <v>113031.93000000001</v>
       </c>
       <c r="J19" s="161"/>
     </row>
@@ -7878,239 +8110,242 @@
         <v>57</v>
       </c>
       <c r="B20" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C20" s="163" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D20" s="163" t="s">
-        <v>60</v>
+        <v>130</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>71</v>
       </c>
       <c r="E20" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="342"/>
       <c r="G20" s="164">
-        <v>45291</v>
+        <v>45744</v>
       </c>
       <c r="H20" s="164">
-        <v>45291</v>
-      </c>
-      <c r="I20" s="161">
-        <v>1076</v>
+        <v>45744</v>
+      </c>
+      <c r="I20" s="124">
+        <f>I19+120*365</f>
+        <v>156831.93</v>
       </c>
       <c r="J20" s="161"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="163" t="s">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="B21" s="163" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C21" s="163" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="D21" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E21" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="341" t="s">
-        <v>185</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F21" s="341"/>
       <c r="G21" s="164">
-        <v>46203</v>
+        <v>43655</v>
       </c>
       <c r="H21" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I21" s="161">
-        <v>50000</v>
+        <v>43655</v>
+      </c>
+      <c r="I21" s="124">
+        <v>46387</v>
       </c>
       <c r="J21" s="161"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="163" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="B22" s="163" t="s">
         <v>141</v>
       </c>
       <c r="C22" s="163" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="D22" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E22" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F22" s="341"/>
-      <c r="G22" s="164">
-        <v>44249</v>
-      </c>
-      <c r="H22" s="164">
-        <v>44249</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F22" s="341" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="163"/>
+      <c r="H22" s="163"/>
       <c r="I22" s="161"/>
       <c r="J22" s="161"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="163" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="B23" s="163" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C23" s="163" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D23" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E23" s="163" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="F23" s="341" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="G23" s="164">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="H23" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I23" s="161"/>
+        <v>46022</v>
+      </c>
+      <c r="I23" s="161">
+        <v>150000</v>
+      </c>
       <c r="J23" s="161"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="105" t="s">
-        <v>211</v>
+      <c r="A24" s="163" t="s">
+        <v>57</v>
       </c>
       <c r="B24" s="163" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="C24" s="163" t="s">
-        <v>213</v>
-      </c>
-      <c r="D24" s="105" t="s">
-        <v>214</v>
+        <v>1142</v>
+      </c>
+      <c r="D24" s="163" t="s">
+        <v>60</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F24" s="342">
-        <v>2018</v>
-      </c>
-      <c r="G24" s="126">
-        <v>43252</v>
-      </c>
-      <c r="H24" s="105"/>
-      <c r="I24" s="124">
-        <v>50339</v>
+        <v>61</v>
+      </c>
+      <c r="F24" s="342"/>
+      <c r="G24" s="164">
+        <v>45291</v>
+      </c>
+      <c r="H24" s="164">
+        <v>45291</v>
+      </c>
+      <c r="I24" s="161">
+        <v>1076</v>
       </c>
       <c r="J24" s="124"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="105" t="s">
-        <v>211</v>
+      <c r="A25" s="163" t="s">
+        <v>264</v>
       </c>
       <c r="B25" s="163" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="C25" s="163" t="s">
-        <v>220</v>
-      </c>
-      <c r="D25" s="105" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E25" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="342">
-        <v>2024</v>
-      </c>
-      <c r="G25" s="126">
-        <v>45292</v>
-      </c>
-      <c r="H25" s="105"/>
-      <c r="I25" s="124">
-        <v>15411</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="F25" s="341" t="s">
+        <v>270</v>
+      </c>
+      <c r="G25" s="164">
+        <v>43440</v>
+      </c>
+      <c r="H25" s="164">
+        <v>43440</v>
+      </c>
+      <c r="I25" s="161"/>
       <c r="J25" s="124"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="105" t="s">
-        <v>211</v>
+      <c r="A26" s="163" t="s">
+        <v>264</v>
       </c>
       <c r="B26" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="105" t="s">
-        <v>224</v>
+        <v>161</v>
+      </c>
+      <c r="C26" s="163" t="s">
+        <v>278</v>
       </c>
       <c r="D26" s="163" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="E26" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F26" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G26" s="126">
-        <v>43983</v>
-      </c>
-      <c r="H26" s="105"/>
-      <c r="I26" s="124">
-        <v>28334</v>
+      <c r="F26" s="341" t="s">
+        <v>280</v>
+      </c>
+      <c r="G26" s="164">
+        <v>42855</v>
+      </c>
+      <c r="H26" s="164">
+        <v>42855</v>
+      </c>
+      <c r="I26" s="161">
+        <v>400</v>
       </c>
       <c r="J26" s="124"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="163" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="B27" s="163" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C27" s="163" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="D27" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E27" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="341">
-        <v>2020</v>
+        <v>124</v>
+      </c>
+      <c r="F27" s="341" t="s">
+        <v>286</v>
       </c>
       <c r="G27" s="163"/>
       <c r="H27" s="163"/>
-      <c r="I27" s="161"/>
+      <c r="I27" s="161">
+        <v>150000</v>
+      </c>
       <c r="J27" s="161"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="163" t="s">
-        <v>240</v>
-      </c>
-      <c r="B28" s="163" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" s="163" t="s">
-        <v>242</v>
-      </c>
-      <c r="D28" s="163" t="s">
+      <c r="A28" s="183" t="s">
+        <v>297</v>
+      </c>
+      <c r="B28" s="183" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="183" t="s">
+        <v>298</v>
+      </c>
+      <c r="D28" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="163" t="s">
-        <v>124</v>
+      <c r="E28" s="183" t="s">
+        <v>192</v>
       </c>
       <c r="F28" s="341" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="G28" s="163"/>
       <c r="H28" s="163"/>
@@ -8119,221 +8354,223 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="163" t="s">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="B29" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C29" s="163" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="D29" s="163" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E29" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="341" t="s">
-        <v>256</v>
-      </c>
-      <c r="G29" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H29" s="164">
-        <v>46203</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F29" s="341"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="163"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="163" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="B30" s="163" t="s">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="C30" s="163" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="D30" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>267</v>
+        <v>148</v>
       </c>
       <c r="F30" s="341" t="s">
-        <v>270</v>
-      </c>
-      <c r="G30" s="164">
-        <v>43440</v>
-      </c>
-      <c r="H30" s="164">
-        <v>43440</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="G30" s="163"/>
+      <c r="H30" s="163"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="163" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="B31" s="163" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="C31" s="163" t="s">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="D31" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E31" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="341" t="s">
-        <v>280</v>
-      </c>
-      <c r="G31" s="164">
-        <v>42855</v>
-      </c>
-      <c r="H31" s="164">
-        <v>42855</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F31" s="341"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
       <c r="I31" s="161">
-        <v>400</v>
+        <v>30000</v>
       </c>
       <c r="J31" s="161"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="163" t="s">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="B32" s="163" t="s">
-        <v>161</v>
+        <v>357</v>
       </c>
       <c r="C32" s="163" t="s">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="D32" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E32" s="163" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F32" s="341" t="s">
-        <v>286</v>
-      </c>
-      <c r="G32" s="163"/>
-      <c r="H32" s="163"/>
+        <v>362</v>
+      </c>
+      <c r="G32" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H32" s="164">
+        <v>46203</v>
+      </c>
       <c r="I32" s="161">
         <v>150000</v>
       </c>
       <c r="J32" s="161"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="183" t="s">
-        <v>297</v>
-      </c>
-      <c r="B33" s="183" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="183" t="s">
-        <v>298</v>
-      </c>
-      <c r="D33" s="183" t="s">
+      <c r="A33" s="163" t="s">
+        <v>374</v>
+      </c>
+      <c r="B33" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="163" t="s">
+        <v>375</v>
+      </c>
+      <c r="D33" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="183" t="s">
-        <v>192</v>
+      <c r="E33" s="163" t="s">
+        <v>61</v>
       </c>
       <c r="F33" s="341" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="G33" s="163"/>
       <c r="H33" s="163"/>
-      <c r="I33" s="161"/>
+      <c r="I33" s="161">
+        <v>100</v>
+      </c>
       <c r="J33" s="161"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="163" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="B34" s="163" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="C34" s="163" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="D34" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E34" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F34" s="341"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="163"/>
-      <c r="I34" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F34" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="G34" s="164">
+        <v>46053</v>
+      </c>
+      <c r="H34" s="164">
+        <v>46053</v>
+      </c>
+      <c r="I34" s="161">
+        <v>5591</v>
+      </c>
       <c r="J34" s="161"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="163" t="s">
-        <v>316</v>
+        <v>399</v>
       </c>
       <c r="B35" s="163" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C35" s="163" t="s">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="D35" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E35" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="341"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="163"/>
-      <c r="I35" s="161">
-        <v>25000</v>
+      <c r="F35" s="341" t="s">
+        <v>405</v>
+      </c>
+      <c r="G35" s="164">
+        <v>45447</v>
+      </c>
+      <c r="H35" s="164">
+        <v>45447</v>
+      </c>
+      <c r="I35" s="343">
+        <v>250000</v>
       </c>
       <c r="J35" s="161"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="163" t="s">
-        <v>316</v>
+        <v>399</v>
       </c>
       <c r="B36" s="163" t="s">
         <v>318</v>
       </c>
       <c r="C36" s="163" t="s">
-        <v>319</v>
+        <v>414</v>
       </c>
       <c r="D36" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="341">
-        <v>2025</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F36" s="341"/>
       <c r="G36" s="163"/>
       <c r="H36" s="163"/>
       <c r="I36" s="161">
-        <v>25000</v>
+        <v>44286</v>
       </c>
       <c r="J36" s="161"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="163" t="s">
-        <v>316</v>
+        <v>399</v>
       </c>
       <c r="B37" s="163" t="s">
         <v>318</v>
       </c>
       <c r="C37" s="163" t="s">
-        <v>319</v>
+        <v>414</v>
       </c>
       <c r="D37" s="163" t="s">
         <v>71</v>
@@ -8345,19 +8582,19 @@
       <c r="G37" s="163"/>
       <c r="H37" s="163"/>
       <c r="I37" s="161">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="J37" s="161"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="163" t="s">
-        <v>334</v>
+        <v>428</v>
       </c>
       <c r="B38" s="163" t="s">
-        <v>335</v>
+        <v>429</v>
       </c>
       <c r="C38" s="163" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="D38" s="163" t="s">
         <v>143</v>
@@ -8365,9 +8602,7 @@
       <c r="E38" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F38" s="341" t="s">
-        <v>337</v>
-      </c>
+      <c r="F38" s="341"/>
       <c r="G38" s="163"/>
       <c r="H38" s="163"/>
       <c r="I38" s="161"/>
@@ -8375,67 +8610,70 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="163" t="s">
-        <v>334</v>
+        <v>434</v>
       </c>
       <c r="B39" s="163" t="s">
-        <v>58</v>
+        <v>435</v>
       </c>
       <c r="C39" s="163" t="s">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="D39" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E39" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="341"/>
-      <c r="G39" s="163"/>
-      <c r="H39" s="163"/>
-      <c r="I39" s="161">
-        <v>30000</v>
+        <v>61</v>
+      </c>
+      <c r="F39" s="342"/>
+      <c r="G39" s="126">
+        <v>43891</v>
+      </c>
+      <c r="H39" s="126">
+        <v>43891</v>
+      </c>
+      <c r="I39" s="124">
+        <f>28213+43839</f>
+        <v>72052</v>
       </c>
       <c r="J39" s="161"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="163" t="s">
-        <v>356</v>
+        <v>443</v>
       </c>
       <c r="B40" s="163" t="s">
-        <v>357</v>
+        <v>444</v>
       </c>
       <c r="C40" s="163" t="s">
-        <v>358</v>
+        <v>445</v>
       </c>
       <c r="D40" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E40" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F40" s="341" t="s">
-        <v>362</v>
-      </c>
-      <c r="G40" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H40" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I40" s="161">
-        <v>150000</v>
-      </c>
-      <c r="J40" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F40" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G40" s="126"/>
+      <c r="H40" s="126">
+        <v>45657</v>
+      </c>
+      <c r="I40" s="124">
+        <v>37239</v>
+      </c>
+      <c r="J40" s="343"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="163" t="s">
-        <v>374</v>
+        <v>462</v>
       </c>
       <c r="B41" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C41" s="163" t="s">
-        <v>375</v>
+        <v>463</v>
       </c>
       <c r="D41" s="163" t="s">
         <v>143</v>
@@ -8443,85 +8681,79 @@
       <c r="E41" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="G41" s="163"/>
-      <c r="H41" s="163"/>
-      <c r="I41" s="161">
-        <v>100</v>
+      <c r="F41" s="342">
+        <v>2015</v>
+      </c>
+      <c r="G41" s="126">
+        <v>42005</v>
+      </c>
+      <c r="H41" s="126">
+        <v>42005</v>
+      </c>
+      <c r="I41" s="343">
+        <v>18427</v>
       </c>
       <c r="J41" s="161"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="163" t="s">
-        <v>385</v>
+        <v>462</v>
       </c>
       <c r="B42" s="163" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="C42" s="163" t="s">
-        <v>386</v>
+        <v>463</v>
       </c>
       <c r="D42" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E42" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="G42" s="164">
-        <v>46053</v>
-      </c>
-      <c r="H42" s="164">
-        <v>46053</v>
-      </c>
-      <c r="I42" s="161">
-        <v>5591</v>
+      <c r="F42" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G42" s="163"/>
+      <c r="H42" s="163"/>
+      <c r="I42" s="343">
+        <v>2650</v>
       </c>
       <c r="J42" s="161"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B43" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="163" t="s">
-        <v>401</v>
+        <v>463</v>
       </c>
       <c r="D43" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E43" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="341" t="s">
-        <v>405</v>
-      </c>
-      <c r="G43" s="164">
-        <v>45447</v>
-      </c>
-      <c r="H43" s="164">
-        <v>45447</v>
-      </c>
+      <c r="F43" s="341"/>
+      <c r="G43" s="163"/>
+      <c r="H43" s="163"/>
       <c r="I43" s="343">
-        <v>250000</v>
-      </c>
-      <c r="J43" s="343"/>
+        <v>73662.5</v>
+      </c>
+      <c r="J43" s="124"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B44" s="163" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C44" s="163" t="s">
-        <v>414</v>
+        <v>477</v>
       </c>
       <c r="D44" s="163" t="s">
         <v>143</v>
@@ -8529,69 +8761,77 @@
       <c r="E44" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="341"/>
-      <c r="G44" s="163"/>
-      <c r="H44" s="163"/>
+      <c r="F44" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G44" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H44" s="126">
+        <v>43831</v>
+      </c>
       <c r="I44" s="161">
-        <v>44286</v>
-      </c>
-      <c r="J44" s="161"/>
+        <v>4760</v>
+      </c>
+      <c r="J44" s="124"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B45" s="163" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C45" s="163" t="s">
-        <v>414</v>
+        <v>477</v>
       </c>
       <c r="D45" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E45" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F45" s="341"/>
-      <c r="G45" s="163"/>
-      <c r="H45" s="163"/>
-      <c r="I45" s="161">
-        <v>300000</v>
-      </c>
-      <c r="J45" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F45" s="342"/>
+      <c r="G45" s="126">
+        <v>45260</v>
+      </c>
+      <c r="H45" s="126">
+        <v>45261</v>
+      </c>
+      <c r="I45" s="124"/>
+      <c r="J45" s="124"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="163" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="B46" s="163" t="s">
-        <v>429</v>
+        <v>58</v>
       </c>
       <c r="C46" s="163" t="s">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="D46" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E46" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F46" s="341"/>
-      <c r="G46" s="163"/>
-      <c r="H46" s="163"/>
-      <c r="I46" s="161"/>
-      <c r="J46" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F46" s="342"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="124"/>
+      <c r="J46" s="343"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="163" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B47" s="163" t="s">
-        <v>435</v>
+        <v>58</v>
       </c>
       <c r="C47" s="163" t="s">
-        <v>436</v>
+        <v>490</v>
       </c>
       <c r="D47" s="163" t="s">
         <v>143</v>
@@ -8599,28 +8839,29 @@
       <c r="E47" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="342"/>
+      <c r="F47" s="342">
+        <v>2018</v>
+      </c>
       <c r="G47" s="126">
-        <v>43891</v>
+        <v>43101</v>
       </c>
       <c r="H47" s="126">
-        <v>43891</v>
+        <v>43102</v>
       </c>
       <c r="I47" s="124">
-        <f>28213+43839</f>
-        <v>72052</v>
-      </c>
-      <c r="J47" s="124"/>
+        <v>83195</v>
+      </c>
+      <c r="J47" s="343"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="163" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B48" s="163" t="s">
-        <v>444</v>
+        <v>58</v>
       </c>
       <c r="C48" s="163" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="D48" s="163" t="s">
         <v>143</v>
@@ -8628,137 +8869,123 @@
       <c r="E48" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F48" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G48" s="126">
-        <v>43831</v>
+      <c r="F48" s="341">
+        <v>2016</v>
+      </c>
+      <c r="G48" s="164">
+        <v>42370</v>
       </c>
       <c r="H48" s="126">
-        <v>43831</v>
+        <v>42370</v>
       </c>
       <c r="I48" s="124">
-        <v>37239</v>
-      </c>
-      <c r="J48" s="124"/>
+        <v>62577.5</v>
+      </c>
+      <c r="J48" s="343"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="163" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B49" s="163" t="s">
-        <v>444</v>
+        <v>318</v>
       </c>
       <c r="C49" s="163" t="s">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="D49" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E49" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F49" s="342" t="s">
-        <v>453</v>
-      </c>
-      <c r="G49" s="126">
-        <v>45809</v>
-      </c>
-      <c r="H49" s="126">
-        <v>45809</v>
-      </c>
-      <c r="I49" s="124"/>
-      <c r="J49" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F49" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G49" s="164">
+        <v>43617</v>
+      </c>
+      <c r="H49" s="105"/>
+      <c r="I49" s="124">
+        <v>10739</v>
+      </c>
+      <c r="J49" s="161"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B50" s="163" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="C50" s="163" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="D50" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E50" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F50" s="342">
-        <v>2015</v>
-      </c>
-      <c r="G50" s="126">
-        <v>42005</v>
-      </c>
-      <c r="H50" s="126">
-        <v>42005</v>
-      </c>
-      <c r="I50" s="343">
-        <v>18427</v>
-      </c>
-      <c r="J50" s="343"/>
+        <v>124</v>
+      </c>
+      <c r="F50" s="341"/>
+      <c r="G50" s="164">
+        <v>46539</v>
+      </c>
+      <c r="H50" s="163"/>
+      <c r="I50" s="161"/>
+      <c r="J50" s="124"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B51" s="163" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="C51" s="163" t="s">
-        <v>463</v>
-      </c>
-      <c r="D51" s="163" t="s">
-        <v>71</v>
-      </c>
+        <v>1138</v>
+      </c>
+      <c r="D51" s="163"/>
       <c r="E51" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F51" s="341">
-        <v>2019</v>
-      </c>
-      <c r="G51" s="163"/>
+      <c r="F51" s="341"/>
+      <c r="G51" s="164"/>
       <c r="H51" s="163"/>
-      <c r="I51" s="343">
-        <v>2650</v>
-      </c>
-      <c r="J51" s="343"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="124"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B52" s="163" t="s">
-        <v>58</v>
+        <v>357</v>
       </c>
       <c r="C52" s="163" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="D52" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E52" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F52" s="341"/>
-      <c r="G52" s="163"/>
-      <c r="H52" s="163"/>
-      <c r="I52" s="343">
-        <v>73662.5</v>
-      </c>
-      <c r="J52" s="343"/>
+        <v>148</v>
+      </c>
+      <c r="F52" s="342"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="124"/>
+      <c r="J52" s="124"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B53" s="163" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C53" s="163" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="D53" s="163" t="s">
         <v>143</v>
@@ -8766,231 +8993,235 @@
       <c r="E53" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F53" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G53" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H53" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I53" s="161">
-        <v>4760</v>
-      </c>
-      <c r="J53" s="161"/>
+      <c r="F53" s="341" t="s">
+        <v>511</v>
+      </c>
+      <c r="G53" s="164">
+        <v>44530</v>
+      </c>
+      <c r="H53" s="163"/>
+      <c r="I53" s="124">
+        <v>50444</v>
+      </c>
+      <c r="J53" s="124"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B54" s="163" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C54" s="163" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="D54" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F54" s="342"/>
-      <c r="G54" s="126">
-        <v>45260</v>
-      </c>
-      <c r="H54" s="126">
-        <v>45261</v>
-      </c>
-      <c r="I54" s="124"/>
+        <v>124</v>
+      </c>
+      <c r="F54" s="341" t="s">
+        <v>518</v>
+      </c>
+      <c r="G54" s="164">
+        <v>46023</v>
+      </c>
+      <c r="H54" s="163"/>
+      <c r="I54" s="161"/>
       <c r="J54" s="124"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="163" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="B55" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C55" s="163" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="D55" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E55" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="342"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="105"/>
-      <c r="I55" s="124"/>
-      <c r="J55" s="124"/>
+      <c r="F55" s="341">
+        <v>2013</v>
+      </c>
+      <c r="G55" s="164">
+        <v>41275</v>
+      </c>
+      <c r="H55" s="163"/>
+      <c r="I55" s="161">
+        <v>40710</v>
+      </c>
+      <c r="J55" s="161"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="163" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="B56" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C56" s="163" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="D56" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E56" s="163" t="s">
+        <v>124</v>
+      </c>
+      <c r="F56" s="341"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="163"/>
+      <c r="I56" s="161">
+        <v>100000</v>
+      </c>
+      <c r="J56" s="161"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B57" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C57" s="152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D57" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="342">
-        <v>2018</v>
-      </c>
-      <c r="G56" s="126">
-        <v>43101</v>
-      </c>
-      <c r="H56" s="126">
-        <v>43102</v>
-      </c>
-      <c r="I56" s="124">
-        <v>83195</v>
-      </c>
-      <c r="J56" s="124"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B57" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="163" t="s">
-        <v>492</v>
-      </c>
-      <c r="D57" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="163" t="s">
+      <c r="F57" s="338"/>
+      <c r="G57" s="152"/>
+      <c r="H57" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I57" s="337">
+        <v>16874</v>
+      </c>
+      <c r="J57" s="124"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B58" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C58" s="152" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D58" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="341">
-        <v>2016</v>
-      </c>
-      <c r="G57" s="164">
-        <v>42370</v>
-      </c>
-      <c r="H57" s="126">
-        <v>42370</v>
-      </c>
-      <c r="I57" s="124">
-        <v>62577.5</v>
-      </c>
-      <c r="J57" s="124"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B58" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C58" s="163" t="s">
-        <v>496</v>
-      </c>
-      <c r="D58" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E58" s="163" t="s">
+      <c r="F58" s="338"/>
+      <c r="G58" s="152"/>
+      <c r="H58" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I58" s="337">
+        <v>2117</v>
+      </c>
+      <c r="J58" s="124"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B59" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" s="152" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D59" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F58" s="341">
-        <v>2019</v>
-      </c>
-      <c r="G58" s="164">
-        <v>43617</v>
-      </c>
-      <c r="H58" s="105"/>
-      <c r="I58" s="124">
-        <v>10739</v>
-      </c>
-      <c r="J58" s="124"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B59" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C59" s="163" t="s">
-        <v>496</v>
-      </c>
-      <c r="D59" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F59" s="341"/>
-      <c r="G59" s="164">
-        <v>46539</v>
-      </c>
-      <c r="H59" s="163"/>
-      <c r="I59" s="161"/>
+      <c r="F59" s="338"/>
+      <c r="G59" s="152"/>
+      <c r="H59" s="339">
+        <v>45291</v>
+      </c>
+      <c r="I59" s="337">
+        <v>18174</v>
+      </c>
       <c r="J59" s="161"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B60" s="163" t="s">
+      <c r="A60" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B60" s="152" t="s">
         <v>265</v>
       </c>
-      <c r="C60" s="163" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D60" s="163"/>
-      <c r="E60" s="163" t="s">
+      <c r="C60" s="152" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D60" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F60" s="341"/>
-      <c r="G60" s="164"/>
-      <c r="H60" s="163"/>
-      <c r="I60" s="161"/>
+      <c r="F60" s="338"/>
+      <c r="G60" s="152"/>
+      <c r="H60" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I60" s="337">
+        <v>615</v>
+      </c>
       <c r="J60" s="161"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B61" s="163" t="s">
-        <v>357</v>
-      </c>
-      <c r="C61" s="163" t="s">
-        <v>505</v>
-      </c>
-      <c r="D61" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E61" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="342"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="105"/>
-      <c r="I61" s="124"/>
-      <c r="J61" s="124"/>
+      <c r="A61" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B61" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" s="152" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D61" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="F61" s="338"/>
+      <c r="G61" s="152"/>
+      <c r="H61" s="164">
+        <v>45657</v>
+      </c>
+      <c r="I61" s="337">
+        <v>71051</v>
+      </c>
+      <c r="J61" s="161"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="163" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="B62" s="163" t="s">
-        <v>161</v>
+        <v>542</v>
       </c>
       <c r="C62" s="163" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="D62" s="163" t="s">
         <v>143</v>
@@ -8998,105 +9229,101 @@
       <c r="E62" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F62" s="341" t="s">
-        <v>511</v>
-      </c>
-      <c r="G62" s="164">
-        <v>44530</v>
-      </c>
+      <c r="F62" s="341"/>
+      <c r="G62" s="163"/>
       <c r="H62" s="163"/>
-      <c r="I62" s="124">
-        <v>50444</v>
-      </c>
-      <c r="J62" s="124"/>
+      <c r="I62" s="161">
+        <v>26699</v>
+      </c>
+      <c r="J62" s="161"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="163" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="B63" s="163" t="s">
-        <v>161</v>
+        <v>542</v>
       </c>
       <c r="C63" s="163" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="D63" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E63" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F63" s="341" t="s">
-        <v>518</v>
+        <v>148</v>
+      </c>
+      <c r="F63" s="341">
+        <v>2026</v>
       </c>
       <c r="G63" s="164">
-        <v>46023</v>
-      </c>
-      <c r="H63" s="163"/>
+        <v>46203</v>
+      </c>
+      <c r="H63" s="164">
+        <v>46203</v>
+      </c>
       <c r="I63" s="161"/>
       <c r="J63" s="161"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="163" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="B64" s="163" t="s">
-        <v>141</v>
+        <v>429</v>
       </c>
       <c r="C64" s="163" t="s">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="D64" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E64" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F64" s="341">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G64" s="164">
-        <v>41275</v>
-      </c>
-      <c r="H64" s="163"/>
-      <c r="I64" s="161">
-        <v>40710</v>
-      </c>
+        <v>45583</v>
+      </c>
+      <c r="H64" s="164">
+        <v>45583</v>
+      </c>
+      <c r="I64" s="161"/>
       <c r="J64" s="161"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="163" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="B65" s="163" t="s">
-        <v>141</v>
+        <v>429</v>
       </c>
       <c r="C65" s="163" t="s">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="D65" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E65" s="163" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F65" s="341"/>
       <c r="G65" s="163"/>
       <c r="H65" s="163"/>
-      <c r="I65" s="161">
-        <v>100000</v>
-      </c>
+      <c r="I65" s="161"/>
       <c r="J65" s="161"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="163" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="B66" s="163" t="s">
-        <v>542</v>
+        <v>318</v>
       </c>
       <c r="C66" s="163" t="s">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="D66" s="163" t="s">
         <v>143</v>
@@ -9104,32 +9331,38 @@
       <c r="E66" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="341"/>
-      <c r="G66" s="163"/>
-      <c r="H66" s="163"/>
-      <c r="I66" s="161">
-        <v>26699</v>
-      </c>
-      <c r="J66" s="161"/>
+      <c r="F66" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G66" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H66" s="126">
+        <v>43831</v>
+      </c>
+      <c r="I66" s="124">
+        <v>20135</v>
+      </c>
+      <c r="J66" s="124"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="163" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="B67" s="163" t="s">
-        <v>542</v>
+        <v>318</v>
       </c>
       <c r="C67" s="163" t="s">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="D67" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E67" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F67" s="341">
-        <v>2026</v>
+        <v>124</v>
+      </c>
+      <c r="F67" s="341" t="s">
+        <v>584</v>
       </c>
       <c r="G67" s="164">
         <v>46203</v>
@@ -9141,14 +9374,14 @@
       <c r="J67" s="161"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A68" s="163" t="s">
-        <v>561</v>
+      <c r="A68" s="105" t="s">
+        <v>590</v>
       </c>
       <c r="B68" s="163" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C68" s="163" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="D68" s="163" t="s">
         <v>143</v>
@@ -9156,107 +9389,98 @@
       <c r="E68" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F68" s="341">
-        <v>2023</v>
-      </c>
-      <c r="G68" s="164">
-        <v>45583</v>
-      </c>
-      <c r="H68" s="164">
-        <v>45583</v>
-      </c>
-      <c r="I68" s="161"/>
-      <c r="J68" s="161"/>
+      <c r="F68" s="342"/>
+      <c r="G68" s="126">
+        <v>44075</v>
+      </c>
+      <c r="H68" s="105"/>
+      <c r="I68" s="124">
+        <f>67243+12264</f>
+        <v>79507</v>
+      </c>
+      <c r="J68" s="124"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="163" t="s">
-        <v>561</v>
+      <c r="A69" s="105" t="s">
+        <v>590</v>
       </c>
       <c r="B69" s="163" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C69" s="163" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="D69" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E69" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F69" s="341"/>
-      <c r="G69" s="163"/>
-      <c r="H69" s="163"/>
-      <c r="I69" s="161"/>
-      <c r="J69" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F69" s="342"/>
+      <c r="G69" s="242">
+        <v>45679</v>
+      </c>
+      <c r="H69" s="105"/>
+      <c r="I69" s="124"/>
+      <c r="J69" s="124"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="163" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="B70" s="163" t="s">
-        <v>318</v>
+        <v>603</v>
       </c>
       <c r="C70" s="163" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="D70" s="163" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E70" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F70" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G70" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H70" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I70" s="124">
-        <v>20135</v>
-      </c>
-      <c r="J70" s="124"/>
+        <v>192</v>
+      </c>
+      <c r="F70" s="341" t="s">
+        <v>605</v>
+      </c>
+      <c r="G70" s="163"/>
+      <c r="H70" s="163"/>
+      <c r="I70" s="161"/>
+      <c r="J70" s="161"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="163" t="s">
-        <v>578</v>
+        <v>1084</v>
       </c>
       <c r="B71" s="163" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C71" s="163" t="s">
-        <v>579</v>
-      </c>
-      <c r="D71" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F71" s="341" t="s">
-        <v>584</v>
-      </c>
-      <c r="G71" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H71" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I71" s="161"/>
-      <c r="J71" s="161"/>
+        <v>1083</v>
+      </c>
+      <c r="D71" s="163"/>
+      <c r="E71" s="163"/>
+      <c r="F71" s="341"/>
+      <c r="G71" s="126">
+        <v>45291</v>
+      </c>
+      <c r="H71" s="126">
+        <v>45291</v>
+      </c>
+      <c r="I71" s="161">
+        <v>33335</v>
+      </c>
+      <c r="J71" s="124"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A72" s="105" t="s">
-        <v>590</v>
+      <c r="A72" s="163" t="s">
+        <v>613</v>
       </c>
       <c r="B72" s="163" t="s">
-        <v>435</v>
+        <v>58</v>
       </c>
       <c r="C72" s="163" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="D72" s="163" t="s">
         <v>143</v>
@@ -9264,63 +9488,68 @@
       <c r="E72" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="342"/>
+      <c r="F72" s="342">
+        <v>2020</v>
+      </c>
       <c r="G72" s="126">
-        <v>44075</v>
+        <v>43831</v>
       </c>
       <c r="H72" s="105"/>
       <c r="I72" s="124">
-        <f>67243+12264</f>
-        <v>79507</v>
+        <v>9653</v>
       </c>
       <c r="J72" s="124"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73" s="105" t="s">
-        <v>590</v>
+      <c r="A73" s="163" t="s">
+        <v>613</v>
       </c>
       <c r="B73" s="163" t="s">
-        <v>435</v>
+        <v>58</v>
       </c>
       <c r="C73" s="163" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="D73" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="163" t="s">
+      <c r="E73" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="F73" s="342"/>
-      <c r="G73" s="242">
-        <v>45679</v>
-      </c>
-      <c r="H73" s="105"/>
+      <c r="F73" s="342" t="s">
+        <v>618</v>
+      </c>
+      <c r="G73" s="126">
+        <v>45536</v>
+      </c>
+      <c r="H73" s="126">
+        <v>45536</v>
+      </c>
       <c r="I73" s="124"/>
-      <c r="J73" s="124"/>
+      <c r="J73" s="161"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="163" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="B74" s="163" t="s">
-        <v>603</v>
+        <v>141</v>
       </c>
       <c r="C74" s="163" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="D74" s="163" t="s">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="E74" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F74" s="341" t="s">
-        <v>605</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F74" s="341"/>
       <c r="G74" s="163"/>
       <c r="H74" s="163"/>
-      <c r="I74" s="161"/>
+      <c r="I74" s="161">
+        <v>15000</v>
+      </c>
       <c r="J74" s="161"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -9328,27 +9557,21 @@
         <v>613</v>
       </c>
       <c r="B75" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C75" s="163" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D75" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E75" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F75" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G75" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H75" s="105"/>
-      <c r="I75" s="124">
-        <v>9653</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="F75" s="341"/>
+      <c r="G75" s="163"/>
+      <c r="H75" s="163"/>
+      <c r="I75" s="161"/>
       <c r="J75" s="124"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
@@ -9356,27 +9579,27 @@
         <v>613</v>
       </c>
       <c r="B76" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C76" s="163" t="s">
-        <v>614</v>
+        <v>444</v>
+      </c>
+      <c r="C76" s="328" t="s">
+        <v>628</v>
       </c>
       <c r="D76" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="F76" s="342" t="s">
-        <v>618</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E76" s="163" t="s">
+        <v>192</v>
+      </c>
+      <c r="F76" s="342"/>
       <c r="G76" s="126">
-        <v>45536</v>
+        <v>43559</v>
       </c>
       <c r="H76" s="126">
-        <v>45536</v>
-      </c>
-      <c r="I76" s="124"/>
+        <v>43559</v>
+      </c>
+      <c r="I76" s="124">
+        <v>49264</v>
+      </c>
       <c r="J76" s="124"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
@@ -9384,73 +9607,85 @@
         <v>613</v>
       </c>
       <c r="B77" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="163" t="s">
-        <v>621</v>
+        <v>444</v>
+      </c>
+      <c r="C77" s="328" t="s">
+        <v>628</v>
       </c>
       <c r="D77" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E77" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F77" s="341"/>
-      <c r="G77" s="163"/>
-      <c r="H77" s="163"/>
-      <c r="I77" s="161">
-        <v>15000</v>
-      </c>
-      <c r="J77" s="161"/>
+        <v>148</v>
+      </c>
+      <c r="F77" s="342">
+        <v>2023</v>
+      </c>
+      <c r="G77" s="126">
+        <v>45107</v>
+      </c>
+      <c r="H77" s="126">
+        <v>45108</v>
+      </c>
+      <c r="I77" s="124"/>
+      <c r="J77" s="124"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="163" t="s">
         <v>613</v>
       </c>
       <c r="B78" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C78" s="163" t="s">
-        <v>621</v>
+        <v>318</v>
+      </c>
+      <c r="C78" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D78" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E78" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F78" s="341"/>
-      <c r="G78" s="163"/>
-      <c r="H78" s="163"/>
-      <c r="I78" s="161"/>
-      <c r="J78" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F78" s="342">
+        <v>2012</v>
+      </c>
+      <c r="G78" s="126">
+        <v>41061</v>
+      </c>
+      <c r="H78" s="126">
+        <v>41061</v>
+      </c>
+      <c r="I78" s="124">
+        <v>3734</v>
+      </c>
+      <c r="J78" s="124"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="163" t="s">
         <v>613</v>
       </c>
       <c r="B79" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C79" s="328" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C79" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D79" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E79" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F79" s="342"/>
+        <v>61</v>
+      </c>
+      <c r="F79" s="342" t="s">
+        <v>511</v>
+      </c>
       <c r="G79" s="126">
-        <v>43559</v>
+        <v>44501</v>
       </c>
       <c r="H79" s="126">
-        <v>43559</v>
-      </c>
-      <c r="I79" s="124">
-        <v>49264</v>
-      </c>
+        <v>44502</v>
+      </c>
+      <c r="I79" s="124"/>
       <c r="J79" s="124"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
@@ -9458,26 +9693,20 @@
         <v>613</v>
       </c>
       <c r="B80" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C80" s="328" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C80" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D80" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E80" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F80" s="342">
-        <v>2023</v>
-      </c>
-      <c r="G80" s="126">
-        <v>45107</v>
-      </c>
-      <c r="H80" s="126">
-        <v>45108</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F80" s="342"/>
+      <c r="G80" s="105"/>
+      <c r="H80" s="105"/>
       <c r="I80" s="124"/>
       <c r="J80" s="124"/>
     </row>
@@ -9488,338 +9717,340 @@
       <c r="B81" s="163" t="s">
         <v>318</v>
       </c>
-      <c r="C81" s="105" t="s">
-        <v>638</v>
+      <c r="C81" s="163" t="s">
+        <v>649</v>
       </c>
       <c r="D81" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E81" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F81" s="342">
-        <v>2012</v>
+        <v>124</v>
+      </c>
+      <c r="F81" s="344">
+        <v>46508</v>
       </c>
       <c r="G81" s="126">
-        <v>41061</v>
+        <v>46508</v>
       </c>
       <c r="H81" s="126">
-        <v>41061</v>
-      </c>
-      <c r="I81" s="124">
-        <v>3734</v>
-      </c>
+        <v>46508</v>
+      </c>
+      <c r="I81" s="124"/>
       <c r="J81" s="124"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="163" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B82" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C82" s="105" t="s">
-        <v>638</v>
+        <v>265</v>
+      </c>
+      <c r="C82" s="163" t="s">
+        <v>653</v>
       </c>
       <c r="D82" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E82" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F82" s="342" t="s">
-        <v>511</v>
-      </c>
+      <c r="F82" s="342"/>
       <c r="G82" s="126">
-        <v>44501</v>
+        <v>45291</v>
       </c>
       <c r="H82" s="126">
-        <v>44502</v>
-      </c>
-      <c r="I82" s="124"/>
+        <v>45291</v>
+      </c>
+      <c r="I82" s="124">
+        <v>42533</v>
+      </c>
       <c r="J82" s="124"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="163" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B83" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C83" s="105" t="s">
-        <v>638</v>
+        <v>265</v>
+      </c>
+      <c r="C83" s="138" t="s">
+        <v>657</v>
       </c>
       <c r="D83" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E83" s="163" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F83" s="342"/>
-      <c r="G83" s="105"/>
-      <c r="H83" s="105"/>
-      <c r="I83" s="124"/>
+      <c r="G83" s="126">
+        <v>45291</v>
+      </c>
+      <c r="H83" s="126">
+        <v>45291</v>
+      </c>
+      <c r="I83" s="124">
+        <v>15433</v>
+      </c>
       <c r="J83" s="124"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="163" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B84" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C84" s="163" t="s">
-        <v>649</v>
+        <v>265</v>
+      </c>
+      <c r="C84" s="138" t="s">
+        <v>663</v>
       </c>
       <c r="D84" s="163" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E84" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F84" s="344">
-        <v>46508</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F84" s="342"/>
       <c r="G84" s="126">
-        <v>46508</v>
+        <v>45657</v>
       </c>
       <c r="H84" s="126">
-        <v>46508</v>
-      </c>
-      <c r="I84" s="124"/>
+        <v>45657</v>
+      </c>
+      <c r="I84" s="124">
+        <v>24008</v>
+      </c>
       <c r="J84" s="124"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="163" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="B85" s="163" t="s">
         <v>265</v>
       </c>
       <c r="C85" s="163" t="s">
-        <v>653</v>
-      </c>
-      <c r="D85" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E85" s="163" t="s">
-        <v>61</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="D85" s="163"/>
+      <c r="E85" s="163"/>
       <c r="F85" s="342"/>
       <c r="G85" s="126">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H85" s="126">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I85" s="124">
-        <v>42533</v>
+        <v>23534</v>
       </c>
       <c r="J85" s="124"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="163" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="B86" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="C86" s="138" t="s">
-        <v>657</v>
+      <c r="C86" s="163" t="s">
+        <v>668</v>
       </c>
       <c r="D86" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E86" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F86" s="342"/>
-      <c r="G86" s="126">
-        <v>45291</v>
-      </c>
-      <c r="H86" s="126">
-        <v>45291</v>
-      </c>
-      <c r="I86" s="124">
-        <v>15433</v>
+        <v>61</v>
+      </c>
+      <c r="F86" s="341"/>
+      <c r="I86" s="161">
+        <v>5000</v>
       </c>
       <c r="J86" s="124"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="163" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="B87" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C87" s="138" t="s">
-        <v>663</v>
+        <v>182</v>
+      </c>
+      <c r="C87" s="163" t="s">
+        <v>680</v>
       </c>
       <c r="D87" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E87" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F87" s="342"/>
-      <c r="G87" s="126">
-        <v>45657</v>
-      </c>
-      <c r="H87" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I87" s="124">
-        <v>24008</v>
-      </c>
-      <c r="J87" s="124"/>
+      <c r="F87" s="341" t="s">
+        <v>682</v>
+      </c>
+      <c r="G87" s="163"/>
+      <c r="H87" s="163"/>
+      <c r="I87" s="161">
+        <v>111872</v>
+      </c>
+      <c r="J87" s="161"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="163" t="s">
         <v>667</v>
       </c>
       <c r="B88" s="163" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="C88" s="163" t="s">
-        <v>668</v>
-      </c>
-      <c r="D88" s="163"/>
-      <c r="E88" s="163"/>
-      <c r="F88" s="342"/>
-      <c r="G88" s="126">
-        <v>45657</v>
-      </c>
-      <c r="H88" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I88" s="124">
-        <v>23534</v>
-      </c>
-      <c r="J88" s="124"/>
+        <v>691</v>
+      </c>
+      <c r="D88" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" s="341" t="s">
+        <v>694</v>
+      </c>
+      <c r="G88" s="163"/>
+      <c r="H88" s="163"/>
+      <c r="I88" s="161"/>
+      <c r="J88" s="161"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A89" s="163" t="s">
-        <v>667</v>
-      </c>
-      <c r="B89" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C89" s="163" t="s">
-        <v>668</v>
-      </c>
-      <c r="D89" s="163" t="s">
+      <c r="A89" s="183" t="s">
+        <v>703</v>
+      </c>
+      <c r="B89" s="183" t="s">
+        <v>704</v>
+      </c>
+      <c r="C89" s="183" t="s">
+        <v>705</v>
+      </c>
+      <c r="D89" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E89" s="163" t="s">
+      <c r="E89" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="F89" s="341"/>
-      <c r="I89" s="161">
-        <v>5000</v>
+      <c r="F89" s="342" t="s">
+        <v>708</v>
+      </c>
+      <c r="G89" s="126">
+        <v>46023</v>
+      </c>
+      <c r="H89" s="126">
+        <v>46023</v>
+      </c>
+      <c r="I89" s="124">
+        <v>50000</v>
       </c>
       <c r="J89" s="124"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="163" t="s">
-        <v>1084</v>
+        <v>1028</v>
       </c>
       <c r="B90" s="163" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="C90" s="163" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D90" s="163"/>
-      <c r="E90" s="163"/>
-      <c r="F90" s="341"/>
-      <c r="G90" s="126">
-        <v>45291</v>
-      </c>
-      <c r="H90" s="126">
-        <v>45291</v>
+        <v>1029</v>
+      </c>
+      <c r="D90" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E90" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" s="341">
+        <v>2018</v>
+      </c>
+      <c r="G90" s="164">
+        <v>43101</v>
+      </c>
+      <c r="H90" s="164">
+        <v>43101</v>
       </c>
       <c r="I90" s="161">
-        <v>33335</v>
+        <v>14287</v>
       </c>
       <c r="J90" s="124"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="163" t="s">
-        <v>667</v>
+        <v>1028</v>
       </c>
       <c r="B91" s="163" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C91" s="163" t="s">
-        <v>680</v>
+        <v>1029</v>
       </c>
       <c r="D91" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E91" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F91" s="341" t="s">
-        <v>682</v>
-      </c>
-      <c r="G91" s="163"/>
-      <c r="H91" s="163"/>
+      <c r="F91" s="341"/>
+      <c r="G91" s="164"/>
+      <c r="H91" s="164"/>
       <c r="I91" s="161">
-        <v>111872</v>
+        <v>10881</v>
       </c>
       <c r="J91" s="161"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="163" t="s">
-        <v>667</v>
+        <v>1028</v>
       </c>
       <c r="B92" s="163" t="s">
-        <v>357</v>
+        <v>141</v>
       </c>
       <c r="C92" s="163" t="s">
-        <v>691</v>
+        <v>1029</v>
       </c>
       <c r="D92" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E92" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F92" s="341" t="s">
-        <v>694</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E92" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="F92" s="341"/>
       <c r="G92" s="163"/>
       <c r="H92" s="163"/>
       <c r="I92" s="161"/>
       <c r="J92" s="161"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A93" s="183" t="s">
-        <v>703</v>
-      </c>
-      <c r="B93" s="183" t="s">
-        <v>704</v>
-      </c>
-      <c r="C93" s="183" t="s">
-        <v>705</v>
-      </c>
-      <c r="D93" s="183" t="s">
+      <c r="A93" s="163" t="s">
+        <v>718</v>
+      </c>
+      <c r="B93" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" s="163" t="s">
+        <v>375</v>
+      </c>
+      <c r="D93" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E93" s="183" t="s">
+      <c r="E93" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F93" s="342" t="s">
-        <v>708</v>
-      </c>
-      <c r="G93" s="126">
-        <v>46023</v>
-      </c>
-      <c r="H93" s="126">
-        <v>46023</v>
+      <c r="F93" s="341" t="s">
+        <v>721</v>
+      </c>
+      <c r="G93" s="164">
+        <v>44642</v>
+      </c>
+      <c r="H93" s="164">
+        <v>44642</v>
       </c>
       <c r="I93" s="124">
-        <v>50000</v>
+        <v>206097</v>
       </c>
       <c r="J93" s="124"/>
     </row>
@@ -9828,114 +10059,108 @@
         <v>718</v>
       </c>
       <c r="B94" s="163" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="C94" s="163" t="s">
-        <v>375</v>
+        <v>729</v>
       </c>
       <c r="D94" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E94" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="341" t="s">
-        <v>721</v>
+        <v>192</v>
+      </c>
+      <c r="F94" s="341">
+        <v>2015</v>
       </c>
       <c r="G94" s="164">
-        <v>44642</v>
+        <v>42156</v>
       </c>
       <c r="H94" s="164">
-        <v>44642</v>
-      </c>
-      <c r="I94" s="124">
-        <v>206097</v>
-      </c>
-      <c r="J94" s="124"/>
+        <v>42157</v>
+      </c>
+      <c r="I94" s="161"/>
+      <c r="J94" s="161"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="163" t="s">
-        <v>718</v>
+        <v>737</v>
       </c>
       <c r="B95" s="163" t="s">
-        <v>335</v>
+        <v>212</v>
       </c>
       <c r="C95" s="163" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="D95" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E95" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F95" s="341">
-        <v>2015</v>
-      </c>
-      <c r="G95" s="164">
-        <v>42156</v>
-      </c>
-      <c r="H95" s="164">
-        <v>42157</v>
-      </c>
-      <c r="I95" s="161"/>
+        <v>148</v>
+      </c>
+      <c r="F95" s="341" t="s">
+        <v>739</v>
+      </c>
+      <c r="G95" s="163"/>
+      <c r="H95" s="163"/>
+      <c r="I95" s="161">
+        <v>30000</v>
+      </c>
       <c r="J95" s="161"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="163" t="s">
-        <v>737</v>
-      </c>
-      <c r="B96" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C96" s="163" t="s">
-        <v>738</v>
-      </c>
-      <c r="D96" s="163" t="s">
+      <c r="A96" s="183" t="s">
+        <v>575</v>
+      </c>
+      <c r="B96" s="183" t="s">
+        <v>444</v>
+      </c>
+      <c r="C96" s="183" t="s">
+        <v>745</v>
+      </c>
+      <c r="D96" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E96" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F96" s="341" t="s">
-        <v>739</v>
-      </c>
-      <c r="G96" s="163"/>
-      <c r="H96" s="163"/>
-      <c r="I96" s="161">
-        <v>30000</v>
+      <c r="E96" s="183" t="s">
+        <v>61</v>
+      </c>
+      <c r="F96" s="342">
+        <v>2013</v>
+      </c>
+      <c r="G96" s="126">
+        <v>41426</v>
+      </c>
+      <c r="H96" s="126">
+        <v>41426</v>
+      </c>
+      <c r="I96" s="124">
+        <v>94839</v>
       </c>
       <c r="J96" s="161"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A97" s="183" t="s">
+      <c r="A97" s="163" t="s">
         <v>575</v>
       </c>
-      <c r="B97" s="183" t="s">
-        <v>444</v>
-      </c>
-      <c r="C97" s="183" t="s">
-        <v>745</v>
-      </c>
-      <c r="D97" s="183" t="s">
-        <v>143</v>
-      </c>
-      <c r="E97" s="183" t="s">
+      <c r="B97" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C97" s="163" t="s">
+        <v>754</v>
+      </c>
+      <c r="D97" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="E97" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F97" s="342">
-        <v>2013</v>
-      </c>
-      <c r="G97" s="126">
-        <v>41426</v>
-      </c>
-      <c r="H97" s="126">
-        <v>41426</v>
-      </c>
-      <c r="I97" s="124">
-        <v>94839</v>
-      </c>
-      <c r="J97" s="124"/>
+      <c r="F97" s="341"/>
+      <c r="G97" s="163"/>
+      <c r="H97" s="163"/>
+      <c r="I97" s="161">
+        <v>140000</v>
+      </c>
+      <c r="J97" s="161"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="163" t="s">
@@ -9945,7 +10170,7 @@
         <v>58</v>
       </c>
       <c r="C98" s="163" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D98" s="163" t="s">
         <v>214</v>
@@ -9957,7 +10182,7 @@
       <c r="G98" s="163"/>
       <c r="H98" s="163"/>
       <c r="I98" s="161">
-        <v>140000</v>
+        <v>15000</v>
       </c>
       <c r="J98" s="161"/>
     </row>
@@ -9969,20 +10194,20 @@
         <v>58</v>
       </c>
       <c r="C99" s="163" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="D99" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E99" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F99" s="341"/>
+        <v>192</v>
+      </c>
+      <c r="F99" s="341" t="s">
+        <v>772</v>
+      </c>
       <c r="G99" s="163"/>
       <c r="H99" s="163"/>
-      <c r="I99" s="161">
-        <v>15000</v>
-      </c>
+      <c r="I99" s="161"/>
       <c r="J99" s="161"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -9993,20 +10218,26 @@
         <v>58</v>
       </c>
       <c r="C100" s="163" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="D100" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E100" s="163" t="s">
-        <v>192</v>
+        <v>214</v>
+      </c>
+      <c r="E100" s="206" t="s">
+        <v>61</v>
       </c>
       <c r="F100" s="341" t="s">
-        <v>772</v>
-      </c>
-      <c r="G100" s="163"/>
-      <c r="H100" s="163"/>
-      <c r="I100" s="161"/>
+        <v>782</v>
+      </c>
+      <c r="G100" s="164">
+        <v>43773</v>
+      </c>
+      <c r="H100" s="164">
+        <v>43773</v>
+      </c>
+      <c r="I100" s="161">
+        <v>333000</v>
+      </c>
       <c r="J100" s="161"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
@@ -10014,59 +10245,55 @@
         <v>575</v>
       </c>
       <c r="B101" s="163" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="C101" s="163" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="D101" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E101" s="206" t="s">
-        <v>61</v>
-      </c>
-      <c r="F101" s="341" t="s">
-        <v>782</v>
+        <v>143</v>
+      </c>
+      <c r="E101" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="F101" s="341">
+        <v>2025</v>
       </c>
       <c r="G101" s="164">
-        <v>43773</v>
-      </c>
-      <c r="H101" s="164">
-        <v>43773</v>
-      </c>
+        <v>45809</v>
+      </c>
+      <c r="H101" s="163"/>
       <c r="I101" s="161">
-        <v>333000</v>
+        <f>3000000/5</f>
+        <v>600000</v>
       </c>
       <c r="J101" s="161"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="163" t="s">
-        <v>575</v>
+        <v>824</v>
       </c>
       <c r="B102" s="163" t="s">
-        <v>318</v>
+        <v>825</v>
       </c>
       <c r="C102" s="163" t="s">
-        <v>792</v>
-      </c>
-      <c r="D102" s="163" t="s">
-        <v>143</v>
+        <v>826</v>
+      </c>
+      <c r="D102" s="105" t="s">
+        <v>60</v>
       </c>
       <c r="E102" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F102" s="341">
-        <v>2025</v>
-      </c>
-      <c r="G102" s="164">
-        <v>45809</v>
-      </c>
-      <c r="H102" s="163"/>
-      <c r="I102" s="161">
-        <f>3000000/5</f>
-        <v>600000</v>
-      </c>
-      <c r="J102" s="161"/>
+      <c r="F102" s="342"/>
+      <c r="G102" s="105"/>
+      <c r="H102" s="126">
+        <v>45717</v>
+      </c>
+      <c r="I102" s="124">
+        <v>85654</v>
+      </c>
+      <c r="J102" s="124"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="163" t="s">
@@ -10150,162 +10377,63 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="163" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="B106" s="163" t="s">
-        <v>825</v>
+        <v>58</v>
       </c>
       <c r="C106" s="163" t="s">
-        <v>826</v>
-      </c>
-      <c r="D106" s="105" t="s">
-        <v>60</v>
+        <v>840</v>
+      </c>
+      <c r="D106" s="163" t="s">
+        <v>143</v>
       </c>
       <c r="E106" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F106" s="342"/>
-      <c r="G106" s="105"/>
-      <c r="H106" s="126">
-        <v>45717</v>
-      </c>
-      <c r="I106" s="124">
-        <v>85654</v>
-      </c>
-      <c r="J106" s="124"/>
+        <v>192</v>
+      </c>
+      <c r="F106" s="341"/>
+      <c r="G106" s="163"/>
+      <c r="H106" s="163"/>
+      <c r="I106" s="161"/>
+      <c r="J106" s="161"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="163" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="B107" s="163" t="s">
-        <v>58</v>
+        <v>444</v>
       </c>
       <c r="C107" s="163" t="s">
-        <v>840</v>
+        <v>802</v>
       </c>
       <c r="D107" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E107" s="163" t="s">
-        <v>192</v>
+        <v>626</v>
       </c>
       <c r="F107" s="341"/>
       <c r="G107" s="163"/>
       <c r="H107" s="163"/>
-      <c r="I107" s="161"/>
+      <c r="I107" s="161">
+        <v>60000</v>
+      </c>
       <c r="J107" s="161"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A108" s="163" t="s">
-        <v>847</v>
-      </c>
-      <c r="B108" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C108" s="163" t="s">
-        <v>802</v>
-      </c>
-      <c r="D108" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E108" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F108" s="341"/>
-      <c r="G108" s="163"/>
-      <c r="H108" s="163"/>
-      <c r="I108" s="161">
-        <v>60000</v>
-      </c>
-      <c r="J108" s="161"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A109" s="163" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B109" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C109" s="163" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D109" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E109" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F109" s="341">
-        <v>2018</v>
-      </c>
-      <c r="G109" s="164">
-        <v>43101</v>
-      </c>
-      <c r="H109" s="164">
-        <v>43101</v>
-      </c>
-      <c r="I109" s="161">
-        <v>14287</v>
-      </c>
-      <c r="J109" s="161"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A110" s="163" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B110" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C110" s="163" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D110" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E110" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F110" s="341"/>
-      <c r="G110" s="164"/>
-      <c r="H110" s="164"/>
-      <c r="I110" s="161">
-        <v>10881</v>
-      </c>
-      <c r="J110" s="161"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A111" s="163" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B111" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C111" s="163" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D111" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E111" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="F111" s="341"/>
-      <c r="G111" s="163"/>
-      <c r="H111" s="163"/>
-      <c r="I111" s="161"/>
-      <c r="J111" s="161"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A112" s="163"/>
-      <c r="B112" s="163"/>
-      <c r="C112" s="163"/>
-      <c r="D112" s="163"/>
-      <c r="E112" s="163"/>
+      <c r="A108" s="163"/>
+      <c r="B108" s="163"/>
+      <c r="C108" s="163"/>
+      <c r="D108" s="163"/>
+      <c r="E108" s="163"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -17674,7 +17802,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" s="332" t="s">
         <v>1249</v>
       </c>
@@ -17702,7 +17830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A178" s="334"/>
       <c r="B178" s="332"/>
       <c r="C178" s="330" t="s">
@@ -17726,7 +17854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A179" s="332" t="s">
         <v>444</v>
       </c>
@@ -17762,7 +17890,7 @@
         <v>9425</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A180" s="332"/>
       <c r="B180" s="332"/>
       <c r="C180" s="330" t="s">
@@ -17790,7 +17918,7 @@
         <v>24649</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A181" s="332"/>
       <c r="B181" s="332"/>
       <c r="C181" s="330" t="s">
@@ -17823,8 +17951,12 @@
       <c r="R181" s="333">
         <v>3165</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T181" s="333">
+        <f>SUM(R179:R181)</f>
+        <v>37239</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A182" s="332"/>
       <c r="B182" s="332" t="s">
         <v>613</v>
@@ -17850,7 +17982,7 @@
         <v>11026</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A183" s="332"/>
       <c r="B183" s="332"/>
       <c r="C183" s="330" t="s">
@@ -17882,7 +18014,7 @@
       </c>
       <c r="R183" s="333"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" s="332"/>
       <c r="B184" s="332" t="s">
         <v>1147</v>
@@ -17914,7 +18046,7 @@
         <v>6316</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A185" s="332"/>
       <c r="B185" s="332" t="s">
         <v>920</v>
@@ -17958,7 +18090,7 @@
         <v>3602</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A186" s="332"/>
       <c r="B186" s="332"/>
       <c r="C186" s="330" t="s">
@@ -17992,7 +18124,7 @@
         <v>4372</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A187" s="332"/>
       <c r="B187" s="332"/>
       <c r="C187" s="330" t="s">
@@ -18036,7 +18168,7 @@
         <v>33108</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A188" s="332"/>
       <c r="B188" s="332"/>
       <c r="C188" s="330" t="s">
@@ -18068,7 +18200,7 @@
       </c>
       <c r="R188" s="333"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A189" s="332"/>
       <c r="B189" s="332"/>
       <c r="C189" s="330" t="s">
@@ -18102,7 +18234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A190" s="332"/>
       <c r="B190" s="332"/>
       <c r="C190" s="330" t="s">
@@ -18126,7 +18258,7 @@
         <v>5683</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A191" s="332"/>
       <c r="B191" s="332"/>
       <c r="C191" s="330" t="s">
@@ -18172,7 +18304,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A192" s="332"/>
       <c r="B192" s="332"/>
       <c r="C192" s="330" t="s">
@@ -37846,51 +37978,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Dataset</Value>
-    </ProjectType>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Green Economy</Value>
-    </ResearchArea>
-    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
-    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
-      <UserInfo>
-        <DisplayName>Ugne Keliauskaite</DisplayName>
-        <AccountId>1048</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ben McWilliams</DisplayName>
-        <AccountId>22</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Marie Jugé</DisplayName>
-        <AccountId>1714</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </Authors>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38223,7 +38310,71 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Dataset</Value>
+    </ProjectType>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Green Economy</Value>
+    </ResearchArea>
+    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
+    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
+      <UserInfo>
+        <DisplayName>Ugne Keliauskaite</DisplayName>
+        <AccountId>1048</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ben McWilliams</DisplayName>
+        <AccountId>22</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Marie Jugé</DisplayName>
+        <AccountId>1714</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </Authors>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
+    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -38240,29 +38391,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
-    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFD05D3-5EA7-E040-B604-A8F221F87DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C08C08D-62ED-7047-9732-8C5250E04D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
@@ -161,31 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{BB069DC0-8A6E-5949-BC1C-028E6717895D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ugne Keliauskaite:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Oxford</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
       <text>
         <r>
           <rPr>
@@ -218,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
       <text>
         <r>
           <rPr>
@@ -242,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -266,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C87" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C86" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -290,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E100" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
+    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
       <text>
         <r>
           <rPr>
@@ -314,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
+    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
       <text>
         <r>
           <rPr>
@@ -1555,7 +1531,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3540" uniqueCount="1309">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -7222,10 +7198,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I107" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I107" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I107">
-    <sortCondition ref="A1:A107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I106" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I106" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I106">
+    <sortCondition ref="A1:A106"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="8"/>
@@ -7570,7 +7546,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -8145,17 +8121,17 @@
         <v>142</v>
       </c>
       <c r="D21" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E21" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="341"/>
-      <c r="G21" s="164">
-        <v>43655</v>
-      </c>
-      <c r="H21" s="164">
-        <v>43655</v>
+      <c r="G21" s="339">
+        <v>45657</v>
+      </c>
+      <c r="H21" s="339">
+        <v>45657</v>
       </c>
       <c r="I21" s="124">
         <v>46387</v>
@@ -8167,23 +8143,29 @@
         <v>57</v>
       </c>
       <c r="B22" s="163" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C22" s="163" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D22" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E22" s="163" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="F22" s="341" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="163"/>
-      <c r="H22" s="163"/>
-      <c r="I22" s="161"/>
+        <v>166</v>
+      </c>
+      <c r="G22" s="164">
+        <v>46022</v>
+      </c>
+      <c r="H22" s="164">
+        <v>46022</v>
+      </c>
+      <c r="I22" s="161">
+        <v>150000</v>
+      </c>
       <c r="J22" s="161"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -8191,57 +8173,55 @@
         <v>57</v>
       </c>
       <c r="B23" s="163" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C23" s="163" t="s">
-        <v>162</v>
+        <v>1142</v>
       </c>
       <c r="D23" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E23" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="341" t="s">
-        <v>166</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F23" s="342"/>
       <c r="G23" s="164">
-        <v>46022</v>
+        <v>45291</v>
       </c>
       <c r="H23" s="164">
-        <v>46022</v>
+        <v>45291</v>
       </c>
       <c r="I23" s="161">
-        <v>150000</v>
-      </c>
-      <c r="J23" s="161"/>
+        <v>1076</v>
+      </c>
+      <c r="J23" s="124"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="163" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="B24" s="163" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="C24" s="163" t="s">
-        <v>1142</v>
+        <v>266</v>
       </c>
       <c r="D24" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="342"/>
+        <v>267</v>
+      </c>
+      <c r="F24" s="341" t="s">
+        <v>270</v>
+      </c>
       <c r="G24" s="164">
-        <v>45291</v>
+        <v>43440</v>
       </c>
       <c r="H24" s="164">
-        <v>45291</v>
-      </c>
-      <c r="I24" s="161">
-        <v>1076</v>
-      </c>
+        <v>43440</v>
+      </c>
+      <c r="I24" s="161"/>
       <c r="J24" s="124"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -8249,27 +8229,29 @@
         <v>264</v>
       </c>
       <c r="B25" s="163" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C25" s="163" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D25" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E25" s="163" t="s">
-        <v>267</v>
+        <v>61</v>
       </c>
       <c r="F25" s="341" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G25" s="164">
-        <v>43440</v>
+        <v>42855</v>
       </c>
       <c r="H25" s="164">
-        <v>43440</v>
-      </c>
-      <c r="I25" s="161"/>
+        <v>42855</v>
+      </c>
+      <c r="I25" s="161">
+        <v>400</v>
+      </c>
       <c r="J25" s="124"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -8283,70 +8265,62 @@
         <v>278</v>
       </c>
       <c r="D26" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E26" s="163" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F26" s="341" t="s">
-        <v>280</v>
-      </c>
-      <c r="G26" s="164">
-        <v>42855</v>
-      </c>
-      <c r="H26" s="164">
-        <v>42855</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="G26" s="163"/>
+      <c r="H26" s="163"/>
       <c r="I26" s="161">
-        <v>400</v>
-      </c>
-      <c r="J26" s="124"/>
+        <v>150000</v>
+      </c>
+      <c r="J26" s="161"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="163" t="s">
-        <v>264</v>
-      </c>
-      <c r="B27" s="163" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" s="163" t="s">
-        <v>278</v>
-      </c>
-      <c r="D27" s="163" t="s">
+      <c r="A27" s="183" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="183" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="183" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E27" s="163" t="s">
-        <v>124</v>
+      <c r="E27" s="183" t="s">
+        <v>192</v>
       </c>
       <c r="F27" s="341" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="G27" s="163"/>
       <c r="H27" s="163"/>
-      <c r="I27" s="161">
-        <v>150000</v>
-      </c>
+      <c r="I27" s="161"/>
       <c r="J27" s="161"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="183" t="s">
-        <v>297</v>
-      </c>
-      <c r="B28" s="183" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="183" t="s">
-        <v>298</v>
-      </c>
-      <c r="D28" s="183" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="183" t="s">
+      <c r="A28" s="163" t="s">
+        <v>308</v>
+      </c>
+      <c r="B28" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="163" t="s">
+        <v>309</v>
+      </c>
+      <c r="D28" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="163" t="s">
         <v>192</v>
       </c>
-      <c r="F28" s="341" t="s">
-        <v>299</v>
-      </c>
+      <c r="F28" s="341"/>
       <c r="G28" s="163"/>
       <c r="H28" s="163"/>
       <c r="I28" s="161"/>
@@ -8354,21 +8328,23 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="163" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B29" s="163" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="C29" s="163" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="D29" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E29" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F29" s="341"/>
+        <v>148</v>
+      </c>
+      <c r="F29" s="341" t="s">
+        <v>337</v>
+      </c>
       <c r="G29" s="163"/>
       <c r="H29" s="163"/>
       <c r="I29" s="161"/>
@@ -8379,10 +8355,10 @@
         <v>334</v>
       </c>
       <c r="B30" s="163" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="C30" s="163" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="D30" s="163" t="s">
         <v>143</v>
@@ -8390,23 +8366,23 @@
       <c r="E30" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F30" s="341" t="s">
-        <v>337</v>
-      </c>
+      <c r="F30" s="341"/>
       <c r="G30" s="163"/>
       <c r="H30" s="163"/>
-      <c r="I30" s="161"/>
+      <c r="I30" s="161">
+        <v>30000</v>
+      </c>
       <c r="J30" s="161"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="163" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B31" s="163" t="s">
-        <v>58</v>
+        <v>357</v>
       </c>
       <c r="C31" s="163" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D31" s="163" t="s">
         <v>143</v>
@@ -8414,53 +8390,55 @@
       <c r="E31" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="341"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="163"/>
+      <c r="F31" s="341" t="s">
+        <v>362</v>
+      </c>
+      <c r="G31" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H31" s="164">
+        <v>46203</v>
+      </c>
       <c r="I31" s="161">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J31" s="161"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="163" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B32" s="163" t="s">
-        <v>357</v>
+        <v>58</v>
       </c>
       <c r="C32" s="163" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="D32" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E32" s="163" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F32" s="341" t="s">
-        <v>362</v>
-      </c>
-      <c r="G32" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H32" s="164">
-        <v>46203</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="G32" s="163"/>
+      <c r="H32" s="163"/>
       <c r="I32" s="161">
-        <v>150000</v>
+        <v>100</v>
       </c>
       <c r="J32" s="161"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="163" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B33" s="163" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="C33" s="163" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D33" s="163" t="s">
         <v>143</v>
@@ -8469,24 +8447,28 @@
         <v>61</v>
       </c>
       <c r="F33" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="G33" s="163"/>
-      <c r="H33" s="163"/>
+        <v>387</v>
+      </c>
+      <c r="G33" s="164">
+        <v>46053</v>
+      </c>
+      <c r="H33" s="164">
+        <v>46053</v>
+      </c>
       <c r="I33" s="161">
-        <v>100</v>
+        <v>5591</v>
       </c>
       <c r="J33" s="161"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="163" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B34" s="163" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="C34" s="163" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="D34" s="163" t="s">
         <v>143</v>
@@ -8495,16 +8477,16 @@
         <v>61</v>
       </c>
       <c r="F34" s="341" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="G34" s="164">
-        <v>46053</v>
+        <v>45447</v>
       </c>
       <c r="H34" s="164">
-        <v>46053</v>
-      </c>
-      <c r="I34" s="161">
-        <v>5591</v>
+        <v>45447</v>
+      </c>
+      <c r="I34" s="343">
+        <v>250000</v>
       </c>
       <c r="J34" s="161"/>
     </row>
@@ -8513,10 +8495,10 @@
         <v>399</v>
       </c>
       <c r="B35" s="163" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="C35" s="163" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="D35" s="163" t="s">
         <v>143</v>
@@ -8524,17 +8506,11 @@
       <c r="E35" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="341" t="s">
-        <v>405</v>
-      </c>
-      <c r="G35" s="164">
-        <v>45447</v>
-      </c>
-      <c r="H35" s="164">
-        <v>45447</v>
-      </c>
-      <c r="I35" s="343">
-        <v>250000</v>
+      <c r="F35" s="341"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="161">
+        <v>44286</v>
       </c>
       <c r="J35" s="161"/>
     </row>
@@ -8549,31 +8525,31 @@
         <v>414</v>
       </c>
       <c r="D36" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F36" s="341"/>
       <c r="G36" s="163"/>
       <c r="H36" s="163"/>
       <c r="I36" s="161">
-        <v>44286</v>
+        <v>300000</v>
       </c>
       <c r="J36" s="161"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="163" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>318</v>
+        <v>429</v>
       </c>
       <c r="C37" s="163" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="D37" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E37" s="163" t="s">
         <v>148</v>
@@ -8581,42 +8557,47 @@
       <c r="F37" s="341"/>
       <c r="G37" s="163"/>
       <c r="H37" s="163"/>
-      <c r="I37" s="161">
-        <v>300000</v>
-      </c>
+      <c r="I37" s="161"/>
       <c r="J37" s="161"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="163" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B38" s="163" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C38" s="163" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D38" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E38" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F38" s="341"/>
-      <c r="G38" s="163"/>
-      <c r="H38" s="163"/>
-      <c r="I38" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F38" s="342"/>
+      <c r="G38" s="126">
+        <v>43891</v>
+      </c>
+      <c r="H38" s="126">
+        <v>43891</v>
+      </c>
+      <c r="I38" s="124">
+        <f>28213+43839</f>
+        <v>72052</v>
+      </c>
       <c r="J38" s="161"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="163" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B39" s="163" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C39" s="163" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D39" s="163" t="s">
         <v>143</v>
@@ -8624,28 +8605,27 @@
       <c r="E39" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F39" s="342"/>
-      <c r="G39" s="126">
-        <v>43891</v>
-      </c>
+      <c r="F39" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G39" s="126"/>
       <c r="H39" s="126">
-        <v>43891</v>
+        <v>45657</v>
       </c>
       <c r="I39" s="124">
-        <f>28213+43839</f>
-        <v>72052</v>
-      </c>
-      <c r="J39" s="161"/>
+        <v>37239</v>
+      </c>
+      <c r="J39" s="343"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="163" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B40" s="163" t="s">
-        <v>444</v>
+        <v>58</v>
       </c>
       <c r="C40" s="163" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D40" s="163" t="s">
         <v>143</v>
@@ -8654,16 +8634,18 @@
         <v>61</v>
       </c>
       <c r="F40" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G40" s="126"/>
+        <v>2015</v>
+      </c>
+      <c r="G40" s="126">
+        <v>42005</v>
+      </c>
       <c r="H40" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I40" s="124">
-        <v>37239</v>
-      </c>
-      <c r="J40" s="343"/>
+        <v>42005</v>
+      </c>
+      <c r="I40" s="343">
+        <v>18427</v>
+      </c>
+      <c r="J40" s="161"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="163" t="s">
@@ -8676,22 +8658,18 @@
         <v>463</v>
       </c>
       <c r="D41" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E41" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="342">
-        <v>2015</v>
-      </c>
-      <c r="G41" s="126">
-        <v>42005</v>
-      </c>
-      <c r="H41" s="126">
-        <v>42005</v>
-      </c>
+      <c r="F41" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G41" s="163"/>
+      <c r="H41" s="163"/>
       <c r="I41" s="343">
-        <v>18427</v>
+        <v>2650</v>
       </c>
       <c r="J41" s="161"/>
     </row>
@@ -8711,15 +8689,13 @@
       <c r="E42" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="341">
-        <v>2019</v>
-      </c>
+      <c r="F42" s="341"/>
       <c r="G42" s="163"/>
       <c r="H42" s="163"/>
       <c r="I42" s="343">
-        <v>2650</v>
-      </c>
-      <c r="J42" s="161"/>
+        <v>73662.5</v>
+      </c>
+      <c r="J42" s="124"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="163" t="s">
@@ -8729,19 +8705,25 @@
         <v>58</v>
       </c>
       <c r="C43" s="163" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="D43" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E43" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="341"/>
-      <c r="G43" s="163"/>
-      <c r="H43" s="163"/>
-      <c r="I43" s="343">
-        <v>73662.5</v>
+      <c r="F43" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G43" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H43" s="126">
+        <v>43831</v>
+      </c>
+      <c r="I43" s="161">
+        <v>4760</v>
       </c>
       <c r="J43" s="124"/>
     </row>
@@ -8756,23 +8738,19 @@
         <v>477</v>
       </c>
       <c r="D44" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E44" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="342">
-        <v>2020</v>
-      </c>
+      <c r="F44" s="342"/>
       <c r="G44" s="126">
-        <v>43831</v>
+        <v>45260</v>
       </c>
       <c r="H44" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I44" s="161">
-        <v>4760</v>
-      </c>
+        <v>45261</v>
+      </c>
+      <c r="I44" s="124"/>
       <c r="J44" s="124"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -8783,23 +8761,19 @@
         <v>58</v>
       </c>
       <c r="C45" s="163" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D45" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E45" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F45" s="342"/>
-      <c r="G45" s="126">
-        <v>45260</v>
-      </c>
-      <c r="H45" s="126">
-        <v>45261</v>
-      </c>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
       <c r="I45" s="124"/>
-      <c r="J45" s="124"/>
+      <c r="J45" s="343"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="163" t="s">
@@ -8809,7 +8783,7 @@
         <v>58</v>
       </c>
       <c r="C46" s="163" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D46" s="163" t="s">
         <v>143</v>
@@ -8817,10 +8791,18 @@
       <c r="E46" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="342"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="124"/>
+      <c r="F46" s="342">
+        <v>2018</v>
+      </c>
+      <c r="G46" s="126">
+        <v>43101</v>
+      </c>
+      <c r="H46" s="126">
+        <v>43102</v>
+      </c>
+      <c r="I46" s="124">
+        <v>83195</v>
+      </c>
       <c r="J46" s="343"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -8831,7 +8813,7 @@
         <v>58</v>
       </c>
       <c r="C47" s="163" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D47" s="163" t="s">
         <v>143</v>
@@ -8839,17 +8821,17 @@
       <c r="E47" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="342">
-        <v>2018</v>
-      </c>
-      <c r="G47" s="126">
-        <v>43101</v>
+      <c r="F47" s="341">
+        <v>2016</v>
+      </c>
+      <c r="G47" s="164">
+        <v>42370</v>
       </c>
       <c r="H47" s="126">
-        <v>43102</v>
+        <v>42370</v>
       </c>
       <c r="I47" s="124">
-        <v>83195</v>
+        <v>62577.5</v>
       </c>
       <c r="J47" s="343"/>
     </row>
@@ -8858,10 +8840,10 @@
         <v>462</v>
       </c>
       <c r="B48" s="163" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="C48" s="163" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D48" s="163" t="s">
         <v>143</v>
@@ -8870,18 +8852,16 @@
         <v>61</v>
       </c>
       <c r="F48" s="341">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G48" s="164">
-        <v>42370</v>
-      </c>
-      <c r="H48" s="126">
-        <v>42370</v>
-      </c>
+        <v>43617</v>
+      </c>
+      <c r="H48" s="105"/>
       <c r="I48" s="124">
-        <v>62577.5</v>
-      </c>
-      <c r="J48" s="343"/>
+        <v>10739</v>
+      </c>
+      <c r="J48" s="161"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="163" t="s">
@@ -8894,43 +8874,35 @@
         <v>496</v>
       </c>
       <c r="D49" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E49" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="341">
-        <v>2019</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F49" s="341"/>
       <c r="G49" s="164">
-        <v>43617</v>
-      </c>
-      <c r="H49" s="105"/>
-      <c r="I49" s="124">
-        <v>10739</v>
-      </c>
-      <c r="J49" s="161"/>
+        <v>46539</v>
+      </c>
+      <c r="H49" s="163"/>
+      <c r="I49" s="161"/>
+      <c r="J49" s="124"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="163" t="s">
         <v>462</v>
       </c>
       <c r="B50" s="163" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C50" s="163" t="s">
-        <v>496</v>
-      </c>
-      <c r="D50" s="163" t="s">
-        <v>71</v>
-      </c>
+        <v>1138</v>
+      </c>
+      <c r="D50" s="163"/>
       <c r="E50" s="163" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F50" s="341"/>
-      <c r="G50" s="164">
-        <v>46539</v>
-      </c>
+      <c r="G50" s="164"/>
       <c r="H50" s="163"/>
       <c r="I50" s="161"/>
       <c r="J50" s="124"/>
@@ -8940,19 +8912,21 @@
         <v>462</v>
       </c>
       <c r="B51" s="163" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="C51" s="163" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D51" s="163"/>
+        <v>505</v>
+      </c>
+      <c r="D51" s="163" t="s">
+        <v>143</v>
+      </c>
       <c r="E51" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="341"/>
-      <c r="G51" s="164"/>
-      <c r="H51" s="163"/>
-      <c r="I51" s="161"/>
+        <v>148</v>
+      </c>
+      <c r="F51" s="342"/>
+      <c r="G51" s="105"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="124"/>
       <c r="J51" s="124"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -8960,21 +8934,27 @@
         <v>462</v>
       </c>
       <c r="B52" s="163" t="s">
-        <v>357</v>
+        <v>161</v>
       </c>
       <c r="C52" s="163" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D52" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E52" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F52" s="342"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F52" s="341" t="s">
+        <v>511</v>
+      </c>
+      <c r="G52" s="164">
+        <v>44530</v>
+      </c>
+      <c r="H52" s="163"/>
+      <c r="I52" s="124">
+        <v>50444</v>
+      </c>
       <c r="J52" s="124"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
@@ -8988,48 +8968,48 @@
         <v>510</v>
       </c>
       <c r="D53" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E53" s="163" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F53" s="341" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G53" s="164">
-        <v>44530</v>
+        <v>46023</v>
       </c>
       <c r="H53" s="163"/>
-      <c r="I53" s="124">
-        <v>50444</v>
-      </c>
+      <c r="I53" s="161"/>
       <c r="J53" s="124"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="163" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="B54" s="163" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C54" s="163" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="D54" s="163" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F54" s="341" t="s">
-        <v>518</v>
+        <v>61</v>
+      </c>
+      <c r="F54" s="341">
+        <v>2013</v>
       </c>
       <c r="G54" s="164">
-        <v>46023</v>
+        <v>41275</v>
       </c>
       <c r="H54" s="163"/>
-      <c r="I54" s="161"/>
-      <c r="J54" s="124"/>
+      <c r="I54" s="161">
+        <v>40710</v>
+      </c>
+      <c r="J54" s="161"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="163" t="s">
@@ -9042,46 +9022,44 @@
         <v>522</v>
       </c>
       <c r="D55" s="163" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E55" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="341">
-        <v>2013</v>
-      </c>
-      <c r="G55" s="164">
-        <v>41275</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F55" s="341"/>
+      <c r="G55" s="163"/>
       <c r="H55" s="163"/>
       <c r="I55" s="161">
-        <v>40710</v>
+        <v>100000</v>
       </c>
       <c r="J55" s="161"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="163" t="s">
-        <v>521</v>
-      </c>
-      <c r="B56" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="163" t="s">
-        <v>522</v>
-      </c>
-      <c r="D56" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E56" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="341"/>
-      <c r="G56" s="163"/>
-      <c r="H56" s="163"/>
-      <c r="I56" s="161">
-        <v>100000</v>
-      </c>
-      <c r="J56" s="161"/>
+      <c r="A56" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B56" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C56" s="152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D56" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" s="338"/>
+      <c r="G56" s="152"/>
+      <c r="H56" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I56" s="337">
+        <v>16874</v>
+      </c>
+      <c r="J56" s="124"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="152" t="s">
@@ -9091,7 +9069,7 @@
         <v>265</v>
       </c>
       <c r="C57" s="152" t="s">
-        <v>1076</v>
+        <v>1134</v>
       </c>
       <c r="D57" s="152" t="s">
         <v>60</v>
@@ -9105,7 +9083,7 @@
         <v>45657</v>
       </c>
       <c r="I57" s="337">
-        <v>16874</v>
+        <v>2117</v>
       </c>
       <c r="J57" s="124"/>
     </row>
@@ -9117,7 +9095,7 @@
         <v>265</v>
       </c>
       <c r="C58" s="152" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D58" s="152" t="s">
         <v>60</v>
@@ -9128,12 +9106,12 @@
       <c r="F58" s="338"/>
       <c r="G58" s="152"/>
       <c r="H58" s="339">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="I58" s="337">
-        <v>2117</v>
-      </c>
-      <c r="J58" s="124"/>
+        <v>18174</v>
+      </c>
+      <c r="J58" s="161"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="152" t="s">
@@ -9143,7 +9121,7 @@
         <v>265</v>
       </c>
       <c r="C59" s="152" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="D59" s="152" t="s">
         <v>60</v>
@@ -9154,10 +9132,10 @@
       <c r="F59" s="338"/>
       <c r="G59" s="152"/>
       <c r="H59" s="339">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I59" s="337">
-        <v>18174</v>
+        <v>615</v>
       </c>
       <c r="J59" s="161"/>
     </row>
@@ -9169,7 +9147,7 @@
         <v>265</v>
       </c>
       <c r="C60" s="152" t="s">
-        <v>1133</v>
+        <v>1064</v>
       </c>
       <c r="D60" s="152" t="s">
         <v>60</v>
@@ -9179,37 +9157,35 @@
       </c>
       <c r="F60" s="338"/>
       <c r="G60" s="152"/>
-      <c r="H60" s="339">
+      <c r="H60" s="164">
         <v>45657</v>
       </c>
       <c r="I60" s="337">
-        <v>615</v>
+        <v>71051</v>
       </c>
       <c r="J60" s="161"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B61" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C61" s="152" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D61" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" s="152" t="s">
+      <c r="A61" s="163" t="s">
+        <v>541</v>
+      </c>
+      <c r="B61" s="163" t="s">
+        <v>542</v>
+      </c>
+      <c r="C61" s="163" t="s">
+        <v>543</v>
+      </c>
+      <c r="D61" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F61" s="338"/>
-      <c r="G61" s="152"/>
-      <c r="H61" s="164">
-        <v>45657</v>
-      </c>
-      <c r="I61" s="337">
-        <v>71051</v>
+      <c r="F61" s="341"/>
+      <c r="G61" s="163"/>
+      <c r="H61" s="163"/>
+      <c r="I61" s="161">
+        <v>26699</v>
       </c>
       <c r="J61" s="161"/>
     </row>
@@ -9224,43 +9200,47 @@
         <v>543</v>
       </c>
       <c r="D62" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E62" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" s="341"/>
-      <c r="G62" s="163"/>
-      <c r="H62" s="163"/>
-      <c r="I62" s="161">
-        <v>26699</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F62" s="341">
+        <v>2026</v>
+      </c>
+      <c r="G62" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H62" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I62" s="161"/>
       <c r="J62" s="161"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="163" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="B63" s="163" t="s">
-        <v>542</v>
+        <v>429</v>
       </c>
       <c r="C63" s="163" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="D63" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E63" s="163" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F63" s="341">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="G63" s="164">
-        <v>46203</v>
+        <v>45583</v>
       </c>
       <c r="H63" s="164">
-        <v>46203</v>
+        <v>45583</v>
       </c>
       <c r="I63" s="161"/>
       <c r="J63" s="161"/>
@@ -9276,44 +9256,46 @@
         <v>562</v>
       </c>
       <c r="D64" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E64" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64" s="341">
-        <v>2023</v>
-      </c>
-      <c r="G64" s="164">
-        <v>45583</v>
-      </c>
-      <c r="H64" s="164">
-        <v>45583</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F64" s="341"/>
+      <c r="G64" s="163"/>
+      <c r="H64" s="163"/>
       <c r="I64" s="161"/>
       <c r="J64" s="161"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="163" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="B65" s="163" t="s">
-        <v>429</v>
+        <v>318</v>
       </c>
       <c r="C65" s="163" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="D65" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E65" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F65" s="341"/>
-      <c r="G65" s="163"/>
-      <c r="H65" s="163"/>
-      <c r="I65" s="161"/>
-      <c r="J65" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F65" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G65" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H65" s="126">
+        <v>43831</v>
+      </c>
+      <c r="I65" s="124">
+        <v>20135</v>
+      </c>
+      <c r="J65" s="124"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="163" t="s">
@@ -9326,52 +9308,49 @@
         <v>579</v>
       </c>
       <c r="D66" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="163" t="s">
+        <v>124</v>
+      </c>
+      <c r="F66" s="341" t="s">
+        <v>584</v>
+      </c>
+      <c r="G66" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H66" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I66" s="161"/>
+      <c r="J66" s="161"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67" s="105" t="s">
+        <v>590</v>
+      </c>
+      <c r="B67" s="163" t="s">
+        <v>435</v>
+      </c>
+      <c r="C67" s="163" t="s">
+        <v>591</v>
+      </c>
+      <c r="D67" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E66" s="163" t="s">
+      <c r="E67" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G66" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H66" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I66" s="124">
-        <v>20135</v>
-      </c>
-      <c r="J66" s="124"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="163" t="s">
-        <v>578</v>
-      </c>
-      <c r="B67" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C67" s="163" t="s">
-        <v>579</v>
-      </c>
-      <c r="D67" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F67" s="341" t="s">
-        <v>584</v>
-      </c>
-      <c r="G67" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H67" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I67" s="161"/>
-      <c r="J67" s="161"/>
+      <c r="F67" s="342"/>
+      <c r="G67" s="126">
+        <v>44075</v>
+      </c>
+      <c r="H67" s="105"/>
+      <c r="I67" s="124">
+        <f>67243+12264</f>
+        <v>79507</v>
+      </c>
+      <c r="J67" s="124"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="105" t="s">
@@ -9384,91 +9363,92 @@
         <v>591</v>
       </c>
       <c r="D68" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E68" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F68" s="342"/>
-      <c r="G68" s="126">
-        <v>44075</v>
+      <c r="G68" s="242">
+        <v>45679</v>
       </c>
       <c r="H68" s="105"/>
-      <c r="I68" s="124">
-        <f>67243+12264</f>
-        <v>79507</v>
-      </c>
+      <c r="I68" s="124"/>
       <c r="J68" s="124"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="105" t="s">
-        <v>590</v>
+      <c r="A69" s="163" t="s">
+        <v>602</v>
       </c>
       <c r="B69" s="163" t="s">
-        <v>435</v>
+        <v>603</v>
       </c>
       <c r="C69" s="163" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="D69" s="163" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="E69" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F69" s="342"/>
-      <c r="G69" s="242">
-        <v>45679</v>
-      </c>
-      <c r="H69" s="105"/>
-      <c r="I69" s="124"/>
-      <c r="J69" s="124"/>
+        <v>192</v>
+      </c>
+      <c r="F69" s="341" t="s">
+        <v>605</v>
+      </c>
+      <c r="G69" s="163"/>
+      <c r="H69" s="163"/>
+      <c r="I69" s="161"/>
+      <c r="J69" s="161"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="163" t="s">
-        <v>602</v>
+        <v>1084</v>
       </c>
       <c r="B70" s="163" t="s">
-        <v>603</v>
+        <v>265</v>
       </c>
       <c r="C70" s="163" t="s">
-        <v>604</v>
-      </c>
-      <c r="D70" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E70" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F70" s="341" t="s">
-        <v>605</v>
-      </c>
-      <c r="G70" s="163"/>
-      <c r="H70" s="163"/>
-      <c r="I70" s="161"/>
-      <c r="J70" s="161"/>
+        <v>1083</v>
+      </c>
+      <c r="D70" s="163"/>
+      <c r="E70" s="163"/>
+      <c r="F70" s="341"/>
+      <c r="G70" s="126">
+        <v>45291</v>
+      </c>
+      <c r="H70" s="126">
+        <v>45291</v>
+      </c>
+      <c r="I70" s="161">
+        <v>33335</v>
+      </c>
+      <c r="J70" s="124"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="163" t="s">
-        <v>1084</v>
+        <v>613</v>
       </c>
       <c r="B71" s="163" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="C71" s="163" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D71" s="163"/>
-      <c r="E71" s="163"/>
-      <c r="F71" s="341"/>
+        <v>614</v>
+      </c>
+      <c r="D71" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" s="342">
+        <v>2020</v>
+      </c>
       <c r="G71" s="126">
-        <v>45291</v>
-      </c>
-      <c r="H71" s="126">
-        <v>45291</v>
-      </c>
-      <c r="I71" s="161">
-        <v>33335</v>
+        <v>43831</v>
+      </c>
+      <c r="H71" s="105"/>
+      <c r="I71" s="124">
+        <v>9653</v>
       </c>
       <c r="J71" s="124"/>
     </row>
@@ -9483,49 +9463,45 @@
         <v>614</v>
       </c>
       <c r="D72" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E72" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="342">
-        <v>2020</v>
+      <c r="F72" s="342" t="s">
+        <v>618</v>
       </c>
       <c r="G72" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H72" s="105"/>
-      <c r="I72" s="124">
-        <v>9653</v>
-      </c>
-      <c r="J72" s="124"/>
+        <v>45536</v>
+      </c>
+      <c r="H72" s="126">
+        <v>45536</v>
+      </c>
+      <c r="I72" s="124"/>
+      <c r="J72" s="161"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="163" t="s">
         <v>613</v>
       </c>
       <c r="B73" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C73" s="163" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D73" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="105" t="s">
+      <c r="E73" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F73" s="342" t="s">
-        <v>618</v>
-      </c>
-      <c r="G73" s="126">
-        <v>45536</v>
-      </c>
-      <c r="H73" s="126">
-        <v>45536</v>
-      </c>
-      <c r="I73" s="124"/>
+      <c r="F73" s="341"/>
+      <c r="G73" s="163"/>
+      <c r="H73" s="163"/>
+      <c r="I73" s="161">
+        <v>15000</v>
+      </c>
       <c r="J73" s="161"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -9539,39 +9515,43 @@
         <v>621</v>
       </c>
       <c r="D74" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E74" s="163" t="s">
-        <v>61</v>
+        <v>626</v>
       </c>
       <c r="F74" s="341"/>
       <c r="G74" s="163"/>
       <c r="H74" s="163"/>
-      <c r="I74" s="161">
-        <v>15000</v>
-      </c>
-      <c r="J74" s="161"/>
+      <c r="I74" s="161"/>
+      <c r="J74" s="124"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="163" t="s">
         <v>613</v>
       </c>
       <c r="B75" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" s="163" t="s">
-        <v>621</v>
+        <v>444</v>
+      </c>
+      <c r="C75" s="328" t="s">
+        <v>628</v>
       </c>
       <c r="D75" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E75" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F75" s="341"/>
-      <c r="G75" s="163"/>
-      <c r="H75" s="163"/>
-      <c r="I75" s="161"/>
+        <v>192</v>
+      </c>
+      <c r="F75" s="342"/>
+      <c r="G75" s="126">
+        <v>43559</v>
+      </c>
+      <c r="H75" s="126">
+        <v>43559</v>
+      </c>
+      <c r="I75" s="124">
+        <v>49264</v>
+      </c>
       <c r="J75" s="124"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
@@ -9585,21 +9565,21 @@
         <v>628</v>
       </c>
       <c r="D76" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E76" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="342"/>
+        <v>148</v>
+      </c>
+      <c r="F76" s="342">
+        <v>2023</v>
+      </c>
       <c r="G76" s="126">
-        <v>43559</v>
+        <v>45107</v>
       </c>
       <c r="H76" s="126">
-        <v>43559</v>
-      </c>
-      <c r="I76" s="124">
-        <v>49264</v>
-      </c>
+        <v>45108</v>
+      </c>
+      <c r="I76" s="124"/>
       <c r="J76" s="124"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
@@ -9607,27 +9587,29 @@
         <v>613</v>
       </c>
       <c r="B77" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C77" s="328" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C77" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D77" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E77" s="163" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F77" s="342">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="G77" s="126">
-        <v>45107</v>
+        <v>41061</v>
       </c>
       <c r="H77" s="126">
-        <v>45108</v>
-      </c>
-      <c r="I77" s="124"/>
+        <v>41061</v>
+      </c>
+      <c r="I77" s="124">
+        <v>3734</v>
+      </c>
       <c r="J77" s="124"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
@@ -9641,23 +9623,21 @@
         <v>638</v>
       </c>
       <c r="D78" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E78" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="342">
-        <v>2012</v>
+      <c r="F78" s="342" t="s">
+        <v>511</v>
       </c>
       <c r="G78" s="126">
-        <v>41061</v>
+        <v>44501</v>
       </c>
       <c r="H78" s="126">
-        <v>41061</v>
-      </c>
-      <c r="I78" s="124">
-        <v>3734</v>
-      </c>
+        <v>44502</v>
+      </c>
+      <c r="I78" s="124"/>
       <c r="J78" s="124"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
@@ -9674,17 +9654,11 @@
         <v>71</v>
       </c>
       <c r="E79" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F79" s="342" t="s">
-        <v>511</v>
-      </c>
-      <c r="G79" s="126">
-        <v>44501</v>
-      </c>
-      <c r="H79" s="126">
-        <v>44502</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F79" s="342"/>
+      <c r="G79" s="105"/>
+      <c r="H79" s="105"/>
       <c r="I79" s="124"/>
       <c r="J79" s="124"/>
     </row>
@@ -9695,47 +9669,53 @@
       <c r="B80" s="163" t="s">
         <v>318</v>
       </c>
-      <c r="C80" s="105" t="s">
-        <v>638</v>
+      <c r="C80" s="163" t="s">
+        <v>649</v>
       </c>
       <c r="D80" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E80" s="163" t="s">
         <v>124</v>
       </c>
-      <c r="F80" s="342"/>
-      <c r="G80" s="105"/>
-      <c r="H80" s="105"/>
+      <c r="F80" s="344">
+        <v>46508</v>
+      </c>
+      <c r="G80" s="126">
+        <v>46508</v>
+      </c>
+      <c r="H80" s="126">
+        <v>46508</v>
+      </c>
       <c r="I80" s="124"/>
       <c r="J80" s="124"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="163" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B81" s="163" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="C81" s="163" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D81" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E81" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F81" s="344">
-        <v>46508</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F81" s="342"/>
       <c r="G81" s="126">
-        <v>46508</v>
+        <v>45291</v>
       </c>
       <c r="H81" s="126">
-        <v>46508</v>
-      </c>
-      <c r="I81" s="124"/>
+        <v>45291</v>
+      </c>
+      <c r="I81" s="124">
+        <v>42533</v>
+      </c>
       <c r="J81" s="124"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
@@ -9745,14 +9725,14 @@
       <c r="B82" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="C82" s="163" t="s">
-        <v>653</v>
+      <c r="C82" s="138" t="s">
+        <v>657</v>
       </c>
       <c r="D82" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E82" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F82" s="342"/>
       <c r="G82" s="126">
@@ -9762,7 +9742,7 @@
         <v>45291</v>
       </c>
       <c r="I82" s="124">
-        <v>42533</v>
+        <v>15433</v>
       </c>
       <c r="J82" s="124"/>
     </row>
@@ -9774,42 +9754,38 @@
         <v>265</v>
       </c>
       <c r="C83" s="138" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D83" s="163" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E83" s="163" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F83" s="342"/>
       <c r="G83" s="126">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H83" s="126">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I83" s="124">
-        <v>15433</v>
+        <v>24008</v>
       </c>
       <c r="J83" s="124"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="163" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="B84" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="C84" s="138" t="s">
-        <v>663</v>
-      </c>
-      <c r="D84" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E84" s="163" t="s">
-        <v>61</v>
-      </c>
+      <c r="C84" s="163" t="s">
+        <v>668</v>
+      </c>
+      <c r="D84" s="163"/>
+      <c r="E84" s="163"/>
       <c r="F84" s="342"/>
       <c r="G84" s="126">
         <v>45657</v>
@@ -9818,7 +9794,7 @@
         <v>45657</v>
       </c>
       <c r="I84" s="124">
-        <v>24008</v>
+        <v>23534</v>
       </c>
       <c r="J84" s="124"/>
     </row>
@@ -9832,17 +9808,15 @@
       <c r="C85" s="163" t="s">
         <v>668</v>
       </c>
-      <c r="D85" s="163"/>
-      <c r="E85" s="163"/>
-      <c r="F85" s="342"/>
-      <c r="G85" s="126">
-        <v>45657</v>
-      </c>
-      <c r="H85" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I85" s="124">
-        <v>23534</v>
+      <c r="D85" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E85" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F85" s="341"/>
+      <c r="I85" s="161">
+        <v>5000</v>
       </c>
       <c r="J85" s="124"/>
     </row>
@@ -9851,10 +9825,10 @@
         <v>667</v>
       </c>
       <c r="B86" s="163" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C86" s="163" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D86" s="163" t="s">
         <v>143</v>
@@ -9862,21 +9836,25 @@
       <c r="E86" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F86" s="341"/>
+      <c r="F86" s="341" t="s">
+        <v>682</v>
+      </c>
+      <c r="G86" s="163"/>
+      <c r="H86" s="163"/>
       <c r="I86" s="161">
-        <v>5000</v>
-      </c>
-      <c r="J86" s="124"/>
+        <v>111872</v>
+      </c>
+      <c r="J86" s="161"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="163" t="s">
         <v>667</v>
       </c>
       <c r="B87" s="163" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="C87" s="163" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D87" s="163" t="s">
         <v>143</v>
@@ -9885,66 +9863,70 @@
         <v>61</v>
       </c>
       <c r="F87" s="341" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="G87" s="163"/>
       <c r="H87" s="163"/>
-      <c r="I87" s="161">
-        <v>111872</v>
-      </c>
+      <c r="I87" s="161"/>
       <c r="J87" s="161"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="163" t="s">
-        <v>667</v>
-      </c>
-      <c r="B88" s="163" t="s">
-        <v>357</v>
-      </c>
-      <c r="C88" s="163" t="s">
-        <v>691</v>
-      </c>
-      <c r="D88" s="163" t="s">
+      <c r="A88" s="183" t="s">
+        <v>703</v>
+      </c>
+      <c r="B88" s="183" t="s">
+        <v>704</v>
+      </c>
+      <c r="C88" s="183" t="s">
+        <v>705</v>
+      </c>
+      <c r="D88" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="163" t="s">
+      <c r="E88" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="F88" s="341" t="s">
-        <v>694</v>
-      </c>
-      <c r="G88" s="163"/>
-      <c r="H88" s="163"/>
-      <c r="I88" s="161"/>
-      <c r="J88" s="161"/>
+      <c r="F88" s="342" t="s">
+        <v>708</v>
+      </c>
+      <c r="G88" s="126">
+        <v>46023</v>
+      </c>
+      <c r="H88" s="126">
+        <v>46023</v>
+      </c>
+      <c r="I88" s="124">
+        <v>50000</v>
+      </c>
+      <c r="J88" s="124"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A89" s="183" t="s">
-        <v>703</v>
-      </c>
-      <c r="B89" s="183" t="s">
-        <v>704</v>
-      </c>
-      <c r="C89" s="183" t="s">
-        <v>705</v>
-      </c>
-      <c r="D89" s="183" t="s">
+      <c r="A89" s="163" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B89" s="163" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" s="163" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D89" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E89" s="183" t="s">
+      <c r="E89" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F89" s="342" t="s">
-        <v>708</v>
-      </c>
-      <c r="G89" s="126">
-        <v>46023</v>
-      </c>
-      <c r="H89" s="126">
-        <v>46023</v>
-      </c>
-      <c r="I89" s="124">
-        <v>50000</v>
+      <c r="F89" s="341">
+        <v>2018</v>
+      </c>
+      <c r="G89" s="164">
+        <v>43101</v>
+      </c>
+      <c r="H89" s="164">
+        <v>43101</v>
+      </c>
+      <c r="I89" s="161">
+        <v>14287</v>
       </c>
       <c r="J89" s="124"/>
     </row>
@@ -9959,24 +9941,18 @@
         <v>1029</v>
       </c>
       <c r="D90" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E90" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F90" s="341">
-        <v>2018</v>
-      </c>
-      <c r="G90" s="164">
-        <v>43101</v>
-      </c>
-      <c r="H90" s="164">
-        <v>43101</v>
-      </c>
+      <c r="F90" s="341"/>
+      <c r="G90" s="164"/>
+      <c r="H90" s="164"/>
       <c r="I90" s="161">
-        <v>14287</v>
-      </c>
-      <c r="J90" s="124"/>
+        <v>10881</v>
+      </c>
+      <c r="J90" s="161"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="163" t="s">
@@ -9991,150 +9967,150 @@
       <c r="D91" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="E91" s="163" t="s">
-        <v>61</v>
+      <c r="E91" s="105" t="s">
+        <v>148</v>
       </c>
       <c r="F91" s="341"/>
-      <c r="G91" s="164"/>
-      <c r="H91" s="164"/>
-      <c r="I91" s="161">
-        <v>10881</v>
-      </c>
+      <c r="G91" s="163"/>
+      <c r="H91" s="163"/>
+      <c r="I91" s="161"/>
       <c r="J91" s="161"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="163" t="s">
-        <v>1028</v>
+        <v>718</v>
       </c>
       <c r="B92" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C92" s="163" t="s">
-        <v>1029</v>
+        <v>375</v>
       </c>
       <c r="D92" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E92" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="F92" s="341"/>
-      <c r="G92" s="163"/>
-      <c r="H92" s="163"/>
-      <c r="I92" s="161"/>
-      <c r="J92" s="161"/>
+        <v>143</v>
+      </c>
+      <c r="E92" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F92" s="341" t="s">
+        <v>721</v>
+      </c>
+      <c r="G92" s="164">
+        <v>44642</v>
+      </c>
+      <c r="H92" s="164">
+        <v>44642</v>
+      </c>
+      <c r="I92" s="124">
+        <v>206097</v>
+      </c>
+      <c r="J92" s="124"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="163" t="s">
         <v>718</v>
       </c>
       <c r="B93" s="163" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="C93" s="163" t="s">
-        <v>375</v>
+        <v>729</v>
       </c>
       <c r="D93" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E93" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F93" s="341" t="s">
-        <v>721</v>
+        <v>192</v>
+      </c>
+      <c r="F93" s="341">
+        <v>2015</v>
       </c>
       <c r="G93" s="164">
-        <v>44642</v>
+        <v>42156</v>
       </c>
       <c r="H93" s="164">
-        <v>44642</v>
-      </c>
-      <c r="I93" s="124">
-        <v>206097</v>
-      </c>
-      <c r="J93" s="124"/>
+        <v>42157</v>
+      </c>
+      <c r="I93" s="161"/>
+      <c r="J93" s="161"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="163" t="s">
-        <v>718</v>
+        <v>737</v>
       </c>
       <c r="B94" s="163" t="s">
-        <v>335</v>
+        <v>212</v>
       </c>
       <c r="C94" s="163" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="D94" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E94" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F94" s="341">
-        <v>2015</v>
-      </c>
-      <c r="G94" s="164">
-        <v>42156</v>
-      </c>
-      <c r="H94" s="164">
-        <v>42157</v>
-      </c>
-      <c r="I94" s="161"/>
+        <v>148</v>
+      </c>
+      <c r="F94" s="341" t="s">
+        <v>739</v>
+      </c>
+      <c r="G94" s="163"/>
+      <c r="H94" s="163"/>
+      <c r="I94" s="161">
+        <v>30000</v>
+      </c>
       <c r="J94" s="161"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A95" s="163" t="s">
-        <v>737</v>
-      </c>
-      <c r="B95" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C95" s="163" t="s">
-        <v>738</v>
-      </c>
-      <c r="D95" s="163" t="s">
+      <c r="A95" s="183" t="s">
+        <v>575</v>
+      </c>
+      <c r="B95" s="183" t="s">
+        <v>444</v>
+      </c>
+      <c r="C95" s="183" t="s">
+        <v>745</v>
+      </c>
+      <c r="D95" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E95" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F95" s="341" t="s">
-        <v>739</v>
-      </c>
-      <c r="G95" s="163"/>
-      <c r="H95" s="163"/>
-      <c r="I95" s="161">
-        <v>30000</v>
+      <c r="E95" s="183" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" s="342">
+        <v>2013</v>
+      </c>
+      <c r="G95" s="126">
+        <v>41426</v>
+      </c>
+      <c r="H95" s="126">
+        <v>41426</v>
+      </c>
+      <c r="I95" s="124">
+        <v>94839</v>
       </c>
       <c r="J95" s="161"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="183" t="s">
+      <c r="A96" s="163" t="s">
         <v>575</v>
       </c>
-      <c r="B96" s="183" t="s">
-        <v>444</v>
-      </c>
-      <c r="C96" s="183" t="s">
-        <v>745</v>
-      </c>
-      <c r="D96" s="183" t="s">
-        <v>143</v>
-      </c>
-      <c r="E96" s="183" t="s">
+      <c r="B96" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" s="163" t="s">
+        <v>754</v>
+      </c>
+      <c r="D96" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="E96" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F96" s="342">
-        <v>2013</v>
-      </c>
-      <c r="G96" s="126">
-        <v>41426</v>
-      </c>
-      <c r="H96" s="126">
-        <v>41426</v>
-      </c>
-      <c r="I96" s="124">
-        <v>94839</v>
+      <c r="F96" s="341"/>
+      <c r="G96" s="163"/>
+      <c r="H96" s="163"/>
+      <c r="I96" s="161">
+        <v>140000</v>
       </c>
       <c r="J96" s="161"/>
     </row>
@@ -10146,7 +10122,7 @@
         <v>58</v>
       </c>
       <c r="C97" s="163" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D97" s="163" t="s">
         <v>214</v>
@@ -10158,7 +10134,7 @@
       <c r="G97" s="163"/>
       <c r="H97" s="163"/>
       <c r="I97" s="161">
-        <v>140000</v>
+        <v>15000</v>
       </c>
       <c r="J97" s="161"/>
     </row>
@@ -10170,20 +10146,20 @@
         <v>58</v>
       </c>
       <c r="C98" s="163" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="D98" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E98" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F98" s="341"/>
+        <v>192</v>
+      </c>
+      <c r="F98" s="341" t="s">
+        <v>772</v>
+      </c>
       <c r="G98" s="163"/>
       <c r="H98" s="163"/>
-      <c r="I98" s="161">
-        <v>15000</v>
-      </c>
+      <c r="I98" s="161"/>
       <c r="J98" s="161"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
@@ -10194,20 +10170,26 @@
         <v>58</v>
       </c>
       <c r="C99" s="163" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="D99" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E99" s="163" t="s">
-        <v>192</v>
+        <v>214</v>
+      </c>
+      <c r="E99" s="206" t="s">
+        <v>61</v>
       </c>
       <c r="F99" s="341" t="s">
-        <v>772</v>
-      </c>
-      <c r="G99" s="163"/>
-      <c r="H99" s="163"/>
-      <c r="I99" s="161"/>
+        <v>782</v>
+      </c>
+      <c r="G99" s="164">
+        <v>43773</v>
+      </c>
+      <c r="H99" s="164">
+        <v>43773</v>
+      </c>
+      <c r="I99" s="161">
+        <v>333000</v>
+      </c>
       <c r="J99" s="161"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -10215,95 +10197,93 @@
         <v>575</v>
       </c>
       <c r="B100" s="163" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="C100" s="163" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="D100" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E100" s="206" t="s">
-        <v>61</v>
-      </c>
-      <c r="F100" s="341" t="s">
-        <v>782</v>
+        <v>143</v>
+      </c>
+      <c r="E100" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="F100" s="341">
+        <v>2025</v>
       </c>
       <c r="G100" s="164">
-        <v>43773</v>
-      </c>
-      <c r="H100" s="164">
-        <v>43773</v>
-      </c>
+        <v>45809</v>
+      </c>
+      <c r="H100" s="163"/>
       <c r="I100" s="161">
-        <v>333000</v>
+        <f>3000000/5</f>
+        <v>600000</v>
       </c>
       <c r="J100" s="161"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="163" t="s">
-        <v>575</v>
+        <v>824</v>
       </c>
       <c r="B101" s="163" t="s">
-        <v>318</v>
+        <v>825</v>
       </c>
       <c r="C101" s="163" t="s">
-        <v>792</v>
-      </c>
-      <c r="D101" s="163" t="s">
-        <v>143</v>
+        <v>826</v>
+      </c>
+      <c r="D101" s="105" t="s">
+        <v>60</v>
       </c>
       <c r="E101" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F101" s="341">
-        <v>2025</v>
-      </c>
-      <c r="G101" s="164">
-        <v>45809</v>
-      </c>
-      <c r="H101" s="163"/>
-      <c r="I101" s="161">
-        <f>3000000/5</f>
-        <v>600000</v>
-      </c>
-      <c r="J101" s="161"/>
+      <c r="F101" s="342"/>
+      <c r="G101" s="105"/>
+      <c r="H101" s="126">
+        <v>45717</v>
+      </c>
+      <c r="I101" s="124">
+        <v>85654</v>
+      </c>
+      <c r="J101" s="124"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="163" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B102" s="163" t="s">
-        <v>825</v>
+        <v>265</v>
       </c>
       <c r="C102" s="163" t="s">
-        <v>826</v>
-      </c>
-      <c r="D102" s="105" t="s">
-        <v>60</v>
+        <v>811</v>
+      </c>
+      <c r="D102" s="163" t="s">
+        <v>143</v>
       </c>
       <c r="E102" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F102" s="342"/>
-      <c r="G102" s="105"/>
-      <c r="H102" s="126">
-        <v>45717</v>
-      </c>
-      <c r="I102" s="124">
-        <v>85654</v>
-      </c>
-      <c r="J102" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F102" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G102" s="164">
+        <v>43646</v>
+      </c>
+      <c r="H102" s="164">
+        <v>43646</v>
+      </c>
+      <c r="I102" s="161"/>
+      <c r="J102" s="161"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="163" t="s">
         <v>810</v>
       </c>
       <c r="B103" s="163" t="s">
-        <v>265</v>
+        <v>212</v>
       </c>
       <c r="C103" s="163" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="D103" s="163" t="s">
         <v>143</v>
@@ -10311,14 +10291,12 @@
       <c r="E103" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F103" s="341">
-        <v>2019</v>
-      </c>
+      <c r="F103" s="341"/>
       <c r="G103" s="164">
-        <v>43646</v>
+        <v>45183</v>
       </c>
       <c r="H103" s="164">
-        <v>43646</v>
+        <v>45183</v>
       </c>
       <c r="I103" s="161"/>
       <c r="J103" s="161"/>
@@ -10334,99 +10312,73 @@
         <v>817</v>
       </c>
       <c r="D104" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E104" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F104" s="341"/>
       <c r="G104" s="164">
-        <v>45183</v>
+        <v>45777</v>
       </c>
       <c r="H104" s="164">
-        <v>45183</v>
+        <v>45777</v>
       </c>
       <c r="I104" s="161"/>
       <c r="J104" s="161"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="163" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="B105" s="163" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="C105" s="163" t="s">
-        <v>817</v>
+        <v>840</v>
       </c>
       <c r="D105" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E105" s="163" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="F105" s="341"/>
-      <c r="G105" s="164">
-        <v>45777</v>
-      </c>
-      <c r="H105" s="164">
-        <v>45777</v>
-      </c>
+      <c r="G105" s="163"/>
+      <c r="H105" s="163"/>
       <c r="I105" s="161"/>
       <c r="J105" s="161"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="163" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="B106" s="163" t="s">
-        <v>58</v>
+        <v>444</v>
       </c>
       <c r="C106" s="163" t="s">
-        <v>840</v>
+        <v>802</v>
       </c>
       <c r="D106" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E106" s="163" t="s">
-        <v>192</v>
+        <v>626</v>
       </c>
       <c r="F106" s="341"/>
       <c r="G106" s="163"/>
       <c r="H106" s="163"/>
-      <c r="I106" s="161"/>
+      <c r="I106" s="161">
+        <v>60000</v>
+      </c>
       <c r="J106" s="161"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A107" s="163" t="s">
-        <v>847</v>
-      </c>
-      <c r="B107" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C107" s="163" t="s">
-        <v>802</v>
-      </c>
-      <c r="D107" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E107" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F107" s="341"/>
-      <c r="G107" s="163"/>
-      <c r="H107" s="163"/>
-      <c r="I107" s="161">
-        <v>60000</v>
-      </c>
-      <c r="J107" s="161"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A108" s="163"/>
-      <c r="B108" s="163"/>
-      <c r="C108" s="163"/>
-      <c r="D108" s="163"/>
-      <c r="E108" s="163"/>
+      <c r="A107" s="163"/>
+      <c r="B107" s="163"/>
+      <c r="C107" s="163"/>
+      <c r="D107" s="163"/>
+      <c r="E107" s="163"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37978,6 +37930,51 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Dataset</Value>
+    </ProjectType>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Green Economy</Value>
+    </ResearchArea>
+    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
+    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
+      <UserInfo>
+        <DisplayName>Ugne Keliauskaite</DisplayName>
+        <AccountId>1048</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ben McWilliams</DisplayName>
+        <AccountId>22</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Marie Jugé</DisplayName>
+        <AccountId>1714</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </Authors>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38310,66 +38307,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Dataset</Value>
-    </ProjectType>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Green Economy</Value>
-    </ResearchArea>
-    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
-    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
-      <UserInfo>
-        <DisplayName>Ugne Keliauskaite</DisplayName>
-        <AccountId>1048</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ben McWilliams</DisplayName>
-        <AccountId>22</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Marie Jugé</DisplayName>
-        <AccountId>1714</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </Authors>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
-    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -38392,9 +38333,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
+    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C08C08D-62ED-7047-9732-8C5250E04D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD65710-18CC-3D4F-9F84-407C59848E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
@@ -10235,12 +10235,12 @@
         <v>60</v>
       </c>
       <c r="E101" s="163" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="F101" s="342"/>
       <c r="G101" s="105"/>
       <c r="H101" s="126">
-        <v>45717</v>
+        <v>45657</v>
       </c>
       <c r="I101" s="124">
         <v>85654</v>
@@ -37930,15 +37930,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
@@ -37974,7 +37965,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38307,15 +38298,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -38332,7 +38324,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38349,4 +38341,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD65710-18CC-3D4F-9F84-407C59848E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4121EBB2-CB4E-3D41-A243-C2B482BEFFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <author>Ugne Keliauskaite</author>
   </authors>
   <commentList>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{FB35ED95-2CC7-344D-994B-16920F4F8BAC}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{FB35ED95-2CC7-344D-994B-16920F4F8BAC}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{8133A74B-A2B7-1F46-B1E6-817B58D06909}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{8133A74B-A2B7-1F46-B1E6-817B58D06909}">
       <text>
         <r>
           <rPr>
@@ -113,13 +113,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -128,16 +128,25 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-2013-2022</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2013-2022</t>
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{1CB05A61-ED73-9F40-8D60-A96C94868F7E}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{1CB05A61-ED73-9F40-8D60-A96C94868F7E}">
       <text>
         <r>
           <rPr>
@@ -161,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
+    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{145C7E98-B095-C643-8924-514EDD25BEC5}">
       <text>
         <r>
           <rPr>
@@ -194,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
       <text>
         <r>
           <rPr>
@@ -218,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -242,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C86" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C72" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -266,7 +275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
+    <comment ref="E85" authorId="0" shapeId="0" xr:uid="{D8F4CA31-F91E-AF45-ADD2-443248F0B75A}">
       <text>
         <r>
           <rPr>
@@ -290,7 +299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
+    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{348C7426-DCB9-3442-84D9-DE241977A6F5}">
       <text>
         <r>
           <rPr>
@@ -1531,7 +1540,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3540" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="1308">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -5033,9 +5042,6 @@
   </si>
   <si>
     <t>Flins</t>
-  </si>
-  <si>
-    <t>Hambach</t>
   </si>
   <si>
     <t>Toyota Motor Corp.</t>
@@ -7198,10 +7204,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I106" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I106" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I106">
-    <sortCondition ref="A1:A106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I92" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I92" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I92">
+    <sortCondition ref="A1:A92"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="8"/>
@@ -7546,7 +7552,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -7591,273 +7597,281 @@
       <c r="J1" s="337"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="163" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="163" t="s">
-        <v>182</v>
-      </c>
-      <c r="C2" s="163" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="341" t="s">
-        <v>185</v>
-      </c>
-      <c r="G2" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H2" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I2" s="161">
-        <v>50000</v>
+      <c r="A2" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="338"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I2" s="337">
+        <v>17646</v>
       </c>
       <c r="J2" s="337"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="163" t="s">
-        <v>190</v>
+      <c r="A3" s="105" t="s">
+        <v>211</v>
       </c>
       <c r="B3" s="163" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="C3" s="163" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="163" t="s">
-        <v>143</v>
+        <v>213</v>
+      </c>
+      <c r="D3" s="105" t="s">
+        <v>214</v>
       </c>
       <c r="E3" s="163" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="341"/>
-      <c r="G3" s="164">
-        <v>44249</v>
-      </c>
-      <c r="H3" s="164">
-        <v>44249</v>
-      </c>
-      <c r="I3" s="161"/>
+      <c r="F3" s="342">
+        <v>2018</v>
+      </c>
+      <c r="G3" s="126">
+        <v>43252</v>
+      </c>
+      <c r="H3" s="105"/>
+      <c r="I3" s="124">
+        <v>50339</v>
+      </c>
       <c r="J3" s="337"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="163" t="s">
-        <v>201</v>
+      <c r="A4" s="105" t="s">
+        <v>211</v>
       </c>
       <c r="B4" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="163" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="342">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="126">
+        <v>45292</v>
+      </c>
+      <c r="H4" s="105"/>
+      <c r="I4" s="124">
+        <v>15411</v>
+      </c>
+      <c r="J4" s="337"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="105" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G5" s="126">
+        <v>43983</v>
+      </c>
+      <c r="H5" s="105"/>
+      <c r="I5" s="124">
+        <v>28334</v>
+      </c>
+      <c r="J5" s="161"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="163" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="163" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="163" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="163" t="s">
+      <c r="C6" s="163" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="341" t="s">
-        <v>203</v>
-      </c>
-      <c r="G4" s="164">
+      <c r="E6" s="163" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="341" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="164">
         <v>46203</v>
       </c>
-      <c r="H4" s="164">
+      <c r="H6" s="164">
         <v>46203</v>
       </c>
-      <c r="I4" s="161"/>
-      <c r="J4" s="337"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="152" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="152" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="152" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D5" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="338"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I5" s="337">
-        <v>17646</v>
-      </c>
-      <c r="J5" s="337"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="105" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="163" t="s">
-        <v>213</v>
-      </c>
-      <c r="D6" s="105" t="s">
-        <v>214</v>
-      </c>
-      <c r="E6" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="342">
-        <v>2018</v>
-      </c>
-      <c r="G6" s="126">
-        <v>43252</v>
-      </c>
-      <c r="H6" s="105"/>
-      <c r="I6" s="124">
-        <v>50339</v>
-      </c>
-      <c r="J6" s="337"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="105" t="s">
-        <v>211</v>
+      <c r="A7" s="163" t="s">
+        <v>57</v>
       </c>
       <c r="B7" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C7" s="163" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="105" t="s">
-        <v>143</v>
+        <v>59</v>
+      </c>
+      <c r="D7" s="163" t="s">
+        <v>60</v>
       </c>
       <c r="E7" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="342">
-        <v>2024</v>
-      </c>
-      <c r="G7" s="126">
-        <v>45292</v>
-      </c>
-      <c r="H7" s="105"/>
-      <c r="I7" s="124">
-        <v>15411</v>
-      </c>
-      <c r="J7" s="337"/>
+      <c r="F7" s="340">
+        <v>42370</v>
+      </c>
+      <c r="G7" s="163"/>
+      <c r="I7" s="161">
+        <v>28225</v>
+      </c>
+      <c r="J7" s="161"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="105" t="s">
-        <v>211</v>
+      <c r="A8" s="163" t="s">
+        <v>57</v>
       </c>
       <c r="B8" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="105" t="s">
-        <v>224</v>
+      <c r="C8" s="163" t="s">
+        <v>59</v>
       </c>
       <c r="D8" s="163" t="s">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="E8" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G8" s="126">
-        <v>43983</v>
-      </c>
-      <c r="H8" s="105"/>
-      <c r="I8" s="124">
-        <v>28334</v>
+      <c r="F8" s="340">
+        <v>45128</v>
+      </c>
+      <c r="G8" s="163"/>
+      <c r="H8" s="164">
+        <v>45657</v>
+      </c>
+      <c r="I8" s="161">
+        <v>123209</v>
       </c>
       <c r="J8" s="161"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="163" t="s">
-        <v>230</v>
+        <v>57</v>
       </c>
       <c r="B9" s="163" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="C9" s="163" t="s">
-        <v>231</v>
+        <v>99</v>
       </c>
       <c r="D9" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E9" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="341">
-        <v>2020</v>
-      </c>
-      <c r="G9" s="163"/>
-      <c r="H9" s="163"/>
-      <c r="I9" s="161"/>
+      <c r="F9" s="340"/>
+      <c r="G9" s="164">
+        <v>41535</v>
+      </c>
+      <c r="H9" s="164">
+        <v>41535</v>
+      </c>
+      <c r="I9" s="124">
+        <f>250000/9</f>
+        <v>27777.777777777777</v>
+      </c>
       <c r="J9" s="161"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="163" t="s">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="B10" s="163" t="s">
-        <v>241</v>
+        <v>58</v>
       </c>
       <c r="C10" s="163" t="s">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="D10" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E10" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="341" t="s">
-        <v>244</v>
-      </c>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F10" s="340"/>
+      <c r="G10" s="164">
+        <v>45355</v>
+      </c>
+      <c r="H10" s="164">
+        <v>45355</v>
+      </c>
+      <c r="I10" s="124">
+        <v>100000</v>
+      </c>
       <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="163" t="s">
-        <v>253</v>
+        <v>57</v>
       </c>
       <c r="B11" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C11" s="163" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="D11" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E11" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" s="341" t="s">
-        <v>256</v>
+        <v>61</v>
+      </c>
+      <c r="F11" s="341">
+        <v>2015</v>
       </c>
       <c r="G11" s="164">
-        <v>46203</v>
+        <v>42185</v>
       </c>
       <c r="H11" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I11" s="161"/>
+        <v>42185</v>
+      </c>
+      <c r="I11" s="161">
+        <v>20016</v>
+      </c>
       <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -7868,20 +7882,24 @@
         <v>58</v>
       </c>
       <c r="C12" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="163" t="s">
-        <v>60</v>
+        <v>130</v>
+      </c>
+      <c r="D12" s="250" t="s">
+        <v>71</v>
       </c>
       <c r="E12" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="340">
-        <v>42370</v>
-      </c>
-      <c r="G12" s="163"/>
-      <c r="I12" s="161">
-        <v>28225</v>
+      <c r="F12" s="342"/>
+      <c r="G12" s="164">
+        <v>44876</v>
+      </c>
+      <c r="H12" s="164">
+        <v>44876</v>
+      </c>
+      <c r="I12" s="124">
+        <f>342521*0.33</f>
+        <v>113031.93000000001</v>
       </c>
       <c r="J12" s="161"/>
     </row>
@@ -7893,23 +7911,24 @@
         <v>58</v>
       </c>
       <c r="C13" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="163" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="105" t="s">
         <v>71</v>
       </c>
       <c r="E13" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="340">
-        <v>45128</v>
-      </c>
-      <c r="G13" s="163"/>
+      <c r="F13" s="342"/>
+      <c r="G13" s="164">
+        <v>45744</v>
+      </c>
       <c r="H13" s="164">
-        <v>45657</v>
-      </c>
-      <c r="I13" s="161">
-        <v>123209</v>
+        <v>45744</v>
+      </c>
+      <c r="I13" s="124">
+        <f>I12+120*365</f>
+        <v>156831.93</v>
       </c>
       <c r="J13" s="161"/>
     </row>
@@ -7918,27 +7937,26 @@
         <v>57</v>
       </c>
       <c r="B14" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C14" s="163" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="D14" s="163" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E14" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="340"/>
-      <c r="G14" s="164">
-        <v>41535</v>
-      </c>
-      <c r="H14" s="164">
-        <v>41535</v>
+      <c r="F14" s="341"/>
+      <c r="G14" s="339">
+        <v>45657</v>
+      </c>
+      <c r="H14" s="339">
+        <v>45657</v>
       </c>
       <c r="I14" s="124">
-        <f>250000/9</f>
-        <v>27777.777777777777</v>
+        <v>46387</v>
       </c>
       <c r="J14" s="161"/>
     </row>
@@ -7947,38 +7965,40 @@
         <v>57</v>
       </c>
       <c r="B15" s="163" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C15" s="163" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="D15" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E15" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="340"/>
+        <v>124</v>
+      </c>
+      <c r="F15" s="341" t="s">
+        <v>166</v>
+      </c>
       <c r="G15" s="164">
-        <v>45355</v>
+        <v>46022</v>
       </c>
       <c r="H15" s="164">
-        <v>45355</v>
-      </c>
-      <c r="I15" s="124">
-        <v>100000</v>
-      </c>
-      <c r="J15" s="124"/>
+        <v>46022</v>
+      </c>
+      <c r="I15" s="161">
+        <v>150000</v>
+      </c>
+      <c r="J15" s="161"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="163" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C16" s="163" t="s">
-        <v>109</v>
+        <v>1141</v>
       </c>
       <c r="D16" s="163" t="s">
         <v>60</v>
@@ -7986,433 +8006,430 @@
       <c r="E16" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="341">
-        <v>2015</v>
-      </c>
+      <c r="F16" s="342"/>
       <c r="G16" s="164">
-        <v>42185</v>
+        <v>45291</v>
       </c>
       <c r="H16" s="164">
-        <v>42185</v>
+        <v>45291</v>
       </c>
       <c r="I16" s="161">
-        <v>20016</v>
+        <v>1076</v>
       </c>
       <c r="J16" s="124"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="163" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="B17" s="163" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="C17" s="163" t="s">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="D17" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="341"/>
+        <v>267</v>
+      </c>
+      <c r="F17" s="341" t="s">
+        <v>270</v>
+      </c>
       <c r="G17" s="164">
-        <v>44491</v>
+        <v>43440</v>
       </c>
       <c r="H17" s="164">
-        <v>44491</v>
+        <v>43440</v>
       </c>
       <c r="I17" s="161"/>
       <c r="J17" s="124"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="163" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="B18" s="163" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C18" s="163" t="s">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="D18" s="163" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E18" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="341"/>
+        <v>61</v>
+      </c>
+      <c r="F18" s="341" t="s">
+        <v>280</v>
+      </c>
       <c r="G18" s="164">
-        <v>46752</v>
+        <v>42855</v>
       </c>
       <c r="H18" s="164">
-        <v>46752</v>
-      </c>
-      <c r="I18" s="161"/>
-      <c r="J18" s="161"/>
+        <v>42855</v>
+      </c>
+      <c r="I18" s="161">
+        <v>400</v>
+      </c>
+      <c r="J18" s="124"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="163" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="B19" s="163" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C19" s="163" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="250" t="s">
-        <v>71</v>
+        <v>278</v>
+      </c>
+      <c r="D19" s="163" t="s">
+        <v>143</v>
       </c>
       <c r="E19" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="342"/>
-      <c r="G19" s="164">
-        <v>44876</v>
-      </c>
-      <c r="H19" s="164">
-        <v>44876</v>
-      </c>
-      <c r="I19" s="124">
-        <f>342521*0.33</f>
-        <v>113031.93000000001</v>
+        <v>124</v>
+      </c>
+      <c r="F19" s="341" t="s">
+        <v>286</v>
+      </c>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
+      <c r="I19" s="161">
+        <v>150000</v>
       </c>
       <c r="J19" s="161"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="163" t="s">
-        <v>57</v>
+        <v>308</v>
       </c>
       <c r="B20" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="163" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" s="105" t="s">
-        <v>71</v>
+        <v>309</v>
+      </c>
+      <c r="D20" s="163" t="s">
+        <v>214</v>
       </c>
       <c r="E20" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="342"/>
-      <c r="G20" s="164">
-        <v>45744</v>
-      </c>
-      <c r="H20" s="164">
-        <v>45744</v>
-      </c>
-      <c r="I20" s="124">
-        <f>I19+120*365</f>
-        <v>156831.93</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F20" s="341"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="163"/>
+      <c r="I20" s="161"/>
       <c r="J20" s="161"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="163" t="s">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="B21" s="163" t="s">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="C21" s="163" t="s">
-        <v>142</v>
+        <v>336</v>
       </c>
       <c r="D21" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E21" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="341"/>
-      <c r="G21" s="339">
-        <v>45657</v>
-      </c>
-      <c r="H21" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I21" s="124">
-        <v>46387</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F21" s="341" t="s">
+        <v>337</v>
+      </c>
+      <c r="G21" s="163"/>
+      <c r="H21" s="163"/>
+      <c r="I21" s="161"/>
       <c r="J21" s="161"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="163" t="s">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="B22" s="163" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="C22" s="163" t="s">
-        <v>162</v>
+        <v>349</v>
       </c>
       <c r="D22" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E22" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="341" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="164">
-        <v>46022</v>
-      </c>
-      <c r="H22" s="164">
-        <v>46022</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F22" s="341"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="163"/>
       <c r="I22" s="161">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J22" s="161"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="163" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="B23" s="163" t="s">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="C23" s="163" t="s">
-        <v>1142</v>
+        <v>358</v>
       </c>
       <c r="D23" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E23" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="342"/>
+        <v>148</v>
+      </c>
+      <c r="F23" s="341" t="s">
+        <v>362</v>
+      </c>
       <c r="G23" s="164">
-        <v>45291</v>
+        <v>46203</v>
       </c>
       <c r="H23" s="164">
-        <v>45291</v>
+        <v>46203</v>
       </c>
       <c r="I23" s="161">
-        <v>1076</v>
-      </c>
-      <c r="J23" s="124"/>
+        <v>150000</v>
+      </c>
+      <c r="J23" s="161"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="163" t="s">
-        <v>264</v>
+        <v>374</v>
       </c>
       <c r="B24" s="163" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="C24" s="163" t="s">
-        <v>266</v>
+        <v>375</v>
       </c>
       <c r="D24" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>267</v>
+        <v>61</v>
       </c>
       <c r="F24" s="341" t="s">
-        <v>270</v>
-      </c>
-      <c r="G24" s="164">
-        <v>43440</v>
-      </c>
-      <c r="H24" s="164">
-        <v>43440</v>
-      </c>
-      <c r="I24" s="161"/>
-      <c r="J24" s="124"/>
+        <v>377</v>
+      </c>
+      <c r="G24" s="163"/>
+      <c r="H24" s="163"/>
+      <c r="I24" s="161">
+        <v>100</v>
+      </c>
+      <c r="J24" s="161"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="163" t="s">
-        <v>264</v>
+        <v>385</v>
       </c>
       <c r="B25" s="163" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C25" s="163" t="s">
-        <v>278</v>
+        <v>386</v>
       </c>
       <c r="D25" s="163" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="E25" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="341" t="s">
-        <v>280</v>
+        <v>387</v>
       </c>
       <c r="G25" s="164">
-        <v>42855</v>
+        <v>46053</v>
       </c>
       <c r="H25" s="164">
-        <v>42855</v>
+        <v>46053</v>
       </c>
       <c r="I25" s="161">
-        <v>400</v>
-      </c>
-      <c r="J25" s="124"/>
+        <v>5591</v>
+      </c>
+      <c r="J25" s="161"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="163" t="s">
-        <v>264</v>
+        <v>399</v>
       </c>
       <c r="B26" s="163" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="C26" s="163" t="s">
-        <v>278</v>
+        <v>414</v>
       </c>
       <c r="D26" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E26" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="341" t="s">
-        <v>286</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F26" s="341"/>
       <c r="G26" s="163"/>
-      <c r="H26" s="163"/>
+      <c r="H26" s="164">
+        <v>45657</v>
+      </c>
       <c r="I26" s="161">
-        <v>150000</v>
+        <v>55297</v>
       </c>
       <c r="J26" s="161"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="183" t="s">
-        <v>297</v>
-      </c>
-      <c r="B27" s="183" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="183" t="s">
-        <v>298</v>
-      </c>
-      <c r="D27" s="183" t="s">
+      <c r="A27" s="163" t="s">
+        <v>434</v>
+      </c>
+      <c r="B27" s="163" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" s="163" t="s">
+        <v>436</v>
+      </c>
+      <c r="D27" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E27" s="183" t="s">
-        <v>192</v>
-      </c>
-      <c r="F27" s="341" t="s">
-        <v>299</v>
-      </c>
-      <c r="G27" s="163"/>
-      <c r="H27" s="163"/>
-      <c r="I27" s="161"/>
+      <c r="E27" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="342"/>
+      <c r="G27" s="126">
+        <v>43891</v>
+      </c>
+      <c r="H27" s="126">
+        <v>43891</v>
+      </c>
+      <c r="I27" s="124">
+        <f>28213+43839</f>
+        <v>72052</v>
+      </c>
       <c r="J27" s="161"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="163" t="s">
-        <v>308</v>
+        <v>443</v>
       </c>
       <c r="B28" s="163" t="s">
-        <v>58</v>
+        <v>444</v>
       </c>
       <c r="C28" s="163" t="s">
-        <v>309</v>
+        <v>445</v>
       </c>
       <c r="D28" s="163" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E28" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F28" s="341"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="163"/>
-      <c r="I28" s="161"/>
-      <c r="J28" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F28" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G28" s="126"/>
+      <c r="H28" s="126">
+        <v>45657</v>
+      </c>
+      <c r="I28" s="124">
+        <v>37239</v>
+      </c>
+      <c r="J28" s="343"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="163" t="s">
-        <v>334</v>
+        <v>462</v>
       </c>
       <c r="B29" s="163" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="C29" s="163" t="s">
-        <v>336</v>
+        <v>463</v>
       </c>
       <c r="D29" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E29" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="341" t="s">
-        <v>337</v>
-      </c>
-      <c r="G29" s="163"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F29" s="342">
+        <v>2015</v>
+      </c>
+      <c r="G29" s="126">
+        <v>42005</v>
+      </c>
+      <c r="H29" s="126">
+        <v>42005</v>
+      </c>
+      <c r="I29" s="343">
+        <v>18427</v>
+      </c>
       <c r="J29" s="161"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="163" t="s">
-        <v>334</v>
+        <v>462</v>
       </c>
       <c r="B30" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="163" t="s">
-        <v>349</v>
+        <v>463</v>
       </c>
       <c r="D30" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F30" s="341"/>
+        <v>61</v>
+      </c>
+      <c r="F30" s="341">
+        <v>2019</v>
+      </c>
       <c r="G30" s="163"/>
       <c r="H30" s="163"/>
-      <c r="I30" s="161">
-        <v>30000</v>
+      <c r="I30" s="343">
+        <v>2650</v>
       </c>
       <c r="J30" s="161"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="163" t="s">
-        <v>356</v>
+        <v>462</v>
       </c>
       <c r="B31" s="163" t="s">
-        <v>357</v>
+        <v>58</v>
       </c>
       <c r="C31" s="163" t="s">
-        <v>358</v>
+        <v>463</v>
       </c>
       <c r="D31" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E31" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F31" s="341" t="s">
-        <v>362</v>
-      </c>
-      <c r="G31" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H31" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I31" s="161">
-        <v>150000</v>
-      </c>
-      <c r="J31" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F31" s="341"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
+      <c r="I31" s="343">
+        <v>73662.5</v>
+      </c>
+      <c r="J31" s="124"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="163" t="s">
-        <v>374</v>
+        <v>462</v>
       </c>
       <c r="B32" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C32" s="163" t="s">
-        <v>375</v>
+        <v>477</v>
       </c>
       <c r="D32" s="163" t="s">
         <v>143</v>
@@ -8420,55 +8437,55 @@
       <c r="E32" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="G32" s="163"/>
-      <c r="H32" s="163"/>
+      <c r="F32" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G32" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H32" s="126">
+        <v>43831</v>
+      </c>
       <c r="I32" s="161">
-        <v>100</v>
-      </c>
-      <c r="J32" s="161"/>
+        <v>4760</v>
+      </c>
+      <c r="J32" s="124"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="163" t="s">
-        <v>385</v>
+        <v>462</v>
       </c>
       <c r="B33" s="163" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="C33" s="163" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="D33" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E33" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="G33" s="164">
-        <v>46053</v>
-      </c>
-      <c r="H33" s="164">
-        <v>46053</v>
-      </c>
-      <c r="I33" s="161">
-        <v>5591</v>
-      </c>
-      <c r="J33" s="161"/>
+      <c r="F33" s="342"/>
+      <c r="G33" s="126">
+        <v>45260</v>
+      </c>
+      <c r="H33" s="126">
+        <v>45261</v>
+      </c>
+      <c r="I33" s="124"/>
+      <c r="J33" s="124"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B34" s="163" t="s">
         <v>58</v>
       </c>
       <c r="C34" s="163" t="s">
-        <v>401</v>
+        <v>485</v>
       </c>
       <c r="D34" s="163" t="s">
         <v>143</v>
@@ -8476,29 +8493,21 @@
       <c r="E34" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="341" t="s">
-        <v>405</v>
-      </c>
-      <c r="G34" s="164">
-        <v>45447</v>
-      </c>
-      <c r="H34" s="164">
-        <v>45447</v>
-      </c>
-      <c r="I34" s="343">
-        <v>250000</v>
-      </c>
-      <c r="J34" s="161"/>
+      <c r="F34" s="342"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="124"/>
+      <c r="J34" s="343"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B35" s="163" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C35" s="163" t="s">
-        <v>414</v>
+        <v>490</v>
       </c>
       <c r="D35" s="163" t="s">
         <v>143</v>
@@ -8506,69 +8515,87 @@
       <c r="E35" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="341"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="163"/>
-      <c r="I35" s="161">
-        <v>44286</v>
-      </c>
-      <c r="J35" s="161"/>
+      <c r="F35" s="342">
+        <v>2018</v>
+      </c>
+      <c r="G35" s="126">
+        <v>43101</v>
+      </c>
+      <c r="H35" s="126">
+        <v>43102</v>
+      </c>
+      <c r="I35" s="124">
+        <v>83195</v>
+      </c>
+      <c r="J35" s="343"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="163" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B36" s="163" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C36" s="163" t="s">
-        <v>414</v>
+        <v>492</v>
       </c>
       <c r="D36" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F36" s="341"/>
-      <c r="G36" s="163"/>
-      <c r="H36" s="163"/>
-      <c r="I36" s="161">
-        <v>300000</v>
-      </c>
-      <c r="J36" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F36" s="341">
+        <v>2016</v>
+      </c>
+      <c r="G36" s="164">
+        <v>42370</v>
+      </c>
+      <c r="H36" s="126">
+        <v>42370</v>
+      </c>
+      <c r="I36" s="124">
+        <v>62577.5</v>
+      </c>
+      <c r="J36" s="343"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="163" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="B37" s="163" t="s">
-        <v>429</v>
+        <v>318</v>
       </c>
       <c r="C37" s="163" t="s">
-        <v>430</v>
+        <v>496</v>
       </c>
       <c r="D37" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E37" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F37" s="341"/>
-      <c r="G37" s="163"/>
-      <c r="H37" s="163"/>
-      <c r="I37" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F37" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G37" s="164">
+        <v>43617</v>
+      </c>
+      <c r="H37" s="105"/>
+      <c r="I37" s="124">
+        <v>10739</v>
+      </c>
       <c r="J37" s="161"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="163" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B38" s="163" t="s">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="C38" s="163" t="s">
-        <v>436</v>
+        <v>510</v>
       </c>
       <c r="D38" s="163" t="s">
         <v>143</v>
@@ -8576,244 +8603,235 @@
       <c r="E38" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="342"/>
-      <c r="G38" s="126">
-        <v>43891</v>
-      </c>
-      <c r="H38" s="126">
-        <v>43891</v>
-      </c>
+      <c r="F38" s="341" t="s">
+        <v>511</v>
+      </c>
+      <c r="G38" s="164">
+        <v>44530</v>
+      </c>
+      <c r="H38" s="163"/>
       <c r="I38" s="124">
-        <f>28213+43839</f>
-        <v>72052</v>
-      </c>
-      <c r="J38" s="161"/>
+        <v>50444</v>
+      </c>
+      <c r="J38" s="124"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="163" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B39" s="163" t="s">
-        <v>444</v>
+        <v>161</v>
       </c>
       <c r="C39" s="163" t="s">
-        <v>445</v>
+        <v>510</v>
       </c>
       <c r="D39" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E39" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G39" s="126"/>
-      <c r="H39" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I39" s="124">
-        <v>37239</v>
-      </c>
-      <c r="J39" s="343"/>
+        <v>124</v>
+      </c>
+      <c r="F39" s="341" t="s">
+        <v>518</v>
+      </c>
+      <c r="G39" s="164">
+        <v>46023</v>
+      </c>
+      <c r="H39" s="163"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="124"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="163" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="B40" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C40" s="163" t="s">
-        <v>463</v>
+        <v>522</v>
       </c>
       <c r="D40" s="163" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E40" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F40" s="342">
-        <v>2015</v>
-      </c>
-      <c r="G40" s="126">
-        <v>42005</v>
-      </c>
-      <c r="H40" s="126">
-        <v>42005</v>
-      </c>
-      <c r="I40" s="343">
-        <v>18427</v>
+      <c r="F40" s="341">
+        <v>2013</v>
+      </c>
+      <c r="G40" s="164">
+        <v>41275</v>
+      </c>
+      <c r="H40" s="163"/>
+      <c r="I40" s="161">
+        <v>40710</v>
       </c>
       <c r="J40" s="161"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="163" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="B41" s="163" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C41" s="163" t="s">
-        <v>463</v>
+        <v>522</v>
       </c>
       <c r="D41" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E41" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="341">
-        <v>2019</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F41" s="341"/>
       <c r="G41" s="163"/>
       <c r="H41" s="163"/>
-      <c r="I41" s="343">
-        <v>2650</v>
+      <c r="I41" s="161">
+        <v>100000</v>
       </c>
       <c r="J41" s="161"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B42" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="163" t="s">
-        <v>463</v>
-      </c>
-      <c r="D42" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="163" t="s">
+      <c r="A42" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B42" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C42" s="152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="341"/>
-      <c r="G42" s="163"/>
-      <c r="H42" s="163"/>
-      <c r="I42" s="343">
-        <v>73662.5</v>
+      <c r="F42" s="338"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I42" s="337">
+        <v>16874</v>
       </c>
       <c r="J42" s="124"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B43" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="163" t="s">
-        <v>477</v>
-      </c>
-      <c r="D43" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" s="163" t="s">
+      <c r="A43" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B43" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" s="152" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D43" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G43" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H43" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I43" s="161">
-        <v>4760</v>
+      <c r="F43" s="338"/>
+      <c r="G43" s="152"/>
+      <c r="H43" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I43" s="337">
+        <v>2117</v>
       </c>
       <c r="J43" s="124"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B44" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="163" t="s">
-        <v>477</v>
-      </c>
-      <c r="D44" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="163" t="s">
+      <c r="A44" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B44" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="152" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="342"/>
-      <c r="G44" s="126">
-        <v>45260</v>
-      </c>
-      <c r="H44" s="126">
-        <v>45261</v>
-      </c>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
+      <c r="F44" s="338"/>
+      <c r="G44" s="152"/>
+      <c r="H44" s="339">
+        <v>45291</v>
+      </c>
+      <c r="I44" s="337">
+        <v>18174</v>
+      </c>
+      <c r="J44" s="161"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B45" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="163" t="s">
-        <v>485</v>
-      </c>
-      <c r="D45" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" s="163" t="s">
+      <c r="A45" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B45" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C45" s="152" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D45" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="342"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="124"/>
-      <c r="J45" s="343"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="152"/>
+      <c r="H45" s="339">
+        <v>45657</v>
+      </c>
+      <c r="I45" s="337">
+        <v>615</v>
+      </c>
+      <c r="J45" s="161"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B46" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="163" t="s">
-        <v>490</v>
-      </c>
-      <c r="D46" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" s="163" t="s">
+      <c r="A46" s="152" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B46" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="152" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D46" s="152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="342">
-        <v>2018</v>
-      </c>
-      <c r="G46" s="126">
-        <v>43101</v>
-      </c>
-      <c r="H46" s="126">
-        <v>43102</v>
-      </c>
-      <c r="I46" s="124">
-        <v>83195</v>
-      </c>
-      <c r="J46" s="343"/>
+      <c r="F46" s="338"/>
+      <c r="G46" s="152"/>
+      <c r="H46" s="164">
+        <v>45657</v>
+      </c>
+      <c r="I46" s="337">
+        <v>71051</v>
+      </c>
+      <c r="J46" s="161"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="163" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="B47" s="163" t="s">
-        <v>58</v>
+        <v>542</v>
       </c>
       <c r="C47" s="163" t="s">
-        <v>492</v>
+        <v>543</v>
       </c>
       <c r="D47" s="163" t="s">
         <v>143</v>
@@ -8821,383 +8839,388 @@
       <c r="E47" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="341">
-        <v>2016</v>
-      </c>
-      <c r="G47" s="164">
-        <v>42370</v>
-      </c>
-      <c r="H47" s="126">
-        <v>42370</v>
-      </c>
-      <c r="I47" s="124">
-        <v>62577.5</v>
-      </c>
-      <c r="J47" s="343"/>
+      <c r="F47" s="341"/>
+      <c r="G47" s="163"/>
+      <c r="H47" s="163"/>
+      <c r="I47" s="161">
+        <v>26699</v>
+      </c>
+      <c r="J47" s="161"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="163" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="B48" s="163" t="s">
-        <v>318</v>
+        <v>542</v>
       </c>
       <c r="C48" s="163" t="s">
-        <v>496</v>
+        <v>543</v>
       </c>
       <c r="D48" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F48" s="341">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="G48" s="164">
-        <v>43617</v>
-      </c>
-      <c r="H48" s="105"/>
-      <c r="I48" s="124">
-        <v>10739</v>
-      </c>
+        <v>46203</v>
+      </c>
+      <c r="H48" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I48" s="161"/>
       <c r="J48" s="161"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="163" t="s">
-        <v>462</v>
+        <v>561</v>
       </c>
       <c r="B49" s="163" t="s">
-        <v>318</v>
+        <v>429</v>
       </c>
       <c r="C49" s="163" t="s">
-        <v>496</v>
+        <v>562</v>
       </c>
       <c r="D49" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E49" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F49" s="341"/>
+        <v>61</v>
+      </c>
+      <c r="F49" s="341">
+        <v>2023</v>
+      </c>
       <c r="G49" s="164">
-        <v>46539</v>
-      </c>
-      <c r="H49" s="163"/>
+        <v>45583</v>
+      </c>
+      <c r="H49" s="164">
+        <v>45583</v>
+      </c>
       <c r="I49" s="161"/>
-      <c r="J49" s="124"/>
+      <c r="J49" s="161"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="163" t="s">
-        <v>462</v>
+        <v>561</v>
       </c>
       <c r="B50" s="163" t="s">
-        <v>265</v>
+        <v>429</v>
       </c>
       <c r="C50" s="163" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D50" s="163"/>
+        <v>562</v>
+      </c>
+      <c r="D50" s="163" t="s">
+        <v>71</v>
+      </c>
       <c r="E50" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F50" s="341"/>
-      <c r="G50" s="164"/>
+      <c r="G50" s="163"/>
       <c r="H50" s="163"/>
       <c r="I50" s="161"/>
-      <c r="J50" s="124"/>
+      <c r="J50" s="161"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="163" t="s">
-        <v>462</v>
+        <v>578</v>
       </c>
       <c r="B51" s="163" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="C51" s="163" t="s">
-        <v>505</v>
+        <v>579</v>
       </c>
       <c r="D51" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E51" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F51" s="342"/>
-      <c r="G51" s="105"/>
-      <c r="H51" s="105"/>
-      <c r="I51" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F51" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G51" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H51" s="126">
+        <v>43831</v>
+      </c>
+      <c r="I51" s="124">
+        <v>20135</v>
+      </c>
       <c r="J51" s="124"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="163" t="s">
-        <v>462</v>
+        <v>578</v>
       </c>
       <c r="B52" s="163" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="C52" s="163" t="s">
-        <v>510</v>
+        <v>579</v>
       </c>
       <c r="D52" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="163" t="s">
+        <v>124</v>
+      </c>
+      <c r="F52" s="341" t="s">
+        <v>584</v>
+      </c>
+      <c r="G52" s="164">
+        <v>46203</v>
+      </c>
+      <c r="H52" s="164">
+        <v>46203</v>
+      </c>
+      <c r="I52" s="161"/>
+      <c r="J52" s="161"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" s="105" t="s">
+        <v>590</v>
+      </c>
+      <c r="B53" s="163" t="s">
+        <v>435</v>
+      </c>
+      <c r="C53" s="163" t="s">
+        <v>591</v>
+      </c>
+      <c r="D53" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E52" s="163" t="s">
+      <c r="E53" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F52" s="341" t="s">
-        <v>511</v>
-      </c>
-      <c r="G52" s="164">
-        <v>44530</v>
-      </c>
-      <c r="H52" s="163"/>
-      <c r="I52" s="124">
-        <v>50444</v>
-      </c>
-      <c r="J52" s="124"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" s="163" t="s">
-        <v>462</v>
-      </c>
-      <c r="B53" s="163" t="s">
-        <v>161</v>
-      </c>
-      <c r="C53" s="163" t="s">
-        <v>510</v>
-      </c>
-      <c r="D53" s="163" t="s">
+      <c r="F53" s="342"/>
+      <c r="G53" s="126">
+        <v>44075</v>
+      </c>
+      <c r="H53" s="105"/>
+      <c r="I53" s="124">
+        <f>67243+12264</f>
+        <v>79507</v>
+      </c>
+      <c r="J53" s="124"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="105" t="s">
+        <v>590</v>
+      </c>
+      <c r="B54" s="163" t="s">
+        <v>435</v>
+      </c>
+      <c r="C54" s="163" t="s">
+        <v>591</v>
+      </c>
+      <c r="D54" s="163" t="s">
         <v>71</v>
-      </c>
-      <c r="E53" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" s="341" t="s">
-        <v>518</v>
-      </c>
-      <c r="G53" s="164">
-        <v>46023</v>
-      </c>
-      <c r="H53" s="163"/>
-      <c r="I53" s="161"/>
-      <c r="J53" s="124"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="163" t="s">
-        <v>521</v>
-      </c>
-      <c r="B54" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="163" t="s">
-        <v>522</v>
-      </c>
-      <c r="D54" s="163" t="s">
-        <v>60</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="341">
-        <v>2013</v>
-      </c>
-      <c r="G54" s="164">
-        <v>41275</v>
-      </c>
-      <c r="H54" s="163"/>
-      <c r="I54" s="161">
-        <v>40710</v>
-      </c>
-      <c r="J54" s="161"/>
+      <c r="F54" s="342"/>
+      <c r="G54" s="242">
+        <v>45679</v>
+      </c>
+      <c r="H54" s="105"/>
+      <c r="I54" s="124"/>
+      <c r="J54" s="124"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="163" t="s">
-        <v>521</v>
+        <v>602</v>
       </c>
       <c r="B55" s="163" t="s">
-        <v>141</v>
+        <v>603</v>
       </c>
       <c r="C55" s="163" t="s">
-        <v>522</v>
+        <v>604</v>
       </c>
       <c r="D55" s="163" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="E55" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F55" s="341"/>
+        <v>192</v>
+      </c>
+      <c r="F55" s="341" t="s">
+        <v>605</v>
+      </c>
       <c r="G55" s="163"/>
       <c r="H55" s="163"/>
-      <c r="I55" s="161">
-        <v>100000</v>
-      </c>
+      <c r="I55" s="161"/>
       <c r="J55" s="161"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B56" s="152" t="s">
+      <c r="A56" s="163" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B56" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="C56" s="152" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D56" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" s="152" t="s">
+      <c r="C56" s="163" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D56" s="163"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="341"/>
+      <c r="G56" s="126">
+        <v>45291</v>
+      </c>
+      <c r="H56" s="126">
+        <v>45291</v>
+      </c>
+      <c r="I56" s="161">
+        <v>33335</v>
+      </c>
+      <c r="J56" s="124"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" s="163" t="s">
+        <v>613</v>
+      </c>
+      <c r="B57" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="163" t="s">
+        <v>614</v>
+      </c>
+      <c r="D57" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="338"/>
-      <c r="G56" s="152"/>
-      <c r="H56" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I56" s="337">
-        <v>16874</v>
-      </c>
-      <c r="J56" s="124"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B57" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C57" s="152" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D57" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="152" t="s">
+      <c r="F57" s="342">
+        <v>2020</v>
+      </c>
+      <c r="G57" s="126">
+        <v>43831</v>
+      </c>
+      <c r="H57" s="105"/>
+      <c r="I57" s="124">
+        <v>9653</v>
+      </c>
+      <c r="J57" s="124"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="163" t="s">
+        <v>613</v>
+      </c>
+      <c r="B58" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="163" t="s">
+        <v>614</v>
+      </c>
+      <c r="D58" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="338"/>
-      <c r="G57" s="152"/>
-      <c r="H57" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I57" s="337">
-        <v>2117</v>
-      </c>
-      <c r="J57" s="124"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B58" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C58" s="152" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D58" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" s="152" t="s">
+      <c r="F58" s="342" t="s">
+        <v>618</v>
+      </c>
+      <c r="G58" s="126">
+        <v>45536</v>
+      </c>
+      <c r="H58" s="126">
+        <v>45536</v>
+      </c>
+      <c r="I58" s="124"/>
+      <c r="J58" s="161"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="163" t="s">
+        <v>613</v>
+      </c>
+      <c r="B59" s="163" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="163" t="s">
+        <v>621</v>
+      </c>
+      <c r="D59" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F58" s="338"/>
-      <c r="G58" s="152"/>
-      <c r="H58" s="339">
-        <v>45291</v>
-      </c>
-      <c r="I58" s="337">
-        <v>18174</v>
-      </c>
-      <c r="J58" s="161"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B59" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C59" s="152" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D59" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="338"/>
-      <c r="G59" s="152"/>
-      <c r="H59" s="339">
-        <v>45657</v>
-      </c>
-      <c r="I59" s="337">
-        <v>615</v>
+      <c r="F59" s="341"/>
+      <c r="G59" s="163"/>
+      <c r="H59" s="163"/>
+      <c r="I59" s="161">
+        <v>15000</v>
       </c>
       <c r="J59" s="161"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="152" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B60" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="C60" s="152" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D60" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E60" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="F60" s="338"/>
-      <c r="G60" s="152"/>
-      <c r="H60" s="164">
-        <v>45657</v>
-      </c>
-      <c r="I60" s="337">
-        <v>71051</v>
-      </c>
-      <c r="J60" s="161"/>
+      <c r="A60" s="163" t="s">
+        <v>613</v>
+      </c>
+      <c r="B60" s="163" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="163" t="s">
+        <v>621</v>
+      </c>
+      <c r="D60" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="163" t="s">
+        <v>626</v>
+      </c>
+      <c r="F60" s="341"/>
+      <c r="G60" s="163"/>
+      <c r="H60" s="163"/>
+      <c r="I60" s="161"/>
+      <c r="J60" s="124"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="163" t="s">
-        <v>541</v>
+        <v>613</v>
       </c>
       <c r="B61" s="163" t="s">
-        <v>542</v>
-      </c>
-      <c r="C61" s="163" t="s">
-        <v>543</v>
+        <v>444</v>
+      </c>
+      <c r="C61" s="328" t="s">
+        <v>628</v>
       </c>
       <c r="D61" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E61" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F61" s="341"/>
-      <c r="G61" s="163"/>
-      <c r="H61" s="163"/>
-      <c r="I61" s="161">
-        <v>26699</v>
-      </c>
-      <c r="J61" s="161"/>
+        <v>192</v>
+      </c>
+      <c r="F61" s="342"/>
+      <c r="G61" s="126">
+        <v>43559</v>
+      </c>
+      <c r="H61" s="126">
+        <v>43559</v>
+      </c>
+      <c r="I61" s="124">
+        <v>49264</v>
+      </c>
+      <c r="J61" s="124"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="163" t="s">
-        <v>541</v>
+        <v>613</v>
       </c>
       <c r="B62" s="163" t="s">
-        <v>542</v>
-      </c>
-      <c r="C62" s="163" t="s">
-        <v>543</v>
+        <v>444</v>
+      </c>
+      <c r="C62" s="328" t="s">
+        <v>628</v>
       </c>
       <c r="D62" s="163" t="s">
         <v>71</v>
@@ -9205,27 +9228,27 @@
       <c r="E62" s="163" t="s">
         <v>148</v>
       </c>
-      <c r="F62" s="341">
-        <v>2026</v>
-      </c>
-      <c r="G62" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H62" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I62" s="161"/>
-      <c r="J62" s="161"/>
+      <c r="F62" s="342">
+        <v>2023</v>
+      </c>
+      <c r="G62" s="126">
+        <v>45107</v>
+      </c>
+      <c r="H62" s="126">
+        <v>45108</v>
+      </c>
+      <c r="I62" s="124"/>
+      <c r="J62" s="124"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="163" t="s">
-        <v>561</v>
+        <v>613</v>
       </c>
       <c r="B63" s="163" t="s">
-        <v>429</v>
-      </c>
-      <c r="C63" s="163" t="s">
-        <v>562</v>
+        <v>318</v>
+      </c>
+      <c r="C63" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D63" s="163" t="s">
         <v>143</v>
@@ -9233,107 +9256,107 @@
       <c r="E63" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="341">
-        <v>2023</v>
-      </c>
-      <c r="G63" s="164">
-        <v>45583</v>
-      </c>
-      <c r="H63" s="164">
-        <v>45583</v>
-      </c>
-      <c r="I63" s="161"/>
-      <c r="J63" s="161"/>
+      <c r="F63" s="342">
+        <v>2012</v>
+      </c>
+      <c r="G63" s="126">
+        <v>41061</v>
+      </c>
+      <c r="H63" s="126">
+        <v>41061</v>
+      </c>
+      <c r="I63" s="124">
+        <v>3734</v>
+      </c>
+      <c r="J63" s="124"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="163" t="s">
-        <v>561</v>
+        <v>613</v>
       </c>
       <c r="B64" s="163" t="s">
-        <v>429</v>
-      </c>
-      <c r="C64" s="163" t="s">
-        <v>562</v>
+        <v>318</v>
+      </c>
+      <c r="C64" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D64" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E64" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F64" s="341"/>
-      <c r="G64" s="163"/>
-      <c r="H64" s="163"/>
-      <c r="I64" s="161"/>
-      <c r="J64" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F64" s="342" t="s">
+        <v>511</v>
+      </c>
+      <c r="G64" s="126">
+        <v>44501</v>
+      </c>
+      <c r="H64" s="126">
+        <v>44502</v>
+      </c>
+      <c r="I64" s="124"/>
+      <c r="J64" s="124"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="163" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="B65" s="163" t="s">
         <v>318</v>
       </c>
-      <c r="C65" s="163" t="s">
-        <v>579</v>
+      <c r="C65" s="105" t="s">
+        <v>638</v>
       </c>
       <c r="D65" s="163" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E65" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F65" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G65" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H65" s="126">
-        <v>43831</v>
-      </c>
-      <c r="I65" s="124">
-        <v>20135</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F65" s="342"/>
+      <c r="G65" s="105"/>
+      <c r="H65" s="105"/>
+      <c r="I65" s="124"/>
       <c r="J65" s="124"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="163" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="B66" s="163" t="s">
         <v>318</v>
       </c>
       <c r="C66" s="163" t="s">
-        <v>579</v>
+        <v>649</v>
       </c>
       <c r="D66" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E66" s="163" t="s">
         <v>124</v>
       </c>
-      <c r="F66" s="341" t="s">
-        <v>584</v>
-      </c>
-      <c r="G66" s="164">
-        <v>46203</v>
-      </c>
-      <c r="H66" s="164">
-        <v>46203</v>
-      </c>
-      <c r="I66" s="161"/>
-      <c r="J66" s="161"/>
+      <c r="F66" s="344">
+        <v>46508</v>
+      </c>
+      <c r="G66" s="126">
+        <v>46508</v>
+      </c>
+      <c r="H66" s="126">
+        <v>46508</v>
+      </c>
+      <c r="I66" s="124"/>
+      <c r="J66" s="124"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="105" t="s">
-        <v>590</v>
+      <c r="A67" s="163" t="s">
+        <v>652</v>
       </c>
       <c r="B67" s="163" t="s">
-        <v>435</v>
+        <v>265</v>
       </c>
       <c r="C67" s="163" t="s">
-        <v>591</v>
+        <v>653</v>
       </c>
       <c r="D67" s="163" t="s">
         <v>143</v>
@@ -9343,96 +9366,105 @@
       </c>
       <c r="F67" s="342"/>
       <c r="G67" s="126">
-        <v>44075</v>
-      </c>
-      <c r="H67" s="105"/>
+        <v>45291</v>
+      </c>
+      <c r="H67" s="126">
+        <v>45291</v>
+      </c>
       <c r="I67" s="124">
-        <f>67243+12264</f>
-        <v>79507</v>
+        <v>42533</v>
       </c>
       <c r="J67" s="124"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A68" s="105" t="s">
-        <v>590</v>
+      <c r="A68" s="163" t="s">
+        <v>652</v>
       </c>
       <c r="B68" s="163" t="s">
-        <v>435</v>
-      </c>
-      <c r="C68" s="163" t="s">
-        <v>591</v>
+        <v>265</v>
+      </c>
+      <c r="C68" s="138" t="s">
+        <v>657</v>
       </c>
       <c r="D68" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E68" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F68" s="342"/>
-      <c r="G68" s="242">
-        <v>45679</v>
-      </c>
-      <c r="H68" s="105"/>
-      <c r="I68" s="124"/>
+      <c r="G68" s="126">
+        <v>45291</v>
+      </c>
+      <c r="H68" s="126">
+        <v>45291</v>
+      </c>
+      <c r="I68" s="124">
+        <v>15433</v>
+      </c>
       <c r="J68" s="124"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="163" t="s">
-        <v>602</v>
+        <v>652</v>
       </c>
       <c r="B69" s="163" t="s">
-        <v>603</v>
-      </c>
-      <c r="C69" s="163" t="s">
-        <v>604</v>
+        <v>265</v>
+      </c>
+      <c r="C69" s="138" t="s">
+        <v>663</v>
       </c>
       <c r="D69" s="163" t="s">
         <v>214</v>
       </c>
       <c r="E69" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F69" s="341" t="s">
-        <v>605</v>
-      </c>
-      <c r="G69" s="163"/>
-      <c r="H69" s="163"/>
-      <c r="I69" s="161"/>
-      <c r="J69" s="161"/>
+        <v>61</v>
+      </c>
+      <c r="F69" s="342"/>
+      <c r="G69" s="126">
+        <v>45657</v>
+      </c>
+      <c r="H69" s="126">
+        <v>45657</v>
+      </c>
+      <c r="I69" s="124">
+        <v>24008</v>
+      </c>
+      <c r="J69" s="124"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="163" t="s">
-        <v>1084</v>
+        <v>667</v>
       </c>
       <c r="B70" s="163" t="s">
         <v>265</v>
       </c>
       <c r="C70" s="163" t="s">
-        <v>1083</v>
+        <v>668</v>
       </c>
       <c r="D70" s="163"/>
       <c r="E70" s="163"/>
-      <c r="F70" s="341"/>
+      <c r="F70" s="342"/>
       <c r="G70" s="126">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H70" s="126">
-        <v>45291</v>
-      </c>
-      <c r="I70" s="161">
-        <v>33335</v>
+        <v>45657</v>
+      </c>
+      <c r="I70" s="124">
+        <v>23534</v>
       </c>
       <c r="J70" s="124"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="163" t="s">
-        <v>613</v>
+        <v>667</v>
       </c>
       <c r="B71" s="163" t="s">
-        <v>58</v>
+        <v>265</v>
       </c>
       <c r="C71" s="163" t="s">
-        <v>614</v>
+        <v>668</v>
       </c>
       <c r="D71" s="163" t="s">
         <v>143</v>
@@ -9440,321 +9472,315 @@
       <c r="E71" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F71" s="342">
-        <v>2020</v>
-      </c>
-      <c r="G71" s="126">
-        <v>43831</v>
-      </c>
-      <c r="H71" s="105"/>
-      <c r="I71" s="124">
-        <v>9653</v>
+      <c r="F71" s="341"/>
+      <c r="I71" s="161">
+        <v>5000</v>
       </c>
       <c r="J71" s="124"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="163" t="s">
-        <v>613</v>
+        <v>667</v>
       </c>
       <c r="B72" s="163" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="C72" s="163" t="s">
-        <v>614</v>
+        <v>680</v>
       </c>
       <c r="D72" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E72" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="E72" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="342" t="s">
-        <v>618</v>
-      </c>
-      <c r="G72" s="126">
-        <v>45536</v>
-      </c>
-      <c r="H72" s="126">
-        <v>45536</v>
-      </c>
-      <c r="I72" s="124"/>
+      <c r="F72" s="341" t="s">
+        <v>682</v>
+      </c>
+      <c r="G72" s="163"/>
+      <c r="H72" s="163"/>
+      <c r="I72" s="161">
+        <v>111872</v>
+      </c>
       <c r="J72" s="161"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="163" t="s">
-        <v>613</v>
+        <v>667</v>
       </c>
       <c r="B73" s="163" t="s">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="C73" s="163" t="s">
-        <v>621</v>
+        <v>691</v>
       </c>
       <c r="D73" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E73" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F73" s="341"/>
+      <c r="F73" s="341" t="s">
+        <v>694</v>
+      </c>
       <c r="G73" s="163"/>
       <c r="H73" s="163"/>
-      <c r="I73" s="161">
-        <v>15000</v>
-      </c>
+      <c r="I73" s="161"/>
       <c r="J73" s="161"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" s="163" t="s">
-        <v>613</v>
-      </c>
-      <c r="B74" s="163" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="163" t="s">
-        <v>621</v>
-      </c>
-      <c r="D74" s="163" t="s">
+      <c r="A74" s="183" t="s">
+        <v>703</v>
+      </c>
+      <c r="B74" s="183" t="s">
+        <v>704</v>
+      </c>
+      <c r="C74" s="183" t="s">
+        <v>705</v>
+      </c>
+      <c r="D74" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F74" s="341"/>
-      <c r="G74" s="163"/>
-      <c r="H74" s="163"/>
-      <c r="I74" s="161"/>
+      <c r="E74" s="183" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" s="342" t="s">
+        <v>708</v>
+      </c>
+      <c r="G74" s="126">
+        <v>46023</v>
+      </c>
+      <c r="H74" s="126">
+        <v>46023</v>
+      </c>
+      <c r="I74" s="124">
+        <v>50000</v>
+      </c>
       <c r="J74" s="124"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="163" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B75" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C75" s="328" t="s">
-        <v>628</v>
+        <v>141</v>
+      </c>
+      <c r="C75" s="163" t="s">
+        <v>1029</v>
       </c>
       <c r="D75" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E75" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F75" s="342"/>
-      <c r="G75" s="126">
-        <v>43559</v>
-      </c>
-      <c r="H75" s="126">
-        <v>43559</v>
-      </c>
-      <c r="I75" s="124">
-        <v>49264</v>
+        <v>61</v>
+      </c>
+      <c r="F75" s="341">
+        <v>2018</v>
+      </c>
+      <c r="G75" s="164">
+        <v>43101</v>
+      </c>
+      <c r="H75" s="164">
+        <v>43101</v>
+      </c>
+      <c r="I75" s="161">
+        <v>14287</v>
       </c>
       <c r="J75" s="124"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="163" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B76" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C76" s="328" t="s">
-        <v>628</v>
+        <v>141</v>
+      </c>
+      <c r="C76" s="163" t="s">
+        <v>1029</v>
       </c>
       <c r="D76" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E76" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F76" s="342">
-        <v>2023</v>
-      </c>
-      <c r="G76" s="126">
-        <v>45107</v>
-      </c>
-      <c r="H76" s="126">
-        <v>45108</v>
-      </c>
-      <c r="I76" s="124"/>
-      <c r="J76" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F76" s="341"/>
+      <c r="G76" s="164"/>
+      <c r="H76" s="164"/>
+      <c r="I76" s="161">
+        <v>10881</v>
+      </c>
+      <c r="J76" s="161"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="163" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B77" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C77" s="105" t="s">
-        <v>638</v>
+        <v>141</v>
+      </c>
+      <c r="C77" s="163" t="s">
+        <v>1029</v>
       </c>
       <c r="D77" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E77" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F77" s="342">
-        <v>2012</v>
-      </c>
-      <c r="G77" s="126">
-        <v>41061</v>
-      </c>
-      <c r="H77" s="126">
-        <v>41061</v>
-      </c>
-      <c r="I77" s="124">
-        <v>3734</v>
-      </c>
-      <c r="J77" s="124"/>
+        <v>71</v>
+      </c>
+      <c r="E77" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" s="341"/>
+      <c r="G77" s="163"/>
+      <c r="H77" s="163"/>
+      <c r="I77" s="161"/>
+      <c r="J77" s="161"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="163" t="s">
-        <v>613</v>
+        <v>718</v>
       </c>
       <c r="B78" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C78" s="105" t="s">
-        <v>638</v>
+        <v>58</v>
+      </c>
+      <c r="C78" s="163" t="s">
+        <v>375</v>
       </c>
       <c r="D78" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E78" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="342" t="s">
-        <v>511</v>
-      </c>
-      <c r="G78" s="126">
-        <v>44501</v>
-      </c>
-      <c r="H78" s="126">
-        <v>44502</v>
-      </c>
-      <c r="I78" s="124"/>
+      <c r="F78" s="341" t="s">
+        <v>721</v>
+      </c>
+      <c r="G78" s="164">
+        <v>44642</v>
+      </c>
+      <c r="H78" s="164">
+        <v>44642</v>
+      </c>
+      <c r="I78" s="124">
+        <v>206097</v>
+      </c>
       <c r="J78" s="124"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="163" t="s">
-        <v>613</v>
+        <v>718</v>
       </c>
       <c r="B79" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C79" s="105" t="s">
-        <v>638</v>
+        <v>335</v>
+      </c>
+      <c r="C79" s="163" t="s">
+        <v>729</v>
       </c>
       <c r="D79" s="163" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E79" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F79" s="342"/>
-      <c r="G79" s="105"/>
-      <c r="H79" s="105"/>
-      <c r="I79" s="124"/>
-      <c r="J79" s="124"/>
+        <v>192</v>
+      </c>
+      <c r="F79" s="341">
+        <v>2015</v>
+      </c>
+      <c r="G79" s="164">
+        <v>42156</v>
+      </c>
+      <c r="H79" s="164">
+        <v>42157</v>
+      </c>
+      <c r="I79" s="161"/>
+      <c r="J79" s="161"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="163" t="s">
-        <v>613</v>
+        <v>737</v>
       </c>
       <c r="B80" s="163" t="s">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="C80" s="163" t="s">
-        <v>649</v>
+        <v>738</v>
       </c>
       <c r="D80" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E80" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="F80" s="344">
-        <v>46508</v>
-      </c>
-      <c r="G80" s="126">
-        <v>46508</v>
-      </c>
-      <c r="H80" s="126">
-        <v>46508</v>
-      </c>
-      <c r="I80" s="124"/>
-      <c r="J80" s="124"/>
+        <v>148</v>
+      </c>
+      <c r="F80" s="341" t="s">
+        <v>739</v>
+      </c>
+      <c r="G80" s="163"/>
+      <c r="H80" s="163"/>
+      <c r="I80" s="161">
+        <v>30000</v>
+      </c>
+      <c r="J80" s="161"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="163" t="s">
-        <v>652</v>
-      </c>
-      <c r="B81" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C81" s="163" t="s">
-        <v>653</v>
-      </c>
-      <c r="D81" s="163" t="s">
+      <c r="A81" s="183" t="s">
+        <v>575</v>
+      </c>
+      <c r="B81" s="183" t="s">
+        <v>444</v>
+      </c>
+      <c r="C81" s="183" t="s">
+        <v>745</v>
+      </c>
+      <c r="D81" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="E81" s="163" t="s">
+      <c r="E81" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="F81" s="342"/>
+      <c r="F81" s="342">
+        <v>2013</v>
+      </c>
       <c r="G81" s="126">
-        <v>45291</v>
+        <v>41426</v>
       </c>
       <c r="H81" s="126">
-        <v>45291</v>
+        <v>41426</v>
       </c>
       <c r="I81" s="124">
-        <v>42533</v>
-      </c>
-      <c r="J81" s="124"/>
+        <v>94839</v>
+      </c>
+      <c r="J81" s="161"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="163" t="s">
-        <v>652</v>
+        <v>575</v>
       </c>
       <c r="B82" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C82" s="138" t="s">
-        <v>657</v>
+        <v>58</v>
+      </c>
+      <c r="C82" s="163" t="s">
+        <v>754</v>
       </c>
       <c r="D82" s="163" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E82" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F82" s="342"/>
-      <c r="G82" s="126">
-        <v>45291</v>
-      </c>
-      <c r="H82" s="126">
-        <v>45291</v>
-      </c>
-      <c r="I82" s="124">
-        <v>15433</v>
-      </c>
-      <c r="J82" s="124"/>
+        <v>61</v>
+      </c>
+      <c r="F82" s="341"/>
+      <c r="G82" s="163"/>
+      <c r="H82" s="163"/>
+      <c r="I82" s="161">
+        <v>140000</v>
+      </c>
+      <c r="J82" s="161"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="163" t="s">
-        <v>652</v>
+        <v>575</v>
       </c>
       <c r="B83" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C83" s="138" t="s">
-        <v>663</v>
+        <v>58</v>
+      </c>
+      <c r="C83" s="163" t="s">
+        <v>764</v>
       </c>
       <c r="D83" s="163" t="s">
         <v>214</v>
@@ -9762,153 +9788,160 @@
       <c r="E83" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F83" s="342"/>
-      <c r="G83" s="126">
-        <v>45657</v>
-      </c>
-      <c r="H83" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I83" s="124">
-        <v>24008</v>
-      </c>
-      <c r="J83" s="124"/>
+      <c r="F83" s="341"/>
+      <c r="G83" s="163"/>
+      <c r="H83" s="163"/>
+      <c r="I83" s="161">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="161"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="163" t="s">
-        <v>667</v>
+        <v>575</v>
       </c>
       <c r="B84" s="163" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="C84" s="163" t="s">
-        <v>668</v>
-      </c>
-      <c r="D84" s="163"/>
-      <c r="E84" s="163"/>
-      <c r="F84" s="342"/>
-      <c r="G84" s="126">
-        <v>45657</v>
-      </c>
-      <c r="H84" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I84" s="124">
-        <v>23534</v>
-      </c>
-      <c r="J84" s="124"/>
+        <v>770</v>
+      </c>
+      <c r="D84" s="163" t="s">
+        <v>143</v>
+      </c>
+      <c r="E84" s="163" t="s">
+        <v>192</v>
+      </c>
+      <c r="F84" s="341" t="s">
+        <v>772</v>
+      </c>
+      <c r="G84" s="163"/>
+      <c r="H84" s="163"/>
+      <c r="I84" s="161"/>
+      <c r="J84" s="161"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="163" t="s">
-        <v>667</v>
+        <v>575</v>
       </c>
       <c r="B85" s="163" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="C85" s="163" t="s">
-        <v>668</v>
+        <v>781</v>
       </c>
       <c r="D85" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E85" s="163" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="206" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="341"/>
+      <c r="F85" s="341" t="s">
+        <v>782</v>
+      </c>
+      <c r="G85" s="164">
+        <v>43773</v>
+      </c>
+      <c r="H85" s="164">
+        <v>43773</v>
+      </c>
       <c r="I85" s="161">
-        <v>5000</v>
-      </c>
-      <c r="J85" s="124"/>
+        <v>333000</v>
+      </c>
+      <c r="J85" s="161"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="163" t="s">
-        <v>667</v>
+        <v>575</v>
       </c>
       <c r="B86" s="163" t="s">
-        <v>182</v>
+        <v>318</v>
       </c>
       <c r="C86" s="163" t="s">
-        <v>680</v>
+        <v>792</v>
       </c>
       <c r="D86" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E86" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F86" s="341" t="s">
-        <v>682</v>
-      </c>
-      <c r="G86" s="163"/>
+        <v>148</v>
+      </c>
+      <c r="F86" s="341">
+        <v>2025</v>
+      </c>
+      <c r="G86" s="164">
+        <v>45809</v>
+      </c>
       <c r="H86" s="163"/>
       <c r="I86" s="161">
-        <v>111872</v>
+        <f>3000000/5</f>
+        <v>600000</v>
       </c>
       <c r="J86" s="161"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="163" t="s">
-        <v>667</v>
+        <v>824</v>
       </c>
       <c r="B87" s="163" t="s">
-        <v>357</v>
+        <v>825</v>
       </c>
       <c r="C87" s="163" t="s">
-        <v>691</v>
-      </c>
-      <c r="D87" s="163" t="s">
-        <v>143</v>
+        <v>826</v>
+      </c>
+      <c r="D87" s="105" t="s">
+        <v>60</v>
       </c>
       <c r="E87" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F87" s="341" t="s">
-        <v>694</v>
-      </c>
-      <c r="G87" s="163"/>
-      <c r="H87" s="163"/>
-      <c r="I87" s="161"/>
-      <c r="J87" s="161"/>
+      <c r="F87" s="342"/>
+      <c r="G87" s="105"/>
+      <c r="H87" s="126">
+        <v>45657</v>
+      </c>
+      <c r="I87" s="124">
+        <v>85654</v>
+      </c>
+      <c r="J87" s="124"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="183" t="s">
-        <v>703</v>
-      </c>
-      <c r="B88" s="183" t="s">
-        <v>704</v>
-      </c>
-      <c r="C88" s="183" t="s">
-        <v>705</v>
-      </c>
-      <c r="D88" s="183" t="s">
+      <c r="A88" s="163" t="s">
+        <v>810</v>
+      </c>
+      <c r="B88" s="163" t="s">
+        <v>265</v>
+      </c>
+      <c r="C88" s="163" t="s">
+        <v>811</v>
+      </c>
+      <c r="D88" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="E88" s="183" t="s">
+      <c r="E88" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F88" s="342" t="s">
-        <v>708</v>
-      </c>
-      <c r="G88" s="126">
-        <v>46023</v>
-      </c>
-      <c r="H88" s="126">
-        <v>46023</v>
-      </c>
-      <c r="I88" s="124">
-        <v>50000</v>
-      </c>
-      <c r="J88" s="124"/>
+      <c r="F88" s="341">
+        <v>2019</v>
+      </c>
+      <c r="G88" s="164">
+        <v>43646</v>
+      </c>
+      <c r="H88" s="164">
+        <v>43646</v>
+      </c>
+      <c r="I88" s="161"/>
+      <c r="J88" s="161"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="163" t="s">
-        <v>1028</v>
+        <v>810</v>
       </c>
       <c r="B89" s="163" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="C89" s="163" t="s">
-        <v>1029</v>
+        <v>817</v>
       </c>
       <c r="D89" s="163" t="s">
         <v>143</v>
@@ -9916,59 +9949,57 @@
       <c r="E89" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="F89" s="341">
-        <v>2018</v>
-      </c>
+      <c r="F89" s="341"/>
       <c r="G89" s="164">
-        <v>43101</v>
+        <v>45183</v>
       </c>
       <c r="H89" s="164">
-        <v>43101</v>
-      </c>
-      <c r="I89" s="161">
-        <v>14287</v>
-      </c>
-      <c r="J89" s="124"/>
+        <v>45183</v>
+      </c>
+      <c r="I89" s="161"/>
+      <c r="J89" s="161"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="163" t="s">
-        <v>1028</v>
+        <v>810</v>
       </c>
       <c r="B90" s="163" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="C90" s="163" t="s">
-        <v>1029</v>
+        <v>817</v>
       </c>
       <c r="D90" s="163" t="s">
         <v>71</v>
       </c>
       <c r="E90" s="163" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F90" s="341"/>
-      <c r="G90" s="164"/>
-      <c r="H90" s="164"/>
-      <c r="I90" s="161">
-        <v>10881</v>
-      </c>
+      <c r="G90" s="164">
+        <v>45777</v>
+      </c>
+      <c r="H90" s="164">
+        <v>45777</v>
+      </c>
+      <c r="I90" s="161"/>
       <c r="J90" s="161"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="163" t="s">
-        <v>1028</v>
+        <v>839</v>
       </c>
       <c r="B91" s="163" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C91" s="163" t="s">
-        <v>1029</v>
+        <v>840</v>
       </c>
       <c r="D91" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E91" s="105" t="s">
-        <v>148</v>
+        <v>143</v>
+      </c>
+      <c r="E91" s="163" t="s">
+        <v>192</v>
       </c>
       <c r="F91" s="341"/>
       <c r="G91" s="163"/>
@@ -9978,407 +10009,34 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="163" t="s">
-        <v>718</v>
+        <v>847</v>
       </c>
       <c r="B92" s="163" t="s">
-        <v>58</v>
+        <v>444</v>
       </c>
       <c r="C92" s="163" t="s">
-        <v>375</v>
+        <v>802</v>
       </c>
       <c r="D92" s="163" t="s">
         <v>143</v>
       </c>
       <c r="E92" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F92" s="341" t="s">
-        <v>721</v>
-      </c>
-      <c r="G92" s="164">
-        <v>44642</v>
-      </c>
-      <c r="H92" s="164">
-        <v>44642</v>
-      </c>
-      <c r="I92" s="124">
-        <v>206097</v>
-      </c>
-      <c r="J92" s="124"/>
+        <v>626</v>
+      </c>
+      <c r="F92" s="341"/>
+      <c r="G92" s="163"/>
+      <c r="H92" s="163"/>
+      <c r="I92" s="161">
+        <v>60000</v>
+      </c>
+      <c r="J92" s="161"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A93" s="163" t="s">
-        <v>718</v>
-      </c>
-      <c r="B93" s="163" t="s">
-        <v>335</v>
-      </c>
-      <c r="C93" s="163" t="s">
-        <v>729</v>
-      </c>
-      <c r="D93" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E93" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F93" s="341">
-        <v>2015</v>
-      </c>
-      <c r="G93" s="164">
-        <v>42156</v>
-      </c>
-      <c r="H93" s="164">
-        <v>42157</v>
-      </c>
-      <c r="I93" s="161"/>
-      <c r="J93" s="161"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A94" s="163" t="s">
-        <v>737</v>
-      </c>
-      <c r="B94" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C94" s="163" t="s">
-        <v>738</v>
-      </c>
-      <c r="D94" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E94" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F94" s="341" t="s">
-        <v>739</v>
-      </c>
-      <c r="G94" s="163"/>
-      <c r="H94" s="163"/>
-      <c r="I94" s="161">
-        <v>30000</v>
-      </c>
-      <c r="J94" s="161"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A95" s="183" t="s">
-        <v>575</v>
-      </c>
-      <c r="B95" s="183" t="s">
-        <v>444</v>
-      </c>
-      <c r="C95" s="183" t="s">
-        <v>745</v>
-      </c>
-      <c r="D95" s="183" t="s">
-        <v>143</v>
-      </c>
-      <c r="E95" s="183" t="s">
-        <v>61</v>
-      </c>
-      <c r="F95" s="342">
-        <v>2013</v>
-      </c>
-      <c r="G95" s="126">
-        <v>41426</v>
-      </c>
-      <c r="H95" s="126">
-        <v>41426</v>
-      </c>
-      <c r="I95" s="124">
-        <v>94839</v>
-      </c>
-      <c r="J95" s="161"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="163" t="s">
-        <v>575</v>
-      </c>
-      <c r="B96" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C96" s="163" t="s">
-        <v>754</v>
-      </c>
-      <c r="D96" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E96" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F96" s="341"/>
-      <c r="G96" s="163"/>
-      <c r="H96" s="163"/>
-      <c r="I96" s="161">
-        <v>140000</v>
-      </c>
-      <c r="J96" s="161"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A97" s="163" t="s">
-        <v>575</v>
-      </c>
-      <c r="B97" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C97" s="163" t="s">
-        <v>764</v>
-      </c>
-      <c r="D97" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E97" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F97" s="341"/>
-      <c r="G97" s="163"/>
-      <c r="H97" s="163"/>
-      <c r="I97" s="161">
-        <v>15000</v>
-      </c>
-      <c r="J97" s="161"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A98" s="163" t="s">
-        <v>575</v>
-      </c>
-      <c r="B98" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C98" s="163" t="s">
-        <v>770</v>
-      </c>
-      <c r="D98" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E98" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F98" s="341" t="s">
-        <v>772</v>
-      </c>
-      <c r="G98" s="163"/>
-      <c r="H98" s="163"/>
-      <c r="I98" s="161"/>
-      <c r="J98" s="161"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A99" s="163" t="s">
-        <v>575</v>
-      </c>
-      <c r="B99" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C99" s="163" t="s">
-        <v>781</v>
-      </c>
-      <c r="D99" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="E99" s="206" t="s">
-        <v>61</v>
-      </c>
-      <c r="F99" s="341" t="s">
-        <v>782</v>
-      </c>
-      <c r="G99" s="164">
-        <v>43773</v>
-      </c>
-      <c r="H99" s="164">
-        <v>43773</v>
-      </c>
-      <c r="I99" s="161">
-        <v>333000</v>
-      </c>
-      <c r="J99" s="161"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A100" s="163" t="s">
-        <v>575</v>
-      </c>
-      <c r="B100" s="163" t="s">
-        <v>318</v>
-      </c>
-      <c r="C100" s="163" t="s">
-        <v>792</v>
-      </c>
-      <c r="D100" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E100" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F100" s="341">
-        <v>2025</v>
-      </c>
-      <c r="G100" s="164">
-        <v>45809</v>
-      </c>
-      <c r="H100" s="163"/>
-      <c r="I100" s="161">
-        <f>3000000/5</f>
-        <v>600000</v>
-      </c>
-      <c r="J100" s="161"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A101" s="163" t="s">
-        <v>824</v>
-      </c>
-      <c r="B101" s="163" t="s">
-        <v>825</v>
-      </c>
-      <c r="C101" s="163" t="s">
-        <v>826</v>
-      </c>
-      <c r="D101" s="105" t="s">
-        <v>60</v>
-      </c>
-      <c r="E101" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F101" s="342"/>
-      <c r="G101" s="105"/>
-      <c r="H101" s="126">
-        <v>45657</v>
-      </c>
-      <c r="I101" s="124">
-        <v>85654</v>
-      </c>
-      <c r="J101" s="124"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A102" s="163" t="s">
-        <v>810</v>
-      </c>
-      <c r="B102" s="163" t="s">
-        <v>265</v>
-      </c>
-      <c r="C102" s="163" t="s">
-        <v>811</v>
-      </c>
-      <c r="D102" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E102" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F102" s="341">
-        <v>2019</v>
-      </c>
-      <c r="G102" s="164">
-        <v>43646</v>
-      </c>
-      <c r="H102" s="164">
-        <v>43646</v>
-      </c>
-      <c r="I102" s="161"/>
-      <c r="J102" s="161"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A103" s="163" t="s">
-        <v>810</v>
-      </c>
-      <c r="B103" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C103" s="163" t="s">
-        <v>817</v>
-      </c>
-      <c r="D103" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E103" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="F103" s="341"/>
-      <c r="G103" s="164">
-        <v>45183</v>
-      </c>
-      <c r="H103" s="164">
-        <v>45183</v>
-      </c>
-      <c r="I103" s="161"/>
-      <c r="J103" s="161"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A104" s="163" t="s">
-        <v>810</v>
-      </c>
-      <c r="B104" s="163" t="s">
-        <v>212</v>
-      </c>
-      <c r="C104" s="163" t="s">
-        <v>817</v>
-      </c>
-      <c r="D104" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="E104" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="F104" s="341"/>
-      <c r="G104" s="164">
-        <v>45777</v>
-      </c>
-      <c r="H104" s="164">
-        <v>45777</v>
-      </c>
-      <c r="I104" s="161"/>
-      <c r="J104" s="161"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A105" s="163" t="s">
-        <v>839</v>
-      </c>
-      <c r="B105" s="163" t="s">
-        <v>58</v>
-      </c>
-      <c r="C105" s="163" t="s">
-        <v>840</v>
-      </c>
-      <c r="D105" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E105" s="163" t="s">
-        <v>192</v>
-      </c>
-      <c r="F105" s="341"/>
-      <c r="G105" s="163"/>
-      <c r="H105" s="163"/>
-      <c r="I105" s="161"/>
-      <c r="J105" s="161"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A106" s="163" t="s">
-        <v>847</v>
-      </c>
-      <c r="B106" s="163" t="s">
-        <v>444</v>
-      </c>
-      <c r="C106" s="163" t="s">
-        <v>802</v>
-      </c>
-      <c r="D106" s="163" t="s">
-        <v>143</v>
-      </c>
-      <c r="E106" s="163" t="s">
-        <v>626</v>
-      </c>
-      <c r="F106" s="341"/>
-      <c r="G106" s="163"/>
-      <c r="H106" s="163"/>
-      <c r="I106" s="161">
-        <v>60000</v>
-      </c>
-      <c r="J106" s="161"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A107" s="163"/>
-      <c r="B107" s="163"/>
-      <c r="C107" s="163"/>
-      <c r="D107" s="163"/>
-      <c r="E107" s="163"/>
+      <c r="A93" s="163"/>
+      <c r="B93" s="163"/>
+      <c r="C93" s="163"/>
+      <c r="D93" s="163"/>
+      <c r="E93" s="163"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11288,13 +10946,13 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B24" s="57" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C24" s="307" t="s">
         <v>668</v>
       </c>
       <c r="D24" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E24" s="58"/>
       <c r="F24" s="58" t="s">
@@ -11333,7 +10991,7 @@
         <v>668</v>
       </c>
       <c r="D25" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E25" s="58"/>
       <c r="F25" s="58" t="s">
@@ -12252,13 +11910,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="332" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B3" s="332" t="s">
         <v>1143</v>
       </c>
-      <c r="B3" s="332" t="s">
+      <c r="C3" s="330" t="s">
         <v>1144</v>
-      </c>
-      <c r="C3" s="330" t="s">
-        <v>1145</v>
       </c>
       <c r="D3" s="333"/>
       <c r="E3" s="333"/>
@@ -12286,7 +11944,7 @@
         <v>940</v>
       </c>
       <c r="C4" s="330" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D4" s="333"/>
       <c r="E4" s="333"/>
@@ -12309,10 +11967,10 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="332"/>
       <c r="B5" s="332" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C5" s="330" t="s">
         <v>1147</v>
-      </c>
-      <c r="C5" s="330" t="s">
-        <v>1148</v>
       </c>
       <c r="D5" s="333"/>
       <c r="E5" s="333"/>
@@ -12342,7 +12000,7 @@
       <c r="A6" s="334"/>
       <c r="B6" s="332"/>
       <c r="C6" s="330" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D6" s="333"/>
       <c r="E6" s="333"/>
@@ -12379,10 +12037,10 @@
         <v>212</v>
       </c>
       <c r="B7" s="332" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C7" s="330" t="s">
         <v>1150</v>
-      </c>
-      <c r="C7" s="330" t="s">
-        <v>1151</v>
       </c>
       <c r="D7" s="333"/>
       <c r="E7" s="333"/>
@@ -12412,7 +12070,7 @@
       <c r="A8" s="332"/>
       <c r="B8" s="332"/>
       <c r="C8" s="330" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D8" s="333"/>
       <c r="E8" s="333"/>
@@ -12444,7 +12102,7 @@
       <c r="A9" s="332"/>
       <c r="B9" s="332"/>
       <c r="C9" s="330" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D9" s="333"/>
       <c r="E9" s="333"/>
@@ -12480,7 +12138,7 @@
         <v>934</v>
       </c>
       <c r="C10" s="330" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D10" s="333"/>
       <c r="E10" s="333"/>
@@ -12508,7 +12166,7 @@
         <v>920</v>
       </c>
       <c r="C11" s="330" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D11" s="333"/>
       <c r="E11" s="333"/>
@@ -12542,7 +12200,7 @@
       <c r="A12" s="334"/>
       <c r="B12" s="332"/>
       <c r="C12" s="330" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D12" s="333"/>
       <c r="E12" s="333"/>
@@ -12574,7 +12232,7 @@
         <v>934</v>
       </c>
       <c r="C13" s="330" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D13" s="333"/>
       <c r="E13" s="333"/>
@@ -12600,13 +12258,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="332" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B14" s="332" t="s">
         <v>1158</v>
       </c>
-      <c r="B14" s="332" t="s">
+      <c r="C14" s="330" t="s">
         <v>1159</v>
-      </c>
-      <c r="C14" s="330" t="s">
-        <v>1160</v>
       </c>
       <c r="D14" s="333"/>
       <c r="E14" s="333"/>
@@ -12638,7 +12296,7 @@
       <c r="A15" s="332"/>
       <c r="B15" s="332"/>
       <c r="C15" s="330" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D15" s="333"/>
       <c r="E15" s="333"/>
@@ -12670,7 +12328,7 @@
         <v>934</v>
       </c>
       <c r="C16" s="330" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D16" s="333"/>
       <c r="E16" s="333"/>
@@ -12696,7 +12354,7 @@
         <v>920</v>
       </c>
       <c r="C17" s="330" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D17" s="333"/>
       <c r="E17" s="333"/>
@@ -12720,7 +12378,7 @@
       <c r="A18" s="332"/>
       <c r="B18" s="332"/>
       <c r="C18" s="330" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D18" s="333"/>
       <c r="E18" s="333"/>
@@ -12744,7 +12402,7 @@
       <c r="A19" s="332"/>
       <c r="B19" s="332"/>
       <c r="C19" s="330" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D19" s="333"/>
       <c r="E19" s="333"/>
@@ -12776,7 +12434,7 @@
       <c r="A20" s="332"/>
       <c r="B20" s="332"/>
       <c r="C20" s="330" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D20" s="333"/>
       <c r="E20" s="333"/>
@@ -12800,7 +12458,7 @@
       <c r="A21" s="332"/>
       <c r="B21" s="332"/>
       <c r="C21" s="330" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D21" s="333"/>
       <c r="E21" s="333"/>
@@ -12832,7 +12490,7 @@
       <c r="A22" s="334"/>
       <c r="B22" s="332"/>
       <c r="C22" s="330" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D22" s="333"/>
       <c r="E22" s="333"/>
@@ -12864,13 +12522,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="334" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B23" s="332" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C23" s="330" t="s">
         <v>1169</v>
-      </c>
-      <c r="B23" s="332" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C23" s="330" t="s">
-        <v>1170</v>
       </c>
       <c r="D23" s="333"/>
       <c r="E23" s="333">
@@ -12904,7 +12562,7 @@
         <v>940</v>
       </c>
       <c r="C24" s="330" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D24" s="333"/>
       <c r="E24" s="333"/>
@@ -12932,7 +12590,7 @@
       <c r="A25" s="332"/>
       <c r="B25" s="332"/>
       <c r="C25" s="330" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D25" s="333">
         <v>395</v>
@@ -12986,7 +12644,7 @@
         <v>934</v>
       </c>
       <c r="C26" s="330" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D26" s="333"/>
       <c r="E26" s="333">
@@ -13026,7 +12684,7 @@
       <c r="A27" s="332"/>
       <c r="B27" s="332"/>
       <c r="C27" s="330" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D27" s="333"/>
       <c r="E27" s="333"/>
@@ -13050,7 +12708,7 @@
       <c r="A28" s="332"/>
       <c r="B28" s="332"/>
       <c r="C28" s="330" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D28" s="333"/>
       <c r="E28" s="333"/>
@@ -13076,7 +12734,7 @@
       <c r="A29" s="332"/>
       <c r="B29" s="332"/>
       <c r="C29" s="330" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D29" s="333">
         <v>356</v>
@@ -13128,7 +12786,7 @@
       <c r="A30" s="332"/>
       <c r="B30" s="332"/>
       <c r="C30" s="330" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D30" s="333"/>
       <c r="E30" s="333"/>
@@ -13158,7 +12816,7 @@
       <c r="A31" s="332"/>
       <c r="B31" s="332"/>
       <c r="C31" s="330" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D31" s="333"/>
       <c r="E31" s="333"/>
@@ -14113,10 +13771,10 @@
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="332"/>
       <c r="B62" s="332" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C62" s="330" t="s">
         <v>1139</v>
-      </c>
-      <c r="C62" s="330" t="s">
-        <v>1140</v>
       </c>
       <c r="D62" s="333"/>
       <c r="E62" s="333"/>
@@ -14148,7 +13806,7 @@
       <c r="A63" s="334"/>
       <c r="B63" s="332"/>
       <c r="C63" s="330" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D63" s="333"/>
       <c r="E63" s="333"/>
@@ -14721,10 +14379,10 @@
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="332"/>
       <c r="B80" s="332" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C80" s="330" t="s">
         <v>1179</v>
-      </c>
-      <c r="C80" s="330" t="s">
-        <v>1180</v>
       </c>
       <c r="D80" s="333"/>
       <c r="E80" s="333"/>
@@ -14766,7 +14424,7 @@
         <v>399</v>
       </c>
       <c r="C81" s="330" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D81" s="333"/>
       <c r="E81" s="333"/>
@@ -14790,7 +14448,7 @@
       <c r="A82" s="332"/>
       <c r="B82" s="332"/>
       <c r="C82" s="330" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D82" s="333"/>
       <c r="E82" s="333"/>
@@ -15450,7 +15108,7 @@
         <v>934</v>
       </c>
       <c r="C102" s="330" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D102" s="333"/>
       <c r="E102" s="333"/>
@@ -15476,7 +15134,7 @@
       <c r="A103" s="332"/>
       <c r="B103" s="332"/>
       <c r="C103" s="330" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D103" s="333"/>
       <c r="E103" s="333"/>
@@ -15504,7 +15162,7 @@
         <v>613</v>
       </c>
       <c r="C104" s="330" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D104" s="333"/>
       <c r="E104" s="333"/>
@@ -15534,7 +15192,7 @@
       <c r="A105" s="332"/>
       <c r="B105" s="332"/>
       <c r="C105" s="330" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D105" s="333"/>
       <c r="E105" s="333"/>
@@ -15564,7 +15222,7 @@
       <c r="A106" s="332"/>
       <c r="B106" s="332"/>
       <c r="C106" s="330" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D106" s="333"/>
       <c r="E106" s="333"/>
@@ -15624,7 +15282,7 @@
       <c r="A108" s="332"/>
       <c r="B108" s="332"/>
       <c r="C108" s="330" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D108" s="333"/>
       <c r="E108" s="333"/>
@@ -15647,10 +15305,10 @@
     <row r="109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A109" s="332"/>
       <c r="B109" s="332" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C109" s="330" t="s">
         <v>1189</v>
-      </c>
-      <c r="C109" s="330" t="s">
-        <v>1190</v>
       </c>
       <c r="D109" s="333"/>
       <c r="E109" s="333"/>
@@ -15964,7 +15622,7 @@
       <c r="A119" s="332"/>
       <c r="B119" s="332"/>
       <c r="C119" s="330" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D119" s="333"/>
       <c r="E119" s="333"/>
@@ -15996,7 +15654,7 @@
       <c r="A120" s="332"/>
       <c r="B120" s="332"/>
       <c r="C120" s="330" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D120" s="333"/>
       <c r="E120" s="333"/>
@@ -16026,7 +15684,7 @@
       <c r="A121" s="332"/>
       <c r="B121" s="332"/>
       <c r="C121" s="330" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D121" s="333"/>
       <c r="E121" s="333"/>
@@ -16050,7 +15708,7 @@
       <c r="A122" s="332"/>
       <c r="B122" s="332"/>
       <c r="C122" s="330" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D122" s="333"/>
       <c r="E122" s="333"/>
@@ -16096,7 +15754,7 @@
       <c r="A123" s="332"/>
       <c r="B123" s="332"/>
       <c r="C123" s="330" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D123" s="333"/>
       <c r="E123" s="333"/>
@@ -16130,7 +15788,7 @@
       <c r="A124" s="332"/>
       <c r="B124" s="332"/>
       <c r="C124" s="330" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D124" s="333"/>
       <c r="E124" s="333"/>
@@ -16164,7 +15822,7 @@
       <c r="A125" s="332"/>
       <c r="B125" s="332"/>
       <c r="C125" s="330" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D125" s="333"/>
       <c r="E125" s="333"/>
@@ -16196,7 +15854,7 @@
       <c r="A126" s="332"/>
       <c r="B126" s="332"/>
       <c r="C126" s="330" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D126" s="333"/>
       <c r="E126" s="333"/>
@@ -16224,7 +15882,7 @@
       <c r="A127" s="332"/>
       <c r="B127" s="332"/>
       <c r="C127" s="330" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D127" s="333"/>
       <c r="E127" s="333"/>
@@ -16268,7 +15926,7 @@
       <c r="A128" s="332"/>
       <c r="B128" s="332"/>
       <c r="C128" s="330" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D128" s="333"/>
       <c r="E128" s="333"/>
@@ -16298,7 +15956,7 @@
       <c r="A129" s="332"/>
       <c r="B129" s="332"/>
       <c r="C129" s="330" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D129" s="333"/>
       <c r="E129" s="333"/>
@@ -16342,7 +16000,7 @@
       <c r="A130" s="332"/>
       <c r="B130" s="332"/>
       <c r="C130" s="330" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D130" s="333"/>
       <c r="E130" s="333"/>
@@ -16376,7 +16034,7 @@
       <c r="A131" s="332"/>
       <c r="B131" s="332"/>
       <c r="C131" s="330" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D131" s="333"/>
       <c r="E131" s="333"/>
@@ -16408,7 +16066,7 @@
       <c r="A132" s="332"/>
       <c r="B132" s="332"/>
       <c r="C132" s="330" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D132" s="333"/>
       <c r="E132" s="333"/>
@@ -16436,7 +16094,7 @@
       <c r="A133" s="332"/>
       <c r="B133" s="332"/>
       <c r="C133" s="330" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D133" s="333"/>
       <c r="E133" s="333"/>
@@ -16462,7 +16120,7 @@
       <c r="A134" s="332"/>
       <c r="B134" s="332"/>
       <c r="C134" s="330" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D134" s="333"/>
       <c r="E134" s="333"/>
@@ -16490,7 +16148,7 @@
       <c r="A135" s="332"/>
       <c r="B135" s="332"/>
       <c r="C135" s="330" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D135" s="333"/>
       <c r="E135" s="333"/>
@@ -16518,7 +16176,7 @@
       <c r="A136" s="332"/>
       <c r="B136" s="332"/>
       <c r="C136" s="330" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D136" s="333"/>
       <c r="E136" s="333"/>
@@ -16548,7 +16206,7 @@
       <c r="A137" s="332"/>
       <c r="B137" s="332"/>
       <c r="C137" s="330" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D137" s="333"/>
       <c r="E137" s="333"/>
@@ -16590,7 +16248,7 @@
       <c r="A138" s="332"/>
       <c r="B138" s="332"/>
       <c r="C138" s="330" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D138" s="333"/>
       <c r="E138" s="333"/>
@@ -16614,7 +16272,7 @@
       <c r="A139" s="334"/>
       <c r="B139" s="332"/>
       <c r="C139" s="330" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D139" s="333"/>
       <c r="E139" s="333"/>
@@ -16743,10 +16401,10 @@
         <v>182</v>
       </c>
       <c r="B143" s="332" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C143" s="330" t="s">
         <v>1212</v>
-      </c>
-      <c r="C143" s="330" t="s">
-        <v>1213</v>
       </c>
       <c r="D143" s="333"/>
       <c r="E143" s="333"/>
@@ -16784,7 +16442,7 @@
         <v>934</v>
       </c>
       <c r="C144" s="330" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D144" s="333"/>
       <c r="E144" s="333"/>
@@ -16810,7 +16468,7 @@
       <c r="A145" s="332"/>
       <c r="B145" s="332"/>
       <c r="C145" s="330" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D145" s="333"/>
       <c r="E145" s="333"/>
@@ -16838,7 +16496,7 @@
       <c r="A146" s="332"/>
       <c r="B146" s="332"/>
       <c r="C146" s="330" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D146" s="333"/>
       <c r="E146" s="333"/>
@@ -16870,7 +16528,7 @@
       <c r="A147" s="332"/>
       <c r="B147" s="332"/>
       <c r="C147" s="330" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D147" s="333"/>
       <c r="E147" s="333"/>
@@ -16898,7 +16556,7 @@
         <v>613</v>
       </c>
       <c r="C148" s="330" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D148" s="333"/>
       <c r="E148" s="333"/>
@@ -16926,7 +16584,7 @@
       <c r="A149" s="332"/>
       <c r="B149" s="332"/>
       <c r="C149" s="330" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D149" s="333"/>
       <c r="E149" s="333"/>
@@ -16956,7 +16614,7 @@
       <c r="A150" s="332"/>
       <c r="B150" s="332"/>
       <c r="C150" s="330" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D150" s="333"/>
       <c r="E150" s="333"/>
@@ -16982,7 +16640,7 @@
       <c r="A151" s="332"/>
       <c r="B151" s="332"/>
       <c r="C151" s="330" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D151" s="333"/>
       <c r="E151" s="333"/>
@@ -17014,7 +16672,7 @@
       <c r="A152" s="332"/>
       <c r="B152" s="332"/>
       <c r="C152" s="330" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D152" s="333"/>
       <c r="E152" s="333"/>
@@ -17040,7 +16698,7 @@
       <c r="A153" s="332"/>
       <c r="B153" s="332"/>
       <c r="C153" s="330" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D153" s="333"/>
       <c r="E153" s="333"/>
@@ -17074,7 +16732,7 @@
       <c r="A154" s="332"/>
       <c r="B154" s="332"/>
       <c r="C154" s="330" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D154" s="333"/>
       <c r="E154" s="333"/>
@@ -17106,7 +16764,7 @@
       <c r="A155" s="332"/>
       <c r="B155" s="332"/>
       <c r="C155" s="330" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D155" s="333"/>
       <c r="E155" s="333"/>
@@ -17138,7 +16796,7 @@
       <c r="A156" s="332"/>
       <c r="B156" s="332"/>
       <c r="C156" s="330" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D156" s="333"/>
       <c r="E156" s="333"/>
@@ -17164,7 +16822,7 @@
       <c r="A157" s="332"/>
       <c r="B157" s="332"/>
       <c r="C157" s="330" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D157" s="333"/>
       <c r="E157" s="333"/>
@@ -17190,7 +16848,7 @@
       <c r="A158" s="332"/>
       <c r="B158" s="332"/>
       <c r="C158" s="330" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D158" s="333"/>
       <c r="E158" s="333"/>
@@ -17220,7 +16878,7 @@
       <c r="A159" s="332"/>
       <c r="B159" s="332"/>
       <c r="C159" s="330" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D159" s="333"/>
       <c r="E159" s="333"/>
@@ -17251,10 +16909,10 @@
     <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="332"/>
       <c r="B160" s="332" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C160" s="330" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D160" s="333"/>
       <c r="E160" s="333"/>
@@ -17280,7 +16938,7 @@
         <v>920</v>
       </c>
       <c r="C161" s="330" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D161" s="333"/>
       <c r="E161" s="333"/>
@@ -17304,7 +16962,7 @@
       <c r="A162" s="334"/>
       <c r="B162" s="332"/>
       <c r="C162" s="330" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D162" s="333"/>
       <c r="E162" s="333"/>
@@ -17334,7 +16992,7 @@
         <v>865</v>
       </c>
       <c r="C163" s="330" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D163" s="333"/>
       <c r="E163" s="333"/>
@@ -17376,7 +17034,7 @@
         <v>934</v>
       </c>
       <c r="C164" s="330" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D164" s="333"/>
       <c r="E164" s="333"/>
@@ -17398,13 +17056,13 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A165" s="334" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B165" s="332" t="s">
         <v>934</v>
       </c>
       <c r="C165" s="330" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D165" s="333">
         <v>755</v>
@@ -17438,7 +17096,7 @@
         <v>399</v>
       </c>
       <c r="C166" s="330" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D166" s="333"/>
       <c r="E166" s="333"/>
@@ -17461,10 +17119,10 @@
     <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="332"/>
       <c r="B167" s="332" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C167" s="330" t="s">
         <v>1238</v>
-      </c>
-      <c r="C167" s="330" t="s">
-        <v>1239</v>
       </c>
       <c r="D167" s="333"/>
       <c r="E167" s="333"/>
@@ -17490,7 +17148,7 @@
         <v>613</v>
       </c>
       <c r="C168" s="330" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D168" s="333"/>
       <c r="E168" s="333"/>
@@ -17514,7 +17172,7 @@
       <c r="A169" s="332"/>
       <c r="B169" s="332"/>
       <c r="C169" s="330" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D169" s="333"/>
       <c r="E169" s="333"/>
@@ -17540,7 +17198,7 @@
       <c r="A170" s="332"/>
       <c r="B170" s="332"/>
       <c r="C170" s="330" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D170" s="333"/>
       <c r="E170" s="333"/>
@@ -17570,7 +17228,7 @@
         <v>920</v>
       </c>
       <c r="C171" s="330" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D171" s="333"/>
       <c r="E171" s="333"/>
@@ -17606,7 +17264,7 @@
       <c r="A172" s="332"/>
       <c r="B172" s="332"/>
       <c r="C172" s="330" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D172" s="333"/>
       <c r="E172" s="333"/>
@@ -17634,7 +17292,7 @@
       <c r="A173" s="332"/>
       <c r="B173" s="332"/>
       <c r="C173" s="330" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D173" s="333"/>
       <c r="E173" s="333"/>
@@ -17662,7 +17320,7 @@
       <c r="A174" s="332"/>
       <c r="B174" s="332"/>
       <c r="C174" s="330" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D174" s="333"/>
       <c r="E174" s="333"/>
@@ -17692,7 +17350,7 @@
       <c r="A175" s="332"/>
       <c r="B175" s="332"/>
       <c r="C175" s="330" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D175" s="333"/>
       <c r="E175" s="333"/>
@@ -17722,7 +17380,7 @@
       <c r="A176" s="334"/>
       <c r="B176" s="332"/>
       <c r="C176" s="330" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D176" s="333"/>
       <c r="E176" s="333"/>
@@ -17756,13 +17414,13 @@
     </row>
     <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" s="332" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B177" s="332" t="s">
         <v>399</v>
       </c>
       <c r="C177" s="330" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D177" s="333"/>
       <c r="E177" s="333"/>
@@ -17786,7 +17444,7 @@
       <c r="A178" s="334"/>
       <c r="B178" s="332"/>
       <c r="C178" s="330" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D178" s="333"/>
       <c r="E178" s="333"/>
@@ -17811,10 +17469,10 @@
         <v>444</v>
       </c>
       <c r="B179" s="332" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C179" s="330" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D179" s="333"/>
       <c r="E179" s="333"/>
@@ -17846,7 +17504,7 @@
       <c r="A180" s="332"/>
       <c r="B180" s="332"/>
       <c r="C180" s="330" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D180" s="333"/>
       <c r="E180" s="333"/>
@@ -17874,7 +17532,7 @@
       <c r="A181" s="332"/>
       <c r="B181" s="332"/>
       <c r="C181" s="330" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D181" s="333"/>
       <c r="E181" s="333"/>
@@ -17914,7 +17572,7 @@
         <v>613</v>
       </c>
       <c r="C182" s="330" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D182" s="333"/>
       <c r="E182" s="333"/>
@@ -17969,10 +17627,10 @@
     <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" s="332"/>
       <c r="B184" s="332" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C184" s="330" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D184" s="333"/>
       <c r="E184" s="333"/>
@@ -18004,7 +17662,7 @@
         <v>920</v>
       </c>
       <c r="C185" s="330" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D185" s="333"/>
       <c r="E185" s="333"/>
@@ -18046,7 +17704,7 @@
       <c r="A186" s="332"/>
       <c r="B186" s="332"/>
       <c r="C186" s="330" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D186" s="333"/>
       <c r="E186" s="333"/>
@@ -18080,7 +17738,7 @@
       <c r="A187" s="332"/>
       <c r="B187" s="332"/>
       <c r="C187" s="330" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D187" s="333"/>
       <c r="E187" s="333"/>
@@ -18124,7 +17782,7 @@
       <c r="A188" s="332"/>
       <c r="B188" s="332"/>
       <c r="C188" s="330" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D188" s="333"/>
       <c r="E188" s="333"/>
@@ -18156,7 +17814,7 @@
       <c r="A189" s="332"/>
       <c r="B189" s="332"/>
       <c r="C189" s="330" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D189" s="333"/>
       <c r="E189" s="333"/>
@@ -18190,7 +17848,7 @@
       <c r="A190" s="332"/>
       <c r="B190" s="332"/>
       <c r="C190" s="330" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D190" s="333"/>
       <c r="E190" s="333"/>
@@ -18214,7 +17872,7 @@
       <c r="A191" s="332"/>
       <c r="B191" s="332"/>
       <c r="C191" s="330" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D191" s="333"/>
       <c r="E191" s="333"/>
@@ -18260,7 +17918,7 @@
       <c r="A192" s="332"/>
       <c r="B192" s="332"/>
       <c r="C192" s="330" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D192" s="333"/>
       <c r="E192" s="333"/>
@@ -18284,7 +17942,7 @@
       <c r="A193" s="334"/>
       <c r="B193" s="332"/>
       <c r="C193" s="330" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D193" s="333"/>
       <c r="E193" s="333"/>
@@ -18324,7 +17982,7 @@
         <v>940</v>
       </c>
       <c r="C194" s="330" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D194" s="333"/>
       <c r="E194" s="333"/>
@@ -18364,7 +18022,7 @@
         <v>1119</v>
       </c>
       <c r="C195" s="330" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D195" s="333"/>
       <c r="E195" s="333"/>
@@ -18400,7 +18058,7 @@
         <v>399</v>
       </c>
       <c r="C196" s="330" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D196" s="333"/>
       <c r="E196" s="333"/>
@@ -18434,7 +18092,7 @@
         <v>940</v>
       </c>
       <c r="C197" s="330" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D197" s="333"/>
       <c r="E197" s="333"/>
@@ -18462,7 +18120,7 @@
       <c r="A198" s="332"/>
       <c r="B198" s="332"/>
       <c r="C198" s="330" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D198" s="333"/>
       <c r="E198" s="333"/>
@@ -18496,7 +18154,7 @@
       <c r="A199" s="332"/>
       <c r="B199" s="332"/>
       <c r="C199" s="330" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D199" s="333"/>
       <c r="E199" s="333"/>
@@ -18534,7 +18192,7 @@
         <v>1119</v>
       </c>
       <c r="C200" s="330" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D200" s="333"/>
       <c r="E200" s="333"/>
@@ -18562,7 +18220,7 @@
       <c r="A201" s="332"/>
       <c r="B201" s="332"/>
       <c r="C201" s="330" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D201" s="333"/>
       <c r="E201" s="333"/>
@@ -18608,7 +18266,7 @@
       <c r="A202" s="332"/>
       <c r="B202" s="332"/>
       <c r="C202" s="330" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D202" s="333"/>
       <c r="E202" s="333"/>
@@ -18642,7 +18300,7 @@
       <c r="A203" s="332"/>
       <c r="B203" s="332"/>
       <c r="C203" s="330" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D203" s="333"/>
       <c r="E203" s="333"/>
@@ -18674,7 +18332,7 @@
       <c r="A204" s="332"/>
       <c r="B204" s="332"/>
       <c r="C204" s="330" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D204" s="333"/>
       <c r="E204" s="333"/>
@@ -18706,7 +18364,7 @@
       <c r="A205" s="332"/>
       <c r="B205" s="332"/>
       <c r="C205" s="330" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D205" s="333"/>
       <c r="E205" s="333"/>
@@ -18730,7 +18388,7 @@
       <c r="A206" s="332"/>
       <c r="B206" s="332"/>
       <c r="C206" s="330" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D206" s="333"/>
       <c r="E206" s="333"/>
@@ -19363,10 +19021,10 @@
     <row r="226" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A226" s="332"/>
       <c r="B226" s="332" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C226" s="330" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D226" s="333"/>
       <c r="E226" s="333"/>
@@ -19396,7 +19054,7 @@
       <c r="A227" s="332"/>
       <c r="B227" s="332"/>
       <c r="C227" s="330" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D227" s="333"/>
       <c r="E227" s="333"/>
@@ -19428,7 +19086,7 @@
         <v>920</v>
       </c>
       <c r="C228" s="330" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D228" s="333"/>
       <c r="E228" s="333"/>
@@ -19460,7 +19118,7 @@
       <c r="A229" s="332"/>
       <c r="B229" s="332"/>
       <c r="C229" s="330" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D229" s="333"/>
       <c r="E229" s="333"/>
@@ -19492,7 +19150,7 @@
       <c r="A230" s="332"/>
       <c r="B230" s="332"/>
       <c r="C230" s="330" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D230" s="333"/>
       <c r="E230" s="333"/>
@@ -19516,7 +19174,7 @@
       <c r="A231" s="334"/>
       <c r="B231" s="332"/>
       <c r="C231" s="330" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D231" s="333"/>
       <c r="E231" s="333"/>
@@ -19549,10 +19207,10 @@
         <v>603</v>
       </c>
       <c r="B232" s="332" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C232" s="330" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D232" s="333">
         <v>50</v>
@@ -19584,7 +19242,7 @@
       <c r="A233" s="332"/>
       <c r="B233" s="332"/>
       <c r="C233" s="330" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D233" s="333"/>
       <c r="E233" s="333"/>
@@ -19632,7 +19290,7 @@
       <c r="A234" s="332"/>
       <c r="B234" s="332"/>
       <c r="C234" s="330" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D234" s="333"/>
       <c r="E234" s="333"/>
@@ -19670,7 +19328,7 @@
       <c r="A235" s="332"/>
       <c r="B235" s="332"/>
       <c r="C235" s="330" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D235" s="333"/>
       <c r="E235" s="333"/>
@@ -19708,7 +19366,7 @@
       <c r="A236" s="334"/>
       <c r="B236" s="332"/>
       <c r="C236" s="330" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D236" s="333"/>
       <c r="E236" s="333"/>
@@ -19819,10 +19477,10 @@
     <row r="239" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A239" s="332"/>
       <c r="B239" s="332" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C239" s="330" t="s">
         <v>1288</v>
-      </c>
-      <c r="C239" s="330" t="s">
-        <v>1289</v>
       </c>
       <c r="D239" s="333"/>
       <c r="E239" s="333"/>
@@ -19850,7 +19508,7 @@
       <c r="A240" s="332"/>
       <c r="B240" s="332"/>
       <c r="C240" s="330" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D240" s="333"/>
       <c r="E240" s="333"/>
@@ -19886,7 +19544,7 @@
       <c r="A241" s="332"/>
       <c r="B241" s="332"/>
       <c r="C241" s="330" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D241" s="333"/>
       <c r="E241" s="333"/>
@@ -19922,7 +19580,7 @@
         <v>940</v>
       </c>
       <c r="C242" s="330" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D242" s="333"/>
       <c r="E242" s="333"/>
@@ -19950,7 +19608,7 @@
         <v>934</v>
       </c>
       <c r="C243" s="330" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D243" s="333"/>
       <c r="E243" s="333"/>
@@ -19978,7 +19636,7 @@
       <c r="A244" s="332"/>
       <c r="B244" s="332"/>
       <c r="C244" s="330" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D244" s="333"/>
       <c r="E244" s="333"/>
@@ -20004,7 +19662,7 @@
         <v>1119</v>
       </c>
       <c r="C245" s="330" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D245" s="333">
         <v>12</v>
@@ -20058,7 +19716,7 @@
         <v>613</v>
       </c>
       <c r="C246" s="330" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D246" s="333"/>
       <c r="E246" s="333"/>
@@ -20082,7 +19740,7 @@
       <c r="A247" s="332"/>
       <c r="B247" s="332"/>
       <c r="C247" s="330" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D247" s="333"/>
       <c r="E247" s="333"/>
@@ -20116,7 +19774,7 @@
       <c r="A248" s="332"/>
       <c r="B248" s="332"/>
       <c r="C248" s="330" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D248" s="333"/>
       <c r="E248" s="333"/>
@@ -20147,10 +19805,10 @@
     <row r="249" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A249" s="332"/>
       <c r="B249" s="332" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C249" s="330" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D249" s="333"/>
       <c r="E249" s="333"/>
@@ -20180,7 +19838,7 @@
       <c r="A250" s="332"/>
       <c r="B250" s="332"/>
       <c r="C250" s="330" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D250" s="333"/>
       <c r="E250" s="333"/>
@@ -20212,7 +19870,7 @@
       <c r="A251" s="332"/>
       <c r="B251" s="332"/>
       <c r="C251" s="330" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D251" s="333"/>
       <c r="E251" s="333"/>
@@ -20244,7 +19902,7 @@
       <c r="A252" s="332"/>
       <c r="B252" s="332"/>
       <c r="C252" s="330" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D252" s="333"/>
       <c r="E252" s="333"/>
@@ -20280,7 +19938,7 @@
       <c r="A253" s="332"/>
       <c r="B253" s="332"/>
       <c r="C253" s="330" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D253" s="333"/>
       <c r="E253" s="333"/>
@@ -20316,7 +19974,7 @@
       <c r="A254" s="332"/>
       <c r="B254" s="332"/>
       <c r="C254" s="330" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D254" s="333"/>
       <c r="E254" s="333"/>
@@ -20348,7 +20006,7 @@
         <v>920</v>
       </c>
       <c r="C255" s="330" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D255" s="333"/>
       <c r="E255" s="333"/>
@@ -20382,7 +20040,7 @@
       <c r="A256" s="332"/>
       <c r="B256" s="332"/>
       <c r="C256" s="330" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D256" s="333"/>
       <c r="E256" s="333"/>
@@ -20408,7 +20066,7 @@
       <c r="A257" s="334"/>
       <c r="B257" s="332"/>
       <c r="C257" s="330" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D257" s="333"/>
       <c r="E257" s="333"/>
@@ -20434,7 +20092,7 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" s="335" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B258" s="335"/>
       <c r="C258" s="335"/>
@@ -37930,42 +37588,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Dataset</Value>
-    </ProjectType>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Green Economy</Value>
-    </ResearchArea>
-    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
-    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
-      <UserInfo>
-        <DisplayName>Ugne Keliauskaite</DisplayName>
-        <AccountId>1048</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ben McWilliams</DisplayName>
-        <AccountId>22</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Marie Jugé</DisplayName>
-        <AccountId>1714</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </Authors>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38298,6 +37920,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Dataset</Value>
+    </ProjectType>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Green Economy</Value>
+    </ResearchArea>
+    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
+    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
+      <UserInfo>
+        <DisplayName>Ugne Keliauskaite</DisplayName>
+        <AccountId>1048</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ben McWilliams</DisplayName>
+        <AccountId>22</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Marie Jugé</DisplayName>
+        <AccountId>1714</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </Authors>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -38308,23 +37966,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38343,6 +37984,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
   <ds:schemaRefs>

--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4121EBB2-CB4E-3D41-A243-C2B482BEFFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC9A6C6-8B26-7E42-B12B-7D3A3A89B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="6" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{4FE482CA-0ADC-8C4B-B773-F4E4B47D6927}">
       <text>
         <r>
           <rPr>
@@ -146,13 +146,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{1CB05A61-ED73-9F40-8D60-A96C94868F7E}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{28932D39-8FFD-DD45-AA3D-6740EE1F647A}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -161,12 +161,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-that produced electric model (previous electic model discontinued)</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2013-2022</t>
         </r>
       </text>
     </comment>
@@ -257,7 +266,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -266,12 +275,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Turin</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Turin</t>
         </r>
       </text>
     </comment>
@@ -1540,7 +1558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3468" uniqueCount="1309">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -4882,9 +4900,6 @@
     <t>Poissy</t>
   </si>
   <si>
-    <t>Srellantis</t>
-  </si>
-  <si>
     <t>Citroen C5 Aircross PHEV</t>
   </si>
   <si>
@@ -5552,6 +5567,12 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>BMW Series 1 and 2; Mini Countryman</t>
   </si>
 </sst>
 </file>
@@ -6166,7 +6187,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="345">
+  <cellXfs count="346">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6682,13 +6703,34 @@
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{E9361510-FC41-794E-963D-B228D8116D9F}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7018,7 +7060,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1623059</xdr:colOff>
+      <xdr:colOff>1592579</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>143806</xdr:rowOff>
     </xdr:to>
@@ -7061,7 +7103,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>845820</xdr:colOff>
+      <xdr:colOff>815340</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>145080</xdr:rowOff>
     </xdr:to>
@@ -7204,21 +7246,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:I92" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I92" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J92" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J92" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I92">
     <sortCondition ref="A1:A92"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{8195EC2C-EAFD-0248-8064-890DEBB2CF88}" name="country" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6D1EA899-5C16-9C45-99E8-4DEB01873247}" name="city" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{370650D5-6DD9-6B4E-9175-7EFEE1896586}" name="investment_type" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{9E50EEA0-4B08-C24B-B9DD-82808F97FE2D}" name="investment_status" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{64210756-8BE1-8E41-AE97-DED54BB2C3A7}" name="reported_production" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{D1ECD513-C00E-5A41-8FCD-5B5994F74BDB}" name="production_date_original" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{16C1B018-C17F-1D42-9D20-14601B26CA45}" name="production_date_current" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{CF19F16F-E593-1846-973E-64DBF9B072F7}" name="production_reported" dataDxfId="0"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{8195EC2C-EAFD-0248-8064-890DEBB2CF88}" name="country" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{6D1EA899-5C16-9C45-99E8-4DEB01873247}" name="city" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{370650D5-6DD9-6B4E-9175-7EFEE1896586}" name="investment_type" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{9E50EEA0-4B08-C24B-B9DD-82808F97FE2D}" name="investment_status" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{64210756-8BE1-8E41-AE97-DED54BB2C3A7}" name="reported_production" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{D1ECD513-C00E-5A41-8FCD-5B5994F74BDB}" name="production_date_original" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{16C1B018-C17F-1D42-9D20-14601B26CA45}" name="production_date_current" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CF19F16F-E593-1846-973E-64DBF9B072F7}" name="production_reported" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{7532BFA3-1489-6548-843B-B432F7653BCB}" name="note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7564,9 +7607,10 @@
     <col min="7" max="7" width="22.83203125" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="29.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="146" t="s">
         <v>2</v>
       </c>
@@ -7594,7 +7638,9 @@
       <c r="I1" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="337"/>
+      <c r="J1" s="153" t="s">
+        <v>1307</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="152" t="s">
@@ -7620,7 +7666,7 @@
       <c r="I2" s="337">
         <v>17646</v>
       </c>
-      <c r="J2" s="337"/>
+      <c r="J2" s="345"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="105" t="s">
@@ -7648,7 +7694,7 @@
       <c r="I3" s="124">
         <v>50339</v>
       </c>
-      <c r="J3" s="337"/>
+      <c r="J3" s="345"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="105" t="s">
@@ -7676,7 +7722,7 @@
       <c r="I4" s="124">
         <v>15411</v>
       </c>
-      <c r="J4" s="337"/>
+      <c r="J4" s="345"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="105" t="s">
@@ -7732,7 +7778,7 @@
         <v>46203</v>
       </c>
       <c r="I6" s="161"/>
-      <c r="J6" s="124"/>
+      <c r="J6" s="161"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="163" t="s">
@@ -7805,14 +7851,13 @@
       </c>
       <c r="F9" s="340"/>
       <c r="G9" s="164">
-        <v>41535</v>
+        <v>45657</v>
       </c>
       <c r="H9" s="164">
-        <v>41535</v>
+        <v>45657</v>
       </c>
       <c r="I9" s="124">
-        <f>250000/9</f>
-        <v>27777.777777777777</v>
+        <v>32192</v>
       </c>
       <c r="J9" s="161"/>
     </row>
@@ -7827,22 +7872,24 @@
         <v>99</v>
       </c>
       <c r="D10" s="163" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E10" s="163" t="s">
         <v>61</v>
       </c>
       <c r="F10" s="340"/>
       <c r="G10" s="164">
-        <v>45355</v>
+        <v>45657</v>
       </c>
       <c r="H10" s="164">
-        <v>45355</v>
+        <v>45657</v>
       </c>
       <c r="I10" s="124">
-        <v>100000</v>
-      </c>
-      <c r="J10" s="124"/>
+        <v>32192</v>
+      </c>
+      <c r="J10" s="161" t="s">
+        <v>1308</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="163" t="s">
@@ -7872,7 +7919,7 @@
       <c r="I11" s="161">
         <v>20016</v>
       </c>
-      <c r="J11" s="124"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="163" t="s">
@@ -7998,7 +8045,7 @@
         <v>141</v>
       </c>
       <c r="C16" s="163" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D16" s="163" t="s">
         <v>60</v>
@@ -8016,7 +8063,7 @@
       <c r="I16" s="161">
         <v>1076</v>
       </c>
-      <c r="J16" s="124"/>
+      <c r="J16" s="161"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="163" t="s">
@@ -8044,7 +8091,7 @@
         <v>43440</v>
       </c>
       <c r="I17" s="161"/>
-      <c r="J17" s="124"/>
+      <c r="J17" s="161"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="163" t="s">
@@ -8074,7 +8121,7 @@
       <c r="I18" s="161">
         <v>400</v>
       </c>
-      <c r="J18" s="124"/>
+      <c r="J18" s="161"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="163" t="s">
@@ -8339,7 +8386,7 @@
       <c r="I28" s="124">
         <v>37239</v>
       </c>
-      <c r="J28" s="343"/>
+      <c r="J28" s="161"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="163" t="s">
@@ -8419,7 +8466,7 @@
       <c r="I31" s="343">
         <v>73662.5</v>
       </c>
-      <c r="J31" s="124"/>
+      <c r="J31" s="161"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="163" t="s">
@@ -8449,7 +8496,7 @@
       <c r="I32" s="161">
         <v>4760</v>
       </c>
-      <c r="J32" s="124"/>
+      <c r="J32" s="161"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="163" t="s">
@@ -8475,7 +8522,7 @@
         <v>45261</v>
       </c>
       <c r="I33" s="124"/>
-      <c r="J33" s="124"/>
+      <c r="J33" s="161"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="163" t="s">
@@ -8497,7 +8544,7 @@
       <c r="G34" s="105"/>
       <c r="H34" s="105"/>
       <c r="I34" s="124"/>
-      <c r="J34" s="343"/>
+      <c r="J34" s="161"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="163" t="s">
@@ -8527,7 +8574,7 @@
       <c r="I35" s="124">
         <v>83195</v>
       </c>
-      <c r="J35" s="343"/>
+      <c r="J35" s="161"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="163" t="s">
@@ -8557,7 +8604,7 @@
       <c r="I36" s="124">
         <v>62577.5</v>
       </c>
-      <c r="J36" s="343"/>
+      <c r="J36" s="161"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="163" t="s">
@@ -8613,7 +8660,7 @@
       <c r="I38" s="124">
         <v>50444</v>
       </c>
-      <c r="J38" s="124"/>
+      <c r="J38" s="161"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="163" t="s">
@@ -8639,7 +8686,7 @@
       </c>
       <c r="H39" s="163"/>
       <c r="I39" s="161"/>
-      <c r="J39" s="124"/>
+      <c r="J39" s="161"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="163" t="s">
@@ -8717,7 +8764,7 @@
       <c r="I42" s="337">
         <v>16874</v>
       </c>
-      <c r="J42" s="124"/>
+      <c r="J42" s="161"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="152" t="s">
@@ -8727,7 +8774,7 @@
         <v>265</v>
       </c>
       <c r="C43" s="152" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D43" s="152" t="s">
         <v>60</v>
@@ -8743,7 +8790,7 @@
       <c r="I43" s="337">
         <v>2117</v>
       </c>
-      <c r="J43" s="124"/>
+      <c r="J43" s="161"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="152" t="s">
@@ -8753,7 +8800,7 @@
         <v>265</v>
       </c>
       <c r="C44" s="152" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D44" s="152" t="s">
         <v>60</v>
@@ -8779,7 +8826,7 @@
         <v>265</v>
       </c>
       <c r="C45" s="152" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D45" s="152" t="s">
         <v>60</v>
@@ -8953,7 +9000,7 @@
       <c r="I51" s="124">
         <v>20135</v>
       </c>
-      <c r="J51" s="124"/>
+      <c r="J51" s="161"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="163" t="s">
@@ -9008,7 +9055,7 @@
         <f>67243+12264</f>
         <v>79507</v>
       </c>
-      <c r="J53" s="124"/>
+      <c r="J53" s="161"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="105" t="s">
@@ -9032,7 +9079,7 @@
       </c>
       <c r="H54" s="105"/>
       <c r="I54" s="124"/>
-      <c r="J54" s="124"/>
+      <c r="J54" s="161"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="163" t="s">
@@ -9060,7 +9107,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="163" t="s">
-        <v>1084</v>
+        <v>613</v>
       </c>
       <c r="B56" s="163" t="s">
         <v>265</v>
@@ -9080,7 +9127,7 @@
       <c r="I56" s="161">
         <v>33335</v>
       </c>
-      <c r="J56" s="124"/>
+      <c r="J56" s="161"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="163" t="s">
@@ -9108,7 +9155,7 @@
       <c r="I57" s="124">
         <v>9653</v>
       </c>
-      <c r="J57" s="124"/>
+      <c r="J57" s="161"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="163" t="s">
@@ -9182,7 +9229,7 @@
       <c r="G60" s="163"/>
       <c r="H60" s="163"/>
       <c r="I60" s="161"/>
-      <c r="J60" s="124"/>
+      <c r="J60" s="161"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="163" t="s">
@@ -9210,7 +9257,7 @@
       <c r="I61" s="124">
         <v>49264</v>
       </c>
-      <c r="J61" s="124"/>
+      <c r="J61" s="161"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="163" t="s">
@@ -9238,7 +9285,7 @@
         <v>45108</v>
       </c>
       <c r="I62" s="124"/>
-      <c r="J62" s="124"/>
+      <c r="J62" s="161"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="163" t="s">
@@ -9268,7 +9315,7 @@
       <c r="I63" s="124">
         <v>3734</v>
       </c>
-      <c r="J63" s="124"/>
+      <c r="J63" s="161"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="163" t="s">
@@ -9296,7 +9343,7 @@
         <v>44502</v>
       </c>
       <c r="I64" s="124"/>
-      <c r="J64" s="124"/>
+      <c r="J64" s="161"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="163" t="s">
@@ -9318,7 +9365,7 @@
       <c r="G65" s="105"/>
       <c r="H65" s="105"/>
       <c r="I65" s="124"/>
-      <c r="J65" s="124"/>
+      <c r="J65" s="161"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="163" t="s">
@@ -9346,7 +9393,7 @@
         <v>46508</v>
       </c>
       <c r="I66" s="124"/>
-      <c r="J66" s="124"/>
+      <c r="J66" s="161"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="163" t="s">
@@ -9374,7 +9421,7 @@
       <c r="I67" s="124">
         <v>42533</v>
       </c>
-      <c r="J67" s="124"/>
+      <c r="J67" s="161"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="163" t="s">
@@ -9402,7 +9449,7 @@
       <c r="I68" s="124">
         <v>15433</v>
       </c>
-      <c r="J68" s="124"/>
+      <c r="J68" s="161"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="163" t="s">
@@ -9430,11 +9477,11 @@
       <c r="I69" s="124">
         <v>24008</v>
       </c>
-      <c r="J69" s="124"/>
+      <c r="J69" s="161"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="163" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B70" s="163" t="s">
         <v>265</v>
@@ -9454,11 +9501,11 @@
       <c r="I70" s="124">
         <v>23534</v>
       </c>
-      <c r="J70" s="124"/>
+      <c r="J70" s="161"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="163" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B71" s="163" t="s">
         <v>265</v>
@@ -9476,11 +9523,11 @@
       <c r="I71" s="161">
         <v>5000</v>
       </c>
-      <c r="J71" s="124"/>
+      <c r="J71" s="161"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="163" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B72" s="163" t="s">
         <v>182</v>
@@ -9506,7 +9553,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="163" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B73" s="163" t="s">
         <v>357</v>
@@ -9529,8 +9576,8 @@
       <c r="J73" s="161"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" s="183" t="s">
-        <v>703</v>
+      <c r="A74" s="163" t="s">
+        <v>652</v>
       </c>
       <c r="B74" s="183" t="s">
         <v>704</v>
@@ -9556,7 +9603,7 @@
       <c r="I74" s="124">
         <v>50000</v>
       </c>
-      <c r="J74" s="124"/>
+      <c r="J74" s="161"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="163" t="s">
@@ -9586,7 +9633,7 @@
       <c r="I75" s="161">
         <v>14287</v>
       </c>
-      <c r="J75" s="124"/>
+      <c r="J75" s="161"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="163" t="s">
@@ -9662,7 +9709,7 @@
       <c r="I78" s="124">
         <v>206097</v>
       </c>
-      <c r="J78" s="124"/>
+      <c r="J78" s="161"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="163" t="s">
@@ -9903,7 +9950,7 @@
       <c r="I87" s="124">
         <v>85654</v>
       </c>
-      <c r="J87" s="124"/>
+      <c r="J87" s="161"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="163" t="s">
@@ -10193,11 +10240,11 @@
         <v>657</v>
       </c>
       <c r="D4" s="303" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E4" s="304"/>
       <c r="F4" s="305" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>635</v>
@@ -10243,7 +10290,7 @@
         <v>668</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E5" s="308"/>
       <c r="F5" s="58"/>
@@ -10289,11 +10336,11 @@
         <v>657</v>
       </c>
       <c r="D6" s="303" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E6" s="304"/>
       <c r="F6" s="309" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>635</v>
@@ -10339,11 +10386,11 @@
         <v>668</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E7" s="308"/>
       <c r="F7" s="309" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>635</v>
@@ -10389,7 +10436,7 @@
         <v>1083</v>
       </c>
       <c r="D8" s="314" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E8" s="315"/>
       <c r="F8" s="58"/>
@@ -10426,11 +10473,11 @@
         <v>653</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E9" s="64"/>
       <c r="F9" s="309" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G9" s="58" t="s">
         <v>635</v>
@@ -10478,7 +10525,7 @@
         <v>668</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E10" s="308"/>
       <c r="F10" s="58"/>
@@ -10518,7 +10565,7 @@
         <v>668</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E11" s="308"/>
       <c r="F11" s="309" t="s">
@@ -10553,11 +10600,11 @@
         <v>1083</v>
       </c>
       <c r="D12" s="314" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E12" s="315"/>
       <c r="F12" s="309" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>635</v>
@@ -10592,7 +10639,7 @@
         <v>663</v>
       </c>
       <c r="D13" s="319" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E13" s="320"/>
       <c r="F13" s="58"/>
@@ -10629,7 +10676,7 @@
         <v>653</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E14" s="64"/>
       <c r="F14" s="58"/>
@@ -10662,7 +10709,7 @@
         <v>653</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="58"/>
@@ -10693,7 +10740,7 @@
         <v>663</v>
       </c>
       <c r="D16" s="320" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E16" s="320"/>
       <c r="F16" s="58"/>
@@ -10720,11 +10767,11 @@
         <v>653</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E17" s="64"/>
       <c r="F17" s="309" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>635</v>
@@ -10761,7 +10808,7 @@
         <v>663</v>
       </c>
       <c r="D18" s="319" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E18" s="320"/>
       <c r="F18" s="58"/>
@@ -10790,7 +10837,7 @@
         <v>653</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E19" s="64"/>
       <c r="F19" s="58"/>
@@ -10821,7 +10868,7 @@
         <v>653</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E20" s="64"/>
       <c r="F20" s="58"/>
@@ -10848,7 +10895,7 @@
         <v>663</v>
       </c>
       <c r="D21" s="319" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="E21" s="320"/>
       <c r="F21" s="58"/>
@@ -10877,7 +10924,7 @@
         <v>668</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E22" s="308"/>
       <c r="F22" s="58"/>
@@ -10912,11 +10959,11 @@
         <v>668</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E23" s="308"/>
       <c r="F23" s="309" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G23" s="58" t="s">
         <v>635</v>
@@ -10946,13 +10993,13 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B24" s="57" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C24" s="307" t="s">
         <v>668</v>
       </c>
       <c r="D24" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E24" s="58"/>
       <c r="F24" s="58" t="s">
@@ -10991,7 +11038,7 @@
         <v>668</v>
       </c>
       <c r="D25" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E25" s="58"/>
       <c r="F25" s="58" t="s">
@@ -11048,7 +11095,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B29" s="8" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -11057,7 +11104,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B30" s="319" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C30" s="319"/>
       <c r="D30" s="319"/>
@@ -11066,7 +11113,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B31" s="303" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C31" s="303"/>
       <c r="D31" s="304"/>
@@ -11075,7 +11122,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B32" s="314" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C32" s="314"/>
       <c r="D32" s="314"/>
@@ -11084,7 +11131,7 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="27" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
@@ -11098,17 +11145,17 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
@@ -11311,7 +11358,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="297"/>
@@ -11348,10 +11395,10 @@
         <v>1076</v>
       </c>
       <c r="C4" s="323" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D4" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E4" s="58"/>
       <c r="F4" s="58"/>
@@ -11375,7 +11422,7 @@
         <v>215</v>
       </c>
       <c r="U4" s="262" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="V4" s="326">
         <f>SUMIF(B4:B13, "Douai ", R4:R13)</f>
@@ -11392,10 +11439,10 @@
         <v>1076</v>
       </c>
       <c r="C5" s="323" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E5" s="58"/>
       <c r="F5" s="58"/>
@@ -11419,7 +11466,7 @@
         <v>4081</v>
       </c>
       <c r="U5" s="262" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="V5" s="326">
         <f>SUMIF(B4:B13, "Batilly", R4:R13)</f>
@@ -11433,13 +11480,13 @@
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="57"/>
       <c r="B6" s="262" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C6" s="262" t="s">
         <v>1130</v>
       </c>
-      <c r="C6" s="262" t="s">
-        <v>1131</v>
-      </c>
       <c r="D6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E6" s="58"/>
       <c r="F6" s="58"/>
@@ -11459,7 +11506,7 @@
         <v>13349</v>
       </c>
       <c r="U6" s="262" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="V6" s="326">
         <f>SUMIF(B4:B13, "Flins", R4:R13)</f>
@@ -11479,7 +11526,7 @@
         <v>1071</v>
       </c>
       <c r="D7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E7" s="58">
         <v>15</v>
@@ -11527,7 +11574,7 @@
         <v>11184</v>
       </c>
       <c r="U7" s="262" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="V7" s="326">
         <f>SUMIF(B5:B14, "Sandouville", R5:R14)</f>
@@ -11547,7 +11594,7 @@
         <v>1071</v>
       </c>
       <c r="D8" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E8" s="58"/>
       <c r="F8" s="58"/>
@@ -11575,13 +11622,13 @@
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="57"/>
       <c r="B9" s="262" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C9" s="324" t="s">
         <v>1134</v>
       </c>
-      <c r="C9" s="324" t="s">
-        <v>1135</v>
-      </c>
       <c r="D9" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E9" s="58"/>
       <c r="F9" s="58"/>
@@ -11625,13 +11672,13 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="57"/>
       <c r="B10" s="262" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C10" s="323" t="s">
         <v>1130</v>
       </c>
-      <c r="C10" s="323" t="s">
-        <v>1131</v>
-      </c>
       <c r="D10" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E10" s="58"/>
       <c r="F10" s="58"/>
@@ -11669,13 +11716,13 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="57"/>
       <c r="B11" s="262" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C11" s="324" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D11" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E11" s="58"/>
       <c r="F11" s="58"/>
@@ -11700,13 +11747,13 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="57"/>
       <c r="B12" s="262" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C12" s="324" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D12" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E12" s="58"/>
       <c r="F12" s="58"/>
@@ -11731,13 +11778,13 @@
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="57"/>
       <c r="B13" s="262" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C13" s="325" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D13" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E13" s="58"/>
       <c r="F13" s="58"/>
@@ -11783,7 +11830,7 @@
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G22" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -11910,13 +11957,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="332" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B3" s="332" t="s">
         <v>1142</v>
       </c>
-      <c r="B3" s="332" t="s">
+      <c r="C3" s="330" t="s">
         <v>1143</v>
-      </c>
-      <c r="C3" s="330" t="s">
-        <v>1144</v>
       </c>
       <c r="D3" s="333"/>
       <c r="E3" s="333"/>
@@ -11944,7 +11991,7 @@
         <v>940</v>
       </c>
       <c r="C4" s="330" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D4" s="333"/>
       <c r="E4" s="333"/>
@@ -11967,10 +12014,10 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="332"/>
       <c r="B5" s="332" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C5" s="330" t="s">
         <v>1146</v>
-      </c>
-      <c r="C5" s="330" t="s">
-        <v>1147</v>
       </c>
       <c r="D5" s="333"/>
       <c r="E5" s="333"/>
@@ -12000,7 +12047,7 @@
       <c r="A6" s="334"/>
       <c r="B6" s="332"/>
       <c r="C6" s="330" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D6" s="333"/>
       <c r="E6" s="333"/>
@@ -12037,10 +12084,10 @@
         <v>212</v>
       </c>
       <c r="B7" s="332" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C7" s="330" t="s">
         <v>1149</v>
-      </c>
-      <c r="C7" s="330" t="s">
-        <v>1150</v>
       </c>
       <c r="D7" s="333"/>
       <c r="E7" s="333"/>
@@ -12070,7 +12117,7 @@
       <c r="A8" s="332"/>
       <c r="B8" s="332"/>
       <c r="C8" s="330" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D8" s="333"/>
       <c r="E8" s="333"/>
@@ -12102,7 +12149,7 @@
       <c r="A9" s="332"/>
       <c r="B9" s="332"/>
       <c r="C9" s="330" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D9" s="333"/>
       <c r="E9" s="333"/>
@@ -12138,7 +12185,7 @@
         <v>934</v>
       </c>
       <c r="C10" s="330" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D10" s="333"/>
       <c r="E10" s="333"/>
@@ -12166,7 +12213,7 @@
         <v>920</v>
       </c>
       <c r="C11" s="330" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D11" s="333"/>
       <c r="E11" s="333"/>
@@ -12200,7 +12247,7 @@
       <c r="A12" s="334"/>
       <c r="B12" s="332"/>
       <c r="C12" s="330" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D12" s="333"/>
       <c r="E12" s="333"/>
@@ -12232,7 +12279,7 @@
         <v>934</v>
       </c>
       <c r="C13" s="330" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D13" s="333"/>
       <c r="E13" s="333"/>
@@ -12258,13 +12305,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="332" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B14" s="332" t="s">
         <v>1157</v>
       </c>
-      <c r="B14" s="332" t="s">
+      <c r="C14" s="330" t="s">
         <v>1158</v>
-      </c>
-      <c r="C14" s="330" t="s">
-        <v>1159</v>
       </c>
       <c r="D14" s="333"/>
       <c r="E14" s="333"/>
@@ -12296,7 +12343,7 @@
       <c r="A15" s="332"/>
       <c r="B15" s="332"/>
       <c r="C15" s="330" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D15" s="333"/>
       <c r="E15" s="333"/>
@@ -12328,7 +12375,7 @@
         <v>934</v>
       </c>
       <c r="C16" s="330" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D16" s="333"/>
       <c r="E16" s="333"/>
@@ -12354,7 +12401,7 @@
         <v>920</v>
       </c>
       <c r="C17" s="330" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D17" s="333"/>
       <c r="E17" s="333"/>
@@ -12378,7 +12425,7 @@
       <c r="A18" s="332"/>
       <c r="B18" s="332"/>
       <c r="C18" s="330" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D18" s="333"/>
       <c r="E18" s="333"/>
@@ -12402,7 +12449,7 @@
       <c r="A19" s="332"/>
       <c r="B19" s="332"/>
       <c r="C19" s="330" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D19" s="333"/>
       <c r="E19" s="333"/>
@@ -12434,7 +12481,7 @@
       <c r="A20" s="332"/>
       <c r="B20" s="332"/>
       <c r="C20" s="330" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D20" s="333"/>
       <c r="E20" s="333"/>
@@ -12458,7 +12505,7 @@
       <c r="A21" s="332"/>
       <c r="B21" s="332"/>
       <c r="C21" s="330" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D21" s="333"/>
       <c r="E21" s="333"/>
@@ -12490,7 +12537,7 @@
       <c r="A22" s="334"/>
       <c r="B22" s="332"/>
       <c r="C22" s="330" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D22" s="333"/>
       <c r="E22" s="333"/>
@@ -12522,13 +12569,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="334" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B23" s="332" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C23" s="330" t="s">
         <v>1168</v>
-      </c>
-      <c r="B23" s="332" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C23" s="330" t="s">
-        <v>1169</v>
       </c>
       <c r="D23" s="333"/>
       <c r="E23" s="333">
@@ -12562,7 +12609,7 @@
         <v>940</v>
       </c>
       <c r="C24" s="330" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D24" s="333"/>
       <c r="E24" s="333"/>
@@ -12590,7 +12637,7 @@
       <c r="A25" s="332"/>
       <c r="B25" s="332"/>
       <c r="C25" s="330" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D25" s="333">
         <v>395</v>
@@ -12644,7 +12691,7 @@
         <v>934</v>
       </c>
       <c r="C26" s="330" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D26" s="333"/>
       <c r="E26" s="333">
@@ -12684,7 +12731,7 @@
       <c r="A27" s="332"/>
       <c r="B27" s="332"/>
       <c r="C27" s="330" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D27" s="333"/>
       <c r="E27" s="333"/>
@@ -12708,7 +12755,7 @@
       <c r="A28" s="332"/>
       <c r="B28" s="332"/>
       <c r="C28" s="330" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D28" s="333"/>
       <c r="E28" s="333"/>
@@ -12734,7 +12781,7 @@
       <c r="A29" s="332"/>
       <c r="B29" s="332"/>
       <c r="C29" s="330" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D29" s="333">
         <v>356</v>
@@ -12786,7 +12833,7 @@
       <c r="A30" s="332"/>
       <c r="B30" s="332"/>
       <c r="C30" s="330" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D30" s="333"/>
       <c r="E30" s="333"/>
@@ -12816,7 +12863,7 @@
       <c r="A31" s="332"/>
       <c r="B31" s="332"/>
       <c r="C31" s="330" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D31" s="333"/>
       <c r="E31" s="333"/>
@@ -12841,10 +12888,10 @@
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="332"/>
       <c r="B32" s="332" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C32" s="330" t="s">
         <v>1119</v>
-      </c>
-      <c r="C32" s="330" t="s">
-        <v>1120</v>
       </c>
       <c r="D32" s="333"/>
       <c r="E32" s="333"/>
@@ -12872,7 +12919,7 @@
       <c r="A33" s="332"/>
       <c r="B33" s="332"/>
       <c r="C33" s="330" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D33" s="333"/>
       <c r="E33" s="333"/>
@@ -12900,7 +12947,7 @@
       <c r="A34" s="332"/>
       <c r="B34" s="332"/>
       <c r="C34" s="330" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D34" s="333"/>
       <c r="E34" s="333"/>
@@ -12924,7 +12971,7 @@
       <c r="A35" s="332"/>
       <c r="B35" s="332"/>
       <c r="C35" s="330" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D35" s="333">
         <v>15</v>
@@ -12976,7 +13023,7 @@
       <c r="A36" s="332"/>
       <c r="B36" s="332"/>
       <c r="C36" s="330" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D36" s="333"/>
       <c r="E36" s="333"/>
@@ -13002,7 +13049,7 @@
       <c r="A37" s="332"/>
       <c r="B37" s="332"/>
       <c r="C37" s="330" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D37" s="333"/>
       <c r="E37" s="333"/>
@@ -13038,7 +13085,7 @@
       <c r="A38" s="332"/>
       <c r="B38" s="332"/>
       <c r="C38" s="330" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D38" s="333"/>
       <c r="E38" s="333"/>
@@ -13068,7 +13115,7 @@
       <c r="A39" s="332"/>
       <c r="B39" s="332"/>
       <c r="C39" s="330" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D39" s="333"/>
       <c r="E39" s="333"/>
@@ -13094,7 +13141,7 @@
       <c r="A40" s="332"/>
       <c r="B40" s="332"/>
       <c r="C40" s="330" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D40" s="333"/>
       <c r="E40" s="333"/>
@@ -13120,7 +13167,7 @@
       <c r="A41" s="332"/>
       <c r="B41" s="332"/>
       <c r="C41" s="330" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D41" s="333"/>
       <c r="E41" s="333"/>
@@ -13170,7 +13217,7 @@
         <v>613</v>
       </c>
       <c r="C42" s="330" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D42" s="333"/>
       <c r="E42" s="333"/>
@@ -13202,7 +13249,7 @@
       <c r="A43" s="332"/>
       <c r="B43" s="332"/>
       <c r="C43" s="330" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D43" s="333"/>
       <c r="E43" s="333"/>
@@ -13234,7 +13281,7 @@
       <c r="A44" s="332"/>
       <c r="B44" s="332"/>
       <c r="C44" s="330" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D44" s="333"/>
       <c r="E44" s="333"/>
@@ -13266,7 +13313,7 @@
       <c r="A45" s="332"/>
       <c r="B45" s="332"/>
       <c r="C45" s="330" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D45" s="333"/>
       <c r="E45" s="333"/>
@@ -13298,7 +13345,7 @@
       <c r="A46" s="332"/>
       <c r="B46" s="332"/>
       <c r="C46" s="330" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D46" s="333"/>
       <c r="E46" s="333"/>
@@ -13332,7 +13379,7 @@
       <c r="A47" s="332"/>
       <c r="B47" s="332"/>
       <c r="C47" s="330" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D47" s="333"/>
       <c r="E47" s="333"/>
@@ -13366,7 +13413,7 @@
       <c r="A48" s="332"/>
       <c r="B48" s="332"/>
       <c r="C48" s="330" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D48" s="333"/>
       <c r="E48" s="333"/>
@@ -13394,7 +13441,7 @@
       <c r="A49" s="332"/>
       <c r="B49" s="332"/>
       <c r="C49" s="330" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D49" s="333"/>
       <c r="E49" s="333"/>
@@ -13422,7 +13469,7 @@
       <c r="A50" s="332"/>
       <c r="B50" s="332"/>
       <c r="C50" s="330" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D50" s="333"/>
       <c r="E50" s="333"/>
@@ -13454,7 +13501,7 @@
       <c r="A51" s="332"/>
       <c r="B51" s="332"/>
       <c r="C51" s="330" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D51" s="333"/>
       <c r="E51" s="333"/>
@@ -13488,7 +13535,7 @@
       <c r="A52" s="332"/>
       <c r="B52" s="332"/>
       <c r="C52" s="330" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D52" s="333"/>
       <c r="E52" s="333"/>
@@ -13518,7 +13565,7 @@
       <c r="A53" s="332"/>
       <c r="B53" s="332"/>
       <c r="C53" s="330" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D53" s="333"/>
       <c r="E53" s="333"/>
@@ -13546,7 +13593,7 @@
       <c r="A54" s="332"/>
       <c r="B54" s="332"/>
       <c r="C54" s="330" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D54" s="333"/>
       <c r="E54" s="333"/>
@@ -13570,7 +13617,7 @@
       <c r="A55" s="332"/>
       <c r="B55" s="332"/>
       <c r="C55" s="330" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D55" s="333"/>
       <c r="E55" s="333"/>
@@ -13604,7 +13651,7 @@
       <c r="A56" s="332"/>
       <c r="B56" s="332"/>
       <c r="C56" s="330" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D56" s="333"/>
       <c r="E56" s="333"/>
@@ -13630,7 +13677,7 @@
       <c r="A57" s="332"/>
       <c r="B57" s="332"/>
       <c r="C57" s="330" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D57" s="333"/>
       <c r="E57" s="333"/>
@@ -13658,7 +13705,7 @@
       <c r="A58" s="332"/>
       <c r="B58" s="332"/>
       <c r="C58" s="330" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D58" s="333"/>
       <c r="E58" s="333"/>
@@ -13682,7 +13729,7 @@
       <c r="A59" s="332"/>
       <c r="B59" s="332"/>
       <c r="C59" s="330" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D59" s="333"/>
       <c r="E59" s="333"/>
@@ -13708,7 +13755,7 @@
       <c r="A60" s="332"/>
       <c r="B60" s="332"/>
       <c r="C60" s="330" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D60" s="333"/>
       <c r="E60" s="333"/>
@@ -13740,7 +13787,7 @@
       <c r="A61" s="332"/>
       <c r="B61" s="332"/>
       <c r="C61" s="330" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D61" s="333"/>
       <c r="E61" s="333"/>
@@ -13771,10 +13818,10 @@
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="332"/>
       <c r="B62" s="332" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C62" s="330" t="s">
         <v>1138</v>
-      </c>
-      <c r="C62" s="330" t="s">
-        <v>1139</v>
       </c>
       <c r="D62" s="333"/>
       <c r="E62" s="333"/>
@@ -13806,7 +13853,7 @@
       <c r="A63" s="334"/>
       <c r="B63" s="332"/>
       <c r="C63" s="330" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D63" s="333"/>
       <c r="E63" s="333"/>
@@ -14379,10 +14426,10 @@
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="332"/>
       <c r="B80" s="332" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C80" s="330" t="s">
         <v>1178</v>
-      </c>
-      <c r="C80" s="330" t="s">
-        <v>1179</v>
       </c>
       <c r="D80" s="333"/>
       <c r="E80" s="333"/>
@@ -14424,7 +14471,7 @@
         <v>399</v>
       </c>
       <c r="C81" s="330" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D81" s="333"/>
       <c r="E81" s="333"/>
@@ -14448,7 +14495,7 @@
       <c r="A82" s="332"/>
       <c r="B82" s="332"/>
       <c r="C82" s="330" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D82" s="333"/>
       <c r="E82" s="333"/>
@@ -15108,7 +15155,7 @@
         <v>934</v>
       </c>
       <c r="C102" s="330" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D102" s="333"/>
       <c r="E102" s="333"/>
@@ -15134,7 +15181,7 @@
       <c r="A103" s="332"/>
       <c r="B103" s="332"/>
       <c r="C103" s="330" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D103" s="333"/>
       <c r="E103" s="333"/>
@@ -15162,7 +15209,7 @@
         <v>613</v>
       </c>
       <c r="C104" s="330" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D104" s="333"/>
       <c r="E104" s="333"/>
@@ -15192,7 +15239,7 @@
       <c r="A105" s="332"/>
       <c r="B105" s="332"/>
       <c r="C105" s="330" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D105" s="333"/>
       <c r="E105" s="333"/>
@@ -15222,7 +15269,7 @@
       <c r="A106" s="332"/>
       <c r="B106" s="332"/>
       <c r="C106" s="330" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D106" s="333"/>
       <c r="E106" s="333"/>
@@ -15282,7 +15329,7 @@
       <c r="A108" s="332"/>
       <c r="B108" s="332"/>
       <c r="C108" s="330" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D108" s="333"/>
       <c r="E108" s="333"/>
@@ -15305,10 +15352,10 @@
     <row r="109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A109" s="332"/>
       <c r="B109" s="332" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C109" s="330" t="s">
         <v>1188</v>
-      </c>
-      <c r="C109" s="330" t="s">
-        <v>1189</v>
       </c>
       <c r="D109" s="333"/>
       <c r="E109" s="333"/>
@@ -15622,7 +15669,7 @@
       <c r="A119" s="332"/>
       <c r="B119" s="332"/>
       <c r="C119" s="330" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D119" s="333"/>
       <c r="E119" s="333"/>
@@ -15654,7 +15701,7 @@
       <c r="A120" s="332"/>
       <c r="B120" s="332"/>
       <c r="C120" s="330" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D120" s="333"/>
       <c r="E120" s="333"/>
@@ -15684,7 +15731,7 @@
       <c r="A121" s="332"/>
       <c r="B121" s="332"/>
       <c r="C121" s="330" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D121" s="333"/>
       <c r="E121" s="333"/>
@@ -15708,7 +15755,7 @@
       <c r="A122" s="332"/>
       <c r="B122" s="332"/>
       <c r="C122" s="330" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D122" s="333"/>
       <c r="E122" s="333"/>
@@ -15754,7 +15801,7 @@
       <c r="A123" s="332"/>
       <c r="B123" s="332"/>
       <c r="C123" s="330" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D123" s="333"/>
       <c r="E123" s="333"/>
@@ -15788,7 +15835,7 @@
       <c r="A124" s="332"/>
       <c r="B124" s="332"/>
       <c r="C124" s="330" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D124" s="333"/>
       <c r="E124" s="333"/>
@@ -15822,7 +15869,7 @@
       <c r="A125" s="332"/>
       <c r="B125" s="332"/>
       <c r="C125" s="330" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D125" s="333"/>
       <c r="E125" s="333"/>
@@ -15854,7 +15901,7 @@
       <c r="A126" s="332"/>
       <c r="B126" s="332"/>
       <c r="C126" s="330" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D126" s="333"/>
       <c r="E126" s="333"/>
@@ -15882,7 +15929,7 @@
       <c r="A127" s="332"/>
       <c r="B127" s="332"/>
       <c r="C127" s="330" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D127" s="333"/>
       <c r="E127" s="333"/>
@@ -15926,7 +15973,7 @@
       <c r="A128" s="332"/>
       <c r="B128" s="332"/>
       <c r="C128" s="330" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D128" s="333"/>
       <c r="E128" s="333"/>
@@ -15956,7 +16003,7 @@
       <c r="A129" s="332"/>
       <c r="B129" s="332"/>
       <c r="C129" s="330" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D129" s="333"/>
       <c r="E129" s="333"/>
@@ -16000,7 +16047,7 @@
       <c r="A130" s="332"/>
       <c r="B130" s="332"/>
       <c r="C130" s="330" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D130" s="333"/>
       <c r="E130" s="333"/>
@@ -16034,7 +16081,7 @@
       <c r="A131" s="332"/>
       <c r="B131" s="332"/>
       <c r="C131" s="330" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D131" s="333"/>
       <c r="E131" s="333"/>
@@ -16066,7 +16113,7 @@
       <c r="A132" s="332"/>
       <c r="B132" s="332"/>
       <c r="C132" s="330" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D132" s="333"/>
       <c r="E132" s="333"/>
@@ -16094,7 +16141,7 @@
       <c r="A133" s="332"/>
       <c r="B133" s="332"/>
       <c r="C133" s="330" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D133" s="333"/>
       <c r="E133" s="333"/>
@@ -16120,7 +16167,7 @@
       <c r="A134" s="332"/>
       <c r="B134" s="332"/>
       <c r="C134" s="330" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D134" s="333"/>
       <c r="E134" s="333"/>
@@ -16148,7 +16195,7 @@
       <c r="A135" s="332"/>
       <c r="B135" s="332"/>
       <c r="C135" s="330" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D135" s="333"/>
       <c r="E135" s="333"/>
@@ -16176,7 +16223,7 @@
       <c r="A136" s="332"/>
       <c r="B136" s="332"/>
       <c r="C136" s="330" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D136" s="333"/>
       <c r="E136" s="333"/>
@@ -16206,7 +16253,7 @@
       <c r="A137" s="332"/>
       <c r="B137" s="332"/>
       <c r="C137" s="330" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D137" s="333"/>
       <c r="E137" s="333"/>
@@ -16248,7 +16295,7 @@
       <c r="A138" s="332"/>
       <c r="B138" s="332"/>
       <c r="C138" s="330" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D138" s="333"/>
       <c r="E138" s="333"/>
@@ -16272,7 +16319,7 @@
       <c r="A139" s="334"/>
       <c r="B139" s="332"/>
       <c r="C139" s="330" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D139" s="333"/>
       <c r="E139" s="333"/>
@@ -16401,10 +16448,10 @@
         <v>182</v>
       </c>
       <c r="B143" s="332" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C143" s="330" t="s">
         <v>1211</v>
-      </c>
-      <c r="C143" s="330" t="s">
-        <v>1212</v>
       </c>
       <c r="D143" s="333"/>
       <c r="E143" s="333"/>
@@ -16442,7 +16489,7 @@
         <v>934</v>
       </c>
       <c r="C144" s="330" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D144" s="333"/>
       <c r="E144" s="333"/>
@@ -16468,7 +16515,7 @@
       <c r="A145" s="332"/>
       <c r="B145" s="332"/>
       <c r="C145" s="330" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D145" s="333"/>
       <c r="E145" s="333"/>
@@ -16496,7 +16543,7 @@
       <c r="A146" s="332"/>
       <c r="B146" s="332"/>
       <c r="C146" s="330" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D146" s="333"/>
       <c r="E146" s="333"/>
@@ -16528,7 +16575,7 @@
       <c r="A147" s="332"/>
       <c r="B147" s="332"/>
       <c r="C147" s="330" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D147" s="333"/>
       <c r="E147" s="333"/>
@@ -16556,7 +16603,7 @@
         <v>613</v>
       </c>
       <c r="C148" s="330" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D148" s="333"/>
       <c r="E148" s="333"/>
@@ -16584,7 +16631,7 @@
       <c r="A149" s="332"/>
       <c r="B149" s="332"/>
       <c r="C149" s="330" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D149" s="333"/>
       <c r="E149" s="333"/>
@@ -16614,7 +16661,7 @@
       <c r="A150" s="332"/>
       <c r="B150" s="332"/>
       <c r="C150" s="330" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D150" s="333"/>
       <c r="E150" s="333"/>
@@ -16640,7 +16687,7 @@
       <c r="A151" s="332"/>
       <c r="B151" s="332"/>
       <c r="C151" s="330" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D151" s="333"/>
       <c r="E151" s="333"/>
@@ -16672,7 +16719,7 @@
       <c r="A152" s="332"/>
       <c r="B152" s="332"/>
       <c r="C152" s="330" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D152" s="333"/>
       <c r="E152" s="333"/>
@@ -16698,7 +16745,7 @@
       <c r="A153" s="332"/>
       <c r="B153" s="332"/>
       <c r="C153" s="330" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D153" s="333"/>
       <c r="E153" s="333"/>
@@ -16732,7 +16779,7 @@
       <c r="A154" s="332"/>
       <c r="B154" s="332"/>
       <c r="C154" s="330" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D154" s="333"/>
       <c r="E154" s="333"/>
@@ -16764,7 +16811,7 @@
       <c r="A155" s="332"/>
       <c r="B155" s="332"/>
       <c r="C155" s="330" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D155" s="333"/>
       <c r="E155" s="333"/>
@@ -16796,7 +16843,7 @@
       <c r="A156" s="332"/>
       <c r="B156" s="332"/>
       <c r="C156" s="330" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D156" s="333"/>
       <c r="E156" s="333"/>
@@ -16822,7 +16869,7 @@
       <c r="A157" s="332"/>
       <c r="B157" s="332"/>
       <c r="C157" s="330" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D157" s="333"/>
       <c r="E157" s="333"/>
@@ -16848,7 +16895,7 @@
       <c r="A158" s="332"/>
       <c r="B158" s="332"/>
       <c r="C158" s="330" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D158" s="333"/>
       <c r="E158" s="333"/>
@@ -16878,7 +16925,7 @@
       <c r="A159" s="332"/>
       <c r="B159" s="332"/>
       <c r="C159" s="330" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D159" s="333"/>
       <c r="E159" s="333"/>
@@ -16909,10 +16956,10 @@
     <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="332"/>
       <c r="B160" s="332" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C160" s="330" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D160" s="333"/>
       <c r="E160" s="333"/>
@@ -16938,7 +16985,7 @@
         <v>920</v>
       </c>
       <c r="C161" s="330" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D161" s="333"/>
       <c r="E161" s="333"/>
@@ -16962,7 +17009,7 @@
       <c r="A162" s="334"/>
       <c r="B162" s="332"/>
       <c r="C162" s="330" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D162" s="333"/>
       <c r="E162" s="333"/>
@@ -16992,7 +17039,7 @@
         <v>865</v>
       </c>
       <c r="C163" s="330" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D163" s="333"/>
       <c r="E163" s="333"/>
@@ -17034,7 +17081,7 @@
         <v>934</v>
       </c>
       <c r="C164" s="330" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D164" s="333"/>
       <c r="E164" s="333"/>
@@ -17056,13 +17103,13 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A165" s="334" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B165" s="332" t="s">
         <v>934</v>
       </c>
       <c r="C165" s="330" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="D165" s="333">
         <v>755</v>
@@ -17096,7 +17143,7 @@
         <v>399</v>
       </c>
       <c r="C166" s="330" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D166" s="333"/>
       <c r="E166" s="333"/>
@@ -17119,10 +17166,10 @@
     <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="332"/>
       <c r="B167" s="332" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C167" s="330" t="s">
         <v>1237</v>
-      </c>
-      <c r="C167" s="330" t="s">
-        <v>1238</v>
       </c>
       <c r="D167" s="333"/>
       <c r="E167" s="333"/>
@@ -17148,7 +17195,7 @@
         <v>613</v>
       </c>
       <c r="C168" s="330" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D168" s="333"/>
       <c r="E168" s="333"/>
@@ -17172,7 +17219,7 @@
       <c r="A169" s="332"/>
       <c r="B169" s="332"/>
       <c r="C169" s="330" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D169" s="333"/>
       <c r="E169" s="333"/>
@@ -17198,7 +17245,7 @@
       <c r="A170" s="332"/>
       <c r="B170" s="332"/>
       <c r="C170" s="330" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D170" s="333"/>
       <c r="E170" s="333"/>
@@ -17228,7 +17275,7 @@
         <v>920</v>
       </c>
       <c r="C171" s="330" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D171" s="333"/>
       <c r="E171" s="333"/>
@@ -17264,7 +17311,7 @@
       <c r="A172" s="332"/>
       <c r="B172" s="332"/>
       <c r="C172" s="330" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D172" s="333"/>
       <c r="E172" s="333"/>
@@ -17292,7 +17339,7 @@
       <c r="A173" s="332"/>
       <c r="B173" s="332"/>
       <c r="C173" s="330" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D173" s="333"/>
       <c r="E173" s="333"/>
@@ -17320,7 +17367,7 @@
       <c r="A174" s="332"/>
       <c r="B174" s="332"/>
       <c r="C174" s="330" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D174" s="333"/>
       <c r="E174" s="333"/>
@@ -17350,7 +17397,7 @@
       <c r="A175" s="332"/>
       <c r="B175" s="332"/>
       <c r="C175" s="330" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D175" s="333"/>
       <c r="E175" s="333"/>
@@ -17380,7 +17427,7 @@
       <c r="A176" s="334"/>
       <c r="B176" s="332"/>
       <c r="C176" s="330" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D176" s="333"/>
       <c r="E176" s="333"/>
@@ -17414,13 +17461,13 @@
     </row>
     <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" s="332" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B177" s="332" t="s">
         <v>399</v>
       </c>
       <c r="C177" s="330" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D177" s="333"/>
       <c r="E177" s="333"/>
@@ -17444,7 +17491,7 @@
       <c r="A178" s="334"/>
       <c r="B178" s="332"/>
       <c r="C178" s="330" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D178" s="333"/>
       <c r="E178" s="333"/>
@@ -17469,10 +17516,10 @@
         <v>444</v>
       </c>
       <c r="B179" s="332" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C179" s="330" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D179" s="333"/>
       <c r="E179" s="333"/>
@@ -17504,7 +17551,7 @@
       <c r="A180" s="332"/>
       <c r="B180" s="332"/>
       <c r="C180" s="330" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D180" s="333"/>
       <c r="E180" s="333"/>
@@ -17532,7 +17579,7 @@
       <c r="A181" s="332"/>
       <c r="B181" s="332"/>
       <c r="C181" s="330" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D181" s="333"/>
       <c r="E181" s="333"/>
@@ -17572,7 +17619,7 @@
         <v>613</v>
       </c>
       <c r="C182" s="330" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D182" s="333"/>
       <c r="E182" s="333"/>
@@ -17627,10 +17674,10 @@
     <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" s="332"/>
       <c r="B184" s="332" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C184" s="330" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D184" s="333"/>
       <c r="E184" s="333"/>
@@ -17662,7 +17709,7 @@
         <v>920</v>
       </c>
       <c r="C185" s="330" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D185" s="333"/>
       <c r="E185" s="333"/>
@@ -17704,7 +17751,7 @@
       <c r="A186" s="332"/>
       <c r="B186" s="332"/>
       <c r="C186" s="330" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D186" s="333"/>
       <c r="E186" s="333"/>
@@ -17738,7 +17785,7 @@
       <c r="A187" s="332"/>
       <c r="B187" s="332"/>
       <c r="C187" s="330" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D187" s="333"/>
       <c r="E187" s="333"/>
@@ -17782,7 +17829,7 @@
       <c r="A188" s="332"/>
       <c r="B188" s="332"/>
       <c r="C188" s="330" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D188" s="333"/>
       <c r="E188" s="333"/>
@@ -17814,7 +17861,7 @@
       <c r="A189" s="332"/>
       <c r="B189" s="332"/>
       <c r="C189" s="330" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D189" s="333"/>
       <c r="E189" s="333"/>
@@ -17848,7 +17895,7 @@
       <c r="A190" s="332"/>
       <c r="B190" s="332"/>
       <c r="C190" s="330" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D190" s="333"/>
       <c r="E190" s="333"/>
@@ -17872,7 +17919,7 @@
       <c r="A191" s="332"/>
       <c r="B191" s="332"/>
       <c r="C191" s="330" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D191" s="333"/>
       <c r="E191" s="333"/>
@@ -17918,7 +17965,7 @@
       <c r="A192" s="332"/>
       <c r="B192" s="332"/>
       <c r="C192" s="330" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D192" s="333"/>
       <c r="E192" s="333"/>
@@ -17942,7 +17989,7 @@
       <c r="A193" s="334"/>
       <c r="B193" s="332"/>
       <c r="C193" s="330" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D193" s="333"/>
       <c r="E193" s="333"/>
@@ -17982,7 +18029,7 @@
         <v>940</v>
       </c>
       <c r="C194" s="330" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D194" s="333"/>
       <c r="E194" s="333"/>
@@ -18019,10 +18066,10 @@
     <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="334"/>
       <c r="B195" s="332" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C195" s="330" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D195" s="333"/>
       <c r="E195" s="333"/>
@@ -18058,7 +18105,7 @@
         <v>399</v>
       </c>
       <c r="C196" s="330" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D196" s="333"/>
       <c r="E196" s="333"/>
@@ -18092,7 +18139,7 @@
         <v>940</v>
       </c>
       <c r="C197" s="330" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D197" s="333"/>
       <c r="E197" s="333"/>
@@ -18120,7 +18167,7 @@
       <c r="A198" s="332"/>
       <c r="B198" s="332"/>
       <c r="C198" s="330" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D198" s="333"/>
       <c r="E198" s="333"/>
@@ -18154,7 +18201,7 @@
       <c r="A199" s="332"/>
       <c r="B199" s="332"/>
       <c r="C199" s="330" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D199" s="333"/>
       <c r="E199" s="333"/>
@@ -18189,10 +18236,10 @@
     <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="332"/>
       <c r="B200" s="332" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C200" s="330" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D200" s="333"/>
       <c r="E200" s="333"/>
@@ -18220,7 +18267,7 @@
       <c r="A201" s="332"/>
       <c r="B201" s="332"/>
       <c r="C201" s="330" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D201" s="333"/>
       <c r="E201" s="333"/>
@@ -18266,7 +18313,7 @@
       <c r="A202" s="332"/>
       <c r="B202" s="332"/>
       <c r="C202" s="330" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D202" s="333"/>
       <c r="E202" s="333"/>
@@ -18300,7 +18347,7 @@
       <c r="A203" s="332"/>
       <c r="B203" s="332"/>
       <c r="C203" s="330" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D203" s="333"/>
       <c r="E203" s="333"/>
@@ -18332,7 +18379,7 @@
       <c r="A204" s="332"/>
       <c r="B204" s="332"/>
       <c r="C204" s="330" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D204" s="333"/>
       <c r="E204" s="333"/>
@@ -18364,7 +18411,7 @@
       <c r="A205" s="332"/>
       <c r="B205" s="332"/>
       <c r="C205" s="330" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D205" s="333"/>
       <c r="E205" s="333"/>
@@ -18388,7 +18435,7 @@
       <c r="A206" s="332"/>
       <c r="B206" s="332"/>
       <c r="C206" s="330" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D206" s="333"/>
       <c r="E206" s="333"/>
@@ -19021,10 +19068,10 @@
     <row r="226" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A226" s="332"/>
       <c r="B226" s="332" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C226" s="330" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D226" s="333"/>
       <c r="E226" s="333"/>
@@ -19054,7 +19101,7 @@
       <c r="A227" s="332"/>
       <c r="B227" s="332"/>
       <c r="C227" s="330" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D227" s="333"/>
       <c r="E227" s="333"/>
@@ -19086,7 +19133,7 @@
         <v>920</v>
       </c>
       <c r="C228" s="330" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D228" s="333"/>
       <c r="E228" s="333"/>
@@ -19118,7 +19165,7 @@
       <c r="A229" s="332"/>
       <c r="B229" s="332"/>
       <c r="C229" s="330" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D229" s="333"/>
       <c r="E229" s="333"/>
@@ -19150,7 +19197,7 @@
       <c r="A230" s="332"/>
       <c r="B230" s="332"/>
       <c r="C230" s="330" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D230" s="333"/>
       <c r="E230" s="333"/>
@@ -19174,7 +19221,7 @@
       <c r="A231" s="334"/>
       <c r="B231" s="332"/>
       <c r="C231" s="330" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D231" s="333"/>
       <c r="E231" s="333"/>
@@ -19207,10 +19254,10 @@
         <v>603</v>
       </c>
       <c r="B232" s="332" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C232" s="330" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D232" s="333">
         <v>50</v>
@@ -19242,7 +19289,7 @@
       <c r="A233" s="332"/>
       <c r="B233" s="332"/>
       <c r="C233" s="330" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D233" s="333"/>
       <c r="E233" s="333"/>
@@ -19290,7 +19337,7 @@
       <c r="A234" s="332"/>
       <c r="B234" s="332"/>
       <c r="C234" s="330" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D234" s="333"/>
       <c r="E234" s="333"/>
@@ -19328,7 +19375,7 @@
       <c r="A235" s="332"/>
       <c r="B235" s="332"/>
       <c r="C235" s="330" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D235" s="333"/>
       <c r="E235" s="333"/>
@@ -19366,7 +19413,7 @@
       <c r="A236" s="334"/>
       <c r="B236" s="332"/>
       <c r="C236" s="330" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D236" s="333"/>
       <c r="E236" s="333"/>
@@ -19477,10 +19524,10 @@
     <row r="239" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A239" s="332"/>
       <c r="B239" s="332" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C239" s="330" t="s">
         <v>1287</v>
-      </c>
-      <c r="C239" s="330" t="s">
-        <v>1288</v>
       </c>
       <c r="D239" s="333"/>
       <c r="E239" s="333"/>
@@ -19508,7 +19555,7 @@
       <c r="A240" s="332"/>
       <c r="B240" s="332"/>
       <c r="C240" s="330" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D240" s="333"/>
       <c r="E240" s="333"/>
@@ -19544,7 +19591,7 @@
       <c r="A241" s="332"/>
       <c r="B241" s="332"/>
       <c r="C241" s="330" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D241" s="333"/>
       <c r="E241" s="333"/>
@@ -19580,7 +19627,7 @@
         <v>940</v>
       </c>
       <c r="C242" s="330" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D242" s="333"/>
       <c r="E242" s="333"/>
@@ -19608,7 +19655,7 @@
         <v>934</v>
       </c>
       <c r="C243" s="330" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D243" s="333"/>
       <c r="E243" s="333"/>
@@ -19636,7 +19683,7 @@
       <c r="A244" s="332"/>
       <c r="B244" s="332"/>
       <c r="C244" s="330" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D244" s="333"/>
       <c r="E244" s="333"/>
@@ -19659,10 +19706,10 @@
     <row r="245" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A245" s="332"/>
       <c r="B245" s="332" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C245" s="330" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D245" s="333">
         <v>12</v>
@@ -19716,7 +19763,7 @@
         <v>613</v>
       </c>
       <c r="C246" s="330" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D246" s="333"/>
       <c r="E246" s="333"/>
@@ -19740,7 +19787,7 @@
       <c r="A247" s="332"/>
       <c r="B247" s="332"/>
       <c r="C247" s="330" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D247" s="333"/>
       <c r="E247" s="333"/>
@@ -19774,7 +19821,7 @@
       <c r="A248" s="332"/>
       <c r="B248" s="332"/>
       <c r="C248" s="330" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D248" s="333"/>
       <c r="E248" s="333"/>
@@ -19805,10 +19852,10 @@
     <row r="249" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A249" s="332"/>
       <c r="B249" s="332" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C249" s="330" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D249" s="333"/>
       <c r="E249" s="333"/>
@@ -19838,7 +19885,7 @@
       <c r="A250" s="332"/>
       <c r="B250" s="332"/>
       <c r="C250" s="330" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D250" s="333"/>
       <c r="E250" s="333"/>
@@ -19870,7 +19917,7 @@
       <c r="A251" s="332"/>
       <c r="B251" s="332"/>
       <c r="C251" s="330" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D251" s="333"/>
       <c r="E251" s="333"/>
@@ -19902,7 +19949,7 @@
       <c r="A252" s="332"/>
       <c r="B252" s="332"/>
       <c r="C252" s="330" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D252" s="333"/>
       <c r="E252" s="333"/>
@@ -19938,7 +19985,7 @@
       <c r="A253" s="332"/>
       <c r="B253" s="332"/>
       <c r="C253" s="330" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D253" s="333"/>
       <c r="E253" s="333"/>
@@ -19974,7 +20021,7 @@
       <c r="A254" s="332"/>
       <c r="B254" s="332"/>
       <c r="C254" s="330" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D254" s="333"/>
       <c r="E254" s="333"/>
@@ -20006,7 +20053,7 @@
         <v>920</v>
       </c>
       <c r="C255" s="330" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D255" s="333"/>
       <c r="E255" s="333"/>
@@ -20040,7 +20087,7 @@
       <c r="A256" s="332"/>
       <c r="B256" s="332"/>
       <c r="C256" s="330" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D256" s="333"/>
       <c r="E256" s="333"/>
@@ -20066,7 +20113,7 @@
       <c r="A257" s="334"/>
       <c r="B257" s="332"/>
       <c r="C257" s="330" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D257" s="333"/>
       <c r="E257" s="333"/>
@@ -20092,7 +20139,7 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" s="335" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B258" s="335"/>
       <c r="C258" s="335"/>
@@ -34570,19 +34617,19 @@
   <dimension ref="A1:Y80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.6640625" customWidth="1"/>
     <col min="4" max="4" width="36.1640625" customWidth="1"/>
-    <col min="5" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="7.6640625" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="9.1640625" customWidth="1" outlineLevel="1"/>
     <col min="12" max="17" width="10.1640625" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="10.1640625" style="10" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.33203125" style="10" customWidth="1" outlineLevel="1"/>
     <col min="19" max="21" width="10.1640625" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37921,6 +37968,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
@@ -37956,15 +38012,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
@@ -37985,6 +38032,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -37999,12 +38054,4 @@
     <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC9A6C6-8B26-7E42-B12B-7D3A3A89B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E779E6AF-CDA2-7145-9181-E5F07BC4AF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="6" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -9245,7 +9245,7 @@
         <v>143</v>
       </c>
       <c r="E61" s="163" t="s">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="F61" s="342"/>
       <c r="G61" s="126">
@@ -37968,15 +37968,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
@@ -38012,6 +38003,15 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
@@ -38032,14 +38032,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -38054,4 +38046,12 @@
     <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC27236-8C53-544F-BBA6-AA8577DDF84C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37748B45-1967-6F4B-B76A-A6C23515FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="2" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Audi" sheetId="5" r:id="rId6"/>
     <sheet name="Volkswagen" sheetId="19" r:id="rId7"/>
     <sheet name="BMW" sheetId="4" r:id="rId8"/>
-    <sheet name="Mercedes" sheetId="7" r:id="rId9"/>
+    <sheet name="Mercedes Benz" sheetId="7" r:id="rId9"/>
     <sheet name="Stellantis" sheetId="9" r:id="rId10"/>
     <sheet name="Stelantis France" sheetId="13" r:id="rId11"/>
     <sheet name="Renault France" sheetId="14" r:id="rId12"/>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C56" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C55" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -1502,7 +1502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3403" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="1350">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -5597,10 +5597,49 @@
     <t>EQB production in the first phase</t>
   </si>
   <si>
-    <t>Megane E-Tech production starts end 2021</t>
-  </si>
-  <si>
-    <t>Ramping up also for the Scenic BEV by 2024</t>
+    <t>leapmotor T03 production</t>
+  </si>
+  <si>
+    <t>production of the EV Jeep Avenger; Fiat; Alfa Romeo</t>
+  </si>
+  <si>
+    <t>the BEV and Opel Grandland models</t>
+  </si>
+  <si>
+    <t>Megane E-Tech production starts mid-2022; Scenic starts 2024; and the Renault 5</t>
+  </si>
+  <si>
+    <t>Kangoo BEV (van) production begins in 2011</t>
+  </si>
+  <si>
+    <t>Mabuege</t>
+  </si>
+  <si>
+    <t>Original production of the Kangoo</t>
+  </si>
+  <si>
+    <t>Production of new Kangoo van &amp; Nissa</t>
+  </si>
+  <si>
+    <t>v2 Kangoo and some Nissan vans</t>
+  </si>
+  <si>
+    <t>Og production of the Zoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 announcement (inside €1 billion FR investment) of Zoe doubling </t>
+  </si>
+  <si>
+    <t>Flins site transitioning away from Zoe production</t>
+  </si>
+  <si>
+    <t>first production of the BEV Zoe</t>
+  </si>
+  <si>
+    <t>doubling capacity for the Zoe</t>
+  </si>
+  <si>
+    <t>Produces the Master BEV van</t>
   </si>
 </sst>
 </file>
@@ -6228,7 +6267,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="378">
+  <cellXfs count="354">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6727,9 +6766,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6755,46 +6791,17 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7290,7 +7297,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>552970</xdr:colOff>
+      <xdr:colOff>534669</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>8089</xdr:rowOff>
     </xdr:to>
@@ -7335,10 +7342,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J68" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J68" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J68">
-    <sortCondition ref="A1:A68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J67" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J67" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="France"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J67">
+    <sortCondition ref="A1:A67"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="9"/>
@@ -7684,7 +7697,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -7731,33 +7744,33 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="342" t="s">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="341" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="342" t="s">
+      <c r="B2" s="341" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="342" t="s">
+      <c r="C2" s="341" t="s">
         <v>1082</v>
       </c>
-      <c r="D2" s="342" t="s">
+      <c r="D2" s="341" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="342" t="s">
+      <c r="E2" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="343"/>
-      <c r="G2" s="342"/>
-      <c r="H2" s="344">
+      <c r="F2" s="342"/>
+      <c r="G2" s="341"/>
+      <c r="H2" s="343">
         <v>45657</v>
       </c>
-      <c r="I2" s="345">
+      <c r="I2" s="344">
         <v>17646</v>
       </c>
-      <c r="J2" s="337"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J2" s="336"/>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="104" t="s">
         <v>211</v>
       </c>
@@ -7783,9 +7796,9 @@
       <c r="I3" s="123">
         <v>50339</v>
       </c>
-      <c r="J3" s="337"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J3" s="336"/>
+    </row>
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104" t="s">
         <v>211</v>
       </c>
@@ -7811,9 +7824,9 @@
       <c r="I4" s="123">
         <v>15411</v>
       </c>
-      <c r="J4" s="337"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J4" s="336"/>
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104" t="s">
         <v>211</v>
       </c>
@@ -7841,7 +7854,7 @@
       </c>
       <c r="J5" s="160"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="162" t="s">
         <v>253</v>
       </c>
@@ -7869,7 +7882,7 @@
       <c r="I6" s="160"/>
       <c r="J6" s="160"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="162" t="s">
         <v>57</v>
       </c>
@@ -7898,7 +7911,7 @@
       </c>
       <c r="J7" s="160"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="162" t="s">
         <v>57</v>
       </c>
@@ -7926,7 +7939,7 @@
       </c>
       <c r="J8" s="160"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="162" t="s">
         <v>57</v>
       </c>
@@ -7954,7 +7967,7 @@
       </c>
       <c r="J9" s="160"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="162" t="s">
         <v>57</v>
       </c>
@@ -7983,7 +7996,7 @@
       </c>
       <c r="J10" s="160"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="162" t="s">
         <v>57</v>
       </c>
@@ -8015,7 +8028,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="162" t="s">
         <v>57</v>
       </c>
@@ -8042,7 +8055,7 @@
       </c>
       <c r="J12" s="160"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="162" t="s">
         <v>57</v>
       </c>
@@ -8070,7 +8083,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="162" t="s">
         <v>57</v>
       </c>
@@ -8098,7 +8111,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="162" t="s">
         <v>57</v>
       </c>
@@ -8126,7 +8139,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="162" t="s">
         <v>57</v>
       </c>
@@ -8143,7 +8156,7 @@
         <v>61</v>
       </c>
       <c r="F16" s="333"/>
-      <c r="G16" s="344">
+      <c r="G16" s="343">
         <v>43830</v>
       </c>
       <c r="H16" s="331"/>
@@ -8154,7 +8167,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="162" t="s">
         <v>356</v>
       </c>
@@ -8184,7 +8197,7 @@
       </c>
       <c r="J17" s="160"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="162" t="s">
         <v>385</v>
       </c>
@@ -8214,7 +8227,7 @@
       </c>
       <c r="J18" s="160"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="162" t="s">
         <v>399</v>
       </c>
@@ -8242,7 +8255,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="162" t="s">
         <v>1312</v>
       </c>
@@ -8270,7 +8283,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="162" t="s">
         <v>434</v>
       </c>
@@ -8299,7 +8312,7 @@
       </c>
       <c r="J21" s="160"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="162" t="s">
         <v>443</v>
       </c>
@@ -8329,7 +8342,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="162" t="s">
         <v>462</v>
       </c>
@@ -8355,7 +8368,7 @@
       <c r="I23" s="123"/>
       <c r="J23" s="160"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="162" t="s">
         <v>462</v>
       </c>
@@ -8385,7 +8398,7 @@
       </c>
       <c r="J24" s="160"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="162" t="s">
         <v>462</v>
       </c>
@@ -8415,7 +8428,7 @@
       </c>
       <c r="J25" s="160"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="162" t="s">
         <v>462</v>
       </c>
@@ -8445,7 +8458,7 @@
       </c>
       <c r="J26" s="160"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="162" t="s">
         <v>462</v>
       </c>
@@ -8475,7 +8488,7 @@
       </c>
       <c r="J27" s="160"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="162" t="s">
         <v>462</v>
       </c>
@@ -8501,7 +8514,7 @@
       </c>
       <c r="J28" s="160"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="162" t="s">
         <v>462</v>
       </c>
@@ -8525,7 +8538,7 @@
       </c>
       <c r="J29" s="160"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="162" t="s">
         <v>462</v>
       </c>
@@ -8547,7 +8560,7 @@
       <c r="I30" s="123"/>
       <c r="J30" s="160"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="162" t="s">
         <v>462</v>
       </c>
@@ -8577,7 +8590,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="162" t="s">
         <v>462</v>
       </c>
@@ -8605,255 +8618,263 @@
       </c>
       <c r="J32" s="160"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="338" t="s">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="337" t="s">
         <v>521</v>
       </c>
-      <c r="B33" s="338" t="s">
+      <c r="B33" s="337" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="338" t="s">
+      <c r="C33" s="337" t="s">
         <v>522</v>
       </c>
-      <c r="D33" s="338" t="s">
+      <c r="D33" s="337" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="338" t="s">
+      <c r="E33" s="337" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="339">
+      <c r="F33" s="338">
         <v>2013</v>
       </c>
-      <c r="G33" s="340">
+      <c r="G33" s="339">
         <v>41275</v>
       </c>
-      <c r="H33" s="338"/>
-      <c r="I33" s="341">
+      <c r="H33" s="337"/>
+      <c r="I33" s="340">
         <v>40710</v>
       </c>
       <c r="J33" s="160"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="342" t="s">
+      <c r="A34" s="341" t="s">
         <v>1063</v>
       </c>
-      <c r="B34" s="342" t="s">
+      <c r="B34" s="341" t="s">
         <v>265</v>
       </c>
-      <c r="C34" s="342" t="s">
+      <c r="C34" s="341" t="s">
         <v>1076</v>
       </c>
-      <c r="D34" s="342" t="s">
+      <c r="D34" s="162" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="333"/>
+      <c r="G34" s="163">
+        <v>40908</v>
+      </c>
+      <c r="H34" s="162"/>
+      <c r="I34" s="160">
+        <v>11872</v>
+      </c>
+      <c r="J34" s="160" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B35" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" s="341" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D35" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="342"/>
+      <c r="G35" s="343">
+        <v>45291</v>
+      </c>
+      <c r="H35" s="343"/>
+      <c r="I35" s="344">
+        <v>17562</v>
+      </c>
+      <c r="J35" s="160" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B36" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" s="341" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D36" s="341" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="342" t="s">
+      <c r="E36" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="343"/>
-      <c r="G34" s="342"/>
-      <c r="H34" s="344">
+      <c r="F36" s="342"/>
+      <c r="G36" s="343">
+        <v>43830</v>
+      </c>
+      <c r="H36" s="343"/>
+      <c r="I36" s="344">
+        <v>2117</v>
+      </c>
+      <c r="J36" s="160"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B37" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" s="341" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D37" s="346" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="342"/>
+      <c r="G37" s="341"/>
+      <c r="H37" s="339">
+        <v>44926</v>
+      </c>
+      <c r="I37" s="344">
+        <v>71051</v>
+      </c>
+      <c r="J37" s="160" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B38" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C38" s="341" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D38" s="346" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="342"/>
+      <c r="G38" s="163">
+        <v>41639</v>
+      </c>
+      <c r="H38" s="162"/>
+      <c r="I38" s="160">
+        <v>48013</v>
+      </c>
+      <c r="J38" s="160" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B39" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C39" s="341" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D39" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="333"/>
+      <c r="G39" s="353">
+        <v>44196</v>
+      </c>
+      <c r="H39" s="162"/>
+      <c r="I39" s="336">
+        <v>102187</v>
+      </c>
+      <c r="J39" s="160" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B40" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C40" s="341" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D40" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="341" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="333"/>
+      <c r="G40" s="343">
         <v>45657</v>
       </c>
-      <c r="I34" s="345">
-        <v>16874</v>
-      </c>
-      <c r="J34" s="160"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="342" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B35" s="342" t="s">
-        <v>265</v>
-      </c>
-      <c r="C35" s="342" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D35" s="342" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="342" t="s">
+      <c r="H40" s="162"/>
+      <c r="I40" s="344">
+        <v>0</v>
+      </c>
+      <c r="J40" s="160" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="337" t="s">
+        <v>541</v>
+      </c>
+      <c r="B41" s="337" t="s">
+        <v>542</v>
+      </c>
+      <c r="C41" s="337" t="s">
+        <v>543</v>
+      </c>
+      <c r="D41" s="337" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="337" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="343"/>
-      <c r="G35" s="342"/>
-      <c r="H35" s="344">
-        <v>45657</v>
-      </c>
-      <c r="I35" s="345">
-        <v>2117</v>
-      </c>
-      <c r="J35" s="160"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="342" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B36" s="342" t="s">
-        <v>265</v>
-      </c>
-      <c r="C36" s="342" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D36" s="342" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="342" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="343"/>
-      <c r="G36" s="342"/>
-      <c r="H36" s="344">
-        <v>45657</v>
-      </c>
-      <c r="I36" s="345">
-        <v>615</v>
-      </c>
-      <c r="J36" s="160"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="342" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B37" s="342" t="s">
-        <v>265</v>
-      </c>
-      <c r="C37" s="342" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D37" s="342" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" s="342" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="343"/>
-      <c r="G37" s="342"/>
-      <c r="H37" s="340">
-        <v>44561</v>
-      </c>
-      <c r="I37" s="345">
-        <v>47018</v>
-      </c>
-      <c r="J37" s="160" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="342" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B38" s="342" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" s="342" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D38" s="347" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="342" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="333"/>
-      <c r="G38" s="347"/>
-      <c r="H38" s="163">
-        <v>45657</v>
-      </c>
-      <c r="I38" s="337">
-        <v>71051</v>
-      </c>
-      <c r="J38" s="160" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="342" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B39" s="342" t="s">
-        <v>265</v>
-      </c>
-      <c r="C39" s="342" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D39" s="342" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="342" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="343"/>
-      <c r="G39" s="342"/>
-      <c r="H39" s="344">
-        <v>45291</v>
-      </c>
-      <c r="I39" s="345">
-        <v>18174</v>
-      </c>
-      <c r="J39" s="160"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="338" t="s">
-        <v>541</v>
-      </c>
-      <c r="B40" s="338" t="s">
-        <v>542</v>
-      </c>
-      <c r="C40" s="338" t="s">
-        <v>543</v>
-      </c>
-      <c r="D40" s="338" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="338" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="339"/>
-      <c r="G40" s="340">
+      <c r="F41" s="338"/>
+      <c r="G41" s="339">
         <v>44196</v>
       </c>
-      <c r="H40" s="338"/>
-      <c r="I40" s="341">
+      <c r="H41" s="337"/>
+      <c r="I41" s="340">
         <v>26699</v>
       </c>
-      <c r="J40" s="160"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="162" t="s">
+      <c r="J41" s="160"/>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="162" t="s">
         <v>1316</v>
       </c>
-      <c r="B41" s="162" t="s">
+      <c r="B42" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="C41" s="162" t="s">
+      <c r="C42" s="162" t="s">
         <v>579</v>
-      </c>
-      <c r="D41" s="162" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="334"/>
-      <c r="G41" s="125">
-        <v>44197</v>
-      </c>
-      <c r="H41" s="125"/>
-      <c r="I41" s="123">
-        <v>46589</v>
-      </c>
-      <c r="J41" s="160"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="104" t="s">
-        <v>590</v>
-      </c>
-      <c r="B42" s="162" t="s">
-        <v>435</v>
-      </c>
-      <c r="C42" s="162" t="s">
-        <v>591</v>
       </c>
       <c r="D42" s="162" t="s">
         <v>143</v>
@@ -8863,41 +8884,39 @@
       </c>
       <c r="F42" s="334"/>
       <c r="G42" s="125">
+        <v>44197</v>
+      </c>
+      <c r="H42" s="125"/>
+      <c r="I42" s="123">
+        <v>46589</v>
+      </c>
+      <c r="J42" s="160"/>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="104" t="s">
+        <v>590</v>
+      </c>
+      <c r="B43" s="162" t="s">
+        <v>435</v>
+      </c>
+      <c r="C43" s="162" t="s">
+        <v>591</v>
+      </c>
+      <c r="D43" s="162" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="334"/>
+      <c r="G43" s="125">
         <v>44075</v>
       </c>
-      <c r="H42" s="104"/>
-      <c r="I42" s="123">
+      <c r="H43" s="104"/>
+      <c r="I43" s="123">
         <f>67243+12264</f>
         <v>79507</v>
       </c>
-      <c r="J42" s="160"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="162" t="s">
-        <v>613</v>
-      </c>
-      <c r="B43" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C43" s="162" t="s">
-        <v>649</v>
-      </c>
-      <c r="D43" s="162" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" s="162" t="s">
-        <v>124</v>
-      </c>
-      <c r="F43" s="336">
-        <v>46508</v>
-      </c>
-      <c r="G43" s="125">
-        <v>46508</v>
-      </c>
-      <c r="H43" s="125">
-        <v>46508</v>
-      </c>
-      <c r="I43" s="123"/>
       <c r="J43" s="160"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -8910,57 +8929,59 @@
       <c r="C44" s="162" t="s">
         <v>1083</v>
       </c>
-      <c r="D44" s="162"/>
-      <c r="E44" s="162"/>
+      <c r="D44" s="162" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="162" t="s">
+        <v>61</v>
+      </c>
       <c r="F44" s="333"/>
       <c r="G44" s="125">
-        <v>45291</v>
-      </c>
-      <c r="H44" s="125">
-        <v>45291</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="H44" s="162"/>
       <c r="I44" s="160">
         <v>33335</v>
       </c>
       <c r="J44" s="160"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B45" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C45" s="104" t="s">
-        <v>638</v>
+        <v>444</v>
+      </c>
+      <c r="C45" s="322" t="s">
+        <v>628</v>
       </c>
       <c r="D45" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E45" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="334" t="s">
-        <v>511</v>
-      </c>
+      <c r="F45" s="334"/>
       <c r="G45" s="125">
-        <v>44501</v>
+        <v>43559</v>
       </c>
       <c r="H45" s="125">
-        <v>44502</v>
-      </c>
-      <c r="I45" s="123"/>
+        <v>43559</v>
+      </c>
+      <c r="I45" s="123">
+        <v>49264</v>
+      </c>
       <c r="J45" s="160"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B46" s="162" t="s">
-        <v>444</v>
-      </c>
-      <c r="C46" s="322" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C46" s="104" t="s">
+        <v>638</v>
       </c>
       <c r="D46" s="162" t="s">
         <v>143</v>
@@ -8968,27 +8989,29 @@
       <c r="E46" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="334"/>
+      <c r="F46" s="334">
+        <v>2012</v>
+      </c>
       <c r="G46" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="H46" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="I46" s="123">
-        <v>49264</v>
+        <v>51498</v>
       </c>
       <c r="J46" s="160"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B47" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="C47" s="104" t="s">
-        <v>638</v>
+      <c r="C47" s="321" t="s">
+        <v>1013</v>
       </c>
       <c r="D47" s="162" t="s">
         <v>143</v>
@@ -8996,21 +9019,13 @@
       <c r="E47" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="334">
-        <v>2012</v>
-      </c>
-      <c r="G47" s="125">
-        <v>41061</v>
-      </c>
-      <c r="H47" s="125">
-        <v>41061</v>
-      </c>
-      <c r="I47" s="123">
-        <v>3734</v>
-      </c>
+      <c r="F47" s="333"/>
+      <c r="G47" s="163"/>
+      <c r="H47" s="163"/>
+      <c r="I47" s="160"/>
       <c r="J47" s="160"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="162" t="s">
         <v>613</v>
       </c>
@@ -9030,15 +9045,17 @@
         <v>2020</v>
       </c>
       <c r="G48" s="125">
-        <v>43831</v>
+        <v>45658</v>
       </c>
       <c r="H48" s="104"/>
       <c r="I48" s="123">
-        <v>9653</v>
-      </c>
-      <c r="J48" s="160"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5888</v>
+      </c>
+      <c r="J48" s="160" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="162" t="s">
         <v>613</v>
       </c>
@@ -9068,29 +9085,25 @@
       <c r="A50" s="162" t="s">
         <v>652</v>
       </c>
-      <c r="B50" s="181" t="s">
-        <v>704</v>
-      </c>
-      <c r="C50" s="181" t="s">
-        <v>705</v>
-      </c>
-      <c r="D50" s="181" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" s="181" t="s">
+      <c r="B50" s="162" t="s">
+        <v>265</v>
+      </c>
+      <c r="C50" s="137" t="s">
+        <v>663</v>
+      </c>
+      <c r="D50" s="162" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F50" s="334" t="s">
-        <v>708</v>
-      </c>
+      <c r="F50" s="334"/>
       <c r="G50" s="125">
-        <v>46023</v>
-      </c>
-      <c r="H50" s="125">
-        <v>46023</v>
-      </c>
+        <v>45657</v>
+      </c>
+      <c r="H50" s="125"/>
       <c r="I50" s="123">
-        <v>50000</v>
+        <v>24008</v>
       </c>
       <c r="J50" s="160"/>
     </row>
@@ -9101,8 +9114,8 @@
       <c r="B51" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="137" t="s">
-        <v>663</v>
+      <c r="C51" s="162" t="s">
+        <v>668</v>
       </c>
       <c r="D51" s="162" t="s">
         <v>214</v>
@@ -9112,13 +9125,11 @@
       </c>
       <c r="F51" s="334"/>
       <c r="G51" s="125">
-        <v>45657</v>
-      </c>
-      <c r="H51" s="125">
-        <v>45657</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="H51" s="125"/>
       <c r="I51" s="123">
-        <v>24008</v>
+        <v>23534</v>
       </c>
       <c r="J51" s="160"/>
     </row>
@@ -9130,19 +9141,23 @@
         <v>265</v>
       </c>
       <c r="C52" s="162" t="s">
-        <v>668</v>
-      </c>
-      <c r="D52" s="162"/>
-      <c r="E52" s="162"/>
+        <v>653</v>
+      </c>
+      <c r="D52" s="162" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="162" t="s">
+        <v>61</v>
+      </c>
       <c r="F52" s="334"/>
       <c r="G52" s="125">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="H52" s="125">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="I52" s="123">
-        <v>23534</v>
+        <v>42533</v>
       </c>
       <c r="J52" s="160"/>
     </row>
@@ -9153,14 +9168,14 @@
       <c r="B53" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C53" s="162" t="s">
-        <v>653</v>
+      <c r="C53" s="137" t="s">
+        <v>657</v>
       </c>
       <c r="D53" s="162" t="s">
         <v>143</v>
       </c>
       <c r="E53" s="162" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F53" s="334"/>
       <c r="G53" s="125">
@@ -9170,7 +9185,7 @@
         <v>45291</v>
       </c>
       <c r="I53" s="123">
-        <v>42533</v>
+        <v>15433</v>
       </c>
       <c r="J53" s="160"/>
     </row>
@@ -9181,36 +9196,30 @@
       <c r="B54" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="137" t="s">
-        <v>657</v>
+      <c r="C54" s="162" t="s">
+        <v>668</v>
       </c>
       <c r="D54" s="162" t="s">
         <v>143</v>
       </c>
       <c r="E54" s="162" t="s">
-        <v>148</v>
-      </c>
-      <c r="F54" s="334"/>
-      <c r="G54" s="125">
-        <v>45291</v>
-      </c>
-      <c r="H54" s="125">
-        <v>45291</v>
-      </c>
-      <c r="I54" s="123">
-        <v>15433</v>
+        <v>61</v>
+      </c>
+      <c r="F54" s="333"/>
+      <c r="I54" s="160">
+        <v>5000</v>
       </c>
       <c r="J54" s="160"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="162" t="s">
         <v>652</v>
       </c>
       <c r="B55" s="162" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C55" s="162" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D55" s="162" t="s">
         <v>143</v>
@@ -9218,21 +9227,25 @@
       <c r="E55" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="333"/>
+      <c r="F55" s="333" t="s">
+        <v>682</v>
+      </c>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
       <c r="I55" s="160">
-        <v>5000</v>
+        <v>111872</v>
       </c>
       <c r="J55" s="160"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="162" t="s">
         <v>652</v>
       </c>
       <c r="B56" s="162" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="C56" s="162" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D56" s="162" t="s">
         <v>143</v>
@@ -9240,19 +9253,21 @@
       <c r="E56" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="333" t="s">
-        <v>682</v>
-      </c>
-      <c r="G56" s="162"/>
+      <c r="F56" s="333"/>
+      <c r="G56" s="163">
+        <v>44927</v>
+      </c>
       <c r="H56" s="162"/>
       <c r="I56" s="160">
-        <v>111872</v>
-      </c>
-      <c r="J56" s="160"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+        <v>28788</v>
+      </c>
+      <c r="J56" s="160" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B57" s="162" t="s">
         <v>357</v>
@@ -9261,20 +9276,24 @@
         <v>691</v>
       </c>
       <c r="D57" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E57" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="333" t="s">
-        <v>694</v>
-      </c>
-      <c r="G57" s="162"/>
+      <c r="F57" s="333"/>
+      <c r="G57" s="163">
+        <v>45658</v>
+      </c>
       <c r="H57" s="162"/>
-      <c r="I57" s="160"/>
-      <c r="J57" s="160"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I57" s="160">
+        <v>976</v>
+      </c>
+      <c r="J57" s="160" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="162" t="s">
         <v>1028</v>
       </c>
@@ -9304,7 +9323,7 @@
       </c>
       <c r="J58" s="160"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="162" t="s">
         <v>1028</v>
       </c>
@@ -9328,7 +9347,7 @@
       </c>
       <c r="J59" s="160"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="162" t="s">
         <v>718</v>
       </c>
@@ -9356,33 +9375,31 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="162" t="s">
-        <v>737</v>
+        <v>575</v>
       </c>
       <c r="B61" s="162" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="C61" s="162" t="s">
-        <v>738</v>
+        <v>754</v>
       </c>
       <c r="D61" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E61" s="162" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="333" t="s">
-        <v>739</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F61" s="333"/>
       <c r="G61" s="162"/>
       <c r="H61" s="162"/>
       <c r="I61" s="160">
-        <v>30000</v>
+        <v>140000</v>
       </c>
       <c r="J61" s="160"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="162" t="s">
         <v>575</v>
       </c>
@@ -9390,7 +9407,7 @@
         <v>58</v>
       </c>
       <c r="C62" s="162" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D62" s="162" t="s">
         <v>214</v>
@@ -9399,40 +9416,42 @@
         <v>61</v>
       </c>
       <c r="F62" s="333"/>
-      <c r="G62" s="162"/>
+      <c r="G62" s="163">
+        <v>44926</v>
+      </c>
       <c r="H62" s="162"/>
       <c r="I62" s="160">
-        <v>140000</v>
+        <v>29724</v>
       </c>
       <c r="J62" s="160"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="162" t="s">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="181" t="s">
         <v>575</v>
       </c>
-      <c r="B63" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="C63" s="162" t="s">
-        <v>764</v>
-      </c>
-      <c r="D63" s="162" t="s">
-        <v>214</v>
-      </c>
-      <c r="E63" s="162" t="s">
+      <c r="B63" s="181" t="s">
+        <v>444</v>
+      </c>
+      <c r="C63" s="181" t="s">
+        <v>745</v>
+      </c>
+      <c r="D63" s="181" t="s">
+        <v>143</v>
+      </c>
+      <c r="E63" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="333"/>
-      <c r="G63" s="163">
-        <v>44926</v>
-      </c>
-      <c r="H63" s="162"/>
-      <c r="I63" s="160">
-        <v>29724</v>
+      <c r="F63" s="334"/>
+      <c r="G63" s="125">
+        <v>43830</v>
+      </c>
+      <c r="H63" s="125"/>
+      <c r="I63" s="123">
+        <v>13528</v>
       </c>
       <c r="J63" s="160"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="181" t="s">
         <v>575</v>
       </c>
@@ -9443,74 +9462,74 @@
         <v>745</v>
       </c>
       <c r="D64" s="181" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E64" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F64" s="334"/>
-      <c r="G64" s="125">
-        <v>43830</v>
-      </c>
-      <c r="H64" s="125"/>
-      <c r="I64" s="123">
-        <v>13528</v>
+      <c r="F64" s="333"/>
+      <c r="G64" s="163">
+        <v>45291</v>
+      </c>
+      <c r="H64" s="163"/>
+      <c r="I64" s="160">
+        <v>94839</v>
       </c>
       <c r="J64" s="160"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A65" s="181" t="s">
-        <v>575</v>
-      </c>
-      <c r="B65" s="181" t="s">
-        <v>444</v>
-      </c>
-      <c r="C65" s="181" t="s">
-        <v>745</v>
-      </c>
-      <c r="D65" s="181" t="s">
-        <v>71</v>
-      </c>
-      <c r="E65" s="181" t="s">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="162" t="s">
+        <v>824</v>
+      </c>
+      <c r="B65" s="162" t="s">
+        <v>825</v>
+      </c>
+      <c r="C65" s="162" t="s">
+        <v>826</v>
+      </c>
+      <c r="D65" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="333"/>
-      <c r="G65" s="163">
-        <v>45291</v>
-      </c>
-      <c r="H65" s="163"/>
-      <c r="I65" s="160">
-        <v>94839</v>
+      <c r="F65" s="334"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="125">
+        <v>45657</v>
+      </c>
+      <c r="I65" s="123">
+        <v>85654</v>
       </c>
       <c r="J65" s="160"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="162" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B66" s="162" t="s">
-        <v>825</v>
+        <v>212</v>
       </c>
       <c r="C66" s="162" t="s">
-        <v>826</v>
-      </c>
-      <c r="D66" s="104" t="s">
-        <v>60</v>
+        <v>817</v>
+      </c>
+      <c r="D66" s="162" t="s">
+        <v>143</v>
       </c>
       <c r="E66" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="334"/>
-      <c r="G66" s="104"/>
-      <c r="H66" s="125">
-        <v>45657</v>
-      </c>
-      <c r="I66" s="123">
-        <v>85654</v>
+      <c r="F66" s="333"/>
+      <c r="G66" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H66" s="163"/>
+      <c r="I66" s="160">
+        <v>34001</v>
       </c>
       <c r="J66" s="160"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="162" t="s">
         <v>810</v>
       </c>
@@ -9521,53 +9540,27 @@
         <v>817</v>
       </c>
       <c r="D67" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E67" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F67" s="333"/>
       <c r="G67" s="163">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="H67" s="163"/>
       <c r="I67" s="160">
-        <v>34001</v>
+        <v>133505</v>
       </c>
       <c r="J67" s="160"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A68" s="162" t="s">
-        <v>810</v>
-      </c>
-      <c r="B68" s="162" t="s">
-        <v>212</v>
-      </c>
-      <c r="C68" s="162" t="s">
-        <v>817</v>
-      </c>
-      <c r="D68" s="162" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F68" s="333"/>
-      <c r="G68" s="163">
-        <v>45657</v>
-      </c>
-      <c r="H68" s="163"/>
-      <c r="I68" s="160">
-        <v>133505</v>
-      </c>
-      <c r="J68" s="160"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="162"/>
-      <c r="B69" s="162"/>
-      <c r="C69" s="162"/>
-      <c r="D69" s="162"/>
-      <c r="E69" s="162"/>
+      <c r="A68" s="162"/>
+      <c r="B68" s="162"/>
+      <c r="C68" s="162"/>
+      <c r="D68" s="162"/>
+      <c r="E68" s="162"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9583,20 +9576,25 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D1" t="s">
         <v>318</v>
       </c>
@@ -9646,71 +9644,72 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="98" t="s">
         <v>991</v>
       </c>
       <c r="B2" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D2" s="99" t="s">
+      <c r="C2" s="99" t="s">
         <v>992</v>
       </c>
+      <c r="D2" s="100">
+        <v>202</v>
+      </c>
       <c r="E2" s="100">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="F2" s="100">
-        <v>149</v>
-      </c>
-      <c r="G2" s="100">
         <v>39</v>
       </c>
-      <c r="H2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100">
+        <v>255</v>
+      </c>
       <c r="I2" s="100">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J2" s="100">
-        <v>249</v>
+        <v>444</v>
       </c>
       <c r="K2" s="100">
-        <v>444</v>
+        <v>1091</v>
       </c>
       <c r="L2" s="100">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="M2" s="100">
-        <v>1086</v>
+        <v>803</v>
       </c>
       <c r="N2" s="100">
-        <v>803</v>
+        <v>462</v>
       </c>
       <c r="O2" s="100">
-        <v>462</v>
+        <v>33</v>
       </c>
       <c r="P2" s="100">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="100">
         <v>2</v>
       </c>
-      <c r="R2" s="100"/>
-      <c r="S2" s="101">
+      <c r="Q2" s="100"/>
+      <c r="R2" s="101">
         <v>1</v>
       </c>
-      <c r="T2" s="98" t="s">
+      <c r="S2" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="98" t="s">
         <v>993</v>
       </c>
       <c r="B3" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D3" s="99" t="s">
+      <c r="C3" s="99" t="s">
         <v>994</v>
       </c>
+      <c r="D3" s="100"/>
       <c r="E3" s="100"/>
       <c r="F3" s="100"/>
       <c r="G3" s="100"/>
@@ -9718,34 +9717,34 @@
       <c r="I3" s="100"/>
       <c r="J3" s="100"/>
       <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
+      <c r="L3" s="100">
+        <v>427</v>
+      </c>
       <c r="M3" s="100">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="N3" s="100">
-        <v>204</v>
-      </c>
-      <c r="O3" s="100">
         <v>96</v>
       </c>
+      <c r="O3" s="100"/>
       <c r="P3" s="100"/>
       <c r="Q3" s="100"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="98" t="s">
+      <c r="R3" s="101"/>
+      <c r="S3" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="98" t="s">
         <v>995</v>
       </c>
       <c r="B4" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D4" s="99" t="s">
+      <c r="C4" s="99" t="s">
         <v>996</v>
       </c>
+      <c r="D4" s="100"/>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
       <c r="G4" s="100"/>
@@ -9756,33 +9755,33 @@
       <c r="L4" s="100"/>
       <c r="M4" s="100"/>
       <c r="N4" s="100"/>
-      <c r="O4" s="100"/>
+      <c r="O4" s="100">
+        <v>723</v>
+      </c>
       <c r="P4" s="100">
-        <v>723</v>
+        <v>2250</v>
       </c>
       <c r="Q4" s="100">
-        <v>2250</v>
-      </c>
-      <c r="R4" s="100">
         <v>6261</v>
       </c>
-      <c r="S4" s="101">
+      <c r="R4" s="101">
         <v>3330</v>
       </c>
-      <c r="T4" s="98" t="s">
+      <c r="S4" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="98" t="s">
         <v>997</v>
       </c>
       <c r="B5" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D5" s="99" t="s">
+      <c r="C5" s="99" t="s">
         <v>998</v>
       </c>
+      <c r="D5" s="100"/>
       <c r="E5" s="100"/>
       <c r="F5" s="100"/>
       <c r="G5" s="100"/>
@@ -9793,33 +9792,33 @@
       <c r="L5" s="100"/>
       <c r="M5" s="100"/>
       <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
+      <c r="O5" s="100">
+        <v>361</v>
+      </c>
       <c r="P5" s="100">
-        <v>361</v>
+        <v>3404</v>
       </c>
       <c r="Q5" s="100">
-        <v>3404</v>
-      </c>
-      <c r="R5" s="100">
         <v>6950</v>
       </c>
-      <c r="S5" s="101">
+      <c r="R5" s="101">
         <v>4568</v>
       </c>
-      <c r="T5" s="98" t="s">
+      <c r="S5" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="98" t="s">
         <v>999</v>
       </c>
       <c r="B6" s="98" t="s">
         <v>1000</v>
       </c>
-      <c r="D6" s="99" t="s">
+      <c r="C6" s="99" t="s">
         <v>1001</v>
       </c>
+      <c r="D6" s="100"/>
       <c r="E6" s="100"/>
       <c r="F6" s="100"/>
       <c r="G6" s="100"/>
@@ -9829,36 +9828,36 @@
       <c r="K6" s="100"/>
       <c r="L6" s="100"/>
       <c r="M6" s="100"/>
-      <c r="N6" s="100"/>
+      <c r="N6" s="100">
+        <v>660</v>
+      </c>
       <c r="O6" s="100">
-        <v>660</v>
+        <v>11542</v>
       </c>
       <c r="P6" s="100">
-        <v>11542</v>
+        <v>20566</v>
       </c>
       <c r="Q6" s="100">
-        <v>20566</v>
-      </c>
-      <c r="R6" s="100">
         <v>18761</v>
       </c>
-      <c r="S6" s="101">
+      <c r="R6" s="101">
         <v>14559</v>
       </c>
-      <c r="T6" s="98" t="s">
+      <c r="S6" s="98" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="98" t="s">
         <v>1002</v>
       </c>
       <c r="B7" s="98" t="s">
         <v>1000</v>
       </c>
-      <c r="D7" s="99" t="s">
+      <c r="C7" s="99" t="s">
         <v>1003</v>
       </c>
+      <c r="D7" s="100"/>
       <c r="E7" s="100"/>
       <c r="F7" s="100"/>
       <c r="G7" s="100"/>
@@ -9870,30 +9869,30 @@
       <c r="M7" s="100"/>
       <c r="N7" s="100"/>
       <c r="O7" s="100"/>
-      <c r="P7" s="100"/>
+      <c r="P7" s="100">
+        <v>112</v>
+      </c>
       <c r="Q7" s="100">
-        <v>112</v>
-      </c>
-      <c r="R7" s="100">
         <v>3237</v>
       </c>
-      <c r="S7" s="101">
+      <c r="R7" s="101">
         <v>2067</v>
       </c>
-      <c r="T7" s="98" t="s">
+      <c r="S7" s="98" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="98" t="s">
         <v>1004</v>
       </c>
       <c r="B8" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D8" s="99" t="s">
+      <c r="C8" s="99" t="s">
         <v>1004</v>
       </c>
+      <c r="D8" s="100"/>
       <c r="E8" s="100"/>
       <c r="F8" s="100"/>
       <c r="G8" s="100"/>
@@ -9905,30 +9904,30 @@
       <c r="M8" s="100"/>
       <c r="N8" s="100"/>
       <c r="O8" s="100"/>
-      <c r="P8" s="100"/>
+      <c r="P8" s="100">
+        <v>693</v>
+      </c>
       <c r="Q8" s="100">
-        <v>693</v>
-      </c>
-      <c r="R8" s="100">
         <v>2287</v>
       </c>
-      <c r="S8" s="101">
+      <c r="R8" s="101">
         <v>1310</v>
       </c>
-      <c r="T8" s="98" t="s">
+      <c r="S8" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="98" t="s">
         <v>1005</v>
       </c>
       <c r="B9" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D9" s="99" t="s">
+      <c r="C9" s="99" t="s">
         <v>1005</v>
       </c>
+      <c r="D9" s="100"/>
       <c r="E9" s="100"/>
       <c r="F9" s="100"/>
       <c r="G9" s="100"/>
@@ -9940,30 +9939,30 @@
       <c r="M9" s="100"/>
       <c r="N9" s="100"/>
       <c r="O9" s="100"/>
-      <c r="P9" s="100"/>
+      <c r="P9" s="100">
+        <v>119</v>
+      </c>
       <c r="Q9" s="100">
-        <v>119</v>
-      </c>
-      <c r="R9" s="100">
         <v>417</v>
       </c>
-      <c r="S9" s="101">
+      <c r="R9" s="101">
         <v>242</v>
       </c>
-      <c r="T9" s="98" t="s">
+      <c r="S9" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="98" t="s">
         <v>1006</v>
       </c>
       <c r="B10" s="98" t="s">
         <v>1007</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="C10" s="99" t="s">
         <v>1006</v>
       </c>
+      <c r="D10" s="100"/>
       <c r="E10" s="100"/>
       <c r="F10" s="100"/>
       <c r="G10" s="100"/>
@@ -9977,24 +9976,24 @@
       <c r="O10" s="100"/>
       <c r="P10" s="100"/>
       <c r="Q10" s="100"/>
-      <c r="R10" s="100"/>
-      <c r="S10" s="101">
+      <c r="R10" s="101">
         <v>599</v>
       </c>
-      <c r="T10" s="98" t="s">
+      <c r="S10" s="98" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="98" t="s">
         <v>1008</v>
       </c>
       <c r="B11" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D11" s="99" t="s">
+      <c r="C11" s="99" t="s">
         <v>1009</v>
       </c>
+      <c r="D11" s="100"/>
       <c r="E11" s="100"/>
       <c r="F11" s="100"/>
       <c r="G11" s="100"/>
@@ -10005,33 +10004,33 @@
       <c r="L11" s="100"/>
       <c r="M11" s="100"/>
       <c r="N11" s="100"/>
-      <c r="O11" s="100"/>
+      <c r="O11" s="100">
+        <v>231</v>
+      </c>
       <c r="P11" s="100">
-        <v>231</v>
+        <v>2386</v>
       </c>
       <c r="Q11" s="100">
-        <v>2386</v>
-      </c>
-      <c r="R11" s="100">
         <v>4610</v>
       </c>
-      <c r="S11" s="101">
+      <c r="R11" s="101">
         <v>3594</v>
       </c>
-      <c r="T11" s="98" t="s">
+      <c r="S11" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="98" t="s">
         <v>1010</v>
       </c>
       <c r="B12" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D12" s="99" t="s">
+      <c r="C12" s="99" t="s">
         <v>1011</v>
       </c>
+      <c r="D12" s="100"/>
       <c r="E12" s="100"/>
       <c r="F12" s="100"/>
       <c r="G12" s="100"/>
@@ -10042,33 +10041,33 @@
       <c r="L12" s="100"/>
       <c r="M12" s="100"/>
       <c r="N12" s="100"/>
-      <c r="O12" s="100"/>
+      <c r="O12" s="100">
+        <v>194</v>
+      </c>
       <c r="P12" s="100">
-        <v>194</v>
+        <v>1596</v>
       </c>
       <c r="Q12" s="100">
-        <v>1596</v>
-      </c>
-      <c r="R12" s="100">
         <v>2298</v>
       </c>
-      <c r="S12" s="101">
+      <c r="R12" s="101">
         <v>2909</v>
       </c>
-      <c r="T12" s="98" t="s">
+      <c r="S12" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="98" t="s">
         <v>1012</v>
       </c>
       <c r="B13" s="98" t="s">
         <v>1013</v>
       </c>
-      <c r="D13" s="99" t="s">
+      <c r="C13" s="99" t="s">
         <v>1014</v>
       </c>
+      <c r="D13" s="100"/>
       <c r="E13" s="100"/>
       <c r="F13" s="100"/>
       <c r="G13" s="100"/>
@@ -10078,36 +10077,36 @@
       <c r="K13" s="100"/>
       <c r="L13" s="100"/>
       <c r="M13" s="100"/>
-      <c r="N13" s="100"/>
+      <c r="N13" s="100">
+        <v>16450</v>
+      </c>
       <c r="O13" s="100">
-        <v>16450</v>
+        <v>26908</v>
       </c>
       <c r="P13" s="100">
-        <v>26908</v>
+        <v>29011</v>
       </c>
       <c r="Q13" s="100">
-        <v>29011</v>
-      </c>
-      <c r="R13" s="100">
         <v>34353</v>
       </c>
-      <c r="S13" s="101">
+      <c r="R13" s="101">
         <v>22307</v>
       </c>
-      <c r="T13" s="98" t="s">
+      <c r="S13" s="98" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="98" t="s">
         <v>1015</v>
       </c>
       <c r="B14" s="98" t="s">
         <v>1016</v>
       </c>
-      <c r="D14" s="99" t="s">
+      <c r="C14" s="99" t="s">
         <v>1017</v>
       </c>
+      <c r="D14" s="100"/>
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
@@ -10121,24 +10120,24 @@
       <c r="O14" s="100"/>
       <c r="P14" s="100"/>
       <c r="Q14" s="100"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="101">
+      <c r="R14" s="101">
         <v>118</v>
       </c>
-      <c r="T14" s="98" t="s">
+      <c r="S14" s="98" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="98" t="s">
         <v>1018</v>
       </c>
       <c r="B15" s="98" t="s">
         <v>1019</v>
       </c>
-      <c r="D15" s="99" t="s">
+      <c r="C15" s="99" t="s">
         <v>1018</v>
       </c>
+      <c r="D15" s="100"/>
       <c r="E15" s="100"/>
       <c r="F15" s="100"/>
       <c r="G15" s="100"/>
@@ -10148,36 +10147,36 @@
       <c r="K15" s="100"/>
       <c r="L15" s="100"/>
       <c r="M15" s="100"/>
-      <c r="N15" s="100"/>
+      <c r="N15" s="100">
+        <v>12026</v>
+      </c>
       <c r="O15" s="100">
-        <v>12026</v>
+        <v>27884</v>
       </c>
       <c r="P15" s="100">
-        <v>27884</v>
+        <v>29271</v>
       </c>
       <c r="Q15" s="100">
-        <v>29271</v>
-      </c>
-      <c r="R15" s="100">
         <v>25460</v>
       </c>
-      <c r="S15" s="101">
+      <c r="R15" s="101">
         <v>24442</v>
       </c>
-      <c r="T15" s="98" t="s">
+      <c r="S15" s="98" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="98" t="s">
         <v>1020</v>
       </c>
       <c r="B16" s="98" t="s">
         <v>1021</v>
       </c>
-      <c r="D16" s="99" t="s">
+      <c r="C16" s="99" t="s">
         <v>1022</v>
       </c>
+      <c r="D16" s="100"/>
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
@@ -10190,27 +10189,27 @@
       <c r="N16" s="100"/>
       <c r="O16" s="100"/>
       <c r="P16" s="100"/>
-      <c r="Q16" s="100"/>
-      <c r="R16" s="100">
+      <c r="Q16" s="100">
         <v>5791</v>
       </c>
-      <c r="S16" s="101">
+      <c r="R16" s="101">
         <v>39332</v>
       </c>
-      <c r="T16" s="98" t="s">
+      <c r="S16" s="98" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="98" t="s">
         <v>1023</v>
       </c>
       <c r="B17" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D17" s="99" t="s">
+      <c r="C17" s="99" t="s">
         <v>1023</v>
       </c>
+      <c r="D17" s="100"/>
       <c r="E17" s="100"/>
       <c r="F17" s="100"/>
       <c r="G17" s="100"/>
@@ -10221,33 +10220,33 @@
       <c r="L17" s="100"/>
       <c r="M17" s="100"/>
       <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
+      <c r="O17" s="100">
+        <v>358</v>
+      </c>
       <c r="P17" s="100">
-        <v>358</v>
+        <v>5020</v>
       </c>
       <c r="Q17" s="100">
-        <v>5020</v>
-      </c>
-      <c r="R17" s="100">
         <v>8060</v>
       </c>
-      <c r="S17" s="101">
+      <c r="R17" s="101">
         <v>8422</v>
       </c>
-      <c r="T17" s="98" t="s">
+      <c r="S17" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="98" t="s">
         <v>1024</v>
       </c>
       <c r="B18" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D18" s="99" t="s">
+      <c r="C18" s="99" t="s">
         <v>1024</v>
       </c>
+      <c r="D18" s="100"/>
       <c r="E18" s="100"/>
       <c r="F18" s="100"/>
       <c r="G18" s="100"/>
@@ -10258,84 +10257,84 @@
       <c r="L18" s="100"/>
       <c r="M18" s="100"/>
       <c r="N18" s="100"/>
-      <c r="O18" s="100"/>
+      <c r="O18" s="100">
+        <v>433</v>
+      </c>
       <c r="P18" s="100">
-        <v>433</v>
+        <v>1600</v>
       </c>
       <c r="Q18" s="100">
-        <v>1600</v>
-      </c>
-      <c r="R18" s="100">
         <v>3461</v>
       </c>
-      <c r="S18" s="101">
+      <c r="R18" s="101">
         <v>2680</v>
       </c>
-      <c r="T18" s="98" t="s">
+      <c r="S18" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="98" t="s">
         <v>1025</v>
       </c>
       <c r="B19" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D19" s="99" t="s">
+      <c r="C19" s="99" t="s">
         <v>1025</v>
       </c>
-      <c r="E19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100">
+        <v>80</v>
+      </c>
       <c r="F19" s="100">
         <v>80</v>
       </c>
       <c r="G19" s="100">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H19" s="100">
-        <v>156</v>
+        <v>335</v>
       </c>
       <c r="I19" s="100">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="J19" s="100">
-        <v>388</v>
+        <v>788</v>
       </c>
       <c r="K19" s="100">
-        <v>788</v>
+        <v>1673</v>
       </c>
       <c r="L19" s="100">
-        <v>1673</v>
+        <v>1651</v>
       </c>
       <c r="M19" s="100">
-        <v>1651</v>
+        <v>1213</v>
       </c>
       <c r="N19" s="100">
-        <v>1213</v>
+        <v>283</v>
       </c>
       <c r="O19" s="100">
-        <v>283</v>
-      </c>
-      <c r="P19" s="100">
         <v>1</v>
       </c>
+      <c r="P19" s="100"/>
       <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="98" t="s">
+      <c r="R19" s="101"/>
+      <c r="S19" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="98" t="s">
         <v>1026</v>
       </c>
       <c r="B20" s="98" t="s">
         <v>638</v>
       </c>
-      <c r="D20" s="99" t="s">
+      <c r="C20" s="99" t="s">
         <v>1026</v>
       </c>
+      <c r="D20" s="100"/>
       <c r="E20" s="100"/>
       <c r="F20" s="100"/>
       <c r="G20" s="100"/>
@@ -10343,60 +10342,59 @@
       <c r="I20" s="100"/>
       <c r="J20" s="100"/>
       <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
+      <c r="L20" s="100">
+        <v>570</v>
+      </c>
       <c r="M20" s="100">
-        <v>570</v>
+        <v>263</v>
       </c>
       <c r="N20" s="100">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="O20" s="100">
-        <v>122</v>
-      </c>
-      <c r="P20" s="100">
         <v>2</v>
       </c>
+      <c r="P20" s="100"/>
       <c r="Q20" s="100"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="101"/>
-      <c r="T20" s="98" t="s">
+      <c r="R20" s="101"/>
+      <c r="S20" s="98" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D22" s="54"/>
       <c r="E22" s="54">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="D23" s="98" t="s">
         <v>638</v>
       </c>
       <c r="E23" s="58">
-        <f>SUM(S2:S5,S8,S9,S11:S12,S15,S17:S20)</f>
+        <f>SUM(R2:R5,R8,R9,R11:R12,R15,R17:R20)</f>
         <v>51498</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="D24" s="98" t="s">
         <v>1000</v>
       </c>
       <c r="E24" s="58">
-        <f>SUM(S6:S7)</f>
+        <f>SUM(R6:R7)</f>
         <v>16626</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="D25" s="98" t="s">
         <v>1013</v>
       </c>
       <c r="E25" s="58">
-        <f>SUM(S13,S14)</f>
+        <f>SUM(R13,R14)</f>
         <v>22425</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="D26" s="103" t="s">
         <v>913</v>
       </c>
@@ -10405,21 +10403,21 @@
         <v>90549</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="D28" s="98" t="s">
         <v>914</v>
       </c>
       <c r="E28" s="58">
-        <f>SUM(S2:S9,S17:S20,S11:S15)</f>
+        <f>SUM(R2:R9,R17:R20,R11:R15)</f>
         <v>90549</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="C31" s="346" t="s">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C31" s="345" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B32" s="326"/>
       <c r="C32" s="326" t="s">
         <v>613</v>
@@ -10583,6 +10581,9 @@
   <cols>
     <col min="2" max="2" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -11731,16 +11732,21 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.1640625" customWidth="1"/>
     <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.33203125" customWidth="1"/>
     <col min="23" max="23" width="9.83203125" customWidth="1"/>
@@ -12309,9 +12315,86 @@
         <v>5005</v>
       </c>
     </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.2">
-      <c r="G22" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K17">
+        <v>2011</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1341</v>
+      </c>
+      <c r="O17" s="57">
+        <f>R7</f>
+        <v>11872</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J18" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K18">
+        <v>2023</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1342</v>
+      </c>
+      <c r="O18" s="57">
+        <f>S4+S5+S8</f>
+        <v>5690</v>
+      </c>
+      <c r="P18" s="57">
+        <f>O18+O17</f>
+        <v>17562</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>1135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K21">
+        <v>2012</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1344</v>
+      </c>
+      <c r="Q21">
+        <v>48013</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J22" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K22">
+        <v>2018</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1345</v>
+      </c>
+      <c r="Q22">
+        <v>102187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J24" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K24">
+        <v>2019</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1349</v>
+      </c>
+      <c r="O24" s="57">
+        <f>S9</f>
+        <v>2117</v>
       </c>
     </row>
   </sheetData>
@@ -12749,17 +12832,17 @@
   <dimension ref="A1:T258"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26" style="324" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="324" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" style="324" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" style="324" customWidth="1"/>
     <col min="3" max="3" width="29" style="324" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="324" customWidth="1"/>
-    <col min="5" max="11" width="11.6640625" style="324" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="324" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="324" customWidth="1"/>
+    <col min="6" max="11" width="11.6640625" style="324" customWidth="1"/>
     <col min="12" max="12" width="13" style="324" customWidth="1"/>
     <col min="13" max="13" width="12.33203125" style="324" customWidth="1"/>
     <col min="14" max="17" width="14.6640625" style="324" customWidth="1"/>
     <col min="18" max="18" width="16.1640625" style="324" customWidth="1"/>
-    <col min="19" max="19" width="8.83203125" style="324"/>
-    <col min="20" max="20" width="10.1640625" style="324" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.1640625" style="324" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="8.83203125" style="324"/>
   </cols>
   <sheetData>
@@ -15861,7 +15944,7 @@
         <v>10701</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="326"/>
       <c r="B97" s="326"/>
       <c r="C97" s="324" t="s">
@@ -15893,7 +15976,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="326"/>
       <c r="B98" s="326"/>
       <c r="C98" s="324" t="s">
@@ -15925,7 +16008,7 @@
         <v>16926</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="326"/>
       <c r="B99" s="326"/>
       <c r="C99" s="324" t="s">
@@ -15953,7 +16036,7 @@
       <c r="Q99" s="327"/>
       <c r="R99" s="327"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="326"/>
       <c r="B100" s="326"/>
       <c r="C100" s="324" t="s">
@@ -15993,7 +16076,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="326"/>
       <c r="B101" s="326"/>
       <c r="C101" s="324" t="s">
@@ -16037,7 +16120,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="326"/>
       <c r="B102" s="326" t="s">
         <v>934</v>
@@ -16065,7 +16148,7 @@
       </c>
       <c r="R102" s="327"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="326"/>
       <c r="B103" s="326"/>
       <c r="C103" s="324" t="s">
@@ -16091,7 +16174,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="326"/>
       <c r="B104" s="326" t="s">
         <v>613</v>
@@ -16123,7 +16206,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="326"/>
       <c r="B105" s="326"/>
       <c r="C105" s="324" t="s">
@@ -16153,7 +16236,7 @@
         <v>8038</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="326"/>
       <c r="B106" s="326"/>
       <c r="C106" s="324" t="s">
@@ -16179,7 +16262,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="326"/>
       <c r="B107" s="326"/>
       <c r="C107" s="324" t="s">
@@ -16213,7 +16296,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="326"/>
       <c r="B108" s="326"/>
       <c r="C108" s="324" t="s">
@@ -16236,8 +16319,12 @@
       <c r="R108" s="327">
         <v>395</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S108" s="327">
+        <f>R108+R106</f>
+        <v>5888</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="326"/>
       <c r="B109" s="326" t="s">
         <v>1187</v>
@@ -16269,7 +16356,7 @@
         <v>206097</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="326"/>
       <c r="B110" s="326" t="s">
         <v>920</v>
@@ -16315,7 +16402,7 @@
         <v>20877</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="326"/>
       <c r="B111" s="326"/>
       <c r="C111" s="324" t="s">
@@ -16339,7 +16426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="326"/>
       <c r="B112" s="326"/>
       <c r="C112" s="324" t="s">
@@ -17867,7 +17954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="326"/>
       <c r="B161" s="326" t="s">
         <v>920</v>
@@ -17893,7 +17980,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="328"/>
       <c r="B162" s="326"/>
       <c r="C162" s="324" t="s">
@@ -17919,7 +18006,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" s="326" t="s">
         <v>335</v>
       </c>
@@ -17963,7 +18050,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" s="328"/>
       <c r="B164" s="326" t="s">
         <v>934</v>
@@ -17989,7 +18076,7 @@
       <c r="Q164" s="327"/>
       <c r="R164" s="327"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" s="328" t="s">
         <v>1233</v>
       </c>
@@ -18023,7 +18110,7 @@
       <c r="Q165" s="327"/>
       <c r="R165" s="327"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="326" t="s">
         <v>357</v>
       </c>
@@ -18051,7 +18138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" s="326"/>
       <c r="B167" s="326" t="s">
         <v>1236</v>
@@ -18077,7 +18164,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" s="326"/>
       <c r="B168" s="326" t="s">
         <v>613</v>
@@ -18103,7 +18190,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" s="326"/>
       <c r="B169" s="326"/>
       <c r="C169" s="324" t="s">
@@ -18129,7 +18216,7 @@
         <v>9427</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="326"/>
       <c r="B170" s="326"/>
       <c r="C170" s="324" t="s">
@@ -18156,8 +18243,12 @@
       <c r="R170" s="327">
         <v>17303</v>
       </c>
-    </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S170" s="327">
+        <f>SUM(R168:R170)</f>
+        <v>28788</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" s="326"/>
       <c r="B171" s="326" t="s">
         <v>920</v>
@@ -18195,7 +18286,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" s="326"/>
       <c r="B172" s="326"/>
       <c r="C172" s="324" t="s">
@@ -18223,7 +18314,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" s="326"/>
       <c r="B173" s="326"/>
       <c r="C173" s="324" t="s">
@@ -18251,7 +18342,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="326"/>
       <c r="B174" s="326"/>
       <c r="C174" s="324" t="s">
@@ -18281,7 +18372,7 @@
       <c r="Q174" s="327"/>
       <c r="R174" s="327"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" s="326"/>
       <c r="B175" s="326"/>
       <c r="C175" s="324" t="s">
@@ -18311,7 +18402,7 @@
       </c>
       <c r="R175" s="327"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" s="328"/>
       <c r="B176" s="326"/>
       <c r="C176" s="324" t="s">
@@ -21339,7 +21430,7 @@
       <c r="AK2" s="153" t="s">
         <v>63</v>
       </c>
-      <c r="AL2" s="365">
+      <c r="AL2" s="160">
         <f>0.08*1500*365</f>
         <v>43800</v>
       </c>
@@ -21351,7 +21442,7 @@
       </c>
       <c r="AO2" s="153"/>
       <c r="AP2" s="153"/>
-      <c r="AQ2" s="367">
+      <c r="AQ2" s="247">
         <v>28225</v>
       </c>
       <c r="AR2" s="153" t="s">
@@ -21394,26 +21485,26 @@
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A3" s="107"/>
-      <c r="B3" s="349" t="s">
+      <c r="B3" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="349" t="s">
+      <c r="C3" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="349" t="s">
+      <c r="D3" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349" t="s">
+      <c r="E3" s="162"/>
+      <c r="F3" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="349" t="s">
+      <c r="G3" s="162" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="349" t="s">
+      <c r="I3" s="162" t="s">
         <v>61</v>
       </c>
       <c r="J3" s="163">
@@ -21422,13 +21513,13 @@
       <c r="K3" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="349" t="s">
+      <c r="L3" s="162" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="349" t="s">
+      <c r="M3" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="353">
+      <c r="N3" s="163">
         <v>44408</v>
       </c>
       <c r="O3" s="209" t="s">
@@ -21437,7 +21528,7 @@
       <c r="P3" s="164" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="349" t="s">
+      <c r="Q3" s="162" t="s">
         <v>73</v>
       </c>
       <c r="R3" s="163">
@@ -21446,66 +21537,66 @@
       <c r="S3" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="349"/>
+      <c r="T3" s="162"/>
       <c r="U3" s="165" t="s">
         <v>68</v>
       </c>
-      <c r="V3" s="356">
+      <c r="V3" s="166">
         <v>0.4</v>
       </c>
-      <c r="W3" s="349"/>
-      <c r="X3" s="349"/>
-      <c r="Y3" s="349"/>
-      <c r="Z3" s="349"/>
-      <c r="AA3" s="349"/>
-      <c r="AB3" s="349" t="s">
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC3" s="353">
+      <c r="AC3" s="163">
         <v>44379</v>
       </c>
-      <c r="AD3" s="353">
+      <c r="AD3" s="163">
         <v>44379</v>
       </c>
-      <c r="AE3" s="357"/>
-      <c r="AF3" s="360"/>
-      <c r="AG3" s="360"/>
-      <c r="AH3" s="349"/>
-      <c r="AI3" s="349" t="s">
+      <c r="AE3" s="277"/>
+      <c r="AF3" s="260"/>
+      <c r="AG3" s="260"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="AJ3" s="349"/>
-      <c r="AK3" s="349" t="s">
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="162" t="s">
         <v>76</v>
       </c>
-      <c r="AL3" s="365"/>
-      <c r="AM3" s="349"/>
-      <c r="AN3" s="349"/>
-      <c r="AO3" s="349"/>
-      <c r="AP3" s="349"/>
-      <c r="AQ3" s="367"/>
-      <c r="AR3" s="349"/>
-      <c r="AS3" s="349"/>
-      <c r="AT3" s="349"/>
-      <c r="AU3" s="349"/>
-      <c r="AV3" s="349"/>
-      <c r="AW3" s="349"/>
-      <c r="AX3" s="349" t="s">
+      <c r="AL3" s="160"/>
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="247"/>
+      <c r="AR3" s="162"/>
+      <c r="AS3" s="162"/>
+      <c r="AT3" s="162"/>
+      <c r="AU3" s="162"/>
+      <c r="AV3" s="162"/>
+      <c r="AW3" s="162"/>
+      <c r="AX3" s="162" t="s">
         <v>77</v>
       </c>
-      <c r="AY3" s="349" t="s">
+      <c r="AY3" s="162" t="s">
         <v>78</v>
       </c>
-      <c r="AZ3" s="349" t="s">
+      <c r="AZ3" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA3" s="353">
+      <c r="BA3" s="163">
         <v>45714</v>
       </c>
-      <c r="BB3" s="349" t="s">
+      <c r="BB3" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC3" s="377"/>
+      <c r="BC3" s="167"/>
       <c r="BD3" s="1" t="s">
         <v>79</v>
       </c>
@@ -21521,50 +21612,50 @@
       <c r="BH3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BI3" s="349"/>
-      <c r="BJ3" s="349"/>
-      <c r="BK3" s="349"/>
-      <c r="BL3" s="349"/>
-      <c r="BM3" s="349"/>
-      <c r="BN3" s="348"/>
+      <c r="BI3" s="162"/>
+      <c r="BJ3" s="162"/>
+      <c r="BK3" s="162"/>
+      <c r="BL3" s="162"/>
+      <c r="BM3" s="162"/>
+      <c r="BN3" s="104"/>
     </row>
     <row r="4" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A4" s="107"/>
-      <c r="B4" s="349" t="s">
+      <c r="B4" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="349" t="s">
+      <c r="C4" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="349" t="s">
+      <c r="D4" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349" t="s">
+      <c r="E4" s="162"/>
+      <c r="F4" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="349" t="s">
+      <c r="G4" s="162" t="s">
         <v>59</v>
       </c>
       <c r="H4" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="349" t="s">
+      <c r="I4" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="353">
+      <c r="J4" s="163">
         <v>45128</v>
       </c>
       <c r="K4" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="373" t="s">
+      <c r="L4" s="350" t="s">
         <v>84</v>
       </c>
-      <c r="M4" s="374" t="s">
+      <c r="M4" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="375">
+      <c r="N4" s="351">
         <v>45497</v>
       </c>
       <c r="O4" s="129" t="s">
@@ -21573,100 +21664,100 @@
       <c r="P4" s="168" t="s">
         <v>85</v>
       </c>
-      <c r="Q4" s="374" t="s">
+      <c r="Q4" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="R4" s="375">
+      <c r="R4" s="351">
         <v>45497</v>
       </c>
       <c r="S4" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="T4" s="349"/>
+      <c r="T4" s="162"/>
       <c r="U4" s="165" t="s">
         <v>68</v>
       </c>
-      <c r="V4" s="356">
+      <c r="V4" s="166">
         <v>0.6</v>
       </c>
-      <c r="W4" s="349"/>
-      <c r="X4" s="349"/>
-      <c r="Y4" s="349"/>
-      <c r="Z4" s="349"/>
-      <c r="AA4" s="349"/>
-      <c r="AB4" s="349" t="s">
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="162"/>
+      <c r="AB4" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC4" s="353">
+      <c r="AC4" s="163">
         <v>45128</v>
       </c>
-      <c r="AD4" s="353">
+      <c r="AD4" s="163">
         <v>45128</v>
       </c>
-      <c r="AE4" s="358">
+      <c r="AE4" s="347">
         <v>45128</v>
       </c>
-      <c r="AF4" s="360"/>
-      <c r="AG4" s="360"/>
-      <c r="AH4" s="349"/>
-      <c r="AI4" s="349" t="s">
+      <c r="AF4" s="260"/>
+      <c r="AG4" s="260"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="AJ4" s="349"/>
-      <c r="AK4" s="349" t="s">
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="AL4" s="365">
+      <c r="AL4" s="160">
         <v>300000</v>
       </c>
-      <c r="AM4" s="349" t="s">
+      <c r="AM4" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO4" s="349"/>
-      <c r="AP4" s="349"/>
-      <c r="AQ4" s="367">
+      <c r="AO4" s="162"/>
+      <c r="AP4" s="162"/>
+      <c r="AQ4" s="247">
         <v>123209</v>
       </c>
-      <c r="AR4" s="349" t="s">
+      <c r="AR4" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS4" s="1"/>
-      <c r="AT4" s="348"/>
-      <c r="AU4" s="348"/>
-      <c r="AV4" s="349"/>
-      <c r="AW4" s="349"/>
-      <c r="AX4" s="349" t="s">
+      <c r="AT4" s="104"/>
+      <c r="AU4" s="104"/>
+      <c r="AV4" s="162"/>
+      <c r="AW4" s="162"/>
+      <c r="AX4" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="AY4" s="349" t="s">
+      <c r="AY4" s="162" t="s">
         <v>88</v>
       </c>
-      <c r="AZ4" s="349" t="s">
+      <c r="AZ4" s="162" t="s">
         <v>89</v>
       </c>
-      <c r="BA4" s="353">
+      <c r="BA4" s="163">
         <v>45714</v>
       </c>
-      <c r="BB4" s="349" t="s">
+      <c r="BB4" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC4" s="377"/>
+      <c r="BC4" s="167"/>
       <c r="BD4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="BE4" s="377"/>
-      <c r="BF4" s="377"/>
-      <c r="BG4" s="377"/>
-      <c r="BH4" s="377"/>
-      <c r="BI4" s="349"/>
-      <c r="BJ4" s="349"/>
-      <c r="BK4" s="349"/>
-      <c r="BL4" s="349"/>
-      <c r="BM4" s="349"/>
-      <c r="BN4" s="348"/>
+      <c r="BE4" s="167"/>
+      <c r="BF4" s="167"/>
+      <c r="BG4" s="167"/>
+      <c r="BH4" s="167"/>
+      <c r="BI4" s="162"/>
+      <c r="BJ4" s="162"/>
+      <c r="BK4" s="162"/>
+      <c r="BL4" s="162"/>
+      <c r="BM4" s="162"/>
+      <c r="BN4" s="104"/>
     </row>
     <row r="5" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A5" s="107"/>
@@ -22047,113 +22138,113 @@
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A8" s="107"/>
-      <c r="B8" s="349" t="s">
+      <c r="B8" s="162" t="s">
         <v>107</v>
       </c>
       <c r="C8" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="349" t="s">
+      <c r="D8" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349" t="s">
+      <c r="E8" s="162"/>
+      <c r="F8" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="349" t="s">
+      <c r="G8" s="162" t="s">
         <v>109</v>
       </c>
       <c r="H8" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="349" t="s">
+      <c r="I8" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="349"/>
+      <c r="J8" s="162"/>
       <c r="K8" s="207"/>
-      <c r="L8" s="349"/>
-      <c r="M8" s="349"/>
-      <c r="N8" s="349"/>
-      <c r="O8" s="349"/>
+      <c r="L8" s="162"/>
+      <c r="M8" s="162"/>
+      <c r="N8" s="162"/>
+      <c r="O8" s="162"/>
       <c r="P8" s="164"/>
-      <c r="Q8" s="349"/>
-      <c r="R8" s="349"/>
+      <c r="Q8" s="162"/>
+      <c r="R8" s="162"/>
       <c r="S8" s="180"/>
-      <c r="T8" s="349"/>
+      <c r="T8" s="162"/>
       <c r="U8" s="165"/>
-      <c r="V8" s="356"/>
-      <c r="W8" s="349"/>
-      <c r="X8" s="349"/>
-      <c r="Y8" s="349"/>
-      <c r="Z8" s="349"/>
-      <c r="AA8" s="349"/>
-      <c r="AB8" s="349"/>
-      <c r="AC8" s="349"/>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="357">
+      <c r="V8" s="166"/>
+      <c r="W8" s="162"/>
+      <c r="X8" s="162"/>
+      <c r="Y8" s="162"/>
+      <c r="Z8" s="162"/>
+      <c r="AA8" s="162"/>
+      <c r="AB8" s="162"/>
+      <c r="AC8" s="162"/>
+      <c r="AD8" s="162"/>
+      <c r="AE8" s="277">
         <v>2015</v>
       </c>
-      <c r="AF8" s="361">
+      <c r="AF8" s="261">
         <v>42185</v>
       </c>
-      <c r="AG8" s="361">
+      <c r="AG8" s="261">
         <v>42185</v>
       </c>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349" t="s">
+      <c r="AH8" s="162"/>
+      <c r="AI8" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349" t="s">
+      <c r="AJ8" s="162"/>
+      <c r="AK8" s="162" t="s">
         <v>110</v>
       </c>
-      <c r="AL8" s="365"/>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="349"/>
-      <c r="AP8" s="349"/>
-      <c r="AQ8" s="367">
+      <c r="AL8" s="160"/>
+      <c r="AM8" s="162"/>
+      <c r="AN8" s="162"/>
+      <c r="AO8" s="162"/>
+      <c r="AP8" s="162"/>
+      <c r="AQ8" s="247">
         <v>20016</v>
       </c>
-      <c r="AR8" s="349" t="s">
+      <c r="AR8" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AT8" s="349"/>
-      <c r="AU8" s="349"/>
-      <c r="AV8" s="349"/>
-      <c r="AW8" s="349"/>
-      <c r="AX8" s="349" t="s">
+      <c r="AT8" s="162"/>
+      <c r="AU8" s="162"/>
+      <c r="AV8" s="162"/>
+      <c r="AW8" s="162"/>
+      <c r="AX8" s="162" t="s">
         <v>111</v>
       </c>
-      <c r="AY8" s="349"/>
-      <c r="AZ8" s="349" t="s">
+      <c r="AY8" s="162"/>
+      <c r="AZ8" s="162" t="s">
         <v>89</v>
       </c>
-      <c r="BA8" s="353">
+      <c r="BA8" s="163">
         <v>45714</v>
       </c>
-      <c r="BB8" s="349" t="s">
+      <c r="BB8" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC8" s="349"/>
+      <c r="BC8" s="162"/>
       <c r="BD8" s="1" t="s">
         <v>112</v>
       </c>
       <c r="BE8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BF8" s="377"/>
-      <c r="BG8" s="377"/>
-      <c r="BH8" s="377"/>
-      <c r="BI8" s="349"/>
-      <c r="BJ8" s="349"/>
-      <c r="BK8" s="349"/>
-      <c r="BL8" s="349"/>
-      <c r="BM8" s="349"/>
-      <c r="BN8" s="348"/>
+      <c r="BF8" s="167"/>
+      <c r="BG8" s="167"/>
+      <c r="BH8" s="167"/>
+      <c r="BI8" s="162"/>
+      <c r="BJ8" s="162"/>
+      <c r="BK8" s="162"/>
+      <c r="BL8" s="162"/>
+      <c r="BM8" s="162"/>
+      <c r="BN8" s="104"/>
     </row>
     <row r="9" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A9" s="107"/>
@@ -22574,7 +22665,7 @@
       <c r="I12" s="170" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="371">
+      <c r="J12" s="239">
         <v>45370</v>
       </c>
       <c r="K12" s="124"/>
@@ -22594,7 +22685,7 @@
       <c r="Q12" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="R12" s="376">
+      <c r="R12" s="352">
         <v>44642</v>
       </c>
       <c r="S12" s="80" t="s">
@@ -22791,41 +22882,41 @@
     </row>
     <row r="14" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A14" s="107"/>
-      <c r="B14" s="351" t="s">
+      <c r="B14" s="203" t="s">
         <v>1044</v>
       </c>
-      <c r="C14" s="351" t="s">
+      <c r="C14" s="203" t="s">
         <v>1043</v>
       </c>
-      <c r="D14" s="349" t="s">
+      <c r="D14" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349" t="s">
+      <c r="E14" s="162"/>
+      <c r="F14" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G14" s="349" t="s">
+      <c r="G14" s="162" t="s">
         <v>142</v>
       </c>
       <c r="H14" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="349" t="s">
+      <c r="I14" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J14" s="353">
+      <c r="J14" s="163">
         <v>45181</v>
       </c>
       <c r="K14" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="349" t="s">
+      <c r="L14" s="162" t="s">
         <v>85</v>
       </c>
-      <c r="M14" s="349" t="s">
+      <c r="M14" s="162" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="353">
+      <c r="N14" s="163">
         <v>45180</v>
       </c>
       <c r="O14" s="1" t="s">
@@ -22834,65 +22925,65 @@
       <c r="P14" s="164" t="s">
         <v>85</v>
       </c>
-      <c r="Q14" s="349" t="s">
+      <c r="Q14" s="162" t="s">
         <v>150</v>
       </c>
-      <c r="R14" s="353">
+      <c r="R14" s="163">
         <v>45180</v>
       </c>
       <c r="S14" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T14" s="349"/>
-      <c r="U14" s="356"/>
-      <c r="V14" s="356"/>
-      <c r="W14" s="349"/>
-      <c r="X14" s="349"/>
-      <c r="Y14" s="349"/>
-      <c r="Z14" s="349"/>
-      <c r="AA14" s="349"/>
-      <c r="AB14" s="349"/>
-      <c r="AC14" s="349"/>
-      <c r="AD14" s="349"/>
-      <c r="AE14" s="357" t="s">
+      <c r="T14" s="162"/>
+      <c r="U14" s="166"/>
+      <c r="V14" s="166"/>
+      <c r="W14" s="162"/>
+      <c r="X14" s="162"/>
+      <c r="Y14" s="162"/>
+      <c r="Z14" s="162"/>
+      <c r="AA14" s="162"/>
+      <c r="AB14" s="162"/>
+      <c r="AC14" s="162"/>
+      <c r="AD14" s="162"/>
+      <c r="AE14" s="277" t="s">
         <v>151</v>
       </c>
-      <c r="AF14" s="360"/>
-      <c r="AG14" s="360"/>
-      <c r="AH14" s="349"/>
-      <c r="AI14" s="349" t="s">
+      <c r="AF14" s="260"/>
+      <c r="AG14" s="260"/>
+      <c r="AH14" s="162"/>
+      <c r="AI14" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ14" s="349"/>
-      <c r="AK14" s="349" t="s">
+      <c r="AJ14" s="162"/>
+      <c r="AK14" s="162" t="s">
         <v>152</v>
       </c>
-      <c r="AL14" s="365"/>
-      <c r="AM14" s="349"/>
-      <c r="AN14" s="349"/>
-      <c r="AO14" s="349"/>
-      <c r="AP14" s="349"/>
-      <c r="AQ14" s="367"/>
-      <c r="AR14" s="349"/>
-      <c r="AS14" s="349"/>
-      <c r="AT14" s="349"/>
-      <c r="AU14" s="349"/>
-      <c r="AV14" s="349"/>
-      <c r="AW14" s="349"/>
-      <c r="AX14" s="349" t="s">
+      <c r="AL14" s="160"/>
+      <c r="AM14" s="162"/>
+      <c r="AN14" s="162"/>
+      <c r="AO14" s="162"/>
+      <c r="AP14" s="162"/>
+      <c r="AQ14" s="247"/>
+      <c r="AR14" s="162"/>
+      <c r="AS14" s="162"/>
+      <c r="AT14" s="162"/>
+      <c r="AU14" s="162"/>
+      <c r="AV14" s="162"/>
+      <c r="AW14" s="162"/>
+      <c r="AX14" s="162" t="s">
         <v>153</v>
       </c>
-      <c r="AY14" s="349"/>
-      <c r="AZ14" s="349" t="s">
+      <c r="AY14" s="162"/>
+      <c r="AZ14" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA14" s="353">
+      <c r="BA14" s="163">
         <v>45714</v>
       </c>
-      <c r="BB14" s="349" t="s">
+      <c r="BB14" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC14" s="349"/>
+      <c r="BC14" s="162"/>
       <c r="BD14" s="1" t="s">
         <v>154</v>
       </c>
@@ -22911,18 +23002,18 @@
       <c r="BI14" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="BJ14" s="349"/>
-      <c r="BK14" s="349"/>
-      <c r="BL14" s="349"/>
-      <c r="BM14" s="349"/>
-      <c r="BN14" s="348"/>
+      <c r="BJ14" s="162"/>
+      <c r="BK14" s="162"/>
+      <c r="BL14" s="162"/>
+      <c r="BM14" s="162"/>
+      <c r="BN14" s="104"/>
     </row>
     <row r="15" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A15" s="107"/>
-      <c r="B15" s="349" t="s">
+      <c r="B15" s="162" t="s">
         <v>159</v>
       </c>
-      <c r="C15" s="349" t="s">
+      <c r="C15" s="162" t="s">
         <v>160</v>
       </c>
       <c r="D15" s="162" t="s">
@@ -22950,7 +23041,7 @@
       <c r="L15" s="162" t="s">
         <v>163</v>
       </c>
-      <c r="M15" s="349" t="s">
+      <c r="M15" s="162" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="163">
@@ -22962,7 +23053,7 @@
       <c r="P15" s="164" t="s">
         <v>164</v>
       </c>
-      <c r="Q15" s="349" t="s">
+      <c r="Q15" s="162" t="s">
         <v>165</v>
       </c>
       <c r="R15" s="163">
@@ -23014,7 +23105,7 @@
       <c r="AL15" s="160">
         <v>150000</v>
       </c>
-      <c r="AM15" s="349" t="s">
+      <c r="AM15" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN15" s="4" t="s">
@@ -23073,99 +23164,99 @@
         <f>C16&amp;"_0"</f>
         <v>Z_GB_BMW_Goodwood_0</v>
       </c>
-      <c r="C16" s="348" t="str">
+      <c r="C16" s="104" t="str">
         <f>"Z_GB_BMW_Goodwood"</f>
         <v>Z_GB_BMW_Goodwood</v>
       </c>
-      <c r="D16" s="349" t="s">
+      <c r="D16" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="348"/>
-      <c r="F16" s="349" t="s">
+      <c r="E16" s="104"/>
+      <c r="F16" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G16" s="349" t="s">
+      <c r="G16" s="162" t="s">
         <v>172</v>
       </c>
       <c r="H16" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="349" t="s">
+      <c r="I16" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="348"/>
+      <c r="J16" s="104"/>
       <c r="K16" s="122"/>
-      <c r="L16" s="348"/>
-      <c r="M16" s="348"/>
-      <c r="N16" s="348"/>
-      <c r="O16" s="348"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="104"/>
       <c r="P16" s="121"/>
-      <c r="Q16" s="348"/>
-      <c r="R16" s="348"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="104"/>
       <c r="S16" s="122"/>
-      <c r="T16" s="348"/>
-      <c r="U16" s="348"/>
-      <c r="V16" s="348"/>
-      <c r="W16" s="348"/>
-      <c r="X16" s="348"/>
-      <c r="Y16" s="348"/>
-      <c r="Z16" s="348"/>
-      <c r="AA16" s="348"/>
-      <c r="AB16" s="348"/>
-      <c r="AC16" s="348"/>
-      <c r="AD16" s="348"/>
-      <c r="AE16" s="359"/>
-      <c r="AF16" s="361">
+      <c r="T16" s="104"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="104"/>
+      <c r="W16" s="104"/>
+      <c r="X16" s="104"/>
+      <c r="Y16" s="104"/>
+      <c r="Z16" s="104"/>
+      <c r="AA16" s="104"/>
+      <c r="AB16" s="104"/>
+      <c r="AC16" s="104"/>
+      <c r="AD16" s="104"/>
+      <c r="AE16" s="284"/>
+      <c r="AF16" s="261">
         <v>45291</v>
       </c>
-      <c r="AG16" s="361">
+      <c r="AG16" s="261">
         <v>45291</v>
       </c>
-      <c r="AH16" s="348"/>
-      <c r="AI16" s="349" t="s">
+      <c r="AH16" s="104"/>
+      <c r="AI16" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ16" s="348"/>
-      <c r="AK16" s="349" t="s">
+      <c r="AJ16" s="104"/>
+      <c r="AK16" s="162" t="s">
         <v>173</v>
       </c>
-      <c r="AL16" s="364"/>
-      <c r="AM16" s="348"/>
-      <c r="AN16" s="348"/>
-      <c r="AO16" s="348"/>
-      <c r="AP16" s="348"/>
-      <c r="AQ16" s="367">
+      <c r="AL16" s="123"/>
+      <c r="AM16" s="104"/>
+      <c r="AN16" s="104"/>
+      <c r="AO16" s="104"/>
+      <c r="AP16" s="104"/>
+      <c r="AQ16" s="247">
         <v>1076</v>
       </c>
-      <c r="AR16" s="349" t="s">
+      <c r="AR16" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AT16" s="348"/>
-      <c r="AU16" s="348"/>
-      <c r="AV16" s="348"/>
-      <c r="AW16" s="348"/>
-      <c r="AX16" s="349" t="s">
+      <c r="AT16" s="104"/>
+      <c r="AU16" s="104"/>
+      <c r="AV16" s="104"/>
+      <c r="AW16" s="104"/>
+      <c r="AX16" s="162" t="s">
         <v>174</v>
       </c>
-      <c r="AY16" s="348"/>
-      <c r="AZ16" s="348"/>
-      <c r="BA16" s="348"/>
-      <c r="BB16" s="348"/>
-      <c r="BC16" s="348"/>
-      <c r="BD16" s="348"/>
-      <c r="BE16" s="348"/>
-      <c r="BF16" s="348"/>
-      <c r="BG16" s="348"/>
-      <c r="BH16" s="348"/>
-      <c r="BI16" s="348"/>
-      <c r="BJ16" s="348"/>
-      <c r="BK16" s="348"/>
-      <c r="BL16" s="348"/>
-      <c r="BM16" s="348"/>
-      <c r="BN16" s="348"/>
+      <c r="AY16" s="104"/>
+      <c r="AZ16" s="104"/>
+      <c r="BA16" s="104"/>
+      <c r="BB16" s="104"/>
+      <c r="BC16" s="104"/>
+      <c r="BD16" s="104"/>
+      <c r="BE16" s="104"/>
+      <c r="BF16" s="104"/>
+      <c r="BG16" s="104"/>
+      <c r="BH16" s="104"/>
+      <c r="BI16" s="104"/>
+      <c r="BJ16" s="104"/>
+      <c r="BK16" s="104"/>
+      <c r="BL16" s="104"/>
+      <c r="BM16" s="104"/>
+      <c r="BN16" s="104"/>
     </row>
     <row r="17" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="108" t="s">
@@ -23175,7 +23266,7 @@
         <f>C17&amp;"_1"</f>
         <v>Z_GB_BMW_Goodwood_1</v>
       </c>
-      <c r="C17" s="348" t="str">
+      <c r="C17" s="104" t="str">
         <f>"Z_GB_BMW_Goodwood"</f>
         <v>Z_GB_BMW_Goodwood</v>
       </c>
@@ -23270,42 +23361,42 @@
       <c r="BN17" s="109"/>
     </row>
     <row r="18" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A18" s="348"/>
-      <c r="B18" s="349" t="s">
+      <c r="A18" s="104"/>
+      <c r="B18" s="162" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="349" t="s">
+      <c r="C18" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="349" t="s">
+      <c r="D18" s="162" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349" t="s">
+      <c r="E18" s="162"/>
+      <c r="F18" s="162" t="s">
         <v>182</v>
       </c>
-      <c r="G18" s="349" t="s">
+      <c r="G18" s="162" t="s">
         <v>183</v>
       </c>
       <c r="H18" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I18" s="349" t="s">
+      <c r="I18" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J18" s="353">
+      <c r="J18" s="163">
         <v>45511</v>
       </c>
       <c r="K18" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L18" s="349" t="s">
+      <c r="L18" s="162" t="s">
         <v>184</v>
       </c>
-      <c r="M18" s="349" t="s">
+      <c r="M18" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N18" s="353">
+      <c r="N18" s="163">
         <v>45511</v>
       </c>
       <c r="O18" s="1" t="s">
@@ -23314,211 +23405,211 @@
       <c r="P18" s="164" t="s">
         <v>184</v>
       </c>
-      <c r="Q18" s="349" t="s">
+      <c r="Q18" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R18" s="353">
+      <c r="R18" s="163">
         <v>45511</v>
       </c>
       <c r="S18" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T18" s="349"/>
-      <c r="U18" s="356"/>
-      <c r="V18" s="356"/>
-      <c r="W18" s="349"/>
-      <c r="X18" s="349" t="s">
+      <c r="T18" s="162"/>
+      <c r="U18" s="166"/>
+      <c r="V18" s="166"/>
+      <c r="W18" s="162"/>
+      <c r="X18" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="Y18" s="353">
+      <c r="Y18" s="163">
         <v>45838</v>
       </c>
-      <c r="Z18" s="353">
+      <c r="Z18" s="163">
         <v>45838</v>
       </c>
-      <c r="AA18" s="349"/>
-      <c r="AB18" s="349" t="s">
+      <c r="AA18" s="162"/>
+      <c r="AB18" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="AC18" s="353">
+      <c r="AC18" s="163">
         <v>46022</v>
       </c>
-      <c r="AD18" s="353">
+      <c r="AD18" s="163">
         <v>46022</v>
       </c>
-      <c r="AE18" s="357" t="s">
+      <c r="AE18" s="277" t="s">
         <v>185</v>
       </c>
-      <c r="AF18" s="361">
+      <c r="AF18" s="261">
         <v>46203</v>
       </c>
-      <c r="AG18" s="361">
+      <c r="AG18" s="261">
         <v>46203</v>
       </c>
-      <c r="AH18" s="349"/>
-      <c r="AI18" s="349" t="s">
+      <c r="AH18" s="162"/>
+      <c r="AI18" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ18" s="349"/>
-      <c r="AK18" s="349" t="s">
+      <c r="AJ18" s="162"/>
+      <c r="AK18" s="162" t="s">
         <v>186</v>
       </c>
-      <c r="AL18" s="365">
+      <c r="AL18" s="160">
         <v>50000</v>
       </c>
-      <c r="AM18" s="349" t="s">
+      <c r="AM18" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO18" s="349"/>
-      <c r="AP18" s="349"/>
-      <c r="AQ18" s="367">
+      <c r="AO18" s="162"/>
+      <c r="AP18" s="162"/>
+      <c r="AQ18" s="247">
         <v>50000</v>
       </c>
-      <c r="AR18" s="349" t="s">
+      <c r="AR18" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT18" s="349"/>
-      <c r="AU18" s="349"/>
-      <c r="AV18" s="349">
+      <c r="AT18" s="162"/>
+      <c r="AU18" s="162"/>
+      <c r="AV18" s="162">
         <v>650</v>
       </c>
-      <c r="AW18" s="349"/>
-      <c r="AX18" s="349" t="s">
+      <c r="AW18" s="162"/>
+      <c r="AX18" s="162" t="s">
         <v>187</v>
       </c>
-      <c r="AY18" s="349" t="s">
+      <c r="AY18" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="AZ18" s="349" t="s">
+      <c r="AZ18" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA18" s="353">
+      <c r="BA18" s="163">
         <v>45709</v>
       </c>
-      <c r="BB18" s="349" t="s">
+      <c r="BB18" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC18" s="349"/>
+      <c r="BC18" s="162"/>
       <c r="BD18" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="BE18" s="349"/>
-      <c r="BF18" s="349"/>
-      <c r="BG18" s="349"/>
-      <c r="BH18" s="349"/>
-      <c r="BI18" s="349"/>
-      <c r="BJ18" s="349"/>
-      <c r="BK18" s="349"/>
-      <c r="BL18" s="349"/>
-      <c r="BM18" s="349"/>
-      <c r="BN18" s="348"/>
+      <c r="BE18" s="162"/>
+      <c r="BF18" s="162"/>
+      <c r="BG18" s="162"/>
+      <c r="BH18" s="162"/>
+      <c r="BI18" s="162"/>
+      <c r="BJ18" s="162"/>
+      <c r="BK18" s="162"/>
+      <c r="BL18" s="162"/>
+      <c r="BM18" s="162"/>
+      <c r="BN18" s="104"/>
     </row>
     <row r="19" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A19" s="348"/>
-      <c r="B19" s="349" t="s">
+      <c r="A19" s="104"/>
+      <c r="B19" s="162" t="s">
         <v>1047</v>
       </c>
-      <c r="C19" s="349" t="s">
+      <c r="C19" s="162" t="s">
         <v>1045</v>
       </c>
-      <c r="D19" s="349" t="s">
+      <c r="D19" s="162" t="s">
         <v>190</v>
       </c>
-      <c r="E19" s="349"/>
-      <c r="F19" s="349" t="s">
+      <c r="E19" s="162"/>
+      <c r="F19" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G19" s="349" t="s">
+      <c r="G19" s="162" t="s">
         <v>191</v>
       </c>
       <c r="H19" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I19" s="349" t="s">
+      <c r="I19" s="162" t="s">
         <v>192</v>
       </c>
-      <c r="J19" s="353">
+      <c r="J19" s="163">
         <v>44067</v>
       </c>
       <c r="K19" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="349"/>
-      <c r="M19" s="349"/>
-      <c r="N19" s="349"/>
-      <c r="O19" s="349"/>
+      <c r="L19" s="162"/>
+      <c r="M19" s="162"/>
+      <c r="N19" s="162"/>
+      <c r="O19" s="162"/>
       <c r="P19" s="164"/>
-      <c r="Q19" s="349"/>
-      <c r="R19" s="349"/>
+      <c r="Q19" s="162"/>
+      <c r="R19" s="162"/>
       <c r="S19" s="180"/>
-      <c r="T19" s="349"/>
-      <c r="U19" s="356"/>
-      <c r="V19" s="356"/>
-      <c r="W19" s="349"/>
-      <c r="X19" s="349"/>
-      <c r="Y19" s="349"/>
-      <c r="Z19" s="349"/>
-      <c r="AA19" s="349"/>
-      <c r="AB19" s="349" t="s">
+      <c r="T19" s="162"/>
+      <c r="U19" s="166"/>
+      <c r="V19" s="166"/>
+      <c r="W19" s="162"/>
+      <c r="X19" s="162"/>
+      <c r="Y19" s="162"/>
+      <c r="Z19" s="162"/>
+      <c r="AA19" s="162"/>
+      <c r="AB19" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC19" s="353">
+      <c r="AC19" s="163">
         <v>44249</v>
       </c>
-      <c r="AD19" s="353">
+      <c r="AD19" s="163">
         <v>44249</v>
       </c>
-      <c r="AE19" s="357"/>
-      <c r="AF19" s="361">
+      <c r="AE19" s="277"/>
+      <c r="AF19" s="261">
         <v>44249</v>
       </c>
-      <c r="AG19" s="361">
+      <c r="AG19" s="261">
         <v>44249</v>
       </c>
-      <c r="AH19" s="353">
+      <c r="AH19" s="163">
         <v>45328</v>
       </c>
-      <c r="AI19" s="349" t="s">
+      <c r="AI19" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ19" s="349"/>
-      <c r="AK19" s="349" t="s">
+      <c r="AJ19" s="162"/>
+      <c r="AK19" s="162" t="s">
         <v>193</v>
       </c>
-      <c r="AL19" s="365"/>
-      <c r="AM19" s="349"/>
-      <c r="AN19" s="349"/>
-      <c r="AO19" s="349"/>
-      <c r="AP19" s="349"/>
-      <c r="AQ19" s="367"/>
-      <c r="AR19" s="349"/>
-      <c r="AS19" s="349"/>
-      <c r="AT19" s="349"/>
-      <c r="AU19" s="349"/>
-      <c r="AV19" s="349"/>
-      <c r="AW19" s="349"/>
-      <c r="AX19" s="349" t="s">
+      <c r="AL19" s="160"/>
+      <c r="AM19" s="162"/>
+      <c r="AN19" s="162"/>
+      <c r="AO19" s="162"/>
+      <c r="AP19" s="162"/>
+      <c r="AQ19" s="247"/>
+      <c r="AR19" s="162"/>
+      <c r="AS19" s="162"/>
+      <c r="AT19" s="162"/>
+      <c r="AU19" s="162"/>
+      <c r="AV19" s="162"/>
+      <c r="AW19" s="162"/>
+      <c r="AX19" s="162" t="s">
         <v>194</v>
       </c>
-      <c r="AY19" s="349" t="s">
+      <c r="AY19" s="162" t="s">
         <v>195</v>
       </c>
-      <c r="AZ19" s="349" t="s">
+      <c r="AZ19" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA19" s="353">
+      <c r="BA19" s="163">
         <v>45709</v>
       </c>
-      <c r="BB19" s="349" t="s">
+      <c r="BB19" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC19" s="349"/>
+      <c r="BC19" s="162"/>
       <c r="BD19" s="1" t="s">
         <v>196</v>
       </c>
@@ -23534,115 +23625,115 @@
       <c r="BH19" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="BI19" s="349"/>
-      <c r="BJ19" s="349"/>
-      <c r="BK19" s="349"/>
-      <c r="BL19" s="349"/>
-      <c r="BM19" s="349"/>
-      <c r="BN19" s="348"/>
+      <c r="BI19" s="162"/>
+      <c r="BJ19" s="162"/>
+      <c r="BK19" s="162"/>
+      <c r="BL19" s="162"/>
+      <c r="BM19" s="162"/>
+      <c r="BN19" s="104"/>
     </row>
     <row r="20" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="348"/>
-      <c r="B20" s="349" t="s">
+      <c r="A20" s="104"/>
+      <c r="B20" s="162" t="s">
         <v>1048</v>
       </c>
-      <c r="C20" s="349" t="s">
+      <c r="C20" s="162" t="s">
         <v>1046</v>
       </c>
-      <c r="D20" s="349" t="s">
+      <c r="D20" s="162" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349" t="s">
+      <c r="E20" s="162"/>
+      <c r="F20" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="349" t="s">
+      <c r="G20" s="162" t="s">
         <v>202</v>
       </c>
       <c r="H20" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I20" s="349" t="s">
+      <c r="I20" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J20" s="353">
+      <c r="J20" s="163">
         <v>43354</v>
       </c>
       <c r="K20" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L20" s="349"/>
-      <c r="M20" s="349"/>
-      <c r="N20" s="349"/>
-      <c r="O20" s="349"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="162"/>
+      <c r="N20" s="162"/>
+      <c r="O20" s="162"/>
       <c r="P20" s="164"/>
-      <c r="Q20" s="349"/>
-      <c r="R20" s="349"/>
+      <c r="Q20" s="162"/>
+      <c r="R20" s="162"/>
       <c r="S20" s="180"/>
-      <c r="T20" s="349"/>
-      <c r="U20" s="356"/>
-      <c r="V20" s="356"/>
-      <c r="W20" s="349">
+      <c r="T20" s="162"/>
+      <c r="U20" s="166"/>
+      <c r="V20" s="166"/>
+      <c r="W20" s="162">
         <v>2017</v>
       </c>
-      <c r="X20" s="349"/>
-      <c r="Y20" s="349"/>
-      <c r="Z20" s="349"/>
-      <c r="AA20" s="349"/>
-      <c r="AB20" s="349" t="s">
+      <c r="X20" s="162"/>
+      <c r="Y20" s="162"/>
+      <c r="Z20" s="162"/>
+      <c r="AA20" s="162"/>
+      <c r="AB20" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="AC20" s="353">
+      <c r="AC20" s="163">
         <v>46203</v>
       </c>
-      <c r="AD20" s="353">
+      <c r="AD20" s="163">
         <v>46203</v>
       </c>
-      <c r="AE20" s="357" t="s">
+      <c r="AE20" s="277" t="s">
         <v>203</v>
       </c>
-      <c r="AF20" s="361">
+      <c r="AF20" s="261">
         <v>46203</v>
       </c>
-      <c r="AG20" s="361">
+      <c r="AG20" s="261">
         <v>46203</v>
       </c>
-      <c r="AH20" s="349"/>
-      <c r="AI20" s="349" t="s">
+      <c r="AH20" s="162"/>
+      <c r="AI20" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="AJ20" s="349"/>
-      <c r="AK20" s="349" t="s">
+      <c r="AJ20" s="162"/>
+      <c r="AK20" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="AL20" s="365"/>
-      <c r="AM20" s="349"/>
-      <c r="AN20" s="349"/>
-      <c r="AO20" s="349"/>
-      <c r="AP20" s="349"/>
-      <c r="AQ20" s="367"/>
-      <c r="AR20" s="349"/>
-      <c r="AS20" s="349"/>
-      <c r="AT20" s="349"/>
-      <c r="AU20" s="349"/>
-      <c r="AV20" s="349"/>
-      <c r="AW20" s="349"/>
-      <c r="AX20" s="349" t="s">
+      <c r="AL20" s="160"/>
+      <c r="AM20" s="162"/>
+      <c r="AN20" s="162"/>
+      <c r="AO20" s="162"/>
+      <c r="AP20" s="162"/>
+      <c r="AQ20" s="247"/>
+      <c r="AR20" s="162"/>
+      <c r="AS20" s="162"/>
+      <c r="AT20" s="162"/>
+      <c r="AU20" s="162"/>
+      <c r="AV20" s="162"/>
+      <c r="AW20" s="162"/>
+      <c r="AX20" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="AY20" s="349" t="s">
+      <c r="AY20" s="162" t="s">
         <v>206</v>
       </c>
-      <c r="AZ20" s="349" t="s">
+      <c r="AZ20" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA20" s="353">
+      <c r="BA20" s="163">
         <v>45709</v>
       </c>
-      <c r="BB20" s="349" t="s">
+      <c r="BB20" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC20" s="349"/>
+      <c r="BC20" s="162"/>
       <c r="BD20" s="1" t="s">
         <v>207</v>
       </c>
@@ -23655,13 +23746,13 @@
       <c r="BG20" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="BH20" s="349"/>
-      <c r="BI20" s="349"/>
-      <c r="BJ20" s="349"/>
-      <c r="BK20" s="349"/>
-      <c r="BL20" s="349"/>
-      <c r="BM20" s="349"/>
-      <c r="BN20" s="348"/>
+      <c r="BH20" s="162"/>
+      <c r="BI20" s="162"/>
+      <c r="BJ20" s="162"/>
+      <c r="BK20" s="162"/>
+      <c r="BL20" s="162"/>
+      <c r="BM20" s="162"/>
+      <c r="BN20" s="104"/>
     </row>
     <row r="21" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A21" s="110"/>
@@ -23823,7 +23914,7 @@
       <c r="R22" s="104"/>
       <c r="S22" s="122"/>
       <c r="T22" s="104"/>
-      <c r="U22" s="348"/>
+      <c r="U22" s="104"/>
       <c r="V22" s="104"/>
       <c r="W22" s="104"/>
       <c r="X22" s="104"/>
@@ -23896,7 +23987,7 @@
         <f>C23&amp;"_1"</f>
         <v>Z_DE_Audi_Neckarsulm_1</v>
       </c>
-      <c r="C23" s="348" t="str">
+      <c r="C23" s="104" t="str">
         <f>"Z_DE_"&amp;D23&amp;"_"&amp;G23</f>
         <v>Z_DE_Audi_Neckarsulm</v>
       </c>
@@ -23993,7 +24084,7 @@
       <c r="BN23" s="109"/>
     </row>
     <row r="24" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A24" s="348"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="162" t="s">
         <v>228</v>
       </c>
@@ -24123,42 +24214,42 @@
       <c r="BN24" s="104"/>
     </row>
     <row r="25" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A25" s="348"/>
-      <c r="B25" s="349" t="s">
+      <c r="A25" s="104"/>
+      <c r="B25" s="162" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="349" t="s">
+      <c r="C25" s="162" t="s">
         <v>239</v>
       </c>
-      <c r="D25" s="349" t="s">
+      <c r="D25" s="162" t="s">
         <v>240</v>
       </c>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349" t="s">
+      <c r="E25" s="162"/>
+      <c r="F25" s="162" t="s">
         <v>241</v>
       </c>
-      <c r="G25" s="349" t="s">
+      <c r="G25" s="162" t="s">
         <v>242</v>
       </c>
       <c r="H25" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I25" s="349" t="s">
+      <c r="I25" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="J25" s="353">
+      <c r="J25" s="163">
         <v>43566</v>
       </c>
       <c r="K25" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L25" s="349" t="s">
+      <c r="L25" s="162" t="s">
         <v>243</v>
       </c>
-      <c r="M25" s="349" t="s">
+      <c r="M25" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N25" s="353">
+      <c r="N25" s="163">
         <v>43566</v>
       </c>
       <c r="O25" s="1" t="s">
@@ -24167,72 +24258,72 @@
       <c r="P25" s="164" t="s">
         <v>243</v>
       </c>
-      <c r="Q25" s="349" t="s">
+      <c r="Q25" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R25" s="353">
+      <c r="R25" s="163">
         <v>43566</v>
       </c>
       <c r="S25" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T25" s="349"/>
-      <c r="U25" s="356"/>
-      <c r="V25" s="356"/>
-      <c r="W25" s="349"/>
-      <c r="X25" s="349" t="s">
+      <c r="T25" s="162"/>
+      <c r="U25" s="166"/>
+      <c r="V25" s="166"/>
+      <c r="W25" s="162"/>
+      <c r="X25" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="Y25" s="353">
+      <c r="Y25" s="163">
         <v>43566</v>
       </c>
-      <c r="Z25" s="353">
+      <c r="Z25" s="163">
         <v>43566</v>
       </c>
-      <c r="AA25" s="349"/>
-      <c r="AB25" s="349"/>
-      <c r="AC25" s="349"/>
-      <c r="AD25" s="349"/>
-      <c r="AE25" s="357" t="s">
+      <c r="AA25" s="162"/>
+      <c r="AB25" s="162"/>
+      <c r="AC25" s="162"/>
+      <c r="AD25" s="162"/>
+      <c r="AE25" s="277" t="s">
         <v>244</v>
       </c>
-      <c r="AF25" s="360"/>
-      <c r="AG25" s="360"/>
-      <c r="AH25" s="349"/>
-      <c r="AI25" s="349" t="s">
+      <c r="AF25" s="260"/>
+      <c r="AG25" s="260"/>
+      <c r="AH25" s="162"/>
+      <c r="AI25" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ25" s="349"/>
-      <c r="AK25" s="349" t="s">
+      <c r="AJ25" s="162"/>
+      <c r="AK25" s="162" t="s">
         <v>245</v>
       </c>
-      <c r="AL25" s="365"/>
-      <c r="AM25" s="349"/>
-      <c r="AN25" s="349"/>
-      <c r="AO25" s="349"/>
-      <c r="AP25" s="349"/>
-      <c r="AQ25" s="367"/>
-      <c r="AR25" s="349"/>
-      <c r="AS25" s="349"/>
-      <c r="AT25" s="349"/>
-      <c r="AU25" s="349"/>
-      <c r="AV25" s="349">
+      <c r="AL25" s="160"/>
+      <c r="AM25" s="162"/>
+      <c r="AN25" s="162"/>
+      <c r="AO25" s="162"/>
+      <c r="AP25" s="162"/>
+      <c r="AQ25" s="247"/>
+      <c r="AR25" s="162"/>
+      <c r="AS25" s="162"/>
+      <c r="AT25" s="162"/>
+      <c r="AU25" s="162"/>
+      <c r="AV25" s="162">
         <v>150</v>
       </c>
-      <c r="AW25" s="349"/>
-      <c r="AX25" s="349" t="s">
+      <c r="AW25" s="162"/>
+      <c r="AX25" s="162" t="s">
         <v>246</v>
       </c>
-      <c r="AY25" s="349" t="s">
+      <c r="AY25" s="162" t="s">
         <v>247</v>
       </c>
-      <c r="AZ25" s="349" t="s">
+      <c r="AZ25" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA25" s="353">
+      <c r="BA25" s="163">
         <v>45712</v>
       </c>
-      <c r="BB25" s="349" t="s">
+      <c r="BB25" s="162" t="s">
         <v>67</v>
       </c>
       <c r="BC25" s="1" t="s">
@@ -24247,14 +24338,14 @@
       <c r="BF25" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BG25" s="349"/>
-      <c r="BH25" s="349"/>
-      <c r="BI25" s="349"/>
-      <c r="BJ25" s="349"/>
-      <c r="BK25" s="349"/>
-      <c r="BL25" s="349"/>
-      <c r="BM25" s="349"/>
-      <c r="BN25" s="348"/>
+      <c r="BG25" s="162"/>
+      <c r="BH25" s="162"/>
+      <c r="BI25" s="162"/>
+      <c r="BJ25" s="162"/>
+      <c r="BK25" s="162"/>
+      <c r="BL25" s="162"/>
+      <c r="BM25" s="162"/>
+      <c r="BN25" s="104"/>
     </row>
     <row r="26" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A26" s="127" t="s">
@@ -24399,42 +24490,42 @@
       <c r="BN26" s="104"/>
     </row>
     <row r="27" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A27" s="348"/>
-      <c r="B27" s="349" t="s">
+      <c r="A27" s="104"/>
+      <c r="B27" s="162" t="s">
         <v>262</v>
       </c>
       <c r="C27" s="162" t="s">
         <v>263</v>
       </c>
-      <c r="D27" s="349" t="s">
+      <c r="D27" s="162" t="s">
         <v>264</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349" t="s">
+      <c r="E27" s="162"/>
+      <c r="F27" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="G27" s="349" t="s">
+      <c r="G27" s="162" t="s">
         <v>266</v>
       </c>
       <c r="H27" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="349" t="s">
+      <c r="I27" s="162" t="s">
         <v>267</v>
       </c>
-      <c r="J27" s="353">
+      <c r="J27" s="163">
         <v>42825</v>
       </c>
       <c r="K27" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="349" t="s">
+      <c r="L27" s="162" t="s">
         <v>268</v>
       </c>
-      <c r="M27" s="349" t="s">
+      <c r="M27" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N27" s="353">
+      <c r="N27" s="163">
         <v>42825</v>
       </c>
       <c r="O27" s="1" t="s">
@@ -24443,83 +24534,83 @@
       <c r="P27" s="164" t="s">
         <v>268</v>
       </c>
-      <c r="Q27" s="349" t="s">
+      <c r="Q27" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R27" s="353">
+      <c r="R27" s="163">
         <v>42825</v>
       </c>
       <c r="S27" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T27" s="349"/>
-      <c r="U27" s="356"/>
-      <c r="V27" s="356"/>
-      <c r="W27" s="349" t="s">
+      <c r="T27" s="162"/>
+      <c r="U27" s="166"/>
+      <c r="V27" s="166"/>
+      <c r="W27" s="162" t="s">
         <v>269</v>
       </c>
-      <c r="X27" s="349" t="s">
+      <c r="X27" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="Y27" s="353">
+      <c r="Y27" s="163">
         <v>43190</v>
       </c>
-      <c r="Z27" s="353">
+      <c r="Z27" s="163">
         <v>43190</v>
       </c>
-      <c r="AA27" s="349"/>
-      <c r="AB27" s="349" t="s">
+      <c r="AA27" s="162"/>
+      <c r="AB27" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC27" s="353">
+      <c r="AC27" s="163">
         <v>43440</v>
       </c>
-      <c r="AD27" s="353">
+      <c r="AD27" s="163">
         <v>43440</v>
       </c>
-      <c r="AE27" s="357" t="s">
+      <c r="AE27" s="277" t="s">
         <v>270</v>
       </c>
-      <c r="AF27" s="361">
+      <c r="AF27" s="261">
         <v>43440</v>
       </c>
-      <c r="AG27" s="361">
+      <c r="AG27" s="261">
         <v>43440</v>
       </c>
-      <c r="AH27" s="353">
+      <c r="AH27" s="163">
         <v>44502</v>
       </c>
-      <c r="AI27" s="349" t="s">
+      <c r="AI27" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ27" s="349"/>
-      <c r="AK27" s="349"/>
-      <c r="AL27" s="365"/>
-      <c r="AM27" s="349"/>
-      <c r="AN27" s="349"/>
-      <c r="AO27" s="349"/>
-      <c r="AP27" s="349"/>
-      <c r="AQ27" s="367"/>
-      <c r="AR27" s="349"/>
-      <c r="AS27" s="349"/>
-      <c r="AT27" s="349"/>
-      <c r="AU27" s="349"/>
-      <c r="AV27" s="349"/>
-      <c r="AW27" s="349"/>
-      <c r="AX27" s="349" t="s">
+      <c r="AJ27" s="162"/>
+      <c r="AK27" s="162"/>
+      <c r="AL27" s="160"/>
+      <c r="AM27" s="162"/>
+      <c r="AN27" s="162"/>
+      <c r="AO27" s="162"/>
+      <c r="AP27" s="162"/>
+      <c r="AQ27" s="247"/>
+      <c r="AR27" s="162"/>
+      <c r="AS27" s="162"/>
+      <c r="AT27" s="162"/>
+      <c r="AU27" s="162"/>
+      <c r="AV27" s="162"/>
+      <c r="AW27" s="162"/>
+      <c r="AX27" s="162" t="s">
         <v>271</v>
       </c>
-      <c r="AY27" s="349"/>
-      <c r="AZ27" s="349" t="s">
+      <c r="AY27" s="162"/>
+      <c r="AZ27" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA27" s="353">
+      <c r="BA27" s="163">
         <v>45709</v>
       </c>
-      <c r="BB27" s="349" t="s">
+      <c r="BB27" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC27" s="349"/>
+      <c r="BC27" s="162"/>
       <c r="BD27" s="1" t="s">
         <v>272</v>
       </c>
@@ -24532,51 +24623,51 @@
       <c r="BG27" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="BH27" s="349"/>
-      <c r="BI27" s="349"/>
-      <c r="BJ27" s="349"/>
-      <c r="BK27" s="349"/>
-      <c r="BL27" s="349"/>
-      <c r="BM27" s="349"/>
-      <c r="BN27" s="348"/>
+      <c r="BH27" s="162"/>
+      <c r="BI27" s="162"/>
+      <c r="BJ27" s="162"/>
+      <c r="BK27" s="162"/>
+      <c r="BL27" s="162"/>
+      <c r="BM27" s="162"/>
+      <c r="BN27" s="104"/>
     </row>
     <row r="28" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A28" s="348"/>
+      <c r="A28" s="104"/>
       <c r="B28" s="162" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="349" t="s">
+      <c r="C28" s="162" t="s">
         <v>277</v>
       </c>
-      <c r="D28" s="349" t="s">
+      <c r="D28" s="162" t="s">
         <v>264</v>
       </c>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349" t="s">
+      <c r="E28" s="162"/>
+      <c r="F28" s="162" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="349" t="s">
+      <c r="G28" s="162" t="s">
         <v>278</v>
       </c>
       <c r="H28" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="349" t="s">
+      <c r="I28" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J28" s="353">
+      <c r="J28" s="163">
         <v>42655</v>
       </c>
       <c r="K28" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L28" s="349" t="s">
+      <c r="L28" s="162" t="s">
         <v>232</v>
       </c>
-      <c r="M28" s="349" t="s">
+      <c r="M28" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N28" s="353">
+      <c r="N28" s="163">
         <v>42655</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -24585,109 +24676,109 @@
       <c r="P28" s="164" t="s">
         <v>232</v>
       </c>
-      <c r="Q28" s="349" t="s">
+      <c r="Q28" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R28" s="353">
+      <c r="R28" s="163">
         <v>42655</v>
       </c>
       <c r="S28" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T28" s="349"/>
-      <c r="U28" s="356"/>
-      <c r="V28" s="356"/>
-      <c r="W28" s="349"/>
-      <c r="X28" s="349"/>
-      <c r="Y28" s="349"/>
-      <c r="Z28" s="349"/>
-      <c r="AA28" s="349"/>
-      <c r="AB28" s="349" t="s">
+      <c r="T28" s="162"/>
+      <c r="U28" s="166"/>
+      <c r="V28" s="166"/>
+      <c r="W28" s="162"/>
+      <c r="X28" s="162"/>
+      <c r="Y28" s="162"/>
+      <c r="Z28" s="162"/>
+      <c r="AA28" s="162"/>
+      <c r="AB28" s="162" t="s">
         <v>279</v>
       </c>
-      <c r="AC28" s="353">
+      <c r="AC28" s="163">
         <v>42855</v>
       </c>
-      <c r="AD28" s="353">
+      <c r="AD28" s="163">
         <v>42855</v>
       </c>
-      <c r="AE28" s="357" t="s">
+      <c r="AE28" s="277" t="s">
         <v>280</v>
       </c>
-      <c r="AF28" s="361">
+      <c r="AF28" s="261">
         <v>42855</v>
       </c>
-      <c r="AG28" s="361">
+      <c r="AG28" s="261">
         <v>42855</v>
       </c>
-      <c r="AH28" s="349"/>
-      <c r="AI28" s="349" t="s">
+      <c r="AH28" s="162"/>
+      <c r="AI28" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ28" s="349"/>
-      <c r="AK28" s="349"/>
-      <c r="AL28" s="365">
+      <c r="AJ28" s="162"/>
+      <c r="AK28" s="162"/>
+      <c r="AL28" s="160">
         <v>400</v>
       </c>
-      <c r="AM28" s="349" t="s">
+      <c r="AM28" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO28" s="349"/>
-      <c r="AP28" s="349"/>
-      <c r="AQ28" s="367">
+      <c r="AO28" s="162"/>
+      <c r="AP28" s="162"/>
+      <c r="AQ28" s="247">
         <v>400</v>
       </c>
-      <c r="AR28" s="349" t="s">
+      <c r="AR28" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT28" s="349"/>
-      <c r="AU28" s="349"/>
-      <c r="AV28" s="349">
+      <c r="AT28" s="162"/>
+      <c r="AU28" s="162"/>
+      <c r="AV28" s="162">
         <v>300</v>
       </c>
-      <c r="AW28" s="349"/>
-      <c r="AX28" s="349" t="s">
+      <c r="AW28" s="162"/>
+      <c r="AX28" s="162" t="s">
         <v>281</v>
       </c>
-      <c r="AY28" s="349"/>
-      <c r="AZ28" s="349" t="s">
+      <c r="AY28" s="162"/>
+      <c r="AZ28" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA28" s="353">
+      <c r="BA28" s="163">
         <v>45709</v>
       </c>
-      <c r="BB28" s="349" t="s">
+      <c r="BB28" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC28" s="349"/>
+      <c r="BC28" s="162"/>
       <c r="BD28" s="1" t="s">
         <v>282</v>
       </c>
       <c r="BE28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="BF28" s="349"/>
-      <c r="BG28" s="349"/>
-      <c r="BH28" s="349"/>
-      <c r="BI28" s="349"/>
-      <c r="BJ28" s="349"/>
-      <c r="BK28" s="349"/>
-      <c r="BL28" s="349"/>
-      <c r="BM28" s="349"/>
-      <c r="BN28" s="348"/>
+      <c r="BF28" s="162"/>
+      <c r="BG28" s="162"/>
+      <c r="BH28" s="162"/>
+      <c r="BI28" s="162"/>
+      <c r="BJ28" s="162"/>
+      <c r="BK28" s="162"/>
+      <c r="BL28" s="162"/>
+      <c r="BM28" s="162"/>
+      <c r="BN28" s="104"/>
     </row>
     <row r="29" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A29" s="348"/>
-      <c r="B29" s="349" t="s">
+      <c r="A29" s="104"/>
+      <c r="B29" s="162" t="s">
         <v>284</v>
       </c>
-      <c r="C29" s="349" t="s">
+      <c r="C29" s="162" t="s">
         <v>277</v>
       </c>
       <c r="D29" s="162" t="s">
@@ -25199,44 +25290,44 @@
       <c r="BN32" s="104"/>
     </row>
     <row r="33" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A33" s="348"/>
-      <c r="B33" s="349" t="s">
+      <c r="A33" s="104"/>
+      <c r="B33" s="162" t="s">
         <v>328</v>
       </c>
-      <c r="C33" s="349" t="s">
+      <c r="C33" s="162" t="s">
         <v>315</v>
       </c>
-      <c r="D33" s="349" t="s">
+      <c r="D33" s="162" t="s">
         <v>316</v>
       </c>
-      <c r="E33" s="349" t="s">
+      <c r="E33" s="162" t="s">
         <v>317</v>
       </c>
-      <c r="F33" s="349" t="s">
+      <c r="F33" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="G33" s="349" t="s">
+      <c r="G33" s="162" t="s">
         <v>319</v>
       </c>
       <c r="H33" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I33" s="349" t="s">
+      <c r="I33" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="J33" s="353">
+      <c r="J33" s="163">
         <v>45401</v>
       </c>
       <c r="K33" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L33" s="355" t="s">
+      <c r="L33" s="204" t="s">
         <v>320</v>
       </c>
-      <c r="M33" s="349" t="s">
+      <c r="M33" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N33" s="353">
+      <c r="N33" s="163">
         <v>45401</v>
       </c>
       <c r="O33" s="1" t="s">
@@ -25245,99 +25336,99 @@
       <c r="P33" s="178" t="s">
         <v>72</v>
       </c>
-      <c r="Q33" s="349" t="s">
+      <c r="Q33" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R33" s="353">
+      <c r="R33" s="163">
         <v>45401</v>
       </c>
       <c r="S33" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T33" s="349"/>
-      <c r="U33" s="356" t="s">
+      <c r="T33" s="162"/>
+      <c r="U33" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="V33" s="356">
+      <c r="V33" s="166">
         <v>0.33</v>
       </c>
-      <c r="W33" s="349"/>
-      <c r="X33" s="349"/>
-      <c r="Y33" s="349"/>
-      <c r="Z33" s="349"/>
-      <c r="AA33" s="349"/>
-      <c r="AB33" s="349"/>
-      <c r="AC33" s="349"/>
-      <c r="AD33" s="349"/>
-      <c r="AE33" s="357">
+      <c r="W33" s="162"/>
+      <c r="X33" s="162"/>
+      <c r="Y33" s="162"/>
+      <c r="Z33" s="162"/>
+      <c r="AA33" s="162"/>
+      <c r="AB33" s="162"/>
+      <c r="AC33" s="162"/>
+      <c r="AD33" s="162"/>
+      <c r="AE33" s="277">
         <v>2025</v>
       </c>
-      <c r="AF33" s="360"/>
-      <c r="AG33" s="360"/>
-      <c r="AH33" s="349"/>
-      <c r="AI33" s="349" t="s">
+      <c r="AF33" s="260"/>
+      <c r="AG33" s="260"/>
+      <c r="AH33" s="162"/>
+      <c r="AI33" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="AJ33" s="349"/>
-      <c r="AK33" s="349" t="s">
+      <c r="AJ33" s="162"/>
+      <c r="AK33" s="162" t="s">
         <v>321</v>
       </c>
-      <c r="AL33" s="365">
+      <c r="AL33" s="160">
         <v>25000</v>
       </c>
-      <c r="AM33" s="349" t="s">
+      <c r="AM33" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO33" s="349"/>
-      <c r="AP33" s="349"/>
-      <c r="AQ33" s="367">
+      <c r="AO33" s="162"/>
+      <c r="AP33" s="162"/>
+      <c r="AQ33" s="247">
         <v>25000</v>
       </c>
-      <c r="AR33" s="349" t="s">
+      <c r="AR33" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT33" s="349"/>
-      <c r="AU33" s="349"/>
-      <c r="AV33" s="349"/>
-      <c r="AW33" s="349"/>
-      <c r="AX33" s="349" t="s">
+      <c r="AT33" s="162"/>
+      <c r="AU33" s="162"/>
+      <c r="AV33" s="162"/>
+      <c r="AW33" s="162"/>
+      <c r="AX33" s="162" t="s">
         <v>329</v>
       </c>
-      <c r="AY33" s="349"/>
-      <c r="AZ33" s="349" t="s">
+      <c r="AY33" s="162"/>
+      <c r="AZ33" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA33" s="353">
+      <c r="BA33" s="163">
         <v>45712</v>
       </c>
-      <c r="BB33" s="349" t="s">
+      <c r="BB33" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC33" s="349"/>
-      <c r="BD33" s="349"/>
-      <c r="BE33" s="349"/>
-      <c r="BF33" s="349"/>
-      <c r="BG33" s="349"/>
-      <c r="BH33" s="349"/>
-      <c r="BI33" s="349"/>
-      <c r="BJ33" s="349"/>
-      <c r="BK33" s="349"/>
-      <c r="BL33" s="349"/>
-      <c r="BM33" s="349"/>
-      <c r="BN33" s="348"/>
+      <c r="BC33" s="162"/>
+      <c r="BD33" s="162"/>
+      <c r="BE33" s="162"/>
+      <c r="BF33" s="162"/>
+      <c r="BG33" s="162"/>
+      <c r="BH33" s="162"/>
+      <c r="BI33" s="162"/>
+      <c r="BJ33" s="162"/>
+      <c r="BK33" s="162"/>
+      <c r="BL33" s="162"/>
+      <c r="BM33" s="162"/>
+      <c r="BN33" s="104"/>
     </row>
     <row r="34" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A34" s="348"/>
-      <c r="B34" s="349" t="s">
+      <c r="A34" s="104"/>
+      <c r="B34" s="162" t="s">
         <v>330</v>
       </c>
-      <c r="C34" s="349" t="s">
+      <c r="C34" s="162" t="s">
         <v>315</v>
       </c>
       <c r="D34" s="162" t="s">
@@ -25463,95 +25554,95 @@
       <c r="BN34" s="104"/>
     </row>
     <row r="35" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A35" s="348"/>
-      <c r="B35" s="349" t="s">
+      <c r="A35" s="104"/>
+      <c r="B35" s="162" t="s">
         <v>332</v>
       </c>
       <c r="C35" s="162" t="s">
         <v>333</v>
       </c>
-      <c r="D35" s="349" t="s">
+      <c r="D35" s="162" t="s">
         <v>334</v>
       </c>
-      <c r="E35" s="349"/>
-      <c r="F35" s="349" t="s">
+      <c r="E35" s="162"/>
+      <c r="F35" s="162" t="s">
         <v>335</v>
       </c>
-      <c r="G35" s="349" t="s">
+      <c r="G35" s="162" t="s">
         <v>336</v>
       </c>
       <c r="H35" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I35" s="349" t="s">
+      <c r="I35" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J35" s="353">
+      <c r="J35" s="163">
         <v>44972</v>
       </c>
       <c r="K35" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L35" s="349"/>
-      <c r="M35" s="349"/>
-      <c r="N35" s="349"/>
-      <c r="O35" s="349"/>
+      <c r="L35" s="162"/>
+      <c r="M35" s="162"/>
+      <c r="N35" s="162"/>
+      <c r="O35" s="162"/>
       <c r="P35" s="164"/>
-      <c r="Q35" s="349"/>
-      <c r="R35" s="349"/>
+      <c r="Q35" s="162"/>
+      <c r="R35" s="162"/>
       <c r="S35" s="180"/>
-      <c r="T35" s="349"/>
-      <c r="U35" s="356"/>
-      <c r="V35" s="356"/>
-      <c r="W35" s="349"/>
-      <c r="X35" s="349"/>
-      <c r="Y35" s="349"/>
-      <c r="Z35" s="349"/>
-      <c r="AA35" s="349"/>
-      <c r="AB35" s="349"/>
-      <c r="AC35" s="349"/>
-      <c r="AD35" s="349"/>
-      <c r="AE35" s="357" t="s">
+      <c r="T35" s="162"/>
+      <c r="U35" s="166"/>
+      <c r="V35" s="166"/>
+      <c r="W35" s="162"/>
+      <c r="X35" s="162"/>
+      <c r="Y35" s="162"/>
+      <c r="Z35" s="162"/>
+      <c r="AA35" s="162"/>
+      <c r="AB35" s="162"/>
+      <c r="AC35" s="162"/>
+      <c r="AD35" s="162"/>
+      <c r="AE35" s="277" t="s">
         <v>337</v>
       </c>
-      <c r="AF35" s="360"/>
-      <c r="AG35" s="360"/>
-      <c r="AH35" s="349"/>
-      <c r="AI35" s="349" t="s">
+      <c r="AF35" s="260"/>
+      <c r="AG35" s="260"/>
+      <c r="AH35" s="162"/>
+      <c r="AI35" s="162" t="s">
         <v>338</v>
       </c>
-      <c r="AJ35" s="349"/>
-      <c r="AK35" s="349" t="s">
+      <c r="AJ35" s="162"/>
+      <c r="AK35" s="162" t="s">
         <v>339</v>
       </c>
-      <c r="AL35" s="365"/>
-      <c r="AM35" s="349"/>
-      <c r="AN35" s="349"/>
-      <c r="AO35" s="349"/>
-      <c r="AP35" s="349"/>
-      <c r="AQ35" s="367"/>
-      <c r="AR35" s="349"/>
-      <c r="AS35" s="349"/>
-      <c r="AT35" s="349"/>
-      <c r="AU35" s="349"/>
-      <c r="AV35" s="349"/>
-      <c r="AW35" s="349"/>
-      <c r="AX35" s="349" t="s">
+      <c r="AL35" s="160"/>
+      <c r="AM35" s="162"/>
+      <c r="AN35" s="162"/>
+      <c r="AO35" s="162"/>
+      <c r="AP35" s="162"/>
+      <c r="AQ35" s="247"/>
+      <c r="AR35" s="162"/>
+      <c r="AS35" s="162"/>
+      <c r="AT35" s="162"/>
+      <c r="AU35" s="162"/>
+      <c r="AV35" s="162"/>
+      <c r="AW35" s="162"/>
+      <c r="AX35" s="162" t="s">
         <v>340</v>
       </c>
-      <c r="AY35" s="349" t="s">
+      <c r="AY35" s="162" t="s">
         <v>341</v>
       </c>
-      <c r="AZ35" s="349" t="s">
+      <c r="AZ35" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA35" s="353">
+      <c r="BA35" s="163">
         <v>45712</v>
       </c>
-      <c r="BB35" s="349" t="s">
+      <c r="BB35" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC35" s="349"/>
+      <c r="BC35" s="162"/>
       <c r="BD35" s="1" t="s">
         <v>342</v>
       </c>
@@ -25567,16 +25658,16 @@
       <c r="BH35" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="BI35" s="349"/>
-      <c r="BJ35" s="349"/>
-      <c r="BK35" s="349"/>
-      <c r="BL35" s="349"/>
-      <c r="BM35" s="349"/>
-      <c r="BN35" s="348"/>
+      <c r="BI35" s="162"/>
+      <c r="BJ35" s="162"/>
+      <c r="BK35" s="162"/>
+      <c r="BL35" s="162"/>
+      <c r="BM35" s="162"/>
+      <c r="BN35" s="104"/>
     </row>
     <row r="36" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A36" s="348"/>
-      <c r="B36" s="349" t="s">
+      <c r="A36" s="104"/>
+      <c r="B36" s="162" t="s">
         <v>347</v>
       </c>
       <c r="C36" s="162" t="s">
@@ -25697,42 +25788,42 @@
       <c r="BN36" s="104"/>
     </row>
     <row r="37" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A37" s="348"/>
-      <c r="B37" s="349" t="s">
+      <c r="A37" s="104"/>
+      <c r="B37" s="162" t="s">
         <v>354</v>
       </c>
-      <c r="C37" s="349" t="s">
+      <c r="C37" s="162" t="s">
         <v>355</v>
       </c>
-      <c r="D37" s="349" t="s">
+      <c r="D37" s="162" t="s">
         <v>356</v>
       </c>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349" t="s">
+      <c r="E37" s="162"/>
+      <c r="F37" s="162" t="s">
         <v>357</v>
       </c>
-      <c r="G37" s="349" t="s">
+      <c r="G37" s="162" t="s">
         <v>358</v>
       </c>
       <c r="H37" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I37" s="349" t="s">
+      <c r="I37" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J37" s="353">
+      <c r="J37" s="163">
         <v>44180</v>
       </c>
       <c r="K37" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L37" s="355" t="s">
+      <c r="L37" s="204" t="s">
         <v>359</v>
       </c>
-      <c r="M37" s="349" t="s">
+      <c r="M37" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N37" s="353">
+      <c r="N37" s="163">
         <v>45686</v>
       </c>
       <c r="O37" s="1" t="s">
@@ -25741,99 +25832,99 @@
       <c r="P37" s="178" t="s">
         <v>164</v>
       </c>
-      <c r="Q37" s="349" t="s">
+      <c r="Q37" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R37" s="353">
+      <c r="R37" s="163">
         <v>45686</v>
       </c>
       <c r="S37" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T37" s="349"/>
-      <c r="U37" s="356" t="s">
+      <c r="T37" s="162"/>
+      <c r="U37" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="V37" s="356">
+      <c r="V37" s="166">
         <v>0.5</v>
       </c>
-      <c r="W37" s="349" t="s">
+      <c r="W37" s="162" t="s">
         <v>360</v>
       </c>
-      <c r="X37" s="349"/>
-      <c r="Y37" s="349"/>
-      <c r="Z37" s="349"/>
-      <c r="AA37" s="349" t="s">
+      <c r="X37" s="162"/>
+      <c r="Y37" s="162"/>
+      <c r="Z37" s="162"/>
+      <c r="AA37" s="162" t="s">
         <v>361</v>
       </c>
-      <c r="AB37" s="349" t="s">
+      <c r="AB37" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="AC37" s="353">
+      <c r="AC37" s="163">
         <v>46203</v>
       </c>
-      <c r="AD37" s="353">
+      <c r="AD37" s="163">
         <v>46203</v>
       </c>
-      <c r="AE37" s="357" t="s">
+      <c r="AE37" s="277" t="s">
         <v>362</v>
       </c>
-      <c r="AF37" s="361">
+      <c r="AF37" s="261">
         <v>46203</v>
       </c>
-      <c r="AG37" s="361">
+      <c r="AG37" s="261">
         <v>46203</v>
       </c>
-      <c r="AH37" s="349"/>
-      <c r="AI37" s="349" t="s">
+      <c r="AH37" s="162"/>
+      <c r="AI37" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="AJ37" s="349"/>
-      <c r="AK37" s="349" t="s">
+      <c r="AJ37" s="162"/>
+      <c r="AK37" s="162" t="s">
         <v>363</v>
       </c>
-      <c r="AL37" s="365">
+      <c r="AL37" s="160">
         <v>200000</v>
       </c>
-      <c r="AM37" s="349" t="s">
+      <c r="AM37" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN37" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO37" s="349"/>
-      <c r="AP37" s="349"/>
-      <c r="AQ37" s="367">
+      <c r="AO37" s="162"/>
+      <c r="AP37" s="162"/>
+      <c r="AQ37" s="247">
         <v>150000</v>
       </c>
-      <c r="AR37" s="349" t="s">
+      <c r="AR37" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS37" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT37" s="349"/>
-      <c r="AU37" s="349"/>
-      <c r="AV37" s="349">
+      <c r="AT37" s="162"/>
+      <c r="AU37" s="162"/>
+      <c r="AV37" s="162">
         <v>3000</v>
       </c>
-      <c r="AW37" s="349"/>
-      <c r="AX37" s="349" t="s">
+      <c r="AW37" s="162"/>
+      <c r="AX37" s="162" t="s">
         <v>364</v>
       </c>
-      <c r="AY37" s="349" t="s">
+      <c r="AY37" s="162" t="s">
         <v>365</v>
       </c>
-      <c r="AZ37" s="349" t="s">
+      <c r="AZ37" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA37" s="353">
+      <c r="BA37" s="163">
         <v>45712</v>
       </c>
-      <c r="BB37" s="349" t="s">
+      <c r="BB37" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC37" s="349"/>
+      <c r="BC37" s="162"/>
       <c r="BD37" s="1" t="s">
         <v>366</v>
       </c>
@@ -25852,11 +25943,11 @@
       <c r="BI37" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="BJ37" s="349"/>
-      <c r="BK37" s="349"/>
-      <c r="BL37" s="349"/>
-      <c r="BM37" s="349"/>
-      <c r="BN37" s="348"/>
+      <c r="BJ37" s="162"/>
+      <c r="BK37" s="162"/>
+      <c r="BL37" s="162"/>
+      <c r="BM37" s="162"/>
+      <c r="BN37" s="104"/>
     </row>
     <row r="38" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A38" s="104"/>
@@ -25999,42 +26090,42 @@
       <c r="BN38" s="104"/>
     </row>
     <row r="39" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A39" s="348"/>
-      <c r="B39" s="349" t="s">
+      <c r="A39" s="104"/>
+      <c r="B39" s="162" t="s">
         <v>383</v>
       </c>
-      <c r="C39" s="349" t="s">
+      <c r="C39" s="162" t="s">
         <v>384</v>
       </c>
-      <c r="D39" s="349" t="s">
+      <c r="D39" s="162" t="s">
         <v>385</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349" t="s">
+      <c r="E39" s="162"/>
+      <c r="F39" s="162" t="s">
         <v>182</v>
       </c>
-      <c r="G39" s="349" t="s">
+      <c r="G39" s="162" t="s">
         <v>386</v>
       </c>
       <c r="H39" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="349" t="s">
+      <c r="I39" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J39" s="353">
+      <c r="J39" s="163">
         <v>44722</v>
       </c>
       <c r="K39" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L39" s="355" t="s">
+      <c r="L39" s="204" t="s">
         <v>243</v>
       </c>
-      <c r="M39" s="349" t="s">
+      <c r="M39" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N39" s="353">
+      <c r="N39" s="163">
         <v>45464</v>
       </c>
       <c r="O39" s="1" t="s">
@@ -26043,85 +26134,85 @@
       <c r="P39" s="178" t="s">
         <v>115</v>
       </c>
-      <c r="Q39" s="349" t="s">
+      <c r="Q39" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R39" s="353">
+      <c r="R39" s="163">
         <v>45464</v>
       </c>
       <c r="S39" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T39" s="349"/>
-      <c r="U39" s="356" t="s">
+      <c r="T39" s="162"/>
+      <c r="U39" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="V39" s="356">
+      <c r="V39" s="166">
         <v>0.25</v>
       </c>
-      <c r="W39" s="349"/>
-      <c r="X39" s="349"/>
-      <c r="Y39" s="349"/>
-      <c r="Z39" s="349"/>
-      <c r="AA39" s="349"/>
-      <c r="AB39" s="349" t="s">
+      <c r="W39" s="162"/>
+      <c r="X39" s="162"/>
+      <c r="Y39" s="162"/>
+      <c r="Z39" s="162"/>
+      <c r="AA39" s="162"/>
+      <c r="AB39" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC39" s="353">
+      <c r="AC39" s="163">
         <v>45463</v>
       </c>
-      <c r="AD39" s="353">
+      <c r="AD39" s="163">
         <v>45463</v>
       </c>
-      <c r="AE39" s="357" t="s">
+      <c r="AE39" s="277" t="s">
         <v>387</v>
       </c>
-      <c r="AF39" s="361">
+      <c r="AF39" s="261">
         <v>46053</v>
       </c>
-      <c r="AG39" s="361">
+      <c r="AG39" s="261">
         <v>46053</v>
       </c>
-      <c r="AH39" s="349"/>
-      <c r="AI39" s="349" t="s">
+      <c r="AH39" s="162"/>
+      <c r="AI39" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="AJ39" s="349"/>
-      <c r="AK39" s="349"/>
-      <c r="AL39" s="365"/>
-      <c r="AM39" s="349"/>
-      <c r="AN39" s="349"/>
-      <c r="AO39" s="349"/>
-      <c r="AP39" s="349"/>
-      <c r="AQ39" s="367">
+      <c r="AJ39" s="162"/>
+      <c r="AK39" s="162"/>
+      <c r="AL39" s="160"/>
+      <c r="AM39" s="162"/>
+      <c r="AN39" s="162"/>
+      <c r="AO39" s="162"/>
+      <c r="AP39" s="162"/>
+      <c r="AQ39" s="247">
         <v>5591</v>
       </c>
-      <c r="AR39" s="349" t="s">
+      <c r="AR39" s="162" t="s">
         <v>64</v>
       </c>
-      <c r="AS39" s="349" t="s">
+      <c r="AS39" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="AT39" s="349"/>
-      <c r="AU39" s="349"/>
-      <c r="AV39" s="349"/>
-      <c r="AW39" s="349"/>
-      <c r="AX39" s="349" t="s">
+      <c r="AT39" s="162"/>
+      <c r="AU39" s="162"/>
+      <c r="AV39" s="162"/>
+      <c r="AW39" s="162"/>
+      <c r="AX39" s="162" t="s">
         <v>388</v>
       </c>
-      <c r="AY39" s="349" t="s">
+      <c r="AY39" s="162" t="s">
         <v>389</v>
       </c>
-      <c r="AZ39" s="349" t="s">
+      <c r="AZ39" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA39" s="353">
+      <c r="BA39" s="163">
         <v>45712</v>
       </c>
-      <c r="BB39" s="349" t="s">
+      <c r="BB39" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC39" s="349"/>
+      <c r="BC39" s="162"/>
       <c r="BD39" s="1" t="s">
         <v>390</v>
       </c>
@@ -26143,10 +26234,10 @@
       <c r="BJ39" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="BK39" s="349"/>
-      <c r="BL39" s="349"/>
-      <c r="BM39" s="349"/>
-      <c r="BN39" s="348"/>
+      <c r="BK39" s="162"/>
+      <c r="BL39" s="162"/>
+      <c r="BM39" s="162"/>
+      <c r="BN39" s="104"/>
     </row>
     <row r="40" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A40" s="104"/>
@@ -26307,42 +26398,42 @@
       <c r="BN40" s="104"/>
     </row>
     <row r="41" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A41" s="348"/>
-      <c r="B41" s="369" t="s">
+      <c r="A41" s="104"/>
+      <c r="B41" s="348" t="s">
         <v>412</v>
       </c>
-      <c r="C41" s="369" t="s">
+      <c r="C41" s="348" t="s">
         <v>413</v>
       </c>
-      <c r="D41" s="349" t="s">
+      <c r="D41" s="162" t="s">
         <v>399</v>
       </c>
-      <c r="E41" s="349"/>
-      <c r="F41" s="349" t="s">
+      <c r="E41" s="162"/>
+      <c r="F41" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="G41" s="349" t="s">
+      <c r="G41" s="162" t="s">
         <v>414</v>
       </c>
       <c r="H41" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I41" s="349" t="s">
+      <c r="I41" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J41" s="353">
+      <c r="J41" s="163">
         <v>43846</v>
       </c>
       <c r="K41" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L41" s="355" t="s">
+      <c r="L41" s="204" t="s">
         <v>415</v>
       </c>
-      <c r="M41" s="349" t="s">
+      <c r="M41" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N41" s="353">
+      <c r="N41" s="163">
         <v>43846</v>
       </c>
       <c r="O41" s="1" t="s">
@@ -26351,81 +26442,81 @@
       <c r="P41" s="178" t="s">
         <v>268</v>
       </c>
-      <c r="Q41" s="349" t="s">
+      <c r="Q41" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="R41" s="353">
+      <c r="R41" s="163">
         <v>43846</v>
       </c>
       <c r="S41" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T41" s="349"/>
-      <c r="U41" s="356" t="s">
+      <c r="T41" s="162"/>
+      <c r="U41" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="V41" s="356">
+      <c r="V41" s="166">
         <v>0.25</v>
       </c>
-      <c r="W41" s="349"/>
-      <c r="X41" s="349"/>
-      <c r="Y41" s="349"/>
-      <c r="Z41" s="349"/>
-      <c r="AA41" s="349"/>
-      <c r="AB41" s="349" t="s">
+      <c r="W41" s="162"/>
+      <c r="X41" s="162"/>
+      <c r="Y41" s="162"/>
+      <c r="Z41" s="162"/>
+      <c r="AA41" s="162"/>
+      <c r="AB41" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC41" s="353">
+      <c r="AC41" s="163">
         <v>44152</v>
       </c>
-      <c r="AD41" s="353">
+      <c r="AD41" s="163">
         <v>44152</v>
       </c>
-      <c r="AE41" s="357"/>
-      <c r="AF41" s="360"/>
-      <c r="AG41" s="360"/>
-      <c r="AH41" s="349"/>
-      <c r="AI41" s="349" t="s">
+      <c r="AE41" s="277"/>
+      <c r="AF41" s="260"/>
+      <c r="AG41" s="260"/>
+      <c r="AH41" s="162"/>
+      <c r="AI41" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="AJ41" s="349"/>
-      <c r="AK41" s="349" t="s">
+      <c r="AJ41" s="162"/>
+      <c r="AK41" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="AL41" s="365"/>
-      <c r="AM41" s="349"/>
-      <c r="AN41" s="349"/>
-      <c r="AO41" s="349"/>
-      <c r="AP41" s="349"/>
-      <c r="AQ41" s="367">
+      <c r="AL41" s="160"/>
+      <c r="AM41" s="162"/>
+      <c r="AN41" s="162"/>
+      <c r="AO41" s="162"/>
+      <c r="AP41" s="162"/>
+      <c r="AQ41" s="247">
         <v>44286</v>
       </c>
-      <c r="AR41" s="349" t="s">
+      <c r="AR41" s="162" t="s">
         <v>64</v>
       </c>
-      <c r="AS41" s="349" t="s">
+      <c r="AS41" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="AT41" s="349"/>
-      <c r="AU41" s="349"/>
-      <c r="AV41" s="349"/>
-      <c r="AW41" s="349"/>
-      <c r="AX41" s="349" t="s">
+      <c r="AT41" s="162"/>
+      <c r="AU41" s="162"/>
+      <c r="AV41" s="162"/>
+      <c r="AW41" s="162"/>
+      <c r="AX41" s="162" t="s">
         <v>417</v>
       </c>
-      <c r="AY41" s="349" t="s">
+      <c r="AY41" s="162" t="s">
         <v>418</v>
       </c>
-      <c r="AZ41" s="349" t="s">
+      <c r="AZ41" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA41" s="353">
+      <c r="BA41" s="163">
         <v>45712</v>
       </c>
-      <c r="BB41" s="349" t="s">
+      <c r="BB41" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC41" s="349"/>
+      <c r="BC41" s="162"/>
       <c r="BD41" s="1" t="s">
         <v>419</v>
       </c>
@@ -26438,16 +26529,16 @@
       <c r="BG41" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="BH41" s="349"/>
-      <c r="BI41" s="349"/>
-      <c r="BJ41" s="349"/>
-      <c r="BK41" s="349"/>
-      <c r="BL41" s="349"/>
-      <c r="BM41" s="349"/>
-      <c r="BN41" s="348"/>
+      <c r="BH41" s="162"/>
+      <c r="BI41" s="162"/>
+      <c r="BJ41" s="162"/>
+      <c r="BK41" s="162"/>
+      <c r="BL41" s="162"/>
+      <c r="BM41" s="162"/>
+      <c r="BN41" s="104"/>
     </row>
     <row r="42" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A42" s="348"/>
+      <c r="A42" s="104"/>
       <c r="B42" s="162" t="s">
         <v>423</v>
       </c>
@@ -26564,10 +26655,10 @@
     </row>
     <row r="43" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="104"/>
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="162" t="s">
         <v>426</v>
       </c>
-      <c r="C43" s="349" t="s">
+      <c r="C43" s="162" t="s">
         <v>427</v>
       </c>
       <c r="D43" s="162" t="s">
@@ -26617,7 +26708,7 @@
         <v>65</v>
       </c>
       <c r="T43" s="162"/>
-      <c r="U43" s="356" t="s">
+      <c r="U43" s="166" t="s">
         <v>68</v>
       </c>
       <c r="V43" s="166">
@@ -26643,7 +26734,7 @@
       <c r="AJ43" s="162"/>
       <c r="AK43" s="162"/>
       <c r="AL43" s="160"/>
-      <c r="AM43" s="349"/>
+      <c r="AM43" s="162"/>
       <c r="AN43" s="162"/>
       <c r="AO43" s="162"/>
       <c r="AP43" s="162"/>
@@ -28251,7 +28342,7 @@
         <f>C58&amp;"_0"</f>
         <v>Z_HU_MercedesBenz_Kecskemet_0</v>
       </c>
-      <c r="C58" s="348" t="str">
+      <c r="C58" s="104" t="str">
         <f>"Z_HU_MercedesBenz_"&amp;G58</f>
         <v>Z_HU_MercedesBenz_Kecskemet</v>
       </c>
@@ -28371,7 +28462,7 @@
         <f>C59&amp;"_1"</f>
         <v>Z_HU_MercedesBenz_Kecskemet_1</v>
       </c>
-      <c r="C59" s="348" t="str">
+      <c r="C59" s="104" t="str">
         <f>"Z_HU_MercedesBenz_"&amp;G59</f>
         <v>Z_HU_MercedesBenz_Kecskemet</v>
       </c>
@@ -28482,154 +28573,154 @@
       <c r="BN59" s="109"/>
     </row>
     <row r="60" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A60" s="350" t="s">
+      <c r="A60" s="127" t="s">
         <v>520</v>
       </c>
-      <c r="B60" s="349" t="s">
+      <c r="B60" s="162" t="s">
         <v>1056</v>
       </c>
-      <c r="C60" s="349" t="s">
+      <c r="C60" s="162" t="s">
         <v>1052</v>
       </c>
-      <c r="D60" s="349" t="s">
+      <c r="D60" s="162" t="s">
         <v>521</v>
       </c>
-      <c r="E60" s="349"/>
-      <c r="F60" s="349" t="s">
+      <c r="E60" s="162"/>
+      <c r="F60" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G60" s="349" t="s">
+      <c r="G60" s="162" t="s">
         <v>522</v>
       </c>
       <c r="H60" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="349" t="s">
+      <c r="I60" s="162" t="s">
         <v>61</v>
       </c>
       <c r="J60" s="162"/>
       <c r="K60" s="180"/>
-      <c r="L60" s="349"/>
-      <c r="M60" s="349"/>
-      <c r="N60" s="349"/>
-      <c r="O60" s="349"/>
+      <c r="L60" s="162"/>
+      <c r="M60" s="162"/>
+      <c r="N60" s="162"/>
+      <c r="O60" s="162"/>
       <c r="P60" s="164"/>
-      <c r="Q60" s="349"/>
-      <c r="R60" s="349"/>
+      <c r="Q60" s="162"/>
+      <c r="R60" s="162"/>
       <c r="S60" s="180"/>
-      <c r="T60" s="349"/>
-      <c r="U60" s="356"/>
-      <c r="V60" s="356"/>
-      <c r="W60" s="349"/>
-      <c r="X60" s="349"/>
-      <c r="Y60" s="349"/>
-      <c r="Z60" s="349"/>
-      <c r="AA60" s="349"/>
-      <c r="AB60" s="349"/>
-      <c r="AC60" s="349"/>
-      <c r="AD60" s="349"/>
-      <c r="AE60" s="357">
+      <c r="T60" s="162"/>
+      <c r="U60" s="166"/>
+      <c r="V60" s="166"/>
+      <c r="W60" s="162"/>
+      <c r="X60" s="162"/>
+      <c r="Y60" s="162"/>
+      <c r="Z60" s="162"/>
+      <c r="AA60" s="162"/>
+      <c r="AB60" s="162"/>
+      <c r="AC60" s="162"/>
+      <c r="AD60" s="162"/>
+      <c r="AE60" s="277">
         <v>2013</v>
       </c>
       <c r="AF60" s="261">
         <v>41275</v>
       </c>
-      <c r="AG60" s="360"/>
-      <c r="AH60" s="349"/>
-      <c r="AI60" s="349" t="s">
+      <c r="AG60" s="260"/>
+      <c r="AH60" s="162"/>
+      <c r="AI60" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ60" s="349"/>
-      <c r="AK60" s="349" t="s">
+      <c r="AJ60" s="162"/>
+      <c r="AK60" s="162" t="s">
         <v>523</v>
       </c>
-      <c r="AL60" s="365"/>
-      <c r="AM60" s="349"/>
-      <c r="AN60" s="349"/>
-      <c r="AO60" s="349"/>
-      <c r="AP60" s="349"/>
-      <c r="AQ60" s="367">
+      <c r="AL60" s="160"/>
+      <c r="AM60" s="162"/>
+      <c r="AN60" s="162"/>
+      <c r="AO60" s="162"/>
+      <c r="AP60" s="162"/>
+      <c r="AQ60" s="247">
         <v>40710</v>
       </c>
-      <c r="AR60" s="348" t="s">
+      <c r="AR60" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="AS60" s="349" t="s">
+      <c r="AS60" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="AT60" s="349"/>
-      <c r="AU60" s="349"/>
-      <c r="AV60" s="349"/>
-      <c r="AW60" s="349"/>
-      <c r="AX60" s="349" t="s">
+      <c r="AT60" s="162"/>
+      <c r="AU60" s="162"/>
+      <c r="AV60" s="162"/>
+      <c r="AW60" s="162"/>
+      <c r="AX60" s="162" t="s">
         <v>524</v>
       </c>
-      <c r="AY60" s="349"/>
-      <c r="AZ60" s="349" t="s">
+      <c r="AY60" s="162"/>
+      <c r="AZ60" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BA60" s="353">
+      <c r="BA60" s="163">
         <v>45713</v>
       </c>
-      <c r="BB60" s="349" t="s">
+      <c r="BB60" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC60" s="349"/>
+      <c r="BC60" s="162"/>
       <c r="BD60" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="BE60" s="349" t="s">
+      <c r="BE60" s="162" t="s">
         <v>526</v>
       </c>
-      <c r="BF60" s="349" t="s">
+      <c r="BF60" s="162" t="s">
         <v>526</v>
       </c>
-      <c r="BG60" s="349"/>
-      <c r="BH60" s="349"/>
-      <c r="BI60" s="349"/>
-      <c r="BJ60" s="349"/>
-      <c r="BK60" s="349"/>
-      <c r="BL60" s="349"/>
-      <c r="BM60" s="349"/>
-      <c r="BN60" s="348"/>
+      <c r="BG60" s="162"/>
+      <c r="BH60" s="162"/>
+      <c r="BI60" s="162"/>
+      <c r="BJ60" s="162"/>
+      <c r="BK60" s="162"/>
+      <c r="BL60" s="162"/>
+      <c r="BM60" s="162"/>
+      <c r="BN60" s="104"/>
     </row>
     <row r="61" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="368"/>
-      <c r="B61" s="349" t="s">
+      <c r="A61" s="128"/>
+      <c r="B61" s="162" t="s">
         <v>1057</v>
       </c>
-      <c r="C61" s="349" t="s">
+      <c r="C61" s="162" t="s">
         <v>1052</v>
       </c>
-      <c r="D61" s="349" t="s">
+      <c r="D61" s="162" t="s">
         <v>521</v>
       </c>
-      <c r="E61" s="349"/>
-      <c r="F61" s="349" t="s">
+      <c r="E61" s="162"/>
+      <c r="F61" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G61" s="349" t="s">
+      <c r="G61" s="162" t="s">
         <v>522</v>
       </c>
       <c r="H61" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I61" s="349" t="s">
+      <c r="I61" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="J61" s="353">
+      <c r="J61" s="163">
         <v>44907</v>
       </c>
       <c r="K61" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L61" s="349" t="s">
+      <c r="L61" s="162" t="s">
         <v>527</v>
       </c>
-      <c r="M61" s="349" t="s">
+      <c r="M61" s="162" t="s">
         <v>149</v>
       </c>
-      <c r="N61" s="353">
+      <c r="N61" s="163">
         <v>44907</v>
       </c>
       <c r="O61" s="1" t="s">
@@ -28638,83 +28729,83 @@
       <c r="P61" s="164" t="s">
         <v>528</v>
       </c>
-      <c r="Q61" s="349" t="s">
+      <c r="Q61" s="162" t="s">
         <v>150</v>
       </c>
-      <c r="R61" s="353">
+      <c r="R61" s="163">
         <v>45254</v>
       </c>
       <c r="S61" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T61" s="349"/>
-      <c r="U61" s="356"/>
-      <c r="V61" s="356"/>
-      <c r="W61" s="349"/>
-      <c r="X61" s="349"/>
-      <c r="Y61" s="349"/>
-      <c r="Z61" s="349"/>
-      <c r="AA61" s="349"/>
-      <c r="AB61" s="349" t="s">
+      <c r="T61" s="162"/>
+      <c r="U61" s="166"/>
+      <c r="V61" s="166"/>
+      <c r="W61" s="162"/>
+      <c r="X61" s="162"/>
+      <c r="Y61" s="162"/>
+      <c r="Z61" s="162"/>
+      <c r="AA61" s="162"/>
+      <c r="AB61" s="162" t="s">
         <v>279</v>
       </c>
-      <c r="AC61" s="353">
+      <c r="AC61" s="163">
         <v>45747</v>
       </c>
-      <c r="AD61" s="353">
+      <c r="AD61" s="163">
         <v>45747</v>
       </c>
-      <c r="AE61" s="357"/>
-      <c r="AF61" s="360"/>
-      <c r="AG61" s="360"/>
-      <c r="AH61" s="349"/>
-      <c r="AI61" s="349" t="s">
+      <c r="AE61" s="277"/>
+      <c r="AF61" s="260"/>
+      <c r="AG61" s="260"/>
+      <c r="AH61" s="162"/>
+      <c r="AI61" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ61" s="349"/>
-      <c r="AK61" s="349" t="s">
+      <c r="AJ61" s="162"/>
+      <c r="AK61" s="162" t="s">
         <v>529</v>
       </c>
-      <c r="AL61" s="365">
+      <c r="AL61" s="160">
         <v>100000</v>
       </c>
-      <c r="AM61" s="349" t="s">
+      <c r="AM61" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AN61" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO61" s="349"/>
-      <c r="AP61" s="349"/>
-      <c r="AQ61" s="367">
+      <c r="AO61" s="162"/>
+      <c r="AP61" s="162"/>
+      <c r="AQ61" s="247">
         <v>100000</v>
       </c>
-      <c r="AR61" s="349" t="s">
+      <c r="AR61" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS61" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT61" s="349"/>
-      <c r="AU61" s="349"/>
-      <c r="AV61" s="349"/>
-      <c r="AW61" s="349"/>
-      <c r="AX61" s="349" t="s">
+      <c r="AT61" s="162"/>
+      <c r="AU61" s="162"/>
+      <c r="AV61" s="162"/>
+      <c r="AW61" s="162"/>
+      <c r="AX61" s="162" t="s">
         <v>530</v>
       </c>
-      <c r="AY61" s="349" t="s">
+      <c r="AY61" s="162" t="s">
         <v>418</v>
       </c>
-      <c r="AZ61" s="349" t="s">
+      <c r="AZ61" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BA61" s="353">
+      <c r="BA61" s="163">
         <v>45713</v>
       </c>
-      <c r="BB61" s="349" t="s">
+      <c r="BB61" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC61" s="349"/>
+      <c r="BC61" s="162"/>
       <c r="BD61" s="1" t="s">
         <v>531</v>
       </c>
@@ -28745,7 +28836,7 @@
       <c r="BM61" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="BN61" s="348" t="s">
+      <c r="BN61" s="104" t="s">
         <v>526</v>
       </c>
     </row>
@@ -29001,10 +29092,10 @@
     </row>
     <row r="64" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A64" s="104"/>
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="162" t="s">
         <v>559</v>
       </c>
-      <c r="C64" s="349" t="s">
+      <c r="C64" s="162" t="s">
         <v>560</v>
       </c>
       <c r="D64" s="162" t="s">
@@ -29100,7 +29191,7 @@
         <v>565</v>
       </c>
       <c r="AL64" s="160"/>
-      <c r="AM64" s="349"/>
+      <c r="AM64" s="162"/>
       <c r="AN64" s="162"/>
       <c r="AO64" s="162"/>
       <c r="AP64" s="162"/>
@@ -29153,10 +29244,10 @@
     </row>
     <row r="65" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="104"/>
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="162" t="s">
         <v>572</v>
       </c>
-      <c r="C65" s="349" t="s">
+      <c r="C65" s="162" t="s">
         <v>560</v>
       </c>
       <c r="D65" s="162" t="s">
@@ -29659,7 +29750,7 @@
       <c r="J69" s="239">
         <v>45434</v>
       </c>
-      <c r="K69" s="372" t="s">
+      <c r="K69" s="349" t="s">
         <v>65</v>
       </c>
       <c r="L69" s="109"/>
@@ -30056,42 +30147,42 @@
       <c r="BN72" s="109"/>
     </row>
     <row r="73" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A73" s="348"/>
-      <c r="B73" s="349" t="s">
+      <c r="A73" s="104"/>
+      <c r="B73" s="162" t="s">
         <v>1058</v>
       </c>
-      <c r="C73" s="349" t="s">
+      <c r="C73" s="162" t="s">
         <v>1053</v>
       </c>
-      <c r="D73" s="349" t="s">
+      <c r="D73" s="162" t="s">
         <v>613</v>
       </c>
-      <c r="E73" s="349"/>
-      <c r="F73" s="349" t="s">
+      <c r="E73" s="162"/>
+      <c r="F73" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G73" s="349" t="s">
+      <c r="G73" s="162" t="s">
         <v>621</v>
       </c>
       <c r="H73" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="349" t="s">
+      <c r="I73" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J73" s="353">
+      <c r="J73" s="163">
         <v>44391</v>
       </c>
       <c r="K73" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L73" s="349" t="s">
+      <c r="L73" s="162" t="s">
         <v>136</v>
       </c>
-      <c r="M73" s="349" t="s">
+      <c r="M73" s="162" t="s">
         <v>149</v>
       </c>
-      <c r="N73" s="353">
+      <c r="N73" s="163">
         <v>44383</v>
       </c>
       <c r="O73" s="1" t="s">
@@ -30100,124 +30191,124 @@
       <c r="P73" s="164" t="s">
         <v>136</v>
       </c>
-      <c r="Q73" s="349" t="s">
+      <c r="Q73" s="162" t="s">
         <v>150</v>
       </c>
-      <c r="R73" s="353">
+      <c r="R73" s="163">
         <v>44383</v>
       </c>
       <c r="S73" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T73" s="349"/>
-      <c r="U73" s="356"/>
-      <c r="V73" s="356"/>
-      <c r="W73" s="349"/>
-      <c r="X73" s="349"/>
-      <c r="Y73" s="349"/>
-      <c r="Z73" s="349"/>
-      <c r="AA73" s="349"/>
-      <c r="AB73" s="349" t="s">
+      <c r="T73" s="162"/>
+      <c r="U73" s="166"/>
+      <c r="V73" s="166"/>
+      <c r="W73" s="162"/>
+      <c r="X73" s="162"/>
+      <c r="Y73" s="162"/>
+      <c r="Z73" s="162"/>
+      <c r="AA73" s="162"/>
+      <c r="AB73" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="AC73" s="353">
+      <c r="AC73" s="163">
         <v>45176</v>
       </c>
-      <c r="AD73" s="353">
+      <c r="AD73" s="163">
         <v>45176</v>
       </c>
-      <c r="AE73" s="357"/>
-      <c r="AF73" s="360"/>
-      <c r="AG73" s="360"/>
-      <c r="AH73" s="349"/>
-      <c r="AI73" s="349" t="s">
+      <c r="AE73" s="277"/>
+      <c r="AF73" s="260"/>
+      <c r="AG73" s="260"/>
+      <c r="AH73" s="162"/>
+      <c r="AI73" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ73" s="349"/>
-      <c r="AK73" s="349" t="s">
+      <c r="AJ73" s="162"/>
+      <c r="AK73" s="162" t="s">
         <v>622</v>
       </c>
-      <c r="AL73" s="365"/>
-      <c r="AM73" s="349"/>
-      <c r="AN73" s="349"/>
-      <c r="AO73" s="349"/>
-      <c r="AP73" s="349"/>
-      <c r="AQ73" s="367"/>
-      <c r="AR73" s="349"/>
-      <c r="AS73" s="349"/>
-      <c r="AT73" s="349"/>
-      <c r="AU73" s="349"/>
-      <c r="AV73" s="349"/>
-      <c r="AW73" s="349"/>
-      <c r="AX73" s="349" t="s">
+      <c r="AL73" s="160"/>
+      <c r="AM73" s="162"/>
+      <c r="AN73" s="162"/>
+      <c r="AO73" s="162"/>
+      <c r="AP73" s="162"/>
+      <c r="AQ73" s="247"/>
+      <c r="AR73" s="162"/>
+      <c r="AS73" s="162"/>
+      <c r="AT73" s="162"/>
+      <c r="AU73" s="162"/>
+      <c r="AV73" s="162"/>
+      <c r="AW73" s="162"/>
+      <c r="AX73" s="162" t="s">
         <v>623</v>
       </c>
-      <c r="AY73" s="349" t="s">
+      <c r="AY73" s="162" t="s">
         <v>88</v>
       </c>
-      <c r="AZ73" s="349" t="s">
+      <c r="AZ73" s="162" t="s">
         <v>89</v>
       </c>
-      <c r="BA73" s="353">
+      <c r="BA73" s="163">
         <v>45709</v>
       </c>
-      <c r="BB73" s="349" t="s">
+      <c r="BB73" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="BC73" s="349"/>
+      <c r="BC73" s="162"/>
       <c r="BD73" s="1" t="s">
         <v>624</v>
       </c>
       <c r="BE73" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="BF73" s="349"/>
-      <c r="BG73" s="349"/>
-      <c r="BH73" s="349"/>
-      <c r="BI73" s="349"/>
-      <c r="BJ73" s="349"/>
-      <c r="BK73" s="349"/>
-      <c r="BL73" s="349"/>
-      <c r="BM73" s="349"/>
-      <c r="BN73" s="348"/>
+      <c r="BF73" s="162"/>
+      <c r="BG73" s="162"/>
+      <c r="BH73" s="162"/>
+      <c r="BI73" s="162"/>
+      <c r="BJ73" s="162"/>
+      <c r="BK73" s="162"/>
+      <c r="BL73" s="162"/>
+      <c r="BM73" s="162"/>
+      <c r="BN73" s="104"/>
     </row>
     <row r="74" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="348"/>
-      <c r="B74" s="349" t="s">
+      <c r="A74" s="104"/>
+      <c r="B74" s="162" t="s">
         <v>1059</v>
       </c>
-      <c r="C74" s="349" t="s">
+      <c r="C74" s="162" t="s">
         <v>1053</v>
       </c>
-      <c r="D74" s="349" t="s">
+      <c r="D74" s="162" t="s">
         <v>613</v>
       </c>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349" t="s">
+      <c r="E74" s="162"/>
+      <c r="F74" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G74" s="349" t="s">
+      <c r="G74" s="162" t="s">
         <v>621</v>
       </c>
       <c r="H74" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I74" s="349" t="s">
+      <c r="I74" s="162" t="s">
         <v>626</v>
       </c>
-      <c r="J74" s="353">
+      <c r="J74" s="163">
         <v>45622</v>
       </c>
       <c r="K74" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L74" s="349" t="s">
+      <c r="L74" s="162" t="s">
         <v>243</v>
       </c>
-      <c r="M74" s="349" t="s">
+      <c r="M74" s="162" t="s">
         <v>149</v>
       </c>
-      <c r="N74" s="353">
+      <c r="N74" s="163">
         <v>45622</v>
       </c>
       <c r="O74" s="1" t="s">
@@ -30226,74 +30317,74 @@
       <c r="P74" s="164" t="s">
         <v>243</v>
       </c>
-      <c r="Q74" s="349" t="s">
+      <c r="Q74" s="162" t="s">
         <v>150</v>
       </c>
-      <c r="R74" s="353">
+      <c r="R74" s="163">
         <v>45622</v>
       </c>
       <c r="S74" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="T74" s="349"/>
-      <c r="U74" s="356"/>
-      <c r="V74" s="356"/>
-      <c r="W74" s="349"/>
-      <c r="X74" s="349"/>
-      <c r="Y74" s="349"/>
-      <c r="Z74" s="349"/>
-      <c r="AA74" s="349"/>
-      <c r="AB74" s="349"/>
-      <c r="AC74" s="349"/>
-      <c r="AD74" s="349"/>
-      <c r="AE74" s="357"/>
-      <c r="AF74" s="360"/>
-      <c r="AG74" s="360"/>
-      <c r="AH74" s="349"/>
-      <c r="AI74" s="349" t="s">
+      <c r="T74" s="162"/>
+      <c r="U74" s="166"/>
+      <c r="V74" s="166"/>
+      <c r="W74" s="162"/>
+      <c r="X74" s="162"/>
+      <c r="Y74" s="162"/>
+      <c r="Z74" s="162"/>
+      <c r="AA74" s="162"/>
+      <c r="AB74" s="162"/>
+      <c r="AC74" s="162"/>
+      <c r="AD74" s="162"/>
+      <c r="AE74" s="277"/>
+      <c r="AF74" s="260"/>
+      <c r="AG74" s="260"/>
+      <c r="AH74" s="162"/>
+      <c r="AI74" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ74" s="349"/>
-      <c r="AK74" s="349"/>
-      <c r="AL74" s="365"/>
-      <c r="AM74" s="349"/>
-      <c r="AN74" s="349"/>
-      <c r="AO74" s="349"/>
-      <c r="AP74" s="349"/>
-      <c r="AQ74" s="367"/>
-      <c r="AR74" s="349"/>
-      <c r="AS74" s="349"/>
-      <c r="AT74" s="349"/>
-      <c r="AU74" s="349"/>
-      <c r="AV74" s="349"/>
-      <c r="AW74" s="349"/>
-      <c r="AX74" s="349" t="s">
+      <c r="AJ74" s="162"/>
+      <c r="AK74" s="162"/>
+      <c r="AL74" s="160"/>
+      <c r="AM74" s="162"/>
+      <c r="AN74" s="162"/>
+      <c r="AO74" s="162"/>
+      <c r="AP74" s="162"/>
+      <c r="AQ74" s="247"/>
+      <c r="AR74" s="162"/>
+      <c r="AS74" s="162"/>
+      <c r="AT74" s="162"/>
+      <c r="AU74" s="162"/>
+      <c r="AV74" s="162"/>
+      <c r="AW74" s="162"/>
+      <c r="AX74" s="162" t="s">
         <v>627</v>
       </c>
-      <c r="AY74" s="349" t="s">
+      <c r="AY74" s="162" t="s">
         <v>88</v>
       </c>
-      <c r="AZ74" s="349" t="s">
+      <c r="AZ74" s="162" t="s">
         <v>89</v>
       </c>
-      <c r="BA74" s="353">
+      <c r="BA74" s="163">
         <v>45709</v>
       </c>
-      <c r="BB74" s="349" t="s">
+      <c r="BB74" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="BC74" s="349"/>
-      <c r="BD74" s="349"/>
-      <c r="BE74" s="349"/>
-      <c r="BF74" s="349"/>
-      <c r="BG74" s="349"/>
-      <c r="BH74" s="349"/>
-      <c r="BI74" s="349"/>
-      <c r="BJ74" s="349"/>
-      <c r="BK74" s="349"/>
-      <c r="BL74" s="349"/>
-      <c r="BM74" s="349"/>
-      <c r="BN74" s="348"/>
+      <c r="BC74" s="162"/>
+      <c r="BD74" s="162"/>
+      <c r="BE74" s="162"/>
+      <c r="BF74" s="162"/>
+      <c r="BG74" s="162"/>
+      <c r="BH74" s="162"/>
+      <c r="BI74" s="162"/>
+      <c r="BJ74" s="162"/>
+      <c r="BK74" s="162"/>
+      <c r="BL74" s="162"/>
+      <c r="BM74" s="162"/>
+      <c r="BN74" s="104"/>
     </row>
     <row r="75" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="110"/>
@@ -30625,7 +30716,7 @@
       <c r="BN77" s="104"/>
     </row>
     <row r="78" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="348"/>
+      <c r="A78" s="104"/>
       <c r="B78" s="234" t="str">
         <f>C78&amp;"_1"</f>
         <v>Z_ES_Stellantis_Vigo_1</v>
@@ -30746,7 +30837,7 @@
       <c r="BN78" s="104"/>
     </row>
     <row r="79" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="348"/>
+      <c r="A79" s="104"/>
       <c r="B79" s="233" t="str">
         <f>C79&amp;"_2"</f>
         <v>Z_ES_Stellantis_Vigo_2</v>
@@ -30856,7 +30947,7 @@
       <c r="BN79" s="104"/>
     </row>
     <row r="80" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="348"/>
+      <c r="A80" s="104"/>
       <c r="B80" s="234" t="str">
         <f>C80&amp;"_0"</f>
         <v>Z_ES_Stellantis_Zaragosa_0</v>
@@ -30977,7 +31068,6 @@
     </row>
     <row r="81" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="110"/>
-      <c r="B81" s="352"/>
       <c r="C81" s="106" t="str">
         <f>"Z_FR_"&amp;D81&amp;"_"&amp;G81</f>
         <v>Z_FR_Stellantis _Mulhouse</v>
@@ -31076,105 +31166,105 @@
         <f>"Z_FR_"&amp;D82&amp;"_"&amp;G82</f>
         <v>Z_FR_Stellantis _Rennes</v>
       </c>
-      <c r="D82" s="349" t="s">
+      <c r="D82" s="162" t="s">
         <v>652</v>
       </c>
-      <c r="E82" s="348"/>
-      <c r="F82" s="349" t="s">
+      <c r="E82" s="104"/>
+      <c r="F82" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="G82" s="370" t="s">
+      <c r="G82" s="137" t="s">
         <v>657</v>
       </c>
       <c r="H82" s="164" t="s">
         <v>143</v>
       </c>
-      <c r="I82" s="349" t="s">
+      <c r="I82" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J82" s="354">
+      <c r="J82" s="125">
         <v>45083</v>
       </c>
       <c r="K82" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="L82" s="349" t="s">
+      <c r="L82" s="162" t="s">
         <v>658</v>
       </c>
-      <c r="M82" s="349" t="s">
+      <c r="M82" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N82" s="348"/>
+      <c r="N82" s="104"/>
       <c r="O82" s="1" t="s">
         <v>65</v>
       </c>
       <c r="P82" s="121"/>
-      <c r="Q82" s="348"/>
-      <c r="R82" s="348"/>
+      <c r="Q82" s="104"/>
+      <c r="R82" s="104"/>
       <c r="S82" s="122"/>
-      <c r="T82" s="348"/>
-      <c r="U82" s="348"/>
-      <c r="V82" s="348"/>
-      <c r="W82" s="348"/>
-      <c r="X82" s="348"/>
-      <c r="Y82" s="348"/>
-      <c r="Z82" s="348"/>
-      <c r="AA82" s="348"/>
-      <c r="AB82" s="348"/>
-      <c r="AC82" s="348"/>
-      <c r="AD82" s="348"/>
-      <c r="AE82" s="359">
+      <c r="T82" s="104"/>
+      <c r="U82" s="104"/>
+      <c r="V82" s="104"/>
+      <c r="W82" s="104"/>
+      <c r="X82" s="104"/>
+      <c r="Y82" s="104"/>
+      <c r="Z82" s="104"/>
+      <c r="AA82" s="104"/>
+      <c r="AB82" s="104"/>
+      <c r="AC82" s="104"/>
+      <c r="AD82" s="104"/>
+      <c r="AE82" s="284">
         <v>2025</v>
       </c>
-      <c r="AF82" s="362">
+      <c r="AF82" s="269">
         <v>45809</v>
       </c>
-      <c r="AG82" s="362">
+      <c r="AG82" s="269">
         <v>45809</v>
       </c>
-      <c r="AH82" s="348"/>
-      <c r="AI82" s="349" t="s">
+      <c r="AH82" s="104"/>
+      <c r="AI82" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ82" s="348"/>
-      <c r="AK82" s="349" t="s">
+      <c r="AJ82" s="104"/>
+      <c r="AK82" s="162" t="s">
         <v>659</v>
       </c>
-      <c r="AL82" s="364"/>
-      <c r="AM82" s="348"/>
-      <c r="AN82" s="348"/>
-      <c r="AO82" s="348"/>
-      <c r="AP82" s="348"/>
-      <c r="AQ82" s="366"/>
-      <c r="AR82" s="348"/>
-      <c r="AS82" s="348"/>
-      <c r="AT82" s="348"/>
-      <c r="AU82" s="348"/>
-      <c r="AV82" s="348"/>
-      <c r="AW82" s="348"/>
+      <c r="AL82" s="123"/>
+      <c r="AM82" s="104"/>
+      <c r="AN82" s="104"/>
+      <c r="AO82" s="104"/>
+      <c r="AP82" s="104"/>
+      <c r="AQ82" s="253"/>
+      <c r="AR82" s="104"/>
+      <c r="AS82" s="104"/>
+      <c r="AT82" s="104"/>
+      <c r="AU82" s="104"/>
+      <c r="AV82" s="104"/>
+      <c r="AW82" s="104"/>
       <c r="AX82" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="AY82" s="348"/>
-      <c r="AZ82" s="348"/>
-      <c r="BA82" s="348"/>
-      <c r="BB82" s="348"/>
-      <c r="BC82" s="348"/>
-      <c r="BD82" s="348" t="s">
+      <c r="AY82" s="104"/>
+      <c r="AZ82" s="104"/>
+      <c r="BA82" s="104"/>
+      <c r="BB82" s="104"/>
+      <c r="BC82" s="104"/>
+      <c r="BD82" s="104" t="s">
         <v>661</v>
       </c>
-      <c r="BE82" s="348" t="s">
+      <c r="BE82" s="104" t="s">
         <v>662</v>
       </c>
-      <c r="BF82" s="348"/>
-      <c r="BG82" s="348"/>
-      <c r="BH82" s="348"/>
-      <c r="BI82" s="348"/>
-      <c r="BJ82" s="348"/>
-      <c r="BK82" s="348"/>
-      <c r="BL82" s="348"/>
-      <c r="BM82" s="348"/>
-      <c r="BN82" s="348"/>
+      <c r="BF82" s="104"/>
+      <c r="BG82" s="104"/>
+      <c r="BH82" s="104"/>
+      <c r="BI82" s="104"/>
+      <c r="BJ82" s="104"/>
+      <c r="BK82" s="104"/>
+      <c r="BL82" s="104"/>
+      <c r="BM82" s="104"/>
+      <c r="BN82" s="104"/>
     </row>
     <row r="83" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A83" s="107"/>
@@ -33267,7 +33357,7 @@
       <c r="BN98" s="104"/>
     </row>
     <row r="99" spans="1:66" x14ac:dyDescent="0.2">
-      <c r="A99" s="348"/>
+      <c r="A99" s="104"/>
       <c r="B99" s="162" t="s">
         <v>815</v>
       </c>
@@ -33305,7 +33395,7 @@
       <c r="R99" s="162"/>
       <c r="S99" s="180"/>
       <c r="T99" s="162"/>
-      <c r="U99" s="356"/>
+      <c r="U99" s="166"/>
       <c r="V99" s="166"/>
       <c r="W99" s="162"/>
       <c r="X99" s="162"/>
@@ -33377,7 +33467,7 @@
       <c r="BN99" s="104"/>
     </row>
     <row r="100" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="348"/>
+      <c r="A100" s="104"/>
       <c r="B100" s="162" t="s">
         <v>821</v>
       </c>
@@ -33415,7 +33505,7 @@
       <c r="R100" s="162"/>
       <c r="S100" s="180"/>
       <c r="T100" s="162"/>
-      <c r="U100" s="356"/>
+      <c r="U100" s="166"/>
       <c r="V100" s="166"/>
       <c r="W100" s="162"/>
       <c r="X100" s="162"/>
@@ -33490,99 +33580,99 @@
         <f>"Z_SE_"&amp;D101&amp;"_"&amp;G101</f>
         <v>Z_SE_Volvo_Torslanda</v>
       </c>
-      <c r="D101" s="349" t="s">
+      <c r="D101" s="162" t="s">
         <v>824</v>
       </c>
-      <c r="E101" s="348"/>
-      <c r="F101" s="349" t="s">
+      <c r="E101" s="104"/>
+      <c r="F101" s="162" t="s">
         <v>825</v>
       </c>
-      <c r="G101" s="349" t="s">
+      <c r="G101" s="162" t="s">
         <v>826</v>
       </c>
       <c r="H101" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="I101" s="349" t="s">
+      <c r="I101" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="J101" s="354">
+      <c r="J101" s="125">
         <v>44600</v>
       </c>
       <c r="K101" s="200" t="s">
         <v>65</v>
       </c>
-      <c r="L101" s="348" t="s">
+      <c r="L101" s="104" t="s">
         <v>827</v>
       </c>
-      <c r="M101" s="348" t="s">
+      <c r="M101" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="N101" s="348"/>
-      <c r="O101" s="348"/>
+      <c r="N101" s="104"/>
+      <c r="O101" s="104"/>
       <c r="P101" s="121"/>
-      <c r="Q101" s="348"/>
-      <c r="R101" s="348"/>
+      <c r="Q101" s="104"/>
+      <c r="R101" s="104"/>
       <c r="S101" s="122"/>
-      <c r="T101" s="348"/>
-      <c r="U101" s="348"/>
-      <c r="V101" s="348"/>
-      <c r="W101" s="348"/>
-      <c r="X101" s="348"/>
-      <c r="Y101" s="348"/>
-      <c r="Z101" s="348"/>
-      <c r="AA101" s="348"/>
-      <c r="AB101" s="348"/>
-      <c r="AC101" s="348"/>
-      <c r="AD101" s="348"/>
-      <c r="AE101" s="359"/>
-      <c r="AF101" s="363"/>
-      <c r="AG101" s="362">
+      <c r="T101" s="104"/>
+      <c r="U101" s="104"/>
+      <c r="V101" s="104"/>
+      <c r="W101" s="104"/>
+      <c r="X101" s="104"/>
+      <c r="Y101" s="104"/>
+      <c r="Z101" s="104"/>
+      <c r="AA101" s="104"/>
+      <c r="AB101" s="104"/>
+      <c r="AC101" s="104"/>
+      <c r="AD101" s="104"/>
+      <c r="AE101" s="284"/>
+      <c r="AF101" s="270"/>
+      <c r="AG101" s="269">
         <v>45717</v>
       </c>
-      <c r="AH101" s="348"/>
-      <c r="AI101" s="349" t="s">
+      <c r="AH101" s="104"/>
+      <c r="AI101" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="AJ101" s="348"/>
-      <c r="AK101" s="349" t="s">
+      <c r="AJ101" s="104"/>
+      <c r="AK101" s="162" t="s">
         <v>828</v>
       </c>
-      <c r="AL101" s="364"/>
-      <c r="AM101" s="348"/>
-      <c r="AN101" s="348"/>
-      <c r="AO101" s="348"/>
-      <c r="AP101" s="348"/>
-      <c r="AQ101" s="366"/>
-      <c r="AR101" s="348"/>
+      <c r="AL101" s="123"/>
+      <c r="AM101" s="104"/>
+      <c r="AN101" s="104"/>
+      <c r="AO101" s="104"/>
+      <c r="AP101" s="104"/>
+      <c r="AQ101" s="253"/>
+      <c r="AR101" s="104"/>
       <c r="AS101" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AT101" s="348"/>
-      <c r="AU101" s="348"/>
-      <c r="AV101" s="348"/>
-      <c r="AW101" s="348"/>
-      <c r="AX101" s="348"/>
-      <c r="AY101" s="348"/>
-      <c r="AZ101" s="348"/>
-      <c r="BA101" s="348"/>
-      <c r="BB101" s="348"/>
-      <c r="BC101" s="348"/>
-      <c r="BD101" s="348" t="s">
+      <c r="AT101" s="104"/>
+      <c r="AU101" s="104"/>
+      <c r="AV101" s="104"/>
+      <c r="AW101" s="104"/>
+      <c r="AX101" s="104"/>
+      <c r="AY101" s="104"/>
+      <c r="AZ101" s="104"/>
+      <c r="BA101" s="104"/>
+      <c r="BB101" s="104"/>
+      <c r="BC101" s="104"/>
+      <c r="BD101" s="104" t="s">
         <v>829</v>
       </c>
-      <c r="BE101" s="348" t="s">
+      <c r="BE101" s="104" t="s">
         <v>830</v>
       </c>
-      <c r="BF101" s="348"/>
-      <c r="BG101" s="348"/>
-      <c r="BH101" s="348"/>
-      <c r="BI101" s="348"/>
-      <c r="BJ101" s="348"/>
-      <c r="BK101" s="348"/>
-      <c r="BL101" s="348"/>
-      <c r="BM101" s="348"/>
-      <c r="BN101" s="348"/>
+      <c r="BF101" s="104"/>
+      <c r="BG101" s="104"/>
+      <c r="BH101" s="104"/>
+      <c r="BI101" s="104"/>
+      <c r="BJ101" s="104"/>
+      <c r="BK101" s="104"/>
+      <c r="BL101" s="104"/>
+      <c r="BM101" s="104"/>
+      <c r="BN101" s="104"/>
     </row>
     <row r="102" spans="1:66" x14ac:dyDescent="0.2">
       <c r="A102" s="107"/>
@@ -34113,7 +34203,7 @@
       <c r="BN106" s="106"/>
     </row>
     <row r="107" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="348"/>
+      <c r="A107" s="104"/>
       <c r="B107" s="234" t="str">
         <f>C107&amp;"_1"</f>
         <v>Z_GB_Tata JLR_Halewood_1</v>
@@ -34122,103 +34212,103 @@
         <f>"Z_GB_"&amp;D107&amp;"_"&amp;G107</f>
         <v>Z_GB_Tata JLR_Halewood</v>
       </c>
-      <c r="D107" s="349" t="s">
+      <c r="D107" s="162" t="s">
         <v>1028</v>
       </c>
-      <c r="E107" s="349"/>
-      <c r="F107" s="349" t="s">
+      <c r="E107" s="162"/>
+      <c r="F107" s="162" t="s">
         <v>141</v>
       </c>
-      <c r="G107" s="349" t="s">
+      <c r="G107" s="162" t="s">
         <v>1029</v>
       </c>
       <c r="H107" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="I107" s="349" t="s">
+      <c r="I107" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="J107" s="353">
+      <c r="J107" s="163">
         <v>43430</v>
       </c>
       <c r="K107" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="L107" s="349" t="s">
+      <c r="L107" s="162" t="s">
         <v>163</v>
       </c>
-      <c r="M107" s="349" t="s">
+      <c r="M107" s="162" t="s">
         <v>73</v>
       </c>
-      <c r="N107" s="353">
+      <c r="N107" s="163">
         <v>43430</v>
       </c>
       <c r="O107" s="1"/>
       <c r="P107" s="164"/>
-      <c r="Q107" s="349"/>
-      <c r="R107" s="353"/>
+      <c r="Q107" s="162"/>
+      <c r="R107" s="163"/>
       <c r="S107" s="79"/>
-      <c r="T107" s="349"/>
-      <c r="U107" s="356"/>
-      <c r="V107" s="356"/>
-      <c r="W107" s="349"/>
-      <c r="X107" s="349"/>
-      <c r="Y107" s="349"/>
-      <c r="Z107" s="349"/>
-      <c r="AA107" s="349"/>
-      <c r="AB107" s="349"/>
-      <c r="AC107" s="349"/>
-      <c r="AD107" s="349"/>
-      <c r="AE107" s="357"/>
-      <c r="AF107" s="361"/>
-      <c r="AG107" s="361"/>
-      <c r="AH107" s="349"/>
-      <c r="AI107" s="349" t="s">
+      <c r="T107" s="162"/>
+      <c r="U107" s="166"/>
+      <c r="V107" s="166"/>
+      <c r="W107" s="162"/>
+      <c r="X107" s="162"/>
+      <c r="Y107" s="162"/>
+      <c r="Z107" s="162"/>
+      <c r="AA107" s="162"/>
+      <c r="AB107" s="162"/>
+      <c r="AC107" s="162"/>
+      <c r="AD107" s="162"/>
+      <c r="AE107" s="277"/>
+      <c r="AF107" s="261"/>
+      <c r="AG107" s="261"/>
+      <c r="AH107" s="162"/>
+      <c r="AI107" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="AJ107" s="349"/>
-      <c r="AK107" s="349" t="s">
+      <c r="AJ107" s="162"/>
+      <c r="AK107" s="162" t="s">
         <v>1036</v>
       </c>
-      <c r="AL107" s="365"/>
-      <c r="AM107" s="349"/>
+      <c r="AL107" s="160"/>
+      <c r="AM107" s="162"/>
       <c r="AN107" s="1"/>
-      <c r="AO107" s="349"/>
-      <c r="AP107" s="349"/>
-      <c r="AQ107" s="367">
+      <c r="AO107" s="162"/>
+      <c r="AP107" s="162"/>
+      <c r="AQ107" s="247">
         <v>10881</v>
       </c>
-      <c r="AR107" s="349" t="s">
+      <c r="AR107" s="162" t="s">
         <v>64</v>
       </c>
       <c r="AS107" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT107" s="349"/>
-      <c r="AU107" s="349"/>
-      <c r="AV107" s="349"/>
-      <c r="AW107" s="349"/>
-      <c r="AX107" s="349" t="s">
+      <c r="AT107" s="162"/>
+      <c r="AU107" s="162"/>
+      <c r="AV107" s="162"/>
+      <c r="AW107" s="162"/>
+      <c r="AX107" s="162" t="s">
         <v>1038</v>
       </c>
-      <c r="AY107" s="349"/>
-      <c r="AZ107" s="349"/>
-      <c r="BA107" s="353"/>
-      <c r="BB107" s="349"/>
-      <c r="BC107" s="349"/>
-      <c r="BD107" s="349" t="s">
+      <c r="AY107" s="162"/>
+      <c r="AZ107" s="162"/>
+      <c r="BA107" s="163"/>
+      <c r="BB107" s="162"/>
+      <c r="BC107" s="162"/>
+      <c r="BD107" s="162" t="s">
         <v>1037</v>
       </c>
-      <c r="BE107" s="349"/>
-      <c r="BF107" s="349"/>
-      <c r="BG107" s="349"/>
-      <c r="BH107" s="349"/>
-      <c r="BI107" s="349"/>
-      <c r="BJ107" s="349"/>
-      <c r="BK107" s="349"/>
-      <c r="BL107" s="349"/>
-      <c r="BM107" s="349"/>
-      <c r="BN107" s="348"/>
+      <c r="BE107" s="162"/>
+      <c r="BF107" s="162"/>
+      <c r="BG107" s="162"/>
+      <c r="BH107" s="162"/>
+      <c r="BI107" s="162"/>
+      <c r="BJ107" s="162"/>
+      <c r="BK107" s="162"/>
+      <c r="BL107" s="162"/>
+      <c r="BM107" s="162"/>
+      <c r="BN107" s="104"/>
     </row>
     <row r="108" spans="1:66" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="108"/>
@@ -35951,7 +36041,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C23" s="346" t="s">
+      <c r="C23" s="345" t="s">
         <v>1331</v>
       </c>
     </row>

--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37748B45-1967-6F4B-B76A-A6C23515FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C3167A-DF0C-AE4D-91F0-BC038205645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C55" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C54" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -1502,7 +1502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="1350">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -7342,16 +7342,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J67" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J67" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="France"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J67">
-    <sortCondition ref="A1:A67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J66" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J66" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J66">
+    <sortCondition ref="A1:A66"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="9"/>
@@ -7697,7 +7691,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -7744,7 +7738,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="341" t="s">
         <v>211</v>
       </c>
@@ -7770,7 +7764,7 @@
       </c>
       <c r="J2" s="336"/>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="104" t="s">
         <v>211</v>
       </c>
@@ -7798,7 +7792,7 @@
       </c>
       <c r="J3" s="336"/>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="104" t="s">
         <v>211</v>
       </c>
@@ -7826,7 +7820,7 @@
       </c>
       <c r="J4" s="336"/>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="104" t="s">
         <v>211</v>
       </c>
@@ -7854,7 +7848,7 @@
       </c>
       <c r="J5" s="160"/>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="162" t="s">
         <v>253</v>
       </c>
@@ -7882,7 +7876,7 @@
       <c r="I6" s="160"/>
       <c r="J6" s="160"/>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="162" t="s">
         <v>57</v>
       </c>
@@ -7911,7 +7905,7 @@
       </c>
       <c r="J7" s="160"/>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="162" t="s">
         <v>57</v>
       </c>
@@ -7939,7 +7933,7 @@
       </c>
       <c r="J8" s="160"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="162" t="s">
         <v>57</v>
       </c>
@@ -7967,7 +7961,7 @@
       </c>
       <c r="J9" s="160"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="162" t="s">
         <v>57</v>
       </c>
@@ -7996,7 +7990,7 @@
       </c>
       <c r="J10" s="160"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="162" t="s">
         <v>57</v>
       </c>
@@ -8028,7 +8022,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="162" t="s">
         <v>57</v>
       </c>
@@ -8055,7 +8049,7 @@
       </c>
       <c r="J12" s="160"/>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="162" t="s">
         <v>57</v>
       </c>
@@ -8083,7 +8077,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="162" t="s">
         <v>57</v>
       </c>
@@ -8111,7 +8105,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="162" t="s">
         <v>57</v>
       </c>
@@ -8139,7 +8133,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="162" t="s">
         <v>57</v>
       </c>
@@ -8167,7 +8161,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="162" t="s">
         <v>356</v>
       </c>
@@ -8197,7 +8191,7 @@
       </c>
       <c r="J17" s="160"/>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="162" t="s">
         <v>385</v>
       </c>
@@ -8227,7 +8221,7 @@
       </c>
       <c r="J18" s="160"/>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="162" t="s">
         <v>399</v>
       </c>
@@ -8255,7 +8249,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="162" t="s">
         <v>1312</v>
       </c>
@@ -8283,7 +8277,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="162" t="s">
         <v>434</v>
       </c>
@@ -8312,7 +8306,7 @@
       </c>
       <c r="J21" s="160"/>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="162" t="s">
         <v>443</v>
       </c>
@@ -8342,7 +8336,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="162" t="s">
         <v>462</v>
       </c>
@@ -8368,7 +8362,7 @@
       <c r="I23" s="123"/>
       <c r="J23" s="160"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="162" t="s">
         <v>462</v>
       </c>
@@ -8398,7 +8392,7 @@
       </c>
       <c r="J24" s="160"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="162" t="s">
         <v>462</v>
       </c>
@@ -8409,7 +8403,7 @@
         <v>490</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E25" s="162" t="s">
         <v>61</v>
@@ -8428,7 +8422,7 @@
       </c>
       <c r="J25" s="160"/>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="162" t="s">
         <v>462</v>
       </c>
@@ -8458,7 +8452,7 @@
       </c>
       <c r="J26" s="160"/>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="162" t="s">
         <v>462</v>
       </c>
@@ -8469,7 +8463,7 @@
         <v>463</v>
       </c>
       <c r="D27" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E27" s="162" t="s">
         <v>61</v>
@@ -8488,7 +8482,7 @@
       </c>
       <c r="J27" s="160"/>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="162" t="s">
         <v>462</v>
       </c>
@@ -8514,7 +8508,7 @@
       </c>
       <c r="J28" s="160"/>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="162" t="s">
         <v>462</v>
       </c>
@@ -8538,37 +8532,45 @@
       </c>
       <c r="J29" s="160"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="162" t="s">
         <v>462</v>
       </c>
       <c r="B30" s="162" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C30" s="162" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="D30" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E30" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="334"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="123"/>
-      <c r="J30" s="160"/>
-    </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="F30" s="333" t="s">
+        <v>511</v>
+      </c>
+      <c r="G30" s="163">
+        <v>44530</v>
+      </c>
+      <c r="H30" s="162"/>
+      <c r="I30" s="123">
+        <v>50444</v>
+      </c>
+      <c r="J30" s="160" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="162" t="s">
         <v>462</v>
       </c>
       <c r="B31" s="162" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="C31" s="162" t="s">
-        <v>510</v>
+        <v>1333</v>
       </c>
       <c r="D31" s="162" t="s">
         <v>143</v>
@@ -8576,75 +8578,73 @@
       <c r="E31" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="333" t="s">
-        <v>511</v>
+      <c r="F31" s="333">
+        <v>2019</v>
       </c>
       <c r="G31" s="163">
-        <v>44530</v>
-      </c>
-      <c r="H31" s="162"/>
+        <v>43617</v>
+      </c>
+      <c r="H31" s="104"/>
       <c r="I31" s="123">
-        <v>50444</v>
-      </c>
-      <c r="J31" s="160" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="162" t="s">
-        <v>462</v>
-      </c>
-      <c r="B32" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C32" s="162" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D32" s="162" t="s">
+        <v>10739</v>
+      </c>
+      <c r="J31" s="160"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="337" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="337" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="337" t="s">
+        <v>522</v>
+      </c>
+      <c r="D32" s="337" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="337" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="338">
+        <v>2013</v>
+      </c>
+      <c r="G32" s="339">
+        <v>41275</v>
+      </c>
+      <c r="H32" s="337"/>
+      <c r="I32" s="340">
+        <v>40710</v>
+      </c>
+      <c r="J32" s="160"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B33" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C33" s="341" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D33" s="162" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="162" t="s">
+      <c r="E33" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="333">
-        <v>2019</v>
-      </c>
-      <c r="G32" s="163">
-        <v>43617</v>
-      </c>
-      <c r="H32" s="104"/>
-      <c r="I32" s="123">
-        <v>10739</v>
-      </c>
-      <c r="J32" s="160"/>
-    </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="337" t="s">
-        <v>521</v>
-      </c>
-      <c r="B33" s="337" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="337" t="s">
-        <v>522</v>
-      </c>
-      <c r="D33" s="337" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="337" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="338">
-        <v>2013</v>
-      </c>
-      <c r="G33" s="339">
-        <v>41275</v>
-      </c>
-      <c r="H33" s="337"/>
-      <c r="I33" s="340">
-        <v>40710</v>
-      </c>
-      <c r="J33" s="160"/>
+      <c r="F33" s="333"/>
+      <c r="G33" s="163">
+        <v>40908</v>
+      </c>
+      <c r="H33" s="162"/>
+      <c r="I33" s="160">
+        <v>11872</v>
+      </c>
+      <c r="J33" s="160" t="s">
+        <v>1339</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="341" t="s">
@@ -8656,22 +8656,22 @@
       <c r="C34" s="341" t="s">
         <v>1076</v>
       </c>
-      <c r="D34" s="162" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="162" t="s">
+      <c r="D34" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="333"/>
-      <c r="G34" s="163">
-        <v>40908</v>
-      </c>
-      <c r="H34" s="162"/>
-      <c r="I34" s="160">
-        <v>11872</v>
+      <c r="F34" s="342"/>
+      <c r="G34" s="343">
+        <v>45291</v>
+      </c>
+      <c r="H34" s="343"/>
+      <c r="I34" s="344">
+        <v>17562</v>
       </c>
       <c r="J34" s="160" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -8682,25 +8682,23 @@
         <v>265</v>
       </c>
       <c r="C35" s="341" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D35" s="346" t="s">
-        <v>71</v>
+        <v>1133</v>
+      </c>
+      <c r="D35" s="341" t="s">
+        <v>60</v>
       </c>
       <c r="E35" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F35" s="342"/>
       <c r="G35" s="343">
-        <v>45291</v>
+        <v>43830</v>
       </c>
       <c r="H35" s="343"/>
       <c r="I35" s="344">
-        <v>17562</v>
-      </c>
-      <c r="J35" s="160" t="s">
-        <v>1343</v>
-      </c>
+        <v>2117</v>
+      </c>
+      <c r="J35" s="160"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="341" t="s">
@@ -8710,23 +8708,25 @@
         <v>265</v>
       </c>
       <c r="C36" s="341" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D36" s="341" t="s">
-        <v>60</v>
+        <v>1064</v>
+      </c>
+      <c r="D36" s="346" t="s">
+        <v>143</v>
       </c>
       <c r="E36" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F36" s="342"/>
-      <c r="G36" s="343">
-        <v>43830</v>
-      </c>
-      <c r="H36" s="343"/>
+      <c r="G36" s="341"/>
+      <c r="H36" s="339">
+        <v>44926</v>
+      </c>
       <c r="I36" s="344">
-        <v>2117</v>
-      </c>
-      <c r="J36" s="160"/>
+        <v>71051</v>
+      </c>
+      <c r="J36" s="160" t="s">
+        <v>1338</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="341" t="s">
@@ -8736,24 +8736,24 @@
         <v>265</v>
       </c>
       <c r="C37" s="341" t="s">
-        <v>1064</v>
+        <v>1136</v>
       </c>
       <c r="D37" s="346" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E37" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F37" s="342"/>
-      <c r="G37" s="341"/>
-      <c r="H37" s="339">
-        <v>44926</v>
-      </c>
-      <c r="I37" s="344">
-        <v>71051</v>
+      <c r="G37" s="163">
+        <v>41639</v>
+      </c>
+      <c r="H37" s="162"/>
+      <c r="I37" s="160">
+        <v>48013</v>
       </c>
       <c r="J37" s="160" t="s">
-        <v>1338</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -8767,21 +8767,21 @@
         <v>1136</v>
       </c>
       <c r="D38" s="346" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E38" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="342"/>
-      <c r="G38" s="163">
-        <v>41639</v>
+      <c r="F38" s="333"/>
+      <c r="G38" s="353">
+        <v>44196</v>
       </c>
       <c r="H38" s="162"/>
-      <c r="I38" s="160">
-        <v>48013</v>
+      <c r="I38" s="336">
+        <v>102187</v>
       </c>
       <c r="J38" s="160" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -8801,80 +8801,78 @@
         <v>61</v>
       </c>
       <c r="F39" s="333"/>
-      <c r="G39" s="353">
+      <c r="G39" s="343">
+        <v>45657</v>
+      </c>
+      <c r="H39" s="162"/>
+      <c r="I39" s="344">
+        <v>0</v>
+      </c>
+      <c r="J39" s="160" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="337" t="s">
+        <v>541</v>
+      </c>
+      <c r="B40" s="337" t="s">
+        <v>542</v>
+      </c>
+      <c r="C40" s="337" t="s">
+        <v>543</v>
+      </c>
+      <c r="D40" s="337" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="337" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="338"/>
+      <c r="G40" s="339">
         <v>44196</v>
       </c>
-      <c r="H39" s="162"/>
-      <c r="I39" s="336">
-        <v>102187</v>
-      </c>
-      <c r="J39" s="160" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="341" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B40" s="341" t="s">
-        <v>265</v>
-      </c>
-      <c r="C40" s="341" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D40" s="346" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="341" t="s">
+      <c r="H40" s="337"/>
+      <c r="I40" s="340">
+        <v>26699</v>
+      </c>
+      <c r="J40" s="160"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="162" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B41" s="162" t="s">
+        <v>318</v>
+      </c>
+      <c r="C41" s="162" t="s">
+        <v>579</v>
+      </c>
+      <c r="D41" s="162" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F40" s="333"/>
-      <c r="G40" s="343">
-        <v>45657</v>
-      </c>
-      <c r="H40" s="162"/>
-      <c r="I40" s="344">
-        <v>0</v>
-      </c>
-      <c r="J40" s="160" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="337" t="s">
-        <v>541</v>
-      </c>
-      <c r="B41" s="337" t="s">
-        <v>542</v>
-      </c>
-      <c r="C41" s="337" t="s">
-        <v>543</v>
-      </c>
-      <c r="D41" s="337" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="337" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="338"/>
-      <c r="G41" s="339">
-        <v>44196</v>
-      </c>
-      <c r="H41" s="337"/>
-      <c r="I41" s="340">
-        <v>26699</v>
+      <c r="F41" s="334"/>
+      <c r="G41" s="125">
+        <v>44197</v>
+      </c>
+      <c r="H41" s="125"/>
+      <c r="I41" s="123">
+        <v>46589</v>
       </c>
       <c r="J41" s="160"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="162" t="s">
-        <v>1316</v>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="104" t="s">
+        <v>590</v>
       </c>
       <c r="B42" s="162" t="s">
-        <v>318</v>
+        <v>435</v>
       </c>
       <c r="C42" s="162" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="D42" s="162" t="s">
         <v>143</v>
@@ -8884,38 +8882,38 @@
       </c>
       <c r="F42" s="334"/>
       <c r="G42" s="125">
-        <v>44197</v>
-      </c>
-      <c r="H42" s="125"/>
+        <v>44075</v>
+      </c>
+      <c r="H42" s="104"/>
       <c r="I42" s="123">
-        <v>46589</v>
+        <f>67243+12264</f>
+        <v>79507</v>
       </c>
       <c r="J42" s="160"/>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="104" t="s">
-        <v>590</v>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="162" t="s">
+        <v>613</v>
       </c>
       <c r="B43" s="162" t="s">
-        <v>435</v>
+        <v>265</v>
       </c>
       <c r="C43" s="162" t="s">
-        <v>591</v>
+        <v>1083</v>
       </c>
       <c r="D43" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E43" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="334"/>
+      <c r="F43" s="333"/>
       <c r="G43" s="125">
-        <v>44075</v>
-      </c>
-      <c r="H43" s="104"/>
-      <c r="I43" s="123">
-        <f>67243+12264</f>
-        <v>79507</v>
+        <v>44561</v>
+      </c>
+      <c r="H43" s="162"/>
+      <c r="I43" s="160">
+        <v>33335</v>
       </c>
       <c r="J43" s="160"/>
     </row>
@@ -8924,36 +8922,38 @@
         <v>613</v>
       </c>
       <c r="B44" s="162" t="s">
-        <v>265</v>
-      </c>
-      <c r="C44" s="162" t="s">
-        <v>1083</v>
+        <v>444</v>
+      </c>
+      <c r="C44" s="322" t="s">
+        <v>628</v>
       </c>
       <c r="D44" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E44" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="333"/>
+      <c r="F44" s="334"/>
       <c r="G44" s="125">
-        <v>44561</v>
-      </c>
-      <c r="H44" s="162"/>
-      <c r="I44" s="160">
-        <v>33335</v>
+        <v>43559</v>
+      </c>
+      <c r="H44" s="125">
+        <v>43559</v>
+      </c>
+      <c r="I44" s="123">
+        <v>49264</v>
       </c>
       <c r="J44" s="160"/>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B45" s="162" t="s">
-        <v>444</v>
-      </c>
-      <c r="C45" s="322" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C45" s="104" t="s">
+        <v>638</v>
       </c>
       <c r="D45" s="162" t="s">
         <v>143</v>
@@ -8961,27 +8961,29 @@
       <c r="E45" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="334"/>
+      <c r="F45" s="334">
+        <v>2012</v>
+      </c>
       <c r="G45" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="H45" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="I45" s="123">
-        <v>49264</v>
+        <v>51498</v>
       </c>
       <c r="J45" s="160"/>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B46" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="C46" s="104" t="s">
-        <v>638</v>
+      <c r="C46" s="321" t="s">
+        <v>1013</v>
       </c>
       <c r="D46" s="162" t="s">
         <v>143</v>
@@ -8989,29 +8991,21 @@
       <c r="E46" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="334">
-        <v>2012</v>
-      </c>
-      <c r="G46" s="125">
-        <v>44562</v>
-      </c>
-      <c r="H46" s="125">
-        <v>44562</v>
-      </c>
-      <c r="I46" s="123">
-        <v>51498</v>
-      </c>
+      <c r="F46" s="333"/>
+      <c r="G46" s="163"/>
+      <c r="H46" s="163"/>
+      <c r="I46" s="160"/>
       <c r="J46" s="160"/>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B47" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C47" s="321" t="s">
-        <v>1013</v>
+        <v>58</v>
+      </c>
+      <c r="C47" s="162" t="s">
+        <v>614</v>
       </c>
       <c r="D47" s="162" t="s">
         <v>143</v>
@@ -9019,65 +9013,69 @@
       <c r="E47" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="333"/>
-      <c r="G47" s="163"/>
-      <c r="H47" s="163"/>
-      <c r="I47" s="160"/>
-      <c r="J47" s="160"/>
-    </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="F47" s="334">
+        <v>2020</v>
+      </c>
+      <c r="G47" s="125">
+        <v>45658</v>
+      </c>
+      <c r="H47" s="104"/>
+      <c r="I47" s="123">
+        <v>5888</v>
+      </c>
+      <c r="J47" s="160" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B48" s="162" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C48" s="162" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D48" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E48" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F48" s="334">
-        <v>2020</v>
-      </c>
-      <c r="G48" s="125">
-        <v>45658</v>
-      </c>
-      <c r="H48" s="104"/>
-      <c r="I48" s="123">
-        <v>5888</v>
-      </c>
-      <c r="J48" s="160" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="F48" s="333"/>
+      <c r="G48" s="163">
+        <v>44742</v>
+      </c>
+      <c r="H48" s="162"/>
+      <c r="I48" s="160">
+        <v>15000</v>
+      </c>
+      <c r="J48" s="160"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="162" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B49" s="162" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" s="162" t="s">
-        <v>621</v>
+        <v>265</v>
+      </c>
+      <c r="C49" s="137" t="s">
+        <v>663</v>
       </c>
       <c r="D49" s="162" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="E49" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F49" s="333"/>
-      <c r="G49" s="163">
-        <v>44742</v>
-      </c>
-      <c r="H49" s="162"/>
-      <c r="I49" s="160">
-        <v>15000</v>
+      <c r="F49" s="334"/>
+      <c r="G49" s="125">
+        <v>45657</v>
+      </c>
+      <c r="H49" s="125"/>
+      <c r="I49" s="123">
+        <v>24008</v>
       </c>
       <c r="J49" s="160"/>
     </row>
@@ -9088,8 +9086,8 @@
       <c r="B50" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="137" t="s">
-        <v>663</v>
+      <c r="C50" s="162" t="s">
+        <v>668</v>
       </c>
       <c r="D50" s="162" t="s">
         <v>214</v>
@@ -9099,11 +9097,11 @@
       </c>
       <c r="F50" s="334"/>
       <c r="G50" s="125">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="H50" s="125"/>
       <c r="I50" s="123">
-        <v>24008</v>
+        <v>23534</v>
       </c>
       <c r="J50" s="160"/>
     </row>
@@ -9115,21 +9113,23 @@
         <v>265</v>
       </c>
       <c r="C51" s="162" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="D51" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E51" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F51" s="334"/>
       <c r="G51" s="125">
-        <v>44561</v>
-      </c>
-      <c r="H51" s="125"/>
+        <v>45291</v>
+      </c>
+      <c r="H51" s="125">
+        <v>45291</v>
+      </c>
       <c r="I51" s="123">
-        <v>23534</v>
+        <v>42533</v>
       </c>
       <c r="J51" s="160"/>
     </row>
@@ -9140,14 +9140,14 @@
       <c r="B52" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="162" t="s">
-        <v>653</v>
+      <c r="C52" s="137" t="s">
+        <v>657</v>
       </c>
       <c r="D52" s="162" t="s">
         <v>143</v>
       </c>
       <c r="E52" s="162" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="F52" s="334"/>
       <c r="G52" s="125">
@@ -9157,7 +9157,7 @@
         <v>45291</v>
       </c>
       <c r="I52" s="123">
-        <v>42533</v>
+        <v>15433</v>
       </c>
       <c r="J52" s="160"/>
     </row>
@@ -9168,24 +9168,18 @@
       <c r="B53" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C53" s="137" t="s">
-        <v>657</v>
+      <c r="C53" s="162" t="s">
+        <v>668</v>
       </c>
       <c r="D53" s="162" t="s">
         <v>143</v>
       </c>
       <c r="E53" s="162" t="s">
-        <v>148</v>
-      </c>
-      <c r="F53" s="334"/>
-      <c r="G53" s="125">
-        <v>45291</v>
-      </c>
-      <c r="H53" s="125">
-        <v>45291</v>
-      </c>
-      <c r="I53" s="123">
-        <v>15433</v>
+        <v>61</v>
+      </c>
+      <c r="F53" s="333"/>
+      <c r="I53" s="160">
+        <v>5000</v>
       </c>
       <c r="J53" s="160"/>
     </row>
@@ -9194,10 +9188,10 @@
         <v>652</v>
       </c>
       <c r="B54" s="162" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C54" s="162" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D54" s="162" t="s">
         <v>143</v>
@@ -9205,21 +9199,25 @@
       <c r="E54" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="333"/>
+      <c r="F54" s="333" t="s">
+        <v>682</v>
+      </c>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
       <c r="I54" s="160">
-        <v>5000</v>
+        <v>111872</v>
       </c>
       <c r="J54" s="160"/>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="162" t="s">
         <v>652</v>
       </c>
       <c r="B55" s="162" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="C55" s="162" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D55" s="162" t="s">
         <v>143</v>
@@ -9227,19 +9225,21 @@
       <c r="E55" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="333" t="s">
-        <v>682</v>
-      </c>
-      <c r="G55" s="162"/>
+      <c r="F55" s="333"/>
+      <c r="G55" s="163">
+        <v>44927</v>
+      </c>
       <c r="H55" s="162"/>
       <c r="I55" s="160">
-        <v>111872</v>
-      </c>
-      <c r="J55" s="160"/>
-    </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>28788</v>
+      </c>
+      <c r="J55" s="160" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B56" s="162" t="s">
         <v>357</v>
@@ -9248,52 +9248,54 @@
         <v>691</v>
       </c>
       <c r="D56" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E56" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F56" s="333"/>
       <c r="G56" s="163">
-        <v>44927</v>
+        <v>45658</v>
       </c>
       <c r="H56" s="162"/>
       <c r="I56" s="160">
-        <v>28788</v>
+        <v>976</v>
       </c>
       <c r="J56" s="160" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="162" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B57" s="162" t="s">
-        <v>357</v>
+        <v>141</v>
       </c>
       <c r="C57" s="162" t="s">
-        <v>691</v>
+        <v>1029</v>
       </c>
       <c r="D57" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E57" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="333"/>
+      <c r="F57" s="333">
+        <v>2018</v>
+      </c>
       <c r="G57" s="163">
-        <v>45658</v>
-      </c>
-      <c r="H57" s="162"/>
+        <v>43101</v>
+      </c>
+      <c r="H57" s="163">
+        <v>43101</v>
+      </c>
       <c r="I57" s="160">
-        <v>976</v>
-      </c>
-      <c r="J57" s="160" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>14287</v>
+      </c>
+      <c r="J57" s="160"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="162" t="s">
         <v>1028</v>
       </c>
@@ -9304,78 +9306,72 @@
         <v>1029</v>
       </c>
       <c r="D58" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E58" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F58" s="333">
-        <v>2018</v>
-      </c>
-      <c r="G58" s="163">
-        <v>43101</v>
-      </c>
-      <c r="H58" s="163">
-        <v>43101</v>
-      </c>
+      <c r="F58" s="333"/>
+      <c r="G58" s="163"/>
+      <c r="H58" s="163"/>
       <c r="I58" s="160">
-        <v>14287</v>
+        <v>10881</v>
       </c>
       <c r="J58" s="160"/>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="162" t="s">
-        <v>1028</v>
+        <v>718</v>
       </c>
       <c r="B59" s="162" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C59" s="162" t="s">
-        <v>1029</v>
+        <v>1309</v>
       </c>
       <c r="D59" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E59" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F59" s="333"/>
       <c r="G59" s="163"/>
-      <c r="H59" s="163"/>
-      <c r="I59" s="160">
-        <v>10881</v>
-      </c>
-      <c r="J59" s="160"/>
-    </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="H59" s="163">
+        <v>44561</v>
+      </c>
+      <c r="I59" s="123">
+        <v>206097</v>
+      </c>
+      <c r="J59" s="160" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="162" t="s">
-        <v>718</v>
+        <v>575</v>
       </c>
       <c r="B60" s="162" t="s">
         <v>58</v>
       </c>
       <c r="C60" s="162" t="s">
-        <v>1309</v>
+        <v>754</v>
       </c>
       <c r="D60" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E60" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F60" s="333"/>
-      <c r="G60" s="163"/>
-      <c r="H60" s="163">
-        <v>44561</v>
-      </c>
-      <c r="I60" s="123">
-        <v>206097</v>
-      </c>
-      <c r="J60" s="160" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G60" s="162"/>
+      <c r="H60" s="162"/>
+      <c r="I60" s="160">
+        <v>140000</v>
+      </c>
+      <c r="J60" s="160"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="162" t="s">
         <v>575</v>
       </c>
@@ -9383,7 +9379,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="162" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D61" s="162" t="s">
         <v>214</v>
@@ -9392,40 +9388,42 @@
         <v>61</v>
       </c>
       <c r="F61" s="333"/>
-      <c r="G61" s="162"/>
+      <c r="G61" s="163">
+        <v>44926</v>
+      </c>
       <c r="H61" s="162"/>
       <c r="I61" s="160">
-        <v>140000</v>
+        <v>29724</v>
       </c>
       <c r="J61" s="160"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="162" t="s">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" s="181" t="s">
         <v>575</v>
       </c>
-      <c r="B62" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="C62" s="162" t="s">
-        <v>764</v>
-      </c>
-      <c r="D62" s="162" t="s">
-        <v>214</v>
-      </c>
-      <c r="E62" s="162" t="s">
+      <c r="B62" s="181" t="s">
+        <v>444</v>
+      </c>
+      <c r="C62" s="181" t="s">
+        <v>745</v>
+      </c>
+      <c r="D62" s="181" t="s">
+        <v>143</v>
+      </c>
+      <c r="E62" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F62" s="333"/>
-      <c r="G62" s="163">
-        <v>44926</v>
-      </c>
-      <c r="H62" s="162"/>
-      <c r="I62" s="160">
-        <v>29724</v>
+      <c r="F62" s="334"/>
+      <c r="G62" s="125">
+        <v>43830</v>
+      </c>
+      <c r="H62" s="125"/>
+      <c r="I62" s="123">
+        <v>13528</v>
       </c>
       <c r="J62" s="160"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="181" t="s">
         <v>575</v>
       </c>
@@ -9436,74 +9434,74 @@
         <v>745</v>
       </c>
       <c r="D63" s="181" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E63" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="334"/>
-      <c r="G63" s="125">
-        <v>43830</v>
-      </c>
-      <c r="H63" s="125"/>
-      <c r="I63" s="123">
-        <v>13528</v>
+      <c r="F63" s="333"/>
+      <c r="G63" s="163">
+        <v>45291</v>
+      </c>
+      <c r="H63" s="163"/>
+      <c r="I63" s="160">
+        <v>94839</v>
       </c>
       <c r="J63" s="160"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="181" t="s">
-        <v>575</v>
-      </c>
-      <c r="B64" s="181" t="s">
-        <v>444</v>
-      </c>
-      <c r="C64" s="181" t="s">
-        <v>745</v>
-      </c>
-      <c r="D64" s="181" t="s">
-        <v>71</v>
-      </c>
-      <c r="E64" s="181" t="s">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64" s="162" t="s">
+        <v>824</v>
+      </c>
+      <c r="B64" s="162" t="s">
+        <v>825</v>
+      </c>
+      <c r="C64" s="162" t="s">
+        <v>826</v>
+      </c>
+      <c r="D64" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F64" s="333"/>
-      <c r="G64" s="163">
-        <v>45291</v>
-      </c>
-      <c r="H64" s="163"/>
-      <c r="I64" s="160">
-        <v>94839</v>
+      <c r="F64" s="334"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="125">
+        <v>45657</v>
+      </c>
+      <c r="I64" s="123">
+        <v>85654</v>
       </c>
       <c r="J64" s="160"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="162" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B65" s="162" t="s">
-        <v>825</v>
+        <v>212</v>
       </c>
       <c r="C65" s="162" t="s">
-        <v>826</v>
-      </c>
-      <c r="D65" s="104" t="s">
-        <v>60</v>
+        <v>817</v>
+      </c>
+      <c r="D65" s="162" t="s">
+        <v>143</v>
       </c>
       <c r="E65" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="334"/>
-      <c r="G65" s="104"/>
-      <c r="H65" s="125">
-        <v>45657</v>
-      </c>
-      <c r="I65" s="123">
-        <v>85654</v>
+      <c r="F65" s="333"/>
+      <c r="G65" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H65" s="163"/>
+      <c r="I65" s="160">
+        <v>34001</v>
       </c>
       <c r="J65" s="160"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="162" t="s">
         <v>810</v>
       </c>
@@ -9514,53 +9512,27 @@
         <v>817</v>
       </c>
       <c r="D66" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E66" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F66" s="333"/>
       <c r="G66" s="163">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="H66" s="163"/>
       <c r="I66" s="160">
-        <v>34001</v>
+        <v>133505</v>
       </c>
       <c r="J66" s="160"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="162" t="s">
-        <v>810</v>
-      </c>
-      <c r="B67" s="162" t="s">
-        <v>212</v>
-      </c>
-      <c r="C67" s="162" t="s">
-        <v>817</v>
-      </c>
-      <c r="D67" s="162" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F67" s="333"/>
-      <c r="G67" s="163">
-        <v>45657</v>
-      </c>
-      <c r="H67" s="163"/>
-      <c r="I67" s="160">
-        <v>133505</v>
-      </c>
-      <c r="J67" s="160"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A68" s="162"/>
-      <c r="B68" s="162"/>
-      <c r="C68" s="162"/>
-      <c r="D68" s="162"/>
-      <c r="E68" s="162"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67" s="162"/>
+      <c r="B67" s="162"/>
+      <c r="C67" s="162"/>
+      <c r="D67" s="162"/>
+      <c r="E67" s="162"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38436,15 +38408,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
@@ -38478,6 +38441,15 @@
     </Authors>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38814,14 +38786,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -38834,6 +38798,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C3167A-DF0C-AE4D-91F0-BC038205645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD078216-C424-D142-8D20-41A22427A41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C54" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C53" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -1502,7 +1502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1353">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -5640,6 +5640,15 @@
   </si>
   <si>
     <t>Produces the Master BEV van</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>production of the C5 aircross PHEV</t>
+  </si>
+  <si>
+    <t>legacy built the 3008 PHEV, recently ramped the 3008 and 5008 BEVs (we are considering the latter for investment impute purposes)</t>
   </si>
 </sst>
 </file>
@@ -7248,7 +7257,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>149860</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>134764</xdr:rowOff>
     </xdr:to>
@@ -7342,10 +7351,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J66" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J66" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J66">
-    <sortCondition ref="A1:A66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J65" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J65">
+    <sortCondition ref="A1:A65"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="9"/>
@@ -7691,7 +7700,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -9070,14 +9079,16 @@
         <v>61</v>
       </c>
       <c r="F49" s="334"/>
-      <c r="G49" s="125">
-        <v>45657</v>
-      </c>
-      <c r="H49" s="125"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125">
+        <v>45292</v>
+      </c>
       <c r="I49" s="123">
         <v>24008</v>
       </c>
-      <c r="J49" s="160"/>
+      <c r="J49" s="160" t="s">
+        <v>1352</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="162" t="s">
@@ -9096,10 +9107,10 @@
         <v>61</v>
       </c>
       <c r="F50" s="334"/>
-      <c r="G50" s="125">
-        <v>44561</v>
-      </c>
-      <c r="H50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125">
+        <v>44203</v>
+      </c>
       <c r="I50" s="123">
         <v>23534</v>
       </c>
@@ -9135,41 +9146,41 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B52" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="137" t="s">
+      <c r="C52" s="162" t="s">
         <v>657</v>
       </c>
       <c r="D52" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E52" s="162" t="s">
-        <v>148</v>
-      </c>
-      <c r="F52" s="334"/>
-      <c r="G52" s="125">
-        <v>45291</v>
-      </c>
-      <c r="H52" s="125">
-        <v>45291</v>
-      </c>
-      <c r="I52" s="123">
+        <v>61</v>
+      </c>
+      <c r="F52" s="333"/>
+      <c r="G52" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H52" s="162"/>
+      <c r="I52" s="160">
         <v>15433</v>
       </c>
-      <c r="J52" s="160"/>
+      <c r="J52" s="160" t="s">
+        <v>1351</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="162" t="s">
         <v>652</v>
       </c>
       <c r="B53" s="162" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C53" s="162" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D53" s="162" t="s">
         <v>143</v>
@@ -9177,9 +9188,13 @@
       <c r="E53" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F53" s="333"/>
+      <c r="F53" s="333" t="s">
+        <v>682</v>
+      </c>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
       <c r="I53" s="160">
-        <v>5000</v>
+        <v>111872</v>
       </c>
       <c r="J53" s="160"/>
     </row>
@@ -9188,10 +9203,10 @@
         <v>652</v>
       </c>
       <c r="B54" s="162" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="C54" s="162" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D54" s="162" t="s">
         <v>143</v>
@@ -9199,19 +9214,21 @@
       <c r="E54" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="333" t="s">
-        <v>682</v>
-      </c>
-      <c r="G54" s="162"/>
+      <c r="F54" s="333"/>
+      <c r="G54" s="163">
+        <v>44927</v>
+      </c>
       <c r="H54" s="162"/>
       <c r="I54" s="160">
-        <v>111872</v>
-      </c>
-      <c r="J54" s="160"/>
+        <v>28788</v>
+      </c>
+      <c r="J54" s="160" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B55" s="162" t="s">
         <v>357</v>
@@ -9220,50 +9237,52 @@
         <v>691</v>
       </c>
       <c r="D55" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E55" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F55" s="333"/>
       <c r="G55" s="163">
-        <v>44927</v>
+        <v>45658</v>
       </c>
       <c r="H55" s="162"/>
       <c r="I55" s="160">
-        <v>28788</v>
+        <v>976</v>
       </c>
       <c r="J55" s="160" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="162" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B56" s="162" t="s">
-        <v>357</v>
+        <v>141</v>
       </c>
       <c r="C56" s="162" t="s">
-        <v>691</v>
+        <v>1029</v>
       </c>
       <c r="D56" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E56" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="333"/>
+      <c r="F56" s="333">
+        <v>2018</v>
+      </c>
       <c r="G56" s="163">
-        <v>45658</v>
-      </c>
-      <c r="H56" s="162"/>
+        <v>43101</v>
+      </c>
+      <c r="H56" s="163">
+        <v>43101</v>
+      </c>
       <c r="I56" s="160">
-        <v>976</v>
-      </c>
-      <c r="J56" s="160" t="s">
-        <v>1335</v>
-      </c>
+        <v>14287</v>
+      </c>
+      <c r="J56" s="160"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="162" t="s">
@@ -9276,76 +9295,70 @@
         <v>1029</v>
       </c>
       <c r="D57" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E57" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="333">
-        <v>2018</v>
-      </c>
-      <c r="G57" s="163">
-        <v>43101</v>
-      </c>
-      <c r="H57" s="163">
-        <v>43101</v>
-      </c>
+      <c r="F57" s="333"/>
+      <c r="G57" s="163"/>
+      <c r="H57" s="163"/>
       <c r="I57" s="160">
-        <v>14287</v>
+        <v>10881</v>
       </c>
       <c r="J57" s="160"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="162" t="s">
-        <v>1028</v>
+        <v>718</v>
       </c>
       <c r="B58" s="162" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C58" s="162" t="s">
-        <v>1029</v>
+        <v>1309</v>
       </c>
       <c r="D58" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E58" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F58" s="333"/>
       <c r="G58" s="163"/>
-      <c r="H58" s="163"/>
-      <c r="I58" s="160">
-        <v>10881</v>
-      </c>
-      <c r="J58" s="160"/>
+      <c r="H58" s="163">
+        <v>44561</v>
+      </c>
+      <c r="I58" s="123">
+        <v>206097</v>
+      </c>
+      <c r="J58" s="160" t="s">
+        <v>1311</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="162" t="s">
-        <v>718</v>
+        <v>575</v>
       </c>
       <c r="B59" s="162" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="162" t="s">
-        <v>1309</v>
+        <v>754</v>
       </c>
       <c r="D59" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E59" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F59" s="333"/>
-      <c r="G59" s="163"/>
-      <c r="H59" s="163">
-        <v>44561</v>
-      </c>
-      <c r="I59" s="123">
-        <v>206097</v>
-      </c>
-      <c r="J59" s="160" t="s">
-        <v>1311</v>
-      </c>
+      <c r="G59" s="162"/>
+      <c r="H59" s="162"/>
+      <c r="I59" s="160">
+        <v>140000</v>
+      </c>
+      <c r="J59" s="160"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="162" t="s">
@@ -9355,7 +9368,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="162" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D60" s="162" t="s">
         <v>214</v>
@@ -9364,36 +9377,38 @@
         <v>61</v>
       </c>
       <c r="F60" s="333"/>
-      <c r="G60" s="162"/>
+      <c r="G60" s="163">
+        <v>44926</v>
+      </c>
       <c r="H60" s="162"/>
       <c r="I60" s="160">
-        <v>140000</v>
+        <v>29724</v>
       </c>
       <c r="J60" s="160"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A61" s="162" t="s">
+      <c r="A61" s="181" t="s">
         <v>575</v>
       </c>
-      <c r="B61" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="162" t="s">
-        <v>764</v>
-      </c>
-      <c r="D61" s="162" t="s">
-        <v>214</v>
-      </c>
-      <c r="E61" s="162" t="s">
+      <c r="B61" s="181" t="s">
+        <v>444</v>
+      </c>
+      <c r="C61" s="181" t="s">
+        <v>745</v>
+      </c>
+      <c r="D61" s="181" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F61" s="333"/>
-      <c r="G61" s="163">
-        <v>44926</v>
-      </c>
-      <c r="H61" s="162"/>
-      <c r="I61" s="160">
-        <v>29724</v>
+      <c r="F61" s="334"/>
+      <c r="G61" s="125">
+        <v>43830</v>
+      </c>
+      <c r="H61" s="125"/>
+      <c r="I61" s="123">
+        <v>13528</v>
       </c>
       <c r="J61" s="160"/>
     </row>
@@ -9408,70 +9423,70 @@
         <v>745</v>
       </c>
       <c r="D62" s="181" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E62" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F62" s="334"/>
-      <c r="G62" s="125">
-        <v>43830</v>
-      </c>
-      <c r="H62" s="125"/>
-      <c r="I62" s="123">
-        <v>13528</v>
+      <c r="F62" s="333"/>
+      <c r="G62" s="163">
+        <v>45291</v>
+      </c>
+      <c r="H62" s="163"/>
+      <c r="I62" s="160">
+        <v>94839</v>
       </c>
       <c r="J62" s="160"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="181" t="s">
-        <v>575</v>
-      </c>
-      <c r="B63" s="181" t="s">
-        <v>444</v>
-      </c>
-      <c r="C63" s="181" t="s">
-        <v>745</v>
-      </c>
-      <c r="D63" s="181" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63" s="181" t="s">
+      <c r="A63" s="162" t="s">
+        <v>824</v>
+      </c>
+      <c r="B63" s="162" t="s">
+        <v>825</v>
+      </c>
+      <c r="C63" s="162" t="s">
+        <v>826</v>
+      </c>
+      <c r="D63" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E63" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="333"/>
-      <c r="G63" s="163">
-        <v>45291</v>
-      </c>
-      <c r="H63" s="163"/>
-      <c r="I63" s="160">
-        <v>94839</v>
+      <c r="F63" s="334"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="125">
+        <v>45657</v>
+      </c>
+      <c r="I63" s="123">
+        <v>85654</v>
       </c>
       <c r="J63" s="160"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="162" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B64" s="162" t="s">
-        <v>825</v>
+        <v>212</v>
       </c>
       <c r="C64" s="162" t="s">
-        <v>826</v>
-      </c>
-      <c r="D64" s="104" t="s">
-        <v>60</v>
+        <v>817</v>
+      </c>
+      <c r="D64" s="162" t="s">
+        <v>143</v>
       </c>
       <c r="E64" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F64" s="334"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="125">
-        <v>45657</v>
-      </c>
-      <c r="I64" s="123">
-        <v>85654</v>
+      <c r="F64" s="333"/>
+      <c r="G64" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H64" s="163"/>
+      <c r="I64" s="160">
+        <v>34001</v>
       </c>
       <c r="J64" s="160"/>
     </row>
@@ -9486,53 +9501,27 @@
         <v>817</v>
       </c>
       <c r="D65" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E65" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F65" s="333"/>
       <c r="G65" s="163">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="H65" s="163"/>
       <c r="I65" s="160">
-        <v>34001</v>
+        <v>133505</v>
       </c>
       <c r="J65" s="160"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="162" t="s">
-        <v>810</v>
-      </c>
-      <c r="B66" s="162" t="s">
-        <v>212</v>
-      </c>
-      <c r="C66" s="162" t="s">
-        <v>817</v>
-      </c>
-      <c r="D66" s="162" t="s">
-        <v>71</v>
-      </c>
-      <c r="E66" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F66" s="333"/>
-      <c r="G66" s="163">
-        <v>45657</v>
-      </c>
-      <c r="H66" s="163"/>
-      <c r="I66" s="160">
-        <v>133505</v>
-      </c>
-      <c r="J66" s="160"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="162"/>
-      <c r="B67" s="162"/>
-      <c r="C67" s="162"/>
-      <c r="D67" s="162"/>
-      <c r="E67" s="162"/>
+      <c r="A66" s="162"/>
+      <c r="B66" s="162"/>
+      <c r="C66" s="162"/>
+      <c r="D66" s="162"/>
+      <c r="E66" s="162"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10553,11 +10542,11 @@
   <cols>
     <col min="2" max="2" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="14" width="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.6640625" customWidth="1"/>
     <col min="16" max="16" width="12.6640625" customWidth="1"/>
-    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -11212,7 +11201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="56"/>
       <c r="B17" s="56"/>
       <c r="C17" s="7" t="s">
@@ -11253,7 +11242,7 @@
         <v>3792</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="56"/>
       <c r="B18" s="56"/>
       <c r="C18" s="312" t="s">
@@ -11282,7 +11271,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="56"/>
       <c r="B19" s="56"/>
       <c r="C19" s="7" t="s">
@@ -11313,7 +11302,7 @@
         <v>6416</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" s="56"/>
       <c r="B20" s="56"/>
       <c r="C20" s="7" t="s">
@@ -11340,7 +11329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="56"/>
       <c r="B21" s="56"/>
       <c r="C21" s="312" t="s">
@@ -11369,7 +11358,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" s="56"/>
       <c r="B22" s="56"/>
       <c r="C22" s="301" t="s">
@@ -11404,7 +11393,7 @@
         <v>5228</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" s="56"/>
       <c r="B23" s="56"/>
       <c r="C23" s="301" t="s">
@@ -11443,7 +11432,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B24" s="56" t="s">
         <v>1137</v>
       </c>
@@ -11483,7 +11472,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" s="289"/>
       <c r="B25" s="56"/>
       <c r="C25" s="301" t="s">
@@ -11519,8 +11508,15 @@
       <c r="S25" s="57">
         <v>1487</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U25" t="s">
+        <v>1350</v>
+      </c>
+      <c r="V25" s="57">
+        <f>SUM(S4:S25)</f>
+        <v>105746</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" s="56"/>
       <c r="B26" s="56"/>
       <c r="C26" s="321"/>
@@ -11540,12 +11536,12 @@
       <c r="R26" s="57"/>
       <c r="S26" s="57"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>1110</v>
       </c>
@@ -11554,7 +11550,7 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B30" s="313" t="s">
         <v>1111</v>
       </c>
@@ -11563,7 +11559,7 @@
       <c r="E30" s="313"/>
       <c r="F30" s="313"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B31" s="297" t="s">
         <v>1112</v>
       </c>
@@ -11572,7 +11568,7 @@
       <c r="E31" s="297"/>
       <c r="F31" s="297"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B32" s="308" t="s">
         <v>1113</v>
       </c>
@@ -13858,7 +13854,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="326"/>
       <c r="B33" s="326"/>
       <c r="C33" s="324" t="s">
@@ -13886,7 +13882,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="326"/>
       <c r="B34" s="326"/>
       <c r="C34" s="324" t="s">
@@ -13910,7 +13906,7 @@
         <v>13349</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="326"/>
       <c r="B35" s="326"/>
       <c r="C35" s="324" t="s">
@@ -13962,7 +13958,7 @@
         <v>11184</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="326"/>
       <c r="B36" s="326"/>
       <c r="C36" s="324" t="s">
@@ -13988,7 +13984,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="326"/>
       <c r="B37" s="326"/>
       <c r="C37" s="324" t="s">
@@ -14024,7 +14020,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="326"/>
       <c r="B38" s="326"/>
       <c r="C38" s="324" t="s">
@@ -14054,7 +14050,7 @@
         <v>34732</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="326"/>
       <c r="B39" s="326"/>
       <c r="C39" s="324" t="s">
@@ -14080,7 +14076,7 @@
         <v>22970</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="326"/>
       <c r="B40" s="326"/>
       <c r="C40" s="324" t="s">
@@ -14106,7 +14102,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="326"/>
       <c r="B41" s="326"/>
       <c r="C41" s="324" t="s">
@@ -14154,7 +14150,7 @@
         <v>5005</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="326"/>
       <c r="B42" s="326" t="s">
         <v>613</v>
@@ -14187,8 +14183,9 @@
       <c r="R42" s="327">
         <v>7592</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="327"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="326"/>
       <c r="B43" s="326"/>
       <c r="C43" s="324" t="s">
@@ -14220,7 +14217,7 @@
         <v>3967</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="326"/>
       <c r="B44" s="326"/>
       <c r="C44" s="324" t="s">
@@ -14252,7 +14249,7 @@
       <c r="Q44" s="327"/>
       <c r="R44" s="327"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="326"/>
       <c r="B45" s="326"/>
       <c r="C45" s="324" t="s">
@@ -14284,7 +14281,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="326"/>
       <c r="B46" s="326"/>
       <c r="C46" s="324" t="s">
@@ -14318,7 +14315,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="326"/>
       <c r="B47" s="326"/>
       <c r="C47" s="324" t="s">
@@ -14352,7 +14349,7 @@
         <v>7618</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="326"/>
       <c r="B48" s="326"/>
       <c r="C48" s="324" t="s">
@@ -38408,42 +38405,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Dataset</Value>
-    </ProjectType>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Green Economy</Value>
-    </ResearchArea>
-    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
-    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
-      <UserInfo>
-        <DisplayName>Ugne Keliauskaite</DisplayName>
-        <AccountId>1048</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ben McWilliams</DisplayName>
-        <AccountId>22</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Marie Jugé</DisplayName>
-        <AccountId>1714</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </Authors>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -38452,7 +38413,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38785,24 +38746,43 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Dataset</Value>
+    </ProjectType>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Green Economy</Value>
+    </ResearchArea>
+    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
+    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
+      <UserInfo>
+        <DisplayName>Ugne Keliauskaite</DisplayName>
+        <AccountId>1048</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ben McWilliams</DisplayName>
+        <AccountId>22</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Marie Jugé</DisplayName>
+        <AccountId>1714</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </Authors>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -38810,7 +38790,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38827,4 +38807,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD078216-C424-D142-8D20-41A22427A41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677EEA7B-079B-6045-A911-D3641E87EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -9127,17 +9127,15 @@
         <v>653</v>
       </c>
       <c r="D51" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E51" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F51" s="334"/>
-      <c r="G51" s="125">
-        <v>45291</v>
-      </c>
+      <c r="G51" s="125"/>
       <c r="H51" s="125">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="I51" s="123">
         <v>42533</v>
@@ -38405,15 +38403,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38746,6 +38735,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -38783,14 +38781,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38805,6 +38795,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677EEA7B-079B-6045-A911-D3641E87EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B7E3BF-9EDF-5343-A5A0-18F9B7B2870A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -195,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{212D0BA5-2590-964B-94B4-A29484F5AA04}">
       <text>
         <r>
           <rPr>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
+    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{A6DCB7E2-74E6-854F-8E16-ED35920E6252}">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C53" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
+    <comment ref="C52" authorId="0" shapeId="0" xr:uid="{39646029-FBAA-B440-B731-9434C73CE445}">
       <text>
         <r>
           <rPr>
@@ -1502,7 +1502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3402" uniqueCount="1350">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -5526,15 +5526,6 @@
   </si>
   <si>
     <t>first production of Model Y in 2021</t>
-  </si>
-  <si>
-    <t>Ford Otosan</t>
-  </si>
-  <si>
-    <t>Dolj</t>
-  </si>
-  <si>
-    <t>just four EVs produced in 2024 …</t>
   </si>
   <si>
     <t>these are PHEVs; phase 1</t>
@@ -7351,10 +7342,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J65" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J65">
-    <sortCondition ref="A1:A65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J64" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J64">
+    <sortCondition ref="A1:A64"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{88F84DCB-9434-3D44-9E03-D4FD2CDBE33E}" name="company_name" dataDxfId="9"/>
@@ -7700,7 +7691,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -8028,7 +8019,7 @@
         <v>20016</v>
       </c>
       <c r="J11" s="160" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -8083,7 +8074,7 @@
         <v>51082</v>
       </c>
       <c r="J13" s="160" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -8139,7 +8130,7 @@
         <v>111890</v>
       </c>
       <c r="J15" s="160" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -8167,7 +8158,7 @@
         <v>46387</v>
       </c>
       <c r="J16" s="160" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -8260,13 +8251,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="162" t="s">
-        <v>1312</v>
+        <v>434</v>
       </c>
       <c r="B20" s="162" t="s">
-        <v>1247</v>
+        <v>435</v>
       </c>
       <c r="C20" s="162" t="s">
-        <v>1313</v>
+        <v>436</v>
       </c>
       <c r="D20" s="162" t="s">
         <v>143</v>
@@ -8274,27 +8265,28 @@
       <c r="E20" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="333"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="163">
-        <v>45657</v>
-      </c>
-      <c r="I20" s="160">
-        <v>4</v>
-      </c>
-      <c r="J20" s="160" t="s">
-        <v>1314</v>
-      </c>
+      <c r="F20" s="334"/>
+      <c r="G20" s="125">
+        <v>43891</v>
+      </c>
+      <c r="H20" s="125">
+        <v>43891</v>
+      </c>
+      <c r="I20" s="123">
+        <f>28213+43839</f>
+        <v>72052</v>
+      </c>
+      <c r="J20" s="160"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="162" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B21" s="162" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C21" s="162" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D21" s="162" t="s">
         <v>143</v>
@@ -8302,48 +8294,45 @@
       <c r="E21" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="334"/>
-      <c r="G21" s="125">
-        <v>43891</v>
-      </c>
+      <c r="F21" s="334">
+        <v>2020</v>
+      </c>
+      <c r="G21" s="125"/>
       <c r="H21" s="125">
-        <v>43891</v>
+        <v>44196</v>
       </c>
       <c r="I21" s="123">
-        <f>28213+43839</f>
-        <v>72052</v>
-      </c>
-      <c r="J21" s="160"/>
+        <v>37239</v>
+      </c>
+      <c r="J21" s="160" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="162" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B22" s="162" t="s">
-        <v>444</v>
+        <v>58</v>
       </c>
       <c r="C22" s="162" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E22" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="334">
-        <v>2020</v>
-      </c>
-      <c r="G22" s="125"/>
+      <c r="F22" s="334"/>
+      <c r="G22" s="125">
+        <v>45260</v>
+      </c>
       <c r="H22" s="125">
-        <v>44196</v>
-      </c>
-      <c r="I22" s="123">
-        <v>37239</v>
-      </c>
-      <c r="J22" s="160" t="s">
-        <v>1315</v>
-      </c>
+        <v>45261</v>
+      </c>
+      <c r="I22" s="123"/>
+      <c r="J22" s="160"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="162" t="s">
@@ -8356,19 +8345,23 @@
         <v>477</v>
       </c>
       <c r="D23" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E23" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="334"/>
+      <c r="F23" s="334">
+        <v>2020</v>
+      </c>
       <c r="G23" s="125">
-        <v>45260</v>
+        <v>43831</v>
       </c>
       <c r="H23" s="125">
-        <v>45261</v>
-      </c>
-      <c r="I23" s="123"/>
+        <v>43831</v>
+      </c>
+      <c r="I23" s="160">
+        <v>4760</v>
+      </c>
       <c r="J23" s="160"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -8379,25 +8372,25 @@
         <v>58</v>
       </c>
       <c r="C24" s="162" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="D24" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E24" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="334">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G24" s="125">
-        <v>43831</v>
+        <v>43101</v>
       </c>
       <c r="H24" s="125">
-        <v>43831</v>
-      </c>
-      <c r="I24" s="160">
-        <v>4760</v>
+        <v>43102</v>
+      </c>
+      <c r="I24" s="123">
+        <v>83195</v>
       </c>
       <c r="J24" s="160"/>
     </row>
@@ -8409,25 +8402,25 @@
         <v>58</v>
       </c>
       <c r="C25" s="162" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E25" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="334">
-        <v>2018</v>
-      </c>
-      <c r="G25" s="125">
-        <v>43101</v>
+      <c r="F25" s="333">
+        <v>2016</v>
+      </c>
+      <c r="G25" s="163">
+        <v>42370</v>
       </c>
       <c r="H25" s="125">
-        <v>43102</v>
+        <v>42370</v>
       </c>
       <c r="I25" s="123">
-        <v>83195</v>
+        <v>62577.5</v>
       </c>
       <c r="J25" s="160"/>
     </row>
@@ -8439,25 +8432,25 @@
         <v>58</v>
       </c>
       <c r="C26" s="162" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="D26" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E26" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F26" s="333">
-        <v>2016</v>
-      </c>
-      <c r="G26" s="163">
-        <v>42370</v>
+      <c r="F26" s="334">
+        <v>2015</v>
+      </c>
+      <c r="G26" s="125">
+        <v>42005</v>
       </c>
       <c r="H26" s="125">
-        <v>42370</v>
-      </c>
-      <c r="I26" s="123">
-        <v>62577.5</v>
+        <v>42005</v>
+      </c>
+      <c r="I26" s="335">
+        <v>18427</v>
       </c>
       <c r="J26" s="160"/>
     </row>
@@ -8472,22 +8465,18 @@
         <v>463</v>
       </c>
       <c r="D27" s="162" t="s">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="E27" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="334">
-        <v>2015</v>
-      </c>
-      <c r="G27" s="125">
-        <v>42005</v>
-      </c>
-      <c r="H27" s="125">
-        <v>42005</v>
-      </c>
+      <c r="F27" s="333">
+        <v>2019</v>
+      </c>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
       <c r="I27" s="335">
-        <v>18427</v>
+        <v>2650</v>
       </c>
       <c r="J27" s="160"/>
     </row>
@@ -8507,13 +8496,11 @@
       <c r="E28" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="333">
-        <v>2019</v>
-      </c>
+      <c r="F28" s="333"/>
       <c r="G28" s="162"/>
       <c r="H28" s="162"/>
       <c r="I28" s="335">
-        <v>2650</v>
+        <v>73662.5</v>
       </c>
       <c r="J28" s="160"/>
     </row>
@@ -8522,110 +8509,114 @@
         <v>462</v>
       </c>
       <c r="B29" s="162" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C29" s="162" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="D29" s="162" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="E29" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F29" s="333"/>
-      <c r="G29" s="162"/>
+      <c r="F29" s="333" t="s">
+        <v>511</v>
+      </c>
+      <c r="G29" s="163">
+        <v>44530</v>
+      </c>
       <c r="H29" s="162"/>
-      <c r="I29" s="335">
-        <v>73662.5</v>
-      </c>
-      <c r="J29" s="160"/>
+      <c r="I29" s="123">
+        <v>50444</v>
+      </c>
+      <c r="J29" s="160" t="s">
+        <v>1331</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="162" t="s">
         <v>462</v>
       </c>
       <c r="B30" s="162" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="C30" s="162" t="s">
-        <v>510</v>
+        <v>1330</v>
       </c>
       <c r="D30" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E30" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="333" t="s">
-        <v>511</v>
+      <c r="F30" s="333">
+        <v>2019</v>
       </c>
       <c r="G30" s="163">
-        <v>44530</v>
-      </c>
-      <c r="H30" s="162"/>
+        <v>43617</v>
+      </c>
+      <c r="H30" s="104"/>
       <c r="I30" s="123">
-        <v>50444</v>
-      </c>
-      <c r="J30" s="160" t="s">
-        <v>1334</v>
-      </c>
+        <v>10739</v>
+      </c>
+      <c r="J30" s="160"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="162" t="s">
-        <v>462</v>
-      </c>
-      <c r="B31" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" s="162" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D31" s="162" t="s">
+      <c r="A31" s="337" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="337" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="337" t="s">
+        <v>522</v>
+      </c>
+      <c r="D31" s="337" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="337" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="338">
+        <v>2013</v>
+      </c>
+      <c r="G31" s="339">
+        <v>41275</v>
+      </c>
+      <c r="H31" s="337"/>
+      <c r="I31" s="340">
+        <v>40710</v>
+      </c>
+      <c r="J31" s="160"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="341" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B32" s="341" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="341" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D32" s="162" t="s">
         <v>143</v>
       </c>
-      <c r="E31" s="162" t="s">
+      <c r="E32" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="333">
-        <v>2019</v>
-      </c>
-      <c r="G31" s="163">
-        <v>43617</v>
-      </c>
-      <c r="H31" s="104"/>
-      <c r="I31" s="123">
-        <v>10739</v>
-      </c>
-      <c r="J31" s="160"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="337" t="s">
-        <v>521</v>
-      </c>
-      <c r="B32" s="337" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="337" t="s">
-        <v>522</v>
-      </c>
-      <c r="D32" s="337" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="337" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="338">
-        <v>2013</v>
-      </c>
-      <c r="G32" s="339">
-        <v>41275</v>
-      </c>
-      <c r="H32" s="337"/>
-      <c r="I32" s="340">
-        <v>40710</v>
-      </c>
-      <c r="J32" s="160"/>
+      <c r="F32" s="333"/>
+      <c r="G32" s="163">
+        <v>40908</v>
+      </c>
+      <c r="H32" s="162"/>
+      <c r="I32" s="160">
+        <v>11872</v>
+      </c>
+      <c r="J32" s="160" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="341" t="s">
@@ -8637,22 +8628,22 @@
       <c r="C33" s="341" t="s">
         <v>1076</v>
       </c>
-      <c r="D33" s="162" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" s="162" t="s">
+      <c r="D33" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="333"/>
-      <c r="G33" s="163">
-        <v>40908</v>
-      </c>
-      <c r="H33" s="162"/>
-      <c r="I33" s="160">
-        <v>11872</v>
+      <c r="F33" s="342"/>
+      <c r="G33" s="343">
+        <v>45291</v>
+      </c>
+      <c r="H33" s="343"/>
+      <c r="I33" s="344">
+        <v>17562</v>
       </c>
       <c r="J33" s="160" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -8663,25 +8654,23 @@
         <v>265</v>
       </c>
       <c r="C34" s="341" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D34" s="346" t="s">
-        <v>71</v>
+        <v>1133</v>
+      </c>
+      <c r="D34" s="341" t="s">
+        <v>60</v>
       </c>
       <c r="E34" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F34" s="342"/>
       <c r="G34" s="343">
-        <v>45291</v>
+        <v>43830</v>
       </c>
       <c r="H34" s="343"/>
       <c r="I34" s="344">
-        <v>17562</v>
-      </c>
-      <c r="J34" s="160" t="s">
-        <v>1343</v>
-      </c>
+        <v>2117</v>
+      </c>
+      <c r="J34" s="160"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="341" t="s">
@@ -8691,23 +8680,25 @@
         <v>265</v>
       </c>
       <c r="C35" s="341" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D35" s="341" t="s">
-        <v>60</v>
+        <v>1064</v>
+      </c>
+      <c r="D35" s="346" t="s">
+        <v>143</v>
       </c>
       <c r="E35" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F35" s="342"/>
-      <c r="G35" s="343">
-        <v>43830</v>
-      </c>
-      <c r="H35" s="343"/>
+      <c r="G35" s="341"/>
+      <c r="H35" s="339">
+        <v>44926</v>
+      </c>
       <c r="I35" s="344">
-        <v>2117</v>
-      </c>
-      <c r="J35" s="160"/>
+        <v>71051</v>
+      </c>
+      <c r="J35" s="160" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="341" t="s">
@@ -8717,24 +8708,24 @@
         <v>265</v>
       </c>
       <c r="C36" s="341" t="s">
-        <v>1064</v>
+        <v>1136</v>
       </c>
       <c r="D36" s="346" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E36" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F36" s="342"/>
-      <c r="G36" s="341"/>
-      <c r="H36" s="339">
-        <v>44926</v>
-      </c>
-      <c r="I36" s="344">
-        <v>71051</v>
+      <c r="G36" s="163">
+        <v>41639</v>
+      </c>
+      <c r="H36" s="162"/>
+      <c r="I36" s="160">
+        <v>48013</v>
       </c>
       <c r="J36" s="160" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -8753,16 +8744,16 @@
       <c r="E37" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="F37" s="342"/>
-      <c r="G37" s="163">
-        <v>41639</v>
+      <c r="F37" s="333"/>
+      <c r="G37" s="353">
+        <v>44196</v>
       </c>
       <c r="H37" s="162"/>
-      <c r="I37" s="160">
-        <v>48013</v>
+      <c r="I37" s="336">
+        <v>102187</v>
       </c>
       <c r="J37" s="160" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -8776,86 +8767,84 @@
         <v>1136</v>
       </c>
       <c r="D38" s="346" t="s">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="E38" s="341" t="s">
         <v>61</v>
       </c>
       <c r="F38" s="333"/>
-      <c r="G38" s="353">
+      <c r="G38" s="343">
+        <v>45657</v>
+      </c>
+      <c r="H38" s="162"/>
+      <c r="I38" s="344">
+        <v>0</v>
+      </c>
+      <c r="J38" s="160" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="337" t="s">
+        <v>541</v>
+      </c>
+      <c r="B39" s="337" t="s">
+        <v>542</v>
+      </c>
+      <c r="C39" s="337" t="s">
+        <v>543</v>
+      </c>
+      <c r="D39" s="337" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="337" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="338"/>
+      <c r="G39" s="339">
         <v>44196</v>
       </c>
-      <c r="H38" s="162"/>
-      <c r="I38" s="336">
-        <v>102187</v>
-      </c>
-      <c r="J38" s="160" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="341" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B39" s="341" t="s">
-        <v>265</v>
-      </c>
-      <c r="C39" s="341" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D39" s="346" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="341" t="s">
+      <c r="H39" s="337"/>
+      <c r="I39" s="340">
+        <v>26699</v>
+      </c>
+      <c r="J39" s="160"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="162" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B40" s="162" t="s">
+        <v>318</v>
+      </c>
+      <c r="C40" s="162" t="s">
+        <v>579</v>
+      </c>
+      <c r="D40" s="162" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F39" s="333"/>
-      <c r="G39" s="343">
-        <v>45657</v>
-      </c>
-      <c r="H39" s="162"/>
-      <c r="I39" s="344">
-        <v>0</v>
-      </c>
-      <c r="J39" s="160" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="337" t="s">
-        <v>541</v>
-      </c>
-      <c r="B40" s="337" t="s">
-        <v>542</v>
-      </c>
-      <c r="C40" s="337" t="s">
-        <v>543</v>
-      </c>
-      <c r="D40" s="337" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="337" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="338"/>
-      <c r="G40" s="339">
-        <v>44196</v>
-      </c>
-      <c r="H40" s="337"/>
-      <c r="I40" s="340">
-        <v>26699</v>
+      <c r="F40" s="334"/>
+      <c r="G40" s="125">
+        <v>44197</v>
+      </c>
+      <c r="H40" s="125"/>
+      <c r="I40" s="123">
+        <v>46589</v>
       </c>
       <c r="J40" s="160"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="162" t="s">
-        <v>1316</v>
+      <c r="A41" s="104" t="s">
+        <v>590</v>
       </c>
       <c r="B41" s="162" t="s">
-        <v>318</v>
+        <v>435</v>
       </c>
       <c r="C41" s="162" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="D41" s="162" t="s">
         <v>143</v>
@@ -8865,38 +8854,38 @@
       </c>
       <c r="F41" s="334"/>
       <c r="G41" s="125">
-        <v>44197</v>
-      </c>
-      <c r="H41" s="125"/>
+        <v>44075</v>
+      </c>
+      <c r="H41" s="104"/>
       <c r="I41" s="123">
-        <v>46589</v>
+        <f>67243+12264</f>
+        <v>79507</v>
       </c>
       <c r="J41" s="160"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="104" t="s">
-        <v>590</v>
+      <c r="A42" s="162" t="s">
+        <v>613</v>
       </c>
       <c r="B42" s="162" t="s">
-        <v>435</v>
+        <v>265</v>
       </c>
       <c r="C42" s="162" t="s">
-        <v>591</v>
+        <v>1083</v>
       </c>
       <c r="D42" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E42" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="334"/>
+      <c r="F42" s="333"/>
       <c r="G42" s="125">
-        <v>44075</v>
-      </c>
-      <c r="H42" s="104"/>
-      <c r="I42" s="123">
-        <f>67243+12264</f>
-        <v>79507</v>
+        <v>44561</v>
+      </c>
+      <c r="H42" s="162"/>
+      <c r="I42" s="160">
+        <v>33335</v>
       </c>
       <c r="J42" s="160"/>
     </row>
@@ -8905,24 +8894,26 @@
         <v>613</v>
       </c>
       <c r="B43" s="162" t="s">
-        <v>265</v>
-      </c>
-      <c r="C43" s="162" t="s">
-        <v>1083</v>
+        <v>444</v>
+      </c>
+      <c r="C43" s="322" t="s">
+        <v>628</v>
       </c>
       <c r="D43" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E43" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="333"/>
+      <c r="F43" s="334"/>
       <c r="G43" s="125">
-        <v>44561</v>
-      </c>
-      <c r="H43" s="162"/>
-      <c r="I43" s="160">
-        <v>33335</v>
+        <v>43559</v>
+      </c>
+      <c r="H43" s="125">
+        <v>43559</v>
+      </c>
+      <c r="I43" s="123">
+        <v>49264</v>
       </c>
       <c r="J43" s="160"/>
     </row>
@@ -8931,10 +8922,10 @@
         <v>613</v>
       </c>
       <c r="B44" s="162" t="s">
-        <v>444</v>
-      </c>
-      <c r="C44" s="322" t="s">
-        <v>628</v>
+        <v>318</v>
+      </c>
+      <c r="C44" s="104" t="s">
+        <v>638</v>
       </c>
       <c r="D44" s="162" t="s">
         <v>143</v>
@@ -8942,15 +8933,17 @@
       <c r="E44" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F44" s="334"/>
+      <c r="F44" s="334">
+        <v>2012</v>
+      </c>
       <c r="G44" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="H44" s="125">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="I44" s="123">
-        <v>49264</v>
+        <v>51498</v>
       </c>
       <c r="J44" s="160"/>
     </row>
@@ -8961,8 +8954,8 @@
       <c r="B45" s="162" t="s">
         <v>318</v>
       </c>
-      <c r="C45" s="104" t="s">
-        <v>638</v>
+      <c r="C45" s="321" t="s">
+        <v>1013</v>
       </c>
       <c r="D45" s="162" t="s">
         <v>143</v>
@@ -8970,18 +8963,10 @@
       <c r="E45" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="334">
-        <v>2012</v>
-      </c>
-      <c r="G45" s="125">
-        <v>44562</v>
-      </c>
-      <c r="H45" s="125">
-        <v>44562</v>
-      </c>
-      <c r="I45" s="123">
-        <v>51498</v>
-      </c>
+      <c r="F45" s="333"/>
+      <c r="G45" s="163"/>
+      <c r="H45" s="163"/>
+      <c r="I45" s="160"/>
       <c r="J45" s="160"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -8989,10 +8974,10 @@
         <v>613</v>
       </c>
       <c r="B46" s="162" t="s">
-        <v>318</v>
-      </c>
-      <c r="C46" s="321" t="s">
-        <v>1013</v>
+        <v>58</v>
+      </c>
+      <c r="C46" s="162" t="s">
+        <v>614</v>
       </c>
       <c r="D46" s="162" t="s">
         <v>143</v>
@@ -9000,67 +8985,73 @@
       <c r="E46" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="333"/>
-      <c r="G46" s="163"/>
-      <c r="H46" s="163"/>
-      <c r="I46" s="160"/>
-      <c r="J46" s="160"/>
+      <c r="F46" s="334">
+        <v>2020</v>
+      </c>
+      <c r="G46" s="125">
+        <v>45658</v>
+      </c>
+      <c r="H46" s="104"/>
+      <c r="I46" s="123">
+        <v>5888</v>
+      </c>
+      <c r="J46" s="160" t="s">
+        <v>1334</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="162" t="s">
         <v>613</v>
       </c>
       <c r="B47" s="162" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C47" s="162" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D47" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E47" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="334">
-        <v>2020</v>
-      </c>
-      <c r="G47" s="125">
-        <v>45658</v>
-      </c>
-      <c r="H47" s="104"/>
-      <c r="I47" s="123">
-        <v>5888</v>
-      </c>
-      <c r="J47" s="160" t="s">
-        <v>1337</v>
-      </c>
+      <c r="F47" s="333"/>
+      <c r="G47" s="163">
+        <v>44742</v>
+      </c>
+      <c r="H47" s="162"/>
+      <c r="I47" s="160">
+        <v>15000</v>
+      </c>
+      <c r="J47" s="160"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="162" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B48" s="162" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" s="162" t="s">
-        <v>621</v>
+        <v>265</v>
+      </c>
+      <c r="C48" s="137" t="s">
+        <v>663</v>
       </c>
       <c r="D48" s="162" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="E48" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F48" s="333"/>
-      <c r="G48" s="163">
-        <v>44742</v>
-      </c>
-      <c r="H48" s="162"/>
-      <c r="I48" s="160">
-        <v>15000</v>
-      </c>
-      <c r="J48" s="160"/>
+      <c r="F48" s="334"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125">
+        <v>45292</v>
+      </c>
+      <c r="I48" s="123">
+        <v>24008</v>
+      </c>
+      <c r="J48" s="160" t="s">
+        <v>1349</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="162" t="s">
@@ -9069,8 +9060,8 @@
       <c r="B49" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C49" s="137" t="s">
-        <v>663</v>
+      <c r="C49" s="162" t="s">
+        <v>668</v>
       </c>
       <c r="D49" s="162" t="s">
         <v>214</v>
@@ -9081,14 +9072,12 @@
       <c r="F49" s="334"/>
       <c r="G49" s="125"/>
       <c r="H49" s="125">
-        <v>45292</v>
+        <v>44203</v>
       </c>
       <c r="I49" s="123">
-        <v>24008</v>
-      </c>
-      <c r="J49" s="160" t="s">
-        <v>1352</v>
-      </c>
+        <v>23534</v>
+      </c>
+      <c r="J49" s="160"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="162" t="s">
@@ -9098,7 +9087,7 @@
         <v>265</v>
       </c>
       <c r="C50" s="162" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="D50" s="162" t="s">
         <v>214</v>
@@ -9109,22 +9098,22 @@
       <c r="F50" s="334"/>
       <c r="G50" s="125"/>
       <c r="H50" s="125">
-        <v>44203</v>
+        <v>44926</v>
       </c>
       <c r="I50" s="123">
-        <v>23534</v>
+        <v>42533</v>
       </c>
       <c r="J50" s="160"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B51" s="162" t="s">
         <v>265</v>
       </c>
       <c r="C51" s="162" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D51" s="162" t="s">
         <v>214</v>
@@ -9132,53 +9121,53 @@
       <c r="E51" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F51" s="334"/>
-      <c r="G51" s="125"/>
-      <c r="H51" s="125">
-        <v>44926</v>
-      </c>
-      <c r="I51" s="123">
-        <v>42533</v>
-      </c>
-      <c r="J51" s="160"/>
+      <c r="F51" s="333"/>
+      <c r="G51" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H51" s="162"/>
+      <c r="I51" s="160">
+        <v>15433</v>
+      </c>
+      <c r="J51" s="160" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="162" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B52" s="162" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C52" s="162" t="s">
-        <v>657</v>
+        <v>680</v>
       </c>
       <c r="D52" s="162" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="E52" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F52" s="333"/>
-      <c r="G52" s="163">
-        <v>44196</v>
-      </c>
+      <c r="F52" s="333" t="s">
+        <v>682</v>
+      </c>
+      <c r="G52" s="162"/>
       <c r="H52" s="162"/>
       <c r="I52" s="160">
-        <v>15433</v>
-      </c>
-      <c r="J52" s="160" t="s">
-        <v>1351</v>
-      </c>
+        <v>111872</v>
+      </c>
+      <c r="J52" s="160"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="162" t="s">
         <v>652</v>
       </c>
       <c r="B53" s="162" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="C53" s="162" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D53" s="162" t="s">
         <v>143</v>
@@ -9186,19 +9175,21 @@
       <c r="E53" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F53" s="333" t="s">
-        <v>682</v>
-      </c>
-      <c r="G53" s="162"/>
+      <c r="F53" s="333"/>
+      <c r="G53" s="163">
+        <v>44927</v>
+      </c>
       <c r="H53" s="162"/>
       <c r="I53" s="160">
-        <v>111872</v>
-      </c>
-      <c r="J53" s="160"/>
+        <v>28788</v>
+      </c>
+      <c r="J53" s="160" t="s">
+        <v>1333</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="162" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="B54" s="162" t="s">
         <v>357</v>
@@ -9207,50 +9198,52 @@
         <v>691</v>
       </c>
       <c r="D54" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E54" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F54" s="333"/>
       <c r="G54" s="163">
-        <v>44927</v>
+        <v>45658</v>
       </c>
       <c r="H54" s="162"/>
       <c r="I54" s="160">
-        <v>28788</v>
+        <v>976</v>
       </c>
       <c r="J54" s="160" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="162" t="s">
-        <v>613</v>
+        <v>1028</v>
       </c>
       <c r="B55" s="162" t="s">
-        <v>357</v>
+        <v>141</v>
       </c>
       <c r="C55" s="162" t="s">
-        <v>691</v>
+        <v>1029</v>
       </c>
       <c r="D55" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E55" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="333"/>
+      <c r="F55" s="333">
+        <v>2018</v>
+      </c>
       <c r="G55" s="163">
-        <v>45658</v>
-      </c>
-      <c r="H55" s="162"/>
+        <v>43101</v>
+      </c>
+      <c r="H55" s="163">
+        <v>43101</v>
+      </c>
       <c r="I55" s="160">
-        <v>976</v>
-      </c>
-      <c r="J55" s="160" t="s">
-        <v>1335</v>
-      </c>
+        <v>14287</v>
+      </c>
+      <c r="J55" s="160"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="162" t="s">
@@ -9263,76 +9256,70 @@
         <v>1029</v>
       </c>
       <c r="D56" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E56" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="333">
-        <v>2018</v>
-      </c>
-      <c r="G56" s="163">
-        <v>43101</v>
-      </c>
-      <c r="H56" s="163">
-        <v>43101</v>
-      </c>
+      <c r="F56" s="333"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="163"/>
       <c r="I56" s="160">
-        <v>14287</v>
+        <v>10881</v>
       </c>
       <c r="J56" s="160"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="162" t="s">
-        <v>1028</v>
+        <v>718</v>
       </c>
       <c r="B57" s="162" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="C57" s="162" t="s">
-        <v>1029</v>
+        <v>1309</v>
       </c>
       <c r="D57" s="162" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E57" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F57" s="333"/>
       <c r="G57" s="163"/>
-      <c r="H57" s="163"/>
-      <c r="I57" s="160">
-        <v>10881</v>
-      </c>
-      <c r="J57" s="160"/>
+      <c r="H57" s="163">
+        <v>44561</v>
+      </c>
+      <c r="I57" s="123">
+        <v>206097</v>
+      </c>
+      <c r="J57" s="160" t="s">
+        <v>1311</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="162" t="s">
-        <v>718</v>
+        <v>575</v>
       </c>
       <c r="B58" s="162" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="162" t="s">
-        <v>1309</v>
+        <v>754</v>
       </c>
       <c r="D58" s="162" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E58" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F58" s="333"/>
-      <c r="G58" s="163"/>
-      <c r="H58" s="163">
-        <v>44561</v>
-      </c>
-      <c r="I58" s="123">
-        <v>206097</v>
-      </c>
-      <c r="J58" s="160" t="s">
-        <v>1311</v>
-      </c>
+      <c r="G58" s="162"/>
+      <c r="H58" s="162"/>
+      <c r="I58" s="160">
+        <v>140000</v>
+      </c>
+      <c r="J58" s="160"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="162" t="s">
@@ -9342,7 +9329,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="162" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D59" s="162" t="s">
         <v>214</v>
@@ -9351,36 +9338,38 @@
         <v>61</v>
       </c>
       <c r="F59" s="333"/>
-      <c r="G59" s="162"/>
+      <c r="G59" s="163">
+        <v>44926</v>
+      </c>
       <c r="H59" s="162"/>
       <c r="I59" s="160">
-        <v>140000</v>
+        <v>29724</v>
       </c>
       <c r="J59" s="160"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="162" t="s">
+      <c r="A60" s="181" t="s">
         <v>575</v>
       </c>
-      <c r="B60" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="162" t="s">
-        <v>764</v>
-      </c>
-      <c r="D60" s="162" t="s">
-        <v>214</v>
-      </c>
-      <c r="E60" s="162" t="s">
+      <c r="B60" s="181" t="s">
+        <v>444</v>
+      </c>
+      <c r="C60" s="181" t="s">
+        <v>745</v>
+      </c>
+      <c r="D60" s="181" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F60" s="333"/>
-      <c r="G60" s="163">
-        <v>44926</v>
-      </c>
-      <c r="H60" s="162"/>
-      <c r="I60" s="160">
-        <v>29724</v>
+      <c r="F60" s="334"/>
+      <c r="G60" s="125">
+        <v>43830</v>
+      </c>
+      <c r="H60" s="125"/>
+      <c r="I60" s="123">
+        <v>13528</v>
       </c>
       <c r="J60" s="160"/>
     </row>
@@ -9395,70 +9384,70 @@
         <v>745</v>
       </c>
       <c r="D61" s="181" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E61" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F61" s="334"/>
-      <c r="G61" s="125">
-        <v>43830</v>
-      </c>
-      <c r="H61" s="125"/>
-      <c r="I61" s="123">
-        <v>13528</v>
+      <c r="F61" s="333"/>
+      <c r="G61" s="163">
+        <v>45291</v>
+      </c>
+      <c r="H61" s="163"/>
+      <c r="I61" s="160">
+        <v>94839</v>
       </c>
       <c r="J61" s="160"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="181" t="s">
-        <v>575</v>
-      </c>
-      <c r="B62" s="181" t="s">
-        <v>444</v>
-      </c>
-      <c r="C62" s="181" t="s">
-        <v>745</v>
-      </c>
-      <c r="D62" s="181" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="181" t="s">
+      <c r="A62" s="162" t="s">
+        <v>824</v>
+      </c>
+      <c r="B62" s="162" t="s">
+        <v>825</v>
+      </c>
+      <c r="C62" s="162" t="s">
+        <v>826</v>
+      </c>
+      <c r="D62" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F62" s="333"/>
-      <c r="G62" s="163">
-        <v>45291</v>
-      </c>
-      <c r="H62" s="163"/>
-      <c r="I62" s="160">
-        <v>94839</v>
+      <c r="F62" s="334"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="125">
+        <v>45657</v>
+      </c>
+      <c r="I62" s="123">
+        <v>85654</v>
       </c>
       <c r="J62" s="160"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="162" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B63" s="162" t="s">
-        <v>825</v>
+        <v>212</v>
       </c>
       <c r="C63" s="162" t="s">
-        <v>826</v>
-      </c>
-      <c r="D63" s="104" t="s">
-        <v>60</v>
+        <v>817</v>
+      </c>
+      <c r="D63" s="162" t="s">
+        <v>143</v>
       </c>
       <c r="E63" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="334"/>
-      <c r="G63" s="104"/>
-      <c r="H63" s="125">
-        <v>45657</v>
-      </c>
-      <c r="I63" s="123">
-        <v>85654</v>
+      <c r="F63" s="333"/>
+      <c r="G63" s="163">
+        <v>44196</v>
+      </c>
+      <c r="H63" s="163"/>
+      <c r="I63" s="160">
+        <v>34001</v>
       </c>
       <c r="J63" s="160"/>
     </row>
@@ -9473,53 +9462,27 @@
         <v>817</v>
       </c>
       <c r="D64" s="162" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E64" s="162" t="s">
         <v>61</v>
       </c>
       <c r="F64" s="333"/>
       <c r="G64" s="163">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="H64" s="163"/>
       <c r="I64" s="160">
-        <v>34001</v>
+        <v>133505</v>
       </c>
       <c r="J64" s="160"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A65" s="162" t="s">
-        <v>810</v>
-      </c>
-      <c r="B65" s="162" t="s">
-        <v>212</v>
-      </c>
-      <c r="C65" s="162" t="s">
-        <v>817</v>
-      </c>
-      <c r="D65" s="162" t="s">
-        <v>71</v>
-      </c>
-      <c r="E65" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F65" s="333"/>
-      <c r="G65" s="163">
-        <v>45657</v>
-      </c>
-      <c r="H65" s="163"/>
-      <c r="I65" s="160">
-        <v>133505</v>
-      </c>
-      <c r="J65" s="160"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="162"/>
-      <c r="B66" s="162"/>
-      <c r="C66" s="162"/>
-      <c r="D66" s="162"/>
-      <c r="E66" s="162"/>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="162"/>
+      <c r="B65" s="162"/>
+      <c r="C65" s="162"/>
+      <c r="D65" s="162"/>
+      <c r="E65" s="162"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11507,7 +11470,7 @@
         <v>1487</v>
       </c>
       <c r="U25" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="V25" s="57">
         <f>SUM(S4:S25)</f>
@@ -12283,13 +12246,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J17" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="K17">
         <v>2011</v>
       </c>
       <c r="L17" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="O17" s="57">
         <f>R7</f>
@@ -12298,13 +12261,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J18" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="K18">
         <v>2023</v>
       </c>
       <c r="L18" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="O18" s="57">
         <f>S4+S5+S8</f>
@@ -12328,7 +12291,7 @@
         <v>2012</v>
       </c>
       <c r="L21" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="Q21">
         <v>48013</v>
@@ -12342,7 +12305,7 @@
         <v>2018</v>
       </c>
       <c r="L22" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="Q22">
         <v>102187</v>
@@ -12356,7 +12319,7 @@
         <v>2019</v>
       </c>
       <c r="L24" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="O24" s="57">
         <f>S9</f>
@@ -12755,10 +12718,10 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C14" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D14" s="57">
         <f>N4+N3</f>
@@ -12767,10 +12730,10 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C15" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="D15" s="57">
         <f>SUM(Q2:Q4)</f>
@@ -12779,7 +12742,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D17">
         <v>85654</v>
@@ -35978,10 +35941,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="E17" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -35995,10 +35958,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="E20" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -36009,7 +35972,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C23" s="345" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="24" spans="1:18" s="324" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -36200,7 +36163,7 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C35" s="324" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="D35">
         <v>2021</v>
@@ -37005,7 +36968,7 @@
         <v>8327</v>
       </c>
       <c r="W21" s="22" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
@@ -38403,6 +38366,42 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Dataset</Value>
+    </ProjectType>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
+      <Value>Green Economy</Value>
+    </ResearchArea>
+    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
+    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
+    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
+      <UserInfo>
+        <DisplayName>Ugne Keliauskaite</DisplayName>
+        <AccountId>1048</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Ben McWilliams</DisplayName>
+        <AccountId>22</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Marie Jugé</DisplayName>
+        <AccountId>1714</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </Authors>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38735,7 +38734,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -38744,43 +38743,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectType xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Dataset</Value>
-    </ProjectType>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ResearchArea xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46">
-      <Value>Green Economy</Value>
-    </ResearchArea>
-    <TaxCatchAll xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xsi:nil="true"/>
-    <FinalTitle xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <LinktoPublication xmlns="a800b4a7-713e-40fb-b259-074d23fe1c46" xsi:nil="true"/>
-    <Authors xmlns="b17ea8e4-3fb0-4555-9c20-069a19b46cb2">
-      <UserInfo>
-        <DisplayName>Ugne Keliauskaite</DisplayName>
-        <AccountId>1048</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Ben McWilliams</DisplayName>
-        <AccountId>22</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Marie Jugé</DisplayName>
-        <AccountId>1714</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </Authors>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38799,27 +38779,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a800b4a7-713e-40fb-b259-074d23fe1c46"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/reconcile/storage/input/vehicles_impute.xlsx
+++ b/reconcile/storage/input/vehicles_impute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B7E3BF-9EDF-5343-A5A0-18F9B7B2870A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3CDDD3-12A1-C840-A192-3CD8F74BFAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
+    <workbookView xWindow="23760" yWindow="500" windowWidth="14640" windowHeight="16660" firstSheet="3" activeTab="6" xr2:uid="{BCDF9C02-A93F-4FDD-BCB7-C0839095CF07}"/>
   </bookViews>
   <sheets>
     <sheet name="production_to_impute" sheetId="16" r:id="rId1"/>
@@ -1502,7 +1502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3402" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="1350">
   <si>
     <t>facility_id_readable</t>
   </si>
@@ -7343,7 +7343,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}" name="Table1" displayName="Table1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J64" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}"/>
+  <autoFilter ref="A1:J64" xr:uid="{412528DA-AF97-D649-A38F-E0F2FFD8069D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Germany"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J64">
     <sortCondition ref="A1:A64"/>
   </sortState>
@@ -7738,7 +7744,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="341" t="s">
         <v>211</v>
       </c>
@@ -7764,7 +7770,7 @@
       </c>
       <c r="J2" s="336"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="104" t="s">
         <v>211</v>
       </c>
@@ -7848,7 +7854,7 @@
       </c>
       <c r="J5" s="160"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="162" t="s">
         <v>253</v>
       </c>
@@ -7933,7 +7939,7 @@
       </c>
       <c r="J8" s="160"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="162" t="s">
         <v>57</v>
       </c>
@@ -8133,7 +8139,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="162" t="s">
         <v>57</v>
       </c>
@@ -8161,7 +8167,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="162" t="s">
         <v>356</v>
       </c>
@@ -8191,7 +8197,7 @@
       </c>
       <c r="J17" s="160"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="162" t="s">
         <v>385</v>
       </c>
@@ -8221,7 +8227,7 @@
       </c>
       <c r="J18" s="160"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="162" t="s">
         <v>399</v>
       </c>
@@ -8249,7 +8255,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="162" t="s">
         <v>434</v>
       </c>
@@ -8278,7 +8284,7 @@
       </c>
       <c r="J20" s="160"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="162" t="s">
         <v>443</v>
       </c>
@@ -8504,7 +8510,7 @@
       </c>
       <c r="J28" s="160"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="162" t="s">
         <v>462</v>
       </c>
@@ -8534,7 +8540,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="162" t="s">
         <v>462</v>
       </c>
@@ -8562,7 +8568,7 @@
       </c>
       <c r="J30" s="160"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="337" t="s">
         <v>521</v>
       </c>
@@ -8590,7 +8596,7 @@
       </c>
       <c r="J31" s="160"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8618,7 +8624,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8646,7 +8652,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8672,7 +8678,7 @@
       </c>
       <c r="J34" s="160"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8700,7 +8706,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8728,7 +8734,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8756,7 +8762,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="341" t="s">
         <v>1063</v>
       </c>
@@ -8784,7 +8790,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="337" t="s">
         <v>541</v>
       </c>
@@ -8810,7 +8816,7 @@
       </c>
       <c r="J39" s="160"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="162" t="s">
         <v>1313</v>
       </c>
@@ -8836,7 +8842,7 @@
       </c>
       <c r="J40" s="160"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="104" t="s">
         <v>590</v>
       </c>
@@ -8863,7 +8869,7 @@
       </c>
       <c r="J41" s="160"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="162" t="s">
         <v>613</v>
       </c>
@@ -8889,7 +8895,7 @@
       </c>
       <c r="J42" s="160"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="162" t="s">
         <v>613</v>
       </c>
@@ -8917,7 +8923,7 @@
       </c>
       <c r="J43" s="160"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="162" t="s">
         <v>613</v>
       </c>
@@ -8947,7 +8953,7 @@
       </c>
       <c r="J44" s="160"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="162" t="s">
         <v>613</v>
       </c>
@@ -8999,7 +9005,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="162" t="s">
         <v>613</v>
       </c>
@@ -9025,7 +9031,7 @@
       </c>
       <c r="J47" s="160"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="162" t="s">
         <v>652</v>
       </c>
@@ -9053,7 +9059,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="162" t="s">
         <v>652</v>
       </c>
@@ -9079,7 +9085,7 @@
       </c>
       <c r="J49" s="160"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="162" t="s">
         <v>652</v>
       </c>
@@ -9105,7 +9111,7 @@
       </c>
       <c r="J50" s="160"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="162" t="s">
         <v>613</v>
       </c>
@@ -9133,7 +9139,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="162" t="s">
         <v>652</v>
       </c>
@@ -9159,7 +9165,7 @@
       </c>
       <c r="J52" s="160"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="162" t="s">
         <v>652</v>
       </c>
@@ -9187,7 +9193,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="162" t="s">
         <v>613</v>
       </c>
@@ -9215,7 +9221,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="162" t="s">
         <v>1028</v>
       </c>
@@ -9245,7 +9251,7 @@
       </c>
       <c r="J55" s="160"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="162" t="s">
         <v>1028</v>
       </c>
@@ -9347,7 +9353,7 @@
       </c>
       <c r="J59" s="160"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="181" t="s">
         <v>575</v>
       </c>
@@ -9373,7 +9379,7 @@
       </c>
       <c r="J60" s="160"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="181" t="s">
         <v>575</v>
       </c>
@@ -9399,7 +9405,7 @@
       </c>
       <c r="J61" s="160"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="162" t="s">
         <v>824</v>
       </c>
@@ -9425,7 +9431,7 @@
       </c>
       <c r="J62" s="160"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="162" t="s">
         <v>810</v>
       </c>
@@ -9451,7 +9457,7 @@
       </c>
       <c r="J63" s="160"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="162" t="s">
         <v>810</v>
       </c>
@@ -37392,7 +37398,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -37402,16 +37408,17 @@
     <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="4.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F1" t="s">
         <v>58</v>
       </c>
@@ -37461,7 +37468,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>939</v>
       </c>
@@ -37504,8 +37511,14 @@
         <v>490</v>
       </c>
       <c r="X2" s="58"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z2" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>463</v>
       </c>
@@ -37548,8 +37561,14 @@
         <v>463</v>
       </c>
       <c r="X3" s="58"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z3" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
         <v>943</v>
       </c>
@@ -37588,8 +37607,14 @@
         <v>463</v>
       </c>
       <c r="X4" s="58"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z4" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
         <v>947</v>
       </c>
@@ -37634,8 +37659,14 @@
         <v>490</v>
       </c>
       <c r="X5" s="58"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z5" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
         <v>951</v>
       </c>
@@ -37680,8 +37711,14 @@
         <v>490</v>
       </c>
       <c r="X6" s="58"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z6" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>955</v>
       </c>
@@ -37734,8 +37771,14 @@
         <v>463</v>
       </c>
       <c r="X7" s="58"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
         <v>959</v>
       </c>
@@ -37767,8 +37810,14 @@
         <v>490</v>
       </c>
       <c r="X8" s="58"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="23" t="s">
+        <v>961</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
         <v>960</v>
       </c>
@@ -37812,8 +37861,14 @@
       <c r="Y9" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="23" t="s">
+        <v>962</v>
+      </c>
+      <c r="AC9" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>964</v>
       </c>
@@ -37844,8 +37899,14 @@
         <v>463</v>
       </c>
       <c r="X10" s="58"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
         <v>966</v>
       </c>
@@ -37890,8 +37951,14 @@
         <v>492</v>
       </c>
       <c r="X11" s="58"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="7" t="s">
+        <v>967</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
         <v>968</v>
       </c>
@@ -37928,8 +37995,14 @@
         <v>490</v>
       </c>
       <c r="X12" s="58"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="7" t="s">
+        <v>969</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>970</v>
       </c>
@@ -37968,8 +38041,14 @@
         <v>934</v>
       </c>
       <c r="X13" s="58"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="23" t="s">
+        <v>971</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>972</v>
       </c>
@@ -38005,8 +38084,14 @@
         <v>463</v>
       </c>
       <c r="X14" s="58"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F15" s="56"/>
       <c r="G15" s="7" t="s">
         <v>974</v>
@@ -38038,8 +38123,14 @@
         <v>492</v>
       </c>
       <c r="X15" s="58"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>485</v>
       </c>
@@ -38076,8 +38167,11 @@
         <v>2767</v>
       </c>
       <c r="X16" s="58"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z16" s="7" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>478</v>
       </c>
@@ -38117,8 +38211,14 @@
         <v>490</v>
       </c>
       <c r="X17" s="58"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z17" s="7" t="s">
+        <v>977</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F18" s="56"/>
       <c r="G18" s="7" t="s">
         <v>978</v>
@@ -38145,8 +38245,11 @@
       <c r="U18" s="57"/>
       <c r="V18" s="58"/>
       <c r="X18" s="58"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z18" s="7" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F19" s="56"/>
       <c r="G19" s="7" t="s">
         <v>979</v>
@@ -38188,8 +38291,14 @@
         <v>980</v>
       </c>
       <c r="X19" s="58"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z19" s="7" t="s">
+        <v>979</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F20" s="56"/>
       <c r="G20" s="7" t="s">
         <v>981</v>
@@ -38235,9 +38344,15 @@
         <v>492</v>
       </c>
       <c r="X20" s="58"/>
-    </row>
-    <row r="21" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z20" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="73" t="s">
         <v>901</v>
@@ -38252,7 +38367,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="68" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="76"/>
       <c r="B23" t="s">
         <v>463</v>
@@ -38268,7 +38383,7 @@
         <v>73662.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="76"/>
       <c r="B24" t="s">
         <v>490</v>
@@ -38284,7 +38399,7 @@
         <v>83195</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="76"/>
       <c r="B25" t="s">
         <v>492</v>
@@ -38300,7 +38415,7 @@
         <v>62577.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="76" t="str">
         <f>C16</f>
         <v>Dusseldorf</v>
@@ -38320,7 +38435,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="89"/>
       <c r="B27" s="7" t="s">
         <v>988</v>
@@ -38336,7 +38451,7 @@
         <v>10736</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" s="76"/>
       <c r="B28" t="s">
         <v>913</v>
@@ -38347,7 +38462,7 @@
         <v>222202</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="93"/>
       <c r="B29" s="94" t="s">
         <v>914</v>
@@ -38402,6 +38517,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005608FA096EBB4B4B8A364436FE5AF333" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f258b733f6365362ddc6ad739ca240">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b17ea8e4-3fb0-4555-9c20-069a19b46cb2" xmlns:ns3="a800b4a7-713e-40fb-b259-074d23fe1c46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="392726fe05a3a4dbab19059d5b4c5bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="b17ea8e4-3fb0-4555-9c20-069a19b46cb2"/>
@@ -38734,15 +38858,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A142914-1816-40B5-8946-9D6865A82C7E}">
   <ds:schemaRefs>
@@ -38761,6 +38876,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD7AB568-E6EA-474D-8278-D37477DAFA72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38777,12 +38900,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8781AB9E-9F28-4A8F-99EF-C45B15DD4F97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>